--- a/testBrew.xlsx
+++ b/testBrew.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alfalavalonline-my.sharepoint.com/personal/mahmudul_hasan_alfalaval_com/Documents/Documents/AgenticWorld/EnvoraDeviceConfig/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Agentic World\TestDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{01217BA3-0F91-4F82-823D-03ECF0B45F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5D32D58-079C-4F38-9028-7943CB39358F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C73474-4993-41AD-8BA3-F16422125108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$E$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$F$401</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,8 +30,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -61,14 +59,22 @@
   <commentList>
     <comment ref="B110" authorId="0" shapeId="0" xr:uid="{73D4B7F6-243F-4FF2-99C8-413E3B588F2F}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PIT220-1 / PIT221-1</t>
+        </r>
       </text>
     </comment>
-    <comment ref="D110" authorId="1" shapeId="0" xr:uid="{ACEAC60E-563F-4328-B54F-2D31DA895568}">
+    <comment ref="E110" authorId="1" shapeId="0" xr:uid="{ACEAC60E-563F-4328-B54F-2D31DA895568}">
       <text>
         <r>
           <rPr>
@@ -82,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E110" authorId="1" shapeId="0" xr:uid="{A7EDFD00-73D4-4924-B708-E4D643A140C2}">
+    <comment ref="F110" authorId="1" shapeId="0" xr:uid="{A7EDFD00-73D4-4924-B708-E4D643A140C2}">
       <text>
         <r>
           <rPr>
@@ -98,23 +104,39 @@
     </comment>
     <comment ref="B116" authorId="2" shapeId="0" xr:uid="{4608516B-34DA-4E87-85F1-345F80F368D2}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PIT221-1 / PIT220-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="B130" authorId="3" shapeId="0" xr:uid="{37D13463-1186-4BC6-8059-F81F589B8465}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PCV220-1 / PCV221-1</t>
+        </r>
       </text>
     </comment>
-    <comment ref="D130" authorId="1" shapeId="0" xr:uid="{A163B90D-1EF5-443F-899F-87AE8DB0F188}">
+    <comment ref="E130" authorId="1" shapeId="0" xr:uid="{A163B90D-1EF5-443F-899F-87AE8DB0F188}">
       <text>
         <r>
           <rPr>
@@ -128,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E130" authorId="1" shapeId="0" xr:uid="{BAAAD3C7-27FA-4F29-9DB6-F22ABC6DE4AE}">
+    <comment ref="F130" authorId="1" shapeId="0" xr:uid="{BAAAD3C7-27FA-4F29-9DB6-F22ABC6DE4AE}">
       <text>
         <r>
           <rPr>
@@ -144,23 +166,39 @@
     </comment>
     <comment ref="B132" authorId="4" shapeId="0" xr:uid="{330CC50C-0FF1-4C20-92A7-B1A460F72FE0}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PCV221-1 / PCV220-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="B139" authorId="5" shapeId="0" xr:uid="{C128BBFA-0A9E-4E10-9DCF-02753B677457}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 ST740/ST741</t>
+        </r>
       </text>
     </comment>
-    <comment ref="D139" authorId="1" shapeId="0" xr:uid="{71DF5CC9-8C1C-486E-B5BB-3BCC7CA84727}">
+    <comment ref="E139" authorId="1" shapeId="0" xr:uid="{71DF5CC9-8C1C-486E-B5BB-3BCC7CA84727}">
       <text>
         <r>
           <rPr>
@@ -174,7 +212,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E139" authorId="1" shapeId="0" xr:uid="{27EBACE4-89DD-4A88-804E-3D04F2E87FF6}">
+    <comment ref="F139" authorId="1" shapeId="0" xr:uid="{27EBACE4-89DD-4A88-804E-3D04F2E87FF6}">
       <text>
         <r>
           <rPr>
@@ -190,23 +228,39 @@
     </comment>
     <comment ref="B187" authorId="6" shapeId="0" xr:uid="{FAC71602-7205-4D4E-A8A7-63E13947D7F3}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 LS422b / LS423</t>
+        </r>
       </text>
     </comment>
     <comment ref="B212" authorId="7" shapeId="0" xr:uid="{4A8C6723-E87B-4DCF-BC82-3EEAFFA13634}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 YT750/YT752</t>
+        </r>
       </text>
     </comment>
-    <comment ref="D212" authorId="1" shapeId="0" xr:uid="{7A748396-5D90-45A2-BCDA-09E9D00EB824}">
+    <comment ref="E212" authorId="1" shapeId="0" xr:uid="{7A748396-5D90-45A2-BCDA-09E9D00EB824}">
       <text>
         <r>
           <rPr>
@@ -220,7 +274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E212" authorId="1" shapeId="0" xr:uid="{16457DFC-5263-4B6D-8B35-72B130393DB1}">
+    <comment ref="F212" authorId="1" shapeId="0" xr:uid="{16457DFC-5263-4B6D-8B35-72B130393DB1}">
       <text>
         <r>
           <rPr>
@@ -236,14 +290,22 @@
     </comment>
     <comment ref="B214" authorId="8" shapeId="0" xr:uid="{932F2D4C-D793-48A0-8BED-5F38FC3D7DAF}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 PT375-1/PT376-1</t>
+        </r>
       </text>
     </comment>
-    <comment ref="E214" authorId="1" shapeId="0" xr:uid="{A7A9E8D1-727E-4B93-BDEB-E67DFF623450}">
+    <comment ref="F214" authorId="1" shapeId="0" xr:uid="{A7A9E8D1-727E-4B93-BDEB-E67DFF623450}">
       <text>
         <r>
           <rPr>
@@ -259,31 +321,55 @@
     </comment>
     <comment ref="B218" authorId="9" shapeId="0" xr:uid="{E1E2F944-CF9F-4061-9330-99AC06440908}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative sensors, same PIW:
 TT731b/TT733</t>
+        </r>
       </text>
     </comment>
-    <comment ref="E218" authorId="10" shapeId="0" xr:uid="{F8073023-E3D6-437F-A368-4B60DA804058}">
+    <comment ref="F218" authorId="10" shapeId="0" xr:uid="{F8073023-E3D6-437F-A368-4B60DA804058}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Sensor: TT733</t>
+        </r>
       </text>
     </comment>
     <comment ref="B223" authorId="11" shapeId="0" xr:uid="{FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 TT410-1/TT412-1</t>
+        </r>
       </text>
     </comment>
-    <comment ref="D223" authorId="1" shapeId="0" xr:uid="{3F0AF3B0-2ABB-45F3-8CF9-4442E029B36F}">
+    <comment ref="E223" authorId="1" shapeId="0" xr:uid="{3F0AF3B0-2ABB-45F3-8CF9-4442E029B36F}">
       <text>
         <r>
           <rPr>
@@ -297,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E223" authorId="1" shapeId="0" xr:uid="{A3E2C7FB-DECB-4F99-BA24-43954D3FE9B6}">
+    <comment ref="F223" authorId="1" shapeId="0" xr:uid="{A3E2C7FB-DECB-4F99-BA24-43954D3FE9B6}">
       <text>
         <r>
           <rPr>
@@ -313,22 +399,38 @@
     </comment>
     <comment ref="B243" authorId="12" shapeId="0" xr:uid="{C29E9803-A59F-4197-99DC-10131D1A8691}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Old AV635b-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="B248" authorId="13" shapeId="0" xr:uid="{F05B5C03-D80C-44EE-911F-FD4F08369CD1}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 AV375-1/AV376-1</t>
+        </r>
       </text>
     </comment>
-    <comment ref="D248" authorId="1" shapeId="0" xr:uid="{7EF7BC57-4FCC-448F-8A09-38CD88A5340F}">
+    <comment ref="E248" authorId="1" shapeId="0" xr:uid="{7EF7BC57-4FCC-448F-8A09-38CD88A5340F}">
       <text>
         <r>
           <rPr>
@@ -342,7 +444,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E248" authorId="1" shapeId="0" xr:uid="{08A74F60-F5E0-49A2-82A4-A6305CE3D915}">
+    <comment ref="F248" authorId="1" shapeId="0" xr:uid="{08A74F60-F5E0-49A2-82A4-A6305CE3D915}">
       <text>
         <r>
           <rPr>
@@ -358,23 +460,39 @@
     </comment>
     <comment ref="B252" authorId="14" shapeId="0" xr:uid="{6BE60107-F28C-41F1-A623-84DD5A6A045C}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 AV441-1/AV630-1</t>
+        </r>
       </text>
     </comment>
     <comment ref="B253" authorId="15" shapeId="0" xr:uid="{573F35F3-86C4-417F-BDB5-9F88836E09BB}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Alfa Laval Offc"/>
+            <family val="2"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 506c/AV372-1</t>
+        </r>
       </text>
     </comment>
-    <comment ref="D253" authorId="1" shapeId="0" xr:uid="{68836ADC-7909-428F-90A1-5710219BA6C4}">
+    <comment ref="E253" authorId="1" shapeId="0" xr:uid="{68836ADC-7909-428F-90A1-5710219BA6C4}">
       <text>
         <r>
           <rPr>
@@ -388,7 +506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E253" authorId="1" shapeId="0" xr:uid="{0F67FC6B-9616-46E6-A530-F3FA37297DB6}">
+    <comment ref="F253" authorId="1" shapeId="0" xr:uid="{0F67FC6B-9616-46E6-A530-F3FA37297DB6}">
       <text>
         <r>
           <rPr>
@@ -402,7 +520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D354" authorId="1" shapeId="0" xr:uid="{C0B47CE5-D73E-476B-A5B9-42559C542AEB}">
+    <comment ref="E354" authorId="1" shapeId="0" xr:uid="{C0B47CE5-D73E-476B-A5B9-42559C542AEB}">
       <text>
         <r>
           <rPr>
@@ -416,7 +534,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E354" authorId="1" shapeId="0" xr:uid="{8AB58700-0B5F-4791-8C69-F153ED1BB30F}">
+    <comment ref="F354" authorId="1" shapeId="0" xr:uid="{8AB58700-0B5F-4791-8C69-F153ED1BB30F}">
       <text>
         <r>
           <rPr>
@@ -435,7 +553,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="276">
   <si>
     <t>Tag Label</t>
   </si>
@@ -1227,13 +1345,49 @@
   </si>
   <si>
     <t>AMPS</t>
+  </si>
+  <si>
+    <t>Option</t>
+  </si>
+  <si>
+    <t>3 PHASE</t>
+  </si>
+  <si>
+    <t>BLENDING</t>
+  </si>
+  <si>
+    <t>RECIRCULATION</t>
+  </si>
+  <si>
+    <t>COOLING RECIRCULATION</t>
+  </si>
+  <si>
+    <t>DYNAMIC COOLING</t>
+  </si>
+  <si>
+    <t>L-DRIVE</t>
+  </si>
+  <si>
+    <t>SRU</t>
+  </si>
+  <si>
+    <t>E-DRIVE</t>
+  </si>
+  <si>
+    <t>FEED PUMP</t>
+  </si>
+  <si>
+    <t>CONDITION ALERT</t>
+  </si>
+  <si>
+    <t>E/L-DRIVE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1353,7 +1507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1409,6 +1563,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1922,3984 +2079,4589 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}">
-  <dimension ref="B2:E401"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="B2:F401"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="2" max="2" width="10.69921875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.69921875" style="1" customWidth="1"/>
-    <col min="4" max="5" width="2.296875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="10.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.75" style="1" customWidth="1"/>
+    <col min="5" max="6" width="2.25" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="49.5" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="49.5">
       <c r="B2"/>
       <c r="C2"/>
-      <c r="D2" s="11" t="s">
+      <c r="D2"/>
+      <c r="E2" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:6">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="D3" s="12"/>
+      <c r="D3" s="16" t="s">
+        <v>264</v>
+      </c>
       <c r="E3" s="12"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F3" s="12"/>
+    </row>
+    <row r="4" spans="2:6">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
-      <c r="D4" s="13"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="13"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="2:6">
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
-      <c r="D5" s="14"/>
+      <c r="D5" s="3"/>
       <c r="E5" s="14"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F5" s="14"/>
+    </row>
+    <row r="6" spans="2:6">
       <c r="B6" s="4"/>
       <c r="C6" s="3"/>
-      <c r="D6" s="13"/>
+      <c r="D6" s="3"/>
       <c r="E6" s="13"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F6" s="13"/>
+    </row>
+    <row r="7" spans="2:6">
       <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D7" s="3"/>
       <c r="E7" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F7" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6">
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D8" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D8" s="3"/>
       <c r="E8" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F8" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6">
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D9" s="3"/>
       <c r="E9" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F9" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D10" s="13"/>
+      <c r="D10" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="E10" s="13"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F10" s="13"/>
+    </row>
+    <row r="11" spans="2:6">
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D11" s="3"/>
       <c r="E11" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F11" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6">
       <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D12" s="3"/>
       <c r="E12" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F12" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6">
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D13" s="3"/>
       <c r="E13" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F13" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6">
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="13"/>
+      <c r="D14" s="3"/>
       <c r="E14" s="13"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F14" s="13"/>
+    </row>
+    <row r="15" spans="2:6">
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="13"/>
+      <c r="D15" s="3"/>
       <c r="E15" s="13"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F15" s="13"/>
+    </row>
+    <row r="16" spans="2:6">
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>141</v>
-      </c>
+      <c r="D16" s="3"/>
       <c r="E16" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F16" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6">
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>141</v>
-      </c>
+      <c r="D17" s="3"/>
       <c r="E17" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F17" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>141</v>
+      <c r="D18" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F18" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="13"/>
+      <c r="D19" s="3"/>
       <c r="E19" s="13"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F19" s="13"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="13"/>
+      <c r="D20" s="3"/>
       <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" spans="2:6">
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="13"/>
+      <c r="D21" s="3"/>
       <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F21" s="13"/>
+    </row>
+    <row r="22" spans="2:6">
       <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>140</v>
+      <c r="D22" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F22" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
-      <c r="D23" s="13"/>
+      <c r="D23" s="3"/>
       <c r="E23" s="13"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F23" s="13"/>
+    </row>
+    <row r="24" spans="2:6">
       <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D24" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D24" s="3"/>
       <c r="E24" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F24" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
       <c r="B25" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D25" s="3"/>
       <c r="E25" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F25" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6">
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D26" s="13" t="s">
-        <v>141</v>
+      <c r="D26" s="20" t="s">
+        <v>266</v>
       </c>
       <c r="E26" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F26" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>141</v>
+      <c r="D27" s="20" t="s">
+        <v>266</v>
       </c>
       <c r="E27" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F27" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
       <c r="B28" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>141</v>
+      <c r="D28" s="20" t="s">
+        <v>267</v>
       </c>
       <c r="E28" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F28" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
       <c r="B29" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>141</v>
+      <c r="D29" s="20" t="s">
+        <v>267</v>
       </c>
       <c r="E29" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F29" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D30" s="3"/>
       <c r="E30" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F30" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
       <c r="B31" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D31" s="3"/>
       <c r="E31" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F31" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D32" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D32" s="3"/>
       <c r="E32" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F32" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
       <c r="B33" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D33" s="3"/>
       <c r="E33" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F33" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
       <c r="B34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D34" s="13"/>
+      <c r="D34" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="E34" s="13"/>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F34" s="13"/>
+    </row>
+    <row r="35" spans="2:6">
       <c r="B35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D35" s="13"/>
+      <c r="D35" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="E35" s="13"/>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F35" s="13"/>
+    </row>
+    <row r="36" spans="2:6">
       <c r="B36" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D36" s="3"/>
       <c r="E36" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F36" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
       <c r="B37" s="7" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>140</v>
-      </c>
+      <c r="D37" s="18"/>
       <c r="E37" s="15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F37" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6">
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D38" s="13"/>
+      <c r="D38" s="3"/>
       <c r="E38" s="13"/>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F38" s="13"/>
+    </row>
+    <row r="39" spans="2:6">
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D39" s="13"/>
+      <c r="D39" s="3"/>
       <c r="E39" s="13"/>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F39" s="13"/>
+    </row>
+    <row r="40" spans="2:6">
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
-      <c r="D40" s="13"/>
+      <c r="D40" s="3"/>
       <c r="E40" s="13"/>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F40" s="13"/>
+    </row>
+    <row r="41" spans="2:6">
       <c r="B41" s="7" t="s">
         <v>20</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D41" s="15" t="s">
-        <v>140</v>
-      </c>
+      <c r="D41" s="18"/>
       <c r="E41" s="15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F41" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
       <c r="B42" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D42" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D42" s="3"/>
       <c r="E42" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F42" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
       <c r="B43" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D43" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D43" s="3"/>
       <c r="E43" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F43" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
       <c r="B44" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D44" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D44" s="3"/>
       <c r="E44" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F44" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
       <c r="B45" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D45" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D45" s="3"/>
       <c r="E45" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F45" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
       <c r="B46" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D46" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D46" s="3"/>
       <c r="E46" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F46" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
       <c r="B47" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D47" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D47" s="3"/>
       <c r="E47" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F47" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
       <c r="B48" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D48" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D48" s="3"/>
       <c r="E48" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F48" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
       <c r="B49" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D49" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D49" s="3"/>
       <c r="E49" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F49" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
       <c r="B50" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D50" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D50" s="3"/>
       <c r="E50" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F50" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D51" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D51" s="3"/>
       <c r="E51" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F51" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
       <c r="B52" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D52" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D52" s="3"/>
       <c r="E52" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F52" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
       <c r="B53" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D53" s="3"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
       <c r="B54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D54" s="3"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
       <c r="B55" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="13"/>
+      <c r="D55" s="3"/>
       <c r="E55" s="13"/>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F55" s="13"/>
+    </row>
+    <row r="56" spans="2:6">
       <c r="B56" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C56" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D56" s="13"/>
+      <c r="D56" s="3"/>
       <c r="E56" s="13"/>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F56" s="13"/>
+    </row>
+    <row r="57" spans="2:6">
       <c r="B57" s="6"/>
       <c r="C57" s="3"/>
-      <c r="D57" s="13"/>
+      <c r="D57" s="3"/>
       <c r="E57" s="13"/>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F57" s="13"/>
+    </row>
+    <row r="58" spans="2:6">
       <c r="B58" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D58" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D58" s="3"/>
       <c r="E58" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F58" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D59" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D59" s="3"/>
       <c r="E59" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F59" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6">
       <c r="B60" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D60" s="13"/>
+      <c r="D60" s="3"/>
       <c r="E60" s="13"/>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F60" s="13"/>
+    </row>
+    <row r="61" spans="2:6">
       <c r="B61" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D61" s="13"/>
+      <c r="D61" s="3"/>
       <c r="E61" s="13"/>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F61" s="13"/>
+    </row>
+    <row r="62" spans="2:6">
       <c r="B62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D62" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6">
       <c r="B63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D63" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6">
       <c r="B64" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D64" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6">
       <c r="B65" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D65" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6">
       <c r="B66" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D66" s="13"/>
+      <c r="D66" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="E66" s="13"/>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F66" s="13"/>
+    </row>
+    <row r="67" spans="2:6">
       <c r="B67" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D67" s="13"/>
+      <c r="D67" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="E67" s="13"/>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F67" s="13"/>
+    </row>
+    <row r="68" spans="2:6">
       <c r="B68" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C68" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D68" s="13"/>
+      <c r="D68" s="3"/>
       <c r="E68" s="13"/>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F68" s="13"/>
+    </row>
+    <row r="69" spans="2:6">
       <c r="B69" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D69" s="13"/>
+      <c r="D69" s="3"/>
       <c r="E69" s="13"/>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F69" s="13"/>
+    </row>
+    <row r="70" spans="2:6">
       <c r="B70" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D70" s="13"/>
+      <c r="D70" s="3"/>
       <c r="E70" s="13"/>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F70" s="13"/>
+    </row>
+    <row r="71" spans="2:6">
       <c r="B71" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D71" s="13"/>
+      <c r="D71" s="3"/>
       <c r="E71" s="13"/>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F71" s="13"/>
+    </row>
+    <row r="72" spans="2:6">
       <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D72" s="13"/>
+      <c r="D72" s="3"/>
       <c r="E72" s="13"/>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F72" s="13"/>
+    </row>
+    <row r="73" spans="2:6">
       <c r="B73" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D73" s="13"/>
+      <c r="D73" s="3"/>
       <c r="E73" s="13"/>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F73" s="13"/>
+    </row>
+    <row r="74" spans="2:6">
       <c r="B74" s="6"/>
       <c r="C74" s="3"/>
-      <c r="D74" s="13"/>
+      <c r="D74" s="20"/>
       <c r="E74" s="13"/>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F74" s="13"/>
+    </row>
+    <row r="75" spans="2:6">
       <c r="B75" s="6" t="s">
         <v>13</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D75" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D75" s="3"/>
       <c r="E75" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F75" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6">
       <c r="B76" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D76" s="13" t="s">
-        <v>141</v>
+      <c r="D76" s="20" t="s">
+        <v>266</v>
       </c>
       <c r="E76" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F76" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6">
       <c r="B77" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D77" s="13" t="s">
-        <v>141</v>
+      <c r="D77" s="20" t="s">
+        <v>267</v>
       </c>
       <c r="E77" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F77" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6">
       <c r="B78" s="6" t="s">
         <v>16</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D78" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D78" s="3"/>
       <c r="E78" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F78" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6">
       <c r="B79" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D79" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D79" s="3"/>
       <c r="E79" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F79" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6">
       <c r="B80" s="6" t="s">
         <v>18</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D80" s="13"/>
+      <c r="D80" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="E80" s="13"/>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F80" s="13"/>
+    </row>
+    <row r="81" spans="2:6">
       <c r="B81" s="6" t="s">
         <v>19</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D81" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D81" s="3"/>
       <c r="E81" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F81" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D82" s="13"/>
+      <c r="D82" s="3"/>
       <c r="E82" s="13"/>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F82" s="13"/>
+    </row>
+    <row r="83" spans="2:6">
       <c r="B83" s="6" t="s">
         <v>20</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D83" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D83" s="20"/>
       <c r="E83" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F83" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="84" spans="2:6">
       <c r="B84" s="6" t="s">
         <v>21</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D84" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D84" s="20"/>
       <c r="E84" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F84" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="85" spans="2:6">
       <c r="B85" s="6" t="s">
         <v>22</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D85" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D85" s="20"/>
       <c r="E85" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F85" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" spans="2:6">
       <c r="B86" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D86" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D86" s="20"/>
       <c r="E86" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F86" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="87" spans="2:6">
       <c r="B87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D87" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D87" s="20"/>
       <c r="E87" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F87" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="88" spans="2:6">
       <c r="B88" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D88" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D88" s="20"/>
       <c r="E88" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F88" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="89" spans="2:6">
       <c r="B89" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D89" s="20"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="90" spans="2:6">
       <c r="B90" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D90" s="13"/>
+      <c r="D90" s="3"/>
       <c r="E90" s="13"/>
-    </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F90" s="13"/>
+    </row>
+    <row r="91" spans="2:6">
       <c r="B91" s="6"/>
       <c r="C91" s="3"/>
-      <c r="D91" s="13"/>
+      <c r="D91" s="3"/>
       <c r="E91" s="13"/>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F91" s="13"/>
+    </row>
+    <row r="92" spans="2:6">
       <c r="B92" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D92" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D92" s="20"/>
       <c r="E92" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F92" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="93" spans="2:6">
       <c r="B93" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D93" s="13"/>
+      <c r="D93" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="E93" s="13"/>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F93" s="13"/>
+    </row>
+    <row r="94" spans="2:6">
       <c r="B94" s="6" t="s">
         <v>28</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D94" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6">
       <c r="B95" s="6" t="s">
         <v>29</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D95" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="96" spans="2:6">
       <c r="B96" s="6" t="s">
         <v>30</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D96" s="13"/>
+      <c r="D96" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="E96" s="13"/>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F96" s="13"/>
+    </row>
+    <row r="97" spans="2:6">
       <c r="B97" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D97" s="13"/>
+      <c r="D97" s="3"/>
       <c r="E97" s="13"/>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F97" s="13"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C98" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D98" s="13"/>
+      <c r="D98" s="3"/>
       <c r="E98" s="13"/>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F98" s="13"/>
+    </row>
+    <row r="99" spans="2:6">
       <c r="B99" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D99" s="13"/>
+      <c r="D99" s="3"/>
       <c r="E99" s="13"/>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F99" s="13"/>
+    </row>
+    <row r="100" spans="2:6">
       <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C100" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D100" s="13"/>
+      <c r="D100" s="3"/>
       <c r="E100" s="13"/>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F100" s="13"/>
+    </row>
+    <row r="101" spans="2:6">
       <c r="B101" s="4" t="s">
         <v>31</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D101" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D101" s="3"/>
       <c r="E101" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F101" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D102" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D102" s="3"/>
       <c r="E102" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F102" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="2:6">
       <c r="B103" s="4" t="s">
         <v>33</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D103" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D103" s="3"/>
       <c r="E103" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F103" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="104" spans="2:6">
       <c r="B104" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D104" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D104" s="3"/>
       <c r="E104" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F104" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
       <c r="B105" s="4" t="s">
         <v>35</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D105" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D105" s="3"/>
       <c r="E105" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F105" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="106" spans="2:6">
       <c r="B106" s="4" t="s">
         <v>36</v>
       </c>
       <c r="C106" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D106" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D106" s="3"/>
       <c r="E106" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F106" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="107" spans="2:6">
       <c r="B107" s="4" t="s">
         <v>37</v>
       </c>
       <c r="C107" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="D107" s="13"/>
+      <c r="D107" s="3"/>
       <c r="E107" s="13"/>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F107" s="13"/>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="4"/>
       <c r="C108" s="3"/>
-      <c r="D108" s="13"/>
+      <c r="D108" s="3"/>
       <c r="E108" s="13"/>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F108" s="13"/>
+    </row>
+    <row r="109" spans="2:6">
       <c r="B109" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C109" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D109" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D109" s="3"/>
       <c r="E109" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F109" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="2:6">
       <c r="B110" s="4" t="s">
         <v>39</v>
       </c>
       <c r="C110" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D110" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D110" s="3"/>
       <c r="E110" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F110" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="111" spans="2:6">
       <c r="B111" s="4" t="s">
         <v>40</v>
       </c>
       <c r="C111" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D111" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D111" s="3"/>
       <c r="E111" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F111" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="2:6">
       <c r="B112" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C112" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D112" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D112" s="3"/>
       <c r="E112" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="113" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F112" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="113" spans="2:6">
       <c r="B113" s="4"/>
       <c r="C113" s="3"/>
-      <c r="D113" s="13"/>
+      <c r="D113" s="3"/>
       <c r="E113" s="13"/>
-    </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F113" s="13"/>
+    </row>
+    <row r="114" spans="2:6">
       <c r="B114" s="4" t="s">
         <v>42</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D114" s="13" t="s">
-        <v>141</v>
+      <c r="D114" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E114" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F114" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="115" spans="2:6">
       <c r="B115" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C115" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D115" s="13"/>
+      <c r="D115" s="19"/>
       <c r="E115" s="13"/>
-    </row>
-    <row r="116" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F115" s="13"/>
+    </row>
+    <row r="116" spans="2:6">
       <c r="B116" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C116" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="D116" s="13"/>
+      <c r="D116" s="19" t="s">
+        <v>265</v>
+      </c>
       <c r="E116" s="13"/>
-    </row>
-    <row r="117" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F116" s="13"/>
+    </row>
+    <row r="117" spans="2:6">
       <c r="B117" s="4" t="s">
         <v>44</v>
       </c>
       <c r="C117" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="D117" s="13"/>
+      <c r="D117" s="19"/>
       <c r="E117" s="13"/>
-    </row>
-    <row r="118" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F117" s="13"/>
+    </row>
+    <row r="118" spans="2:6">
       <c r="B118" s="4"/>
       <c r="C118" s="3"/>
-      <c r="D118" s="13"/>
+      <c r="D118" s="3"/>
       <c r="E118" s="13"/>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F118" s="13"/>
+    </row>
+    <row r="119" spans="2:6">
       <c r="B119" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C119" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="D119" s="13" t="s">
-        <v>141</v>
-      </c>
+      <c r="D119" s="3"/>
       <c r="E119" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F119" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="2:6">
       <c r="B120" s="4" t="s">
         <v>46</v>
       </c>
       <c r="C120" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D120" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E120" s="13"/>
+      <c r="F120" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="121" spans="2:6">
       <c r="B121" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C121" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D121" s="13"/>
-      <c r="E121" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D121" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E121" s="13"/>
+      <c r="F121" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="122" spans="2:6">
       <c r="B122" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C122" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D122" s="13" t="s">
-        <v>141</v>
+      <c r="D122" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E122" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F122" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123" spans="2:6">
       <c r="B123" s="4"/>
       <c r="C123" s="3"/>
-      <c r="D123" s="13"/>
+      <c r="D123" s="3"/>
       <c r="E123" s="13"/>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F123" s="13"/>
+    </row>
+    <row r="124" spans="2:6">
       <c r="B124" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C124" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D124" s="13"/>
+      <c r="D124" s="3"/>
       <c r="E124" s="13"/>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F124" s="13"/>
+    </row>
+    <row r="125" spans="2:6">
       <c r="B125" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C125" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D125" s="13"/>
+      <c r="D125" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="E125" s="13"/>
-    </row>
-    <row r="126" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F125" s="13"/>
+    </row>
+    <row r="126" spans="2:6">
       <c r="B126" s="4" t="s">
         <v>51</v>
       </c>
       <c r="C126" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D126" s="13" t="s">
-        <v>140</v>
+      <c r="D126" s="19" t="s">
+        <v>269</v>
       </c>
       <c r="E126" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F126" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" spans="2:6">
       <c r="B127" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C127" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D127" s="13"/>
+      <c r="D127" s="19"/>
       <c r="E127" s="13"/>
-    </row>
-    <row r="128" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F127" s="13"/>
+    </row>
+    <row r="128" spans="2:6">
       <c r="B128" s="4"/>
       <c r="C128" s="3"/>
-      <c r="D128" s="13"/>
+      <c r="D128" s="19"/>
       <c r="E128" s="13"/>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F128" s="13"/>
+    </row>
+    <row r="129" spans="2:6">
       <c r="B129" s="4" t="s">
         <v>52</v>
       </c>
       <c r="C129" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D129" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D129" s="3"/>
       <c r="E129" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F129" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130" spans="2:6">
       <c r="B130" s="4" t="s">
         <v>53</v>
       </c>
       <c r="C130" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D130" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D130" s="3"/>
       <c r="E130" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F130" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="131" spans="2:6">
       <c r="B131" s="4" t="s">
         <v>54</v>
       </c>
       <c r="C131" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D131" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D131" s="3"/>
       <c r="E131" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F131" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="132" spans="2:6">
       <c r="B132" s="4" t="s">
         <v>55</v>
       </c>
       <c r="C132" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D132" s="13"/>
+      <c r="D132" s="3"/>
       <c r="E132" s="13"/>
-    </row>
-    <row r="133" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F132" s="13"/>
+    </row>
+    <row r="133" spans="2:6">
       <c r="B133" s="4"/>
       <c r="C133" s="3"/>
-      <c r="D133" s="13"/>
+      <c r="D133" s="3"/>
       <c r="E133" s="13"/>
-    </row>
-    <row r="134" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F133" s="13"/>
+    </row>
+    <row r="134" spans="2:6">
       <c r="B134" s="4" t="s">
         <v>56</v>
       </c>
       <c r="C134" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D134" s="13" t="s">
-        <v>141</v>
+      <c r="D134" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E134" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="135" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F134" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="135" spans="2:6">
       <c r="B135" s="4" t="s">
         <v>57</v>
       </c>
       <c r="C135" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D135" s="13" t="s">
-        <v>141</v>
+      <c r="D135" s="3" t="s">
+        <v>267</v>
       </c>
       <c r="E135" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F135" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
       <c r="B136" s="4" t="s">
         <v>58</v>
       </c>
       <c r="C136" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D136" s="13" t="s">
-        <v>141</v>
+      <c r="D136" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E136" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="137" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F136" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="137" spans="2:6">
       <c r="B137" s="4" t="s">
         <v>59</v>
       </c>
       <c r="C137" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D137" s="13" t="s">
-        <v>140</v>
+      <c r="D137" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="E137" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="138" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F137" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="138" spans="2:6">
       <c r="B138" s="4"/>
       <c r="C138" s="3"/>
-      <c r="D138" s="13"/>
+      <c r="D138" s="3"/>
       <c r="E138" s="13"/>
-    </row>
-    <row r="139" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F138" s="13"/>
+    </row>
+    <row r="139" spans="2:6">
       <c r="B139" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C139" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D139" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D139" s="3"/>
       <c r="E139" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F139" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
       <c r="B140" s="4"/>
       <c r="C140" s="3"/>
-      <c r="D140" s="13"/>
+      <c r="D140" s="3"/>
       <c r="E140" s="13"/>
-    </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F140" s="13"/>
+    </row>
+    <row r="141" spans="2:6">
       <c r="B141" s="4" t="s">
         <v>61</v>
       </c>
       <c r="C141" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D141" s="14"/>
+      <c r="D141" s="3" t="s">
+        <v>270</v>
+      </c>
       <c r="E141" s="14"/>
-    </row>
-    <row r="142" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F141" s="14"/>
+    </row>
+    <row r="142" spans="2:6">
       <c r="B142" s="4"/>
       <c r="C142" s="3"/>
-      <c r="D142" s="13"/>
+      <c r="D142" s="3"/>
       <c r="E142" s="13"/>
-    </row>
-    <row r="143" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F142" s="13"/>
+    </row>
+    <row r="143" spans="2:6">
       <c r="B143" s="4" t="s">
         <v>62</v>
       </c>
       <c r="C143" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D143" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D143" s="3"/>
       <c r="E143" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="144" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F143" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6">
       <c r="B144" s="4" t="s">
         <v>63</v>
       </c>
       <c r="C144" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D144" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D144" s="3"/>
       <c r="E144" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F144" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="2:6">
       <c r="B145" s="4" t="s">
         <v>64</v>
       </c>
       <c r="C145" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D145" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D145" s="3"/>
       <c r="E145" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F145" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="146" spans="2:6">
       <c r="B146" s="4" t="s">
         <v>65</v>
       </c>
       <c r="C146" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D146" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D146" s="3"/>
       <c r="E146" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F146" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="147" spans="2:6">
       <c r="B147" s="4" t="s">
         <v>66</v>
       </c>
       <c r="C147" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D147" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D147" s="3"/>
       <c r="E147" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F147" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" spans="2:6">
       <c r="B148" s="4" t="s">
         <v>67</v>
       </c>
       <c r="C148" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="D148" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D148" s="3"/>
       <c r="E148" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="149" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F148" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="149" spans="2:6">
       <c r="B149" s="4" t="s">
         <v>68</v>
       </c>
       <c r="C149" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D149" s="13" t="s">
-        <v>140</v>
+      <c r="D149" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="E149" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F149" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="150" spans="2:6">
       <c r="B150" s="4" t="s">
         <v>69</v>
       </c>
       <c r="C150" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D150" s="13"/>
+      <c r="D150" s="3" t="s">
+        <v>271</v>
+      </c>
       <c r="E150" s="13"/>
-    </row>
-    <row r="151" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F150" s="13"/>
+    </row>
+    <row r="151" spans="2:6">
       <c r="B151" s="4" t="s">
         <v>70</v>
       </c>
       <c r="C151" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D151" s="13"/>
+      <c r="D151" s="3" t="s">
+        <v>271</v>
+      </c>
       <c r="E151" s="13"/>
-    </row>
-    <row r="152" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F151" s="13"/>
+    </row>
+    <row r="152" spans="2:6">
       <c r="B152" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C152" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D152" s="13"/>
+      <c r="D152" s="3"/>
       <c r="E152" s="13"/>
-    </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F152" s="13"/>
+    </row>
+    <row r="153" spans="2:6">
       <c r="B153" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C153" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D153" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D153" s="3"/>
       <c r="E153" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F153" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="154" spans="2:6">
       <c r="B154" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C154" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D154" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D154" s="3"/>
       <c r="E154" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F154" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="2:6">
       <c r="B155" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C155" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D155" s="13" t="s">
-        <v>140</v>
+      <c r="D155" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="E155" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F155" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="156" spans="2:6">
       <c r="B156" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C156" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D156" s="13" t="s">
-        <v>140</v>
+      <c r="D156" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="E156" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="157" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F156" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="157" spans="2:6">
       <c r="B157" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C157" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D157" s="13"/>
+      <c r="D157" s="3"/>
       <c r="E157" s="13"/>
-    </row>
-    <row r="158" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F157" s="13"/>
+    </row>
+    <row r="158" spans="2:6">
       <c r="B158" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C158" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D158" s="13"/>
+      <c r="D158" s="3"/>
       <c r="E158" s="13"/>
-    </row>
-    <row r="159" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F158" s="13"/>
+    </row>
+    <row r="159" spans="2:6">
       <c r="B159" s="4"/>
       <c r="C159" s="3"/>
-      <c r="D159" s="13"/>
+      <c r="D159" s="3"/>
       <c r="E159" s="13"/>
-    </row>
-    <row r="160" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F159" s="13"/>
+    </row>
+    <row r="160" spans="2:6">
       <c r="B160" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C160" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D160" s="13"/>
+      <c r="D160" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E160" s="13"/>
-    </row>
-    <row r="161" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F160" s="13"/>
+    </row>
+    <row r="161" spans="2:6">
       <c r="B161" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C161" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D161" s="13"/>
+      <c r="D161" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E161" s="13"/>
-    </row>
-    <row r="162" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F161" s="13"/>
+    </row>
+    <row r="162" spans="2:6">
       <c r="B162" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C162" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="D162" s="13" t="s">
-        <v>141</v>
+      <c r="D162" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E162" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="163" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F162" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="163" spans="2:6">
       <c r="B163" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C163" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="D163" s="13" t="s">
-        <v>141</v>
+      <c r="D163" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E163" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="164" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F163" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
       <c r="B164" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C164" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D164" s="13"/>
-      <c r="E164" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="165" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D164" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E164" s="13"/>
+      <c r="F164" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="165" spans="2:6">
       <c r="B165" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C165" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D165" s="13"/>
-      <c r="E165" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="166" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D165" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E165" s="13"/>
+      <c r="F165" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="166" spans="2:6">
       <c r="B166" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C166" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D166" s="13" t="s">
-        <v>141</v>
+      <c r="D166" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="E166" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="167" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F166" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="167" spans="2:6">
       <c r="B167" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C167" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D167" s="13" t="s">
-        <v>141</v>
+      <c r="D167" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="E167" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="168" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F167" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="168" spans="2:6">
       <c r="B168" s="4" t="s">
         <v>77</v>
       </c>
       <c r="C168" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D168" s="13" t="s">
-        <v>141</v>
+      <c r="D168" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E168" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="169" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F168" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
       <c r="B169" s="4" t="s">
         <v>77</v>
       </c>
       <c r="C169" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D169" s="13" t="s">
-        <v>141</v>
+      <c r="D169" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E169" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="170" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F169" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6">
       <c r="B170" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C170" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D170" s="13"/>
+      <c r="D170" s="3"/>
       <c r="E170" s="13"/>
-    </row>
-    <row r="171" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F170" s="13"/>
+    </row>
+    <row r="171" spans="2:6">
       <c r="B171" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C171" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D171" s="13"/>
+      <c r="D171" s="3"/>
       <c r="E171" s="13"/>
-    </row>
-    <row r="172" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F171" s="13"/>
+    </row>
+    <row r="172" spans="2:6">
       <c r="B172" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C172" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D172" s="13"/>
+      <c r="D172" s="3"/>
       <c r="E172" s="13"/>
-    </row>
-    <row r="173" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F172" s="13"/>
+    </row>
+    <row r="173" spans="2:6">
       <c r="B173" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C173" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D173" s="13"/>
+      <c r="D173" s="3"/>
       <c r="E173" s="13"/>
-    </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F173" s="13"/>
+    </row>
+    <row r="174" spans="2:6">
       <c r="B174" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C174" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D174" s="13"/>
+      <c r="D174" s="3"/>
       <c r="E174" s="13"/>
-    </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F174" s="13"/>
+    </row>
+    <row r="175" spans="2:6">
       <c r="B175" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C175" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D175" s="13"/>
+      <c r="D175" s="3"/>
       <c r="E175" s="13"/>
-    </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F175" s="13"/>
+    </row>
+    <row r="176" spans="2:6">
       <c r="B176" s="4"/>
       <c r="C176" s="3"/>
-      <c r="D176" s="13"/>
+      <c r="D176" s="3"/>
       <c r="E176" s="13"/>
-    </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F176" s="13"/>
+    </row>
+    <row r="177" spans="2:6">
       <c r="B177" s="4" t="s">
         <v>78</v>
       </c>
       <c r="C177" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D177" s="13"/>
+      <c r="D177" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E177" s="13"/>
-    </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F177" s="13"/>
+    </row>
+    <row r="178" spans="2:6">
       <c r="B178" s="4" t="s">
         <v>79</v>
       </c>
       <c r="C178" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="D178" s="13"/>
+      <c r="D178" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E178" s="13"/>
-    </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F178" s="13"/>
+    </row>
+    <row r="179" spans="2:6">
       <c r="B179" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C179" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D179" s="13"/>
+      <c r="D179" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E179" s="13"/>
-    </row>
-    <row r="180" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F179" s="13"/>
+    </row>
+    <row r="180" spans="2:6">
       <c r="B180" s="4" t="s">
         <v>81</v>
       </c>
       <c r="C180" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D180" s="13"/>
+      <c r="D180" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E180" s="13"/>
-    </row>
-    <row r="181" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F180" s="13"/>
+    </row>
+    <row r="181" spans="2:6">
       <c r="B181" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C181" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D181" s="13"/>
+      <c r="D181" s="3"/>
       <c r="E181" s="13"/>
-    </row>
-    <row r="182" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F181" s="13"/>
+    </row>
+    <row r="182" spans="2:6">
       <c r="B182" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C182" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D182" s="13"/>
+      <c r="D182" s="3"/>
       <c r="E182" s="13"/>
-    </row>
-    <row r="183" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F182" s="13"/>
+    </row>
+    <row r="183" spans="2:6">
       <c r="B183" s="4" t="s">
         <v>82</v>
       </c>
       <c r="C183" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D183" s="13"/>
+      <c r="D183" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="E183" s="13"/>
-    </row>
-    <row r="184" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F183" s="13"/>
+    </row>
+    <row r="184" spans="2:6">
       <c r="B184" s="4" t="s">
         <v>83</v>
       </c>
       <c r="C184" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D184" s="13"/>
+      <c r="D184" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E184" s="13"/>
-    </row>
-    <row r="185" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F184" s="13"/>
+    </row>
+    <row r="185" spans="2:6">
       <c r="B185" s="4" t="s">
         <v>84</v>
       </c>
       <c r="C185" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D185" s="13"/>
+      <c r="D185" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E185" s="13"/>
-    </row>
-    <row r="186" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F185" s="13"/>
+    </row>
+    <row r="186" spans="2:6">
       <c r="B186" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C186" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D186" s="13"/>
+      <c r="D186" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E186" s="13"/>
-    </row>
-    <row r="187" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F186" s="13"/>
+    </row>
+    <row r="187" spans="2:6">
       <c r="B187" s="4" t="s">
         <v>86</v>
       </c>
       <c r="C187" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D187" s="13"/>
+      <c r="D187" s="3" t="s">
+        <v>275</v>
+      </c>
       <c r="E187" s="13"/>
-    </row>
-    <row r="188" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F187" s="13"/>
+    </row>
+    <row r="188" spans="2:6">
       <c r="B188" s="4" t="s">
         <v>87</v>
       </c>
       <c r="C188" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="D188" s="13"/>
+      <c r="D188" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E188" s="13"/>
-    </row>
-    <row r="189" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F188" s="13"/>
+    </row>
+    <row r="189" spans="2:6">
       <c r="B189" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C189" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D189" s="13"/>
+      <c r="D189" s="3" t="s">
+        <v>270</v>
+      </c>
       <c r="E189" s="13"/>
-    </row>
-    <row r="190" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F189" s="13"/>
+    </row>
+    <row r="190" spans="2:6">
       <c r="B190" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C190" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D190" s="13"/>
+      <c r="D190" s="3"/>
       <c r="E190" s="13"/>
-    </row>
-    <row r="191" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F190" s="13"/>
+    </row>
+    <row r="191" spans="2:6">
       <c r="B191" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C191" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D191" s="13"/>
+      <c r="D191" s="3"/>
       <c r="E191" s="13"/>
-    </row>
-    <row r="192" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F191" s="13"/>
+    </row>
+    <row r="192" spans="2:6">
       <c r="B192" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C192" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D192" s="13"/>
+      <c r="D192" s="3"/>
       <c r="E192" s="13"/>
-    </row>
-    <row r="193" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F192" s="13"/>
+    </row>
+    <row r="193" spans="2:6">
       <c r="B193" s="4"/>
       <c r="C193" s="3"/>
-      <c r="D193" s="13"/>
+      <c r="D193" s="3"/>
       <c r="E193" s="13"/>
-    </row>
-    <row r="194" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F193" s="13"/>
+    </row>
+    <row r="194" spans="2:6">
       <c r="B194" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C194" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D194" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D194" s="3"/>
       <c r="E194" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="195" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F194" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="195" spans="2:6">
       <c r="B195" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C195" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D195" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D195" s="3"/>
       <c r="E195" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="196" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F195" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="196" spans="2:6">
       <c r="B196" s="4" t="s">
         <v>72</v>
       </c>
       <c r="C196" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D196" s="13" t="s">
-        <v>140</v>
+      <c r="D196" s="3" t="s">
+        <v>271</v>
       </c>
       <c r="E196" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="197" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F196" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="197" spans="2:6">
       <c r="B197" s="4" t="s">
         <v>73</v>
       </c>
       <c r="C197" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="D197" s="13"/>
+      <c r="D197" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E197" s="13"/>
-    </row>
-    <row r="198" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F197" s="13"/>
+    </row>
+    <row r="198" spans="2:6">
       <c r="B198" s="4" t="s">
         <v>74</v>
       </c>
       <c r="C198" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D198" s="13" t="s">
-        <v>141</v>
+      <c r="D198" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E198" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="199" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F198" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="199" spans="2:6">
       <c r="B199" s="4" t="s">
         <v>75</v>
       </c>
       <c r="C199" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D199" s="13"/>
-      <c r="E199" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="200" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D199" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E199" s="13"/>
+      <c r="F199" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="200" spans="2:6">
       <c r="B200" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C200" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D200" s="13" t="s">
-        <v>141</v>
+      <c r="D200" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="E200" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="201" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F200" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="201" spans="2:6">
       <c r="B201" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C201" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D201" s="13" t="s">
-        <v>141</v>
+      <c r="D201" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="E201" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="202" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F201" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="202" spans="2:6">
       <c r="B202" s="4" t="s">
         <v>77</v>
       </c>
       <c r="C202" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D202" s="13" t="s">
-        <v>141</v>
+      <c r="D202" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E202" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="203" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F202" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="203" spans="2:6">
       <c r="B203" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C203" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D203" s="13"/>
+      <c r="D203" s="3"/>
       <c r="E203" s="13"/>
-    </row>
-    <row r="204" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F203" s="13"/>
+    </row>
+    <row r="204" spans="2:6">
       <c r="B204" s="4" t="s">
         <v>89</v>
       </c>
       <c r="C204" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D204" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D204" s="3"/>
       <c r="E204" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="205" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F204" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="205" spans="2:6">
       <c r="B205" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C205" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D205" s="13"/>
+      <c r="D205" s="3"/>
       <c r="E205" s="13"/>
-    </row>
-    <row r="206" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F205" s="13"/>
+    </row>
+    <row r="206" spans="2:6">
       <c r="B206" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C206" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D206" s="13"/>
+      <c r="D206" s="3"/>
       <c r="E206" s="13"/>
-    </row>
-    <row r="207" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F206" s="13"/>
+    </row>
+    <row r="207" spans="2:6">
       <c r="B207" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C207" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D207" s="13"/>
+      <c r="D207" s="3"/>
       <c r="E207" s="13"/>
-    </row>
-    <row r="208" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F207" s="13"/>
+    </row>
+    <row r="208" spans="2:6">
       <c r="B208" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C208" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D208" s="13"/>
+      <c r="D208" s="3"/>
       <c r="E208" s="13"/>
-    </row>
-    <row r="209" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F208" s="13"/>
+    </row>
+    <row r="209" spans="2:6">
       <c r="B209" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C209" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D209" s="13"/>
+      <c r="D209" s="3"/>
       <c r="E209" s="13"/>
-    </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F209" s="13"/>
+    </row>
+    <row r="210" spans="2:6">
       <c r="B210" s="4"/>
       <c r="C210" s="3"/>
-      <c r="D210" s="13"/>
+      <c r="D210" s="3"/>
       <c r="E210" s="13"/>
-    </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F210" s="13"/>
+    </row>
+    <row r="211" spans="2:6">
       <c r="B211" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C211" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D211" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D211" s="3"/>
       <c r="E211" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="212" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F211" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="212" spans="2:6">
       <c r="B212" s="4" t="s">
         <v>91</v>
       </c>
       <c r="C212" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D212" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D212" s="3"/>
       <c r="E212" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="213" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F212" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="213" spans="2:6">
       <c r="B213" s="4" t="s">
         <v>92</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D213" s="13"/>
+      <c r="D213" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E213" s="13"/>
-    </row>
-    <row r="214" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F213" s="13"/>
+    </row>
+    <row r="214" spans="2:6">
       <c r="B214" s="4" t="s">
         <v>93</v>
       </c>
       <c r="C214" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="D214" s="13"/>
-      <c r="E214" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="215" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D214" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E214" s="13"/>
+      <c r="F214" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="215" spans="2:6">
       <c r="B215" s="4"/>
       <c r="C215" s="3"/>
-      <c r="D215" s="13"/>
+      <c r="D215" s="3"/>
       <c r="E215" s="13"/>
-    </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F215" s="13"/>
+    </row>
+    <row r="216" spans="2:6">
       <c r="B216" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C216" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D216" s="13"/>
+      <c r="D216" s="3"/>
       <c r="E216" s="13"/>
-    </row>
-    <row r="217" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F216" s="13"/>
+    </row>
+    <row r="217" spans="2:6">
       <c r="B217" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C217" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D217" s="13"/>
-      <c r="E217" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="218" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D217" s="3"/>
+      <c r="E217" s="13"/>
+      <c r="F217" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="218" spans="2:6">
       <c r="B218" s="4" t="s">
         <v>96</v>
       </c>
       <c r="C218" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D218" s="13"/>
-      <c r="E218" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D218" s="3"/>
+      <c r="E218" s="13"/>
+      <c r="F218" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="219" spans="2:6">
       <c r="B219" s="4" t="s">
         <v>97</v>
       </c>
       <c r="C219" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="D219" s="13" t="s">
-        <v>141</v>
-      </c>
+      <c r="D219" s="3"/>
       <c r="E219" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="220" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F219" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="220" spans="2:6">
       <c r="B220" s="4" t="s">
         <v>98</v>
       </c>
       <c r="C220" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D220" s="13"/>
+      <c r="D220" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E220" s="13"/>
-    </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F220" s="13"/>
+    </row>
+    <row r="221" spans="2:6">
       <c r="B221" s="4" t="s">
         <v>99</v>
       </c>
       <c r="C221" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D221" s="13"/>
+      <c r="D221" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E221" s="13"/>
-    </row>
-    <row r="222" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F221" s="13"/>
+    </row>
+    <row r="222" spans="2:6">
       <c r="B222" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C222" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="D222" s="13"/>
+      <c r="D222" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E222" s="13"/>
-    </row>
-    <row r="223" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F222" s="13"/>
+    </row>
+    <row r="223" spans="2:6">
       <c r="B223" s="4" t="s">
         <v>101</v>
       </c>
       <c r="C223" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D223" s="13" t="s">
-        <v>140</v>
+      <c r="D223" s="3" t="s">
+        <v>269</v>
       </c>
       <c r="E223" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="224" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F223" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="224" spans="2:6">
       <c r="B224" s="4"/>
       <c r="C224" s="3"/>
-      <c r="D224" s="13"/>
+      <c r="D224" s="3"/>
       <c r="E224" s="13"/>
-    </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F224" s="13"/>
+    </row>
+    <row r="225" spans="2:6">
       <c r="B225" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C225" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D225" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D225" s="3"/>
       <c r="E225" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="226" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F225" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="226" spans="2:6">
       <c r="B226" s="4" t="s">
         <v>76</v>
       </c>
       <c r="C226" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D226" s="13" t="s">
-        <v>141</v>
+      <c r="D226" s="3" t="s">
+        <v>273</v>
       </c>
       <c r="E226" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="227" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F226" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="227" spans="2:6">
       <c r="B227" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C227" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D227" s="13"/>
+      <c r="D227" s="3"/>
       <c r="E227" s="13"/>
-    </row>
-    <row r="228" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F227" s="13"/>
+    </row>
+    <row r="228" spans="2:6">
       <c r="B228" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C228" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D228" s="13"/>
+      <c r="D228" s="3"/>
       <c r="E228" s="13"/>
-    </row>
-    <row r="229" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F228" s="13"/>
+    </row>
+    <row r="229" spans="2:6">
       <c r="B229" s="4"/>
       <c r="C229" s="3"/>
-      <c r="D229" s="13"/>
+      <c r="D229" s="3"/>
       <c r="E229" s="13"/>
-    </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F229" s="13"/>
+    </row>
+    <row r="230" spans="2:6">
       <c r="B230" s="4"/>
       <c r="C230" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D230" s="13"/>
+      <c r="D230" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E230" s="13"/>
-    </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F230" s="13"/>
+    </row>
+    <row r="231" spans="2:6">
       <c r="B231" s="4"/>
       <c r="C231" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D231" s="13"/>
+      <c r="D231" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E231" s="13"/>
-    </row>
-    <row r="232" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F231" s="13"/>
+    </row>
+    <row r="232" spans="2:6">
       <c r="B232" s="4"/>
       <c r="C232" s="3"/>
-      <c r="D232" s="13"/>
+      <c r="D232" s="3"/>
       <c r="E232" s="13"/>
-    </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F232" s="13"/>
+    </row>
+    <row r="233" spans="2:6">
       <c r="B233" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C233" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D233" s="13"/>
+      <c r="D233" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E233" s="13"/>
-    </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F233" s="13"/>
+    </row>
+    <row r="234" spans="2:6">
       <c r="B234" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C234" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D234" s="13"/>
+      <c r="D234" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E234" s="13"/>
-    </row>
-    <row r="235" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F234" s="13"/>
+    </row>
+    <row r="235" spans="2:6">
       <c r="B235" s="4" t="s">
         <v>104</v>
       </c>
       <c r="C235" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="D235" s="13"/>
+      <c r="D235" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E235" s="13"/>
-    </row>
-    <row r="236" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F235" s="13"/>
+    </row>
+    <row r="236" spans="2:6">
       <c r="B236" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C236" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D236" s="13"/>
+      <c r="D236" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E236" s="13"/>
-    </row>
-    <row r="237" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F236" s="13"/>
+    </row>
+    <row r="237" spans="2:6">
       <c r="B237" s="4"/>
       <c r="C237" s="3"/>
-      <c r="D237" s="13"/>
+      <c r="D237" s="3"/>
       <c r="E237" s="13"/>
-    </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F237" s="13"/>
+    </row>
+    <row r="238" spans="2:6">
       <c r="B238" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C238" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D238" s="13"/>
+      <c r="D238" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E238" s="13"/>
-    </row>
-    <row r="239" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F238" s="13"/>
+    </row>
+    <row r="239" spans="2:6">
       <c r="B239" s="4" t="s">
         <v>80</v>
       </c>
       <c r="C239" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D239" s="13"/>
+      <c r="D239" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E239" s="13"/>
-    </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F239" s="13"/>
+    </row>
+    <row r="240" spans="2:6">
       <c r="B240" s="4" t="s">
         <v>106</v>
       </c>
       <c r="C240" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D240" s="13"/>
+      <c r="D240" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E240" s="13"/>
-    </row>
-    <row r="241" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F240" s="13"/>
+    </row>
+    <row r="241" spans="2:6">
       <c r="B241" s="4" t="s">
         <v>81</v>
       </c>
       <c r="C241" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="D241" s="13"/>
+      <c r="D241" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="E241" s="13"/>
-    </row>
-    <row r="242" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F241" s="13"/>
+    </row>
+    <row r="242" spans="2:6">
       <c r="B242" s="4"/>
       <c r="C242" s="3"/>
-      <c r="D242" s="13"/>
+      <c r="D242" s="3"/>
       <c r="E242" s="13"/>
-    </row>
-    <row r="243" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F242" s="13"/>
+    </row>
+    <row r="243" spans="2:6">
       <c r="B243" s="4" t="s">
         <v>107</v>
       </c>
       <c r="C243" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D243" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="E243" s="13"/>
-    </row>
-    <row r="244" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D243" s="3"/>
+      <c r="E243" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F243" s="13"/>
+    </row>
+    <row r="244" spans="2:6">
       <c r="B244" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C244" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D244" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D244" s="3"/>
       <c r="E244" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="245" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F244" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="245" spans="2:6">
       <c r="B245" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C245" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D245" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D245" s="3"/>
       <c r="E245" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="246" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F245" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="246" spans="2:6">
       <c r="B246" s="4" t="s">
         <v>110</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D246" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D246" s="3"/>
       <c r="E246" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="247" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F246" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="247" spans="2:6">
       <c r="B247" s="4" t="s">
         <v>111</v>
       </c>
       <c r="C247" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="D247" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D247" s="3"/>
       <c r="E247" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="248" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F247" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="248" spans="2:6">
       <c r="B248" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="D248" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D248" s="3"/>
       <c r="E248" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="249" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F248" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="249" spans="2:6">
       <c r="B249" s="4" t="s">
         <v>113</v>
       </c>
       <c r="C249" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D249" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D249" s="3"/>
       <c r="E249" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="250" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F249" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="250" spans="2:6">
       <c r="B250" s="4" t="s">
         <v>114</v>
       </c>
       <c r="C250" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D250" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D250" s="3"/>
       <c r="E250" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="251" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F250" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="251" spans="2:6">
       <c r="B251" s="4" t="s">
         <v>115</v>
       </c>
       <c r="C251" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D251" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D251" s="3"/>
       <c r="E251" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="252" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F251" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="252" spans="2:6">
       <c r="B252" s="4" t="s">
         <v>116</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D252" s="13"/>
+      <c r="D252" s="3"/>
       <c r="E252" s="13"/>
-    </row>
-    <row r="253" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F252" s="13"/>
+    </row>
+    <row r="253" spans="2:6">
       <c r="B253" s="4" t="s">
         <v>117</v>
       </c>
       <c r="C253" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D253" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D253" s="3"/>
       <c r="E253" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="254" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F253" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="254" spans="2:6">
       <c r="B254" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C254" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D254" s="13"/>
+      <c r="D254" s="3"/>
       <c r="E254" s="13"/>
-    </row>
-    <row r="255" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F254" s="13"/>
+    </row>
+    <row r="255" spans="2:6">
       <c r="B255" s="4" t="s">
         <v>118</v>
       </c>
       <c r="C255" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D255" s="13"/>
+      <c r="D255" s="3"/>
       <c r="E255" s="13"/>
-    </row>
-    <row r="256" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F255" s="13"/>
+    </row>
+    <row r="256" spans="2:6">
       <c r="B256" s="4" t="s">
         <v>119</v>
       </c>
       <c r="C256" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="D256" s="13"/>
+      <c r="D256" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E256" s="13"/>
-    </row>
-    <row r="257" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F256" s="13"/>
+    </row>
+    <row r="257" spans="2:6">
       <c r="B257" s="4" t="s">
         <v>120</v>
       </c>
       <c r="C257" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D257" s="13"/>
+      <c r="D257" s="3" t="s">
+        <v>272</v>
+      </c>
       <c r="E257" s="13"/>
-    </row>
-    <row r="258" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F257" s="13"/>
+    </row>
+    <row r="258" spans="2:6">
       <c r="B258" s="4" t="s">
         <v>121</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D258" s="13"/>
-      <c r="E258" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="259" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D258" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E258" s="13"/>
+      <c r="F258" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="259" spans="2:6">
       <c r="B259" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C259" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="D259" s="13"/>
-      <c r="E259" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="260" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D259" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E259" s="13"/>
+      <c r="F259" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="260" spans="2:6">
       <c r="B260" s="4" t="s">
         <v>123</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D260" s="13"/>
-      <c r="E260" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="261" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D260" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E260" s="13"/>
+      <c r="F260" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="261" spans="2:6">
       <c r="B261" s="4" t="s">
         <v>124</v>
       </c>
       <c r="C261" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D261" s="13"/>
-      <c r="E261" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="262" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D261" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E261" s="13"/>
+      <c r="F261" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="262" spans="2:6">
       <c r="B262" s="4" t="s">
         <v>125</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D262" s="13" t="s">
-        <v>141</v>
+      <c r="D262" s="3" t="s">
+        <v>268</v>
       </c>
       <c r="E262" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="263" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F262" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="263" spans="2:6">
       <c r="B263" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C263" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D263" s="13"/>
+      <c r="D263" s="3"/>
       <c r="E263" s="13"/>
-    </row>
-    <row r="264" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F263" s="13"/>
+    </row>
+    <row r="264" spans="2:6">
       <c r="B264" s="4" t="s">
         <v>126</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D264" s="13"/>
-      <c r="E264" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="265" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D264" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="E264" s="13"/>
+      <c r="F264" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="265" spans="2:6">
       <c r="B265" s="4" t="s">
         <v>127</v>
       </c>
       <c r="C265" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D265" s="13"/>
-      <c r="E265" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="266" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="D265" s="19" t="s">
+        <v>256</v>
+      </c>
+      <c r="E265" s="13"/>
+      <c r="F265" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="266" spans="2:6">
       <c r="B266" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C266" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="D266" s="13"/>
+      <c r="D266" s="19"/>
       <c r="E266" s="13"/>
-    </row>
-    <row r="267" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F266" s="13"/>
+    </row>
+    <row r="267" spans="2:6">
       <c r="B267" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C267" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D267" s="13"/>
+      <c r="D267" s="19"/>
       <c r="E267" s="13"/>
-    </row>
-    <row r="268" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F267" s="13"/>
+    </row>
+    <row r="268" spans="2:6">
       <c r="B268" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C268" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D268" s="13"/>
+      <c r="D268" s="19"/>
       <c r="E268" s="13"/>
-    </row>
-    <row r="269" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F268" s="13"/>
+    </row>
+    <row r="269" spans="2:6">
       <c r="B269" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C269" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D269" s="13"/>
+      <c r="D269" s="19"/>
       <c r="E269" s="13"/>
-    </row>
-    <row r="270" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F269" s="13"/>
+    </row>
+    <row r="270" spans="2:6">
       <c r="B270" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C270" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D270" s="13"/>
+      <c r="D270" s="19"/>
       <c r="E270" s="13"/>
-    </row>
-    <row r="271" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F270" s="13"/>
+    </row>
+    <row r="271" spans="2:6">
       <c r="B271" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C271" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D271" s="13"/>
+      <c r="D271" s="19"/>
       <c r="E271" s="13"/>
-    </row>
-    <row r="272" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F271" s="13"/>
+    </row>
+    <row r="272" spans="2:6">
       <c r="B272" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C272" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D272" s="13"/>
+      <c r="D272" s="19"/>
       <c r="E272" s="13"/>
-    </row>
-    <row r="273" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F272" s="13"/>
+    </row>
+    <row r="273" spans="2:6">
       <c r="B273" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C273" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D273" s="13"/>
+      <c r="D273" s="19"/>
       <c r="E273" s="13"/>
-    </row>
-    <row r="274" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F273" s="13"/>
+    </row>
+    <row r="274" spans="2:6">
       <c r="B274" s="5" t="s">
         <v>128</v>
       </c>
       <c r="C274" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="D274" s="13"/>
+      <c r="D274" s="19"/>
       <c r="E274" s="13"/>
-    </row>
-    <row r="275" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F274" s="13"/>
+    </row>
+    <row r="275" spans="2:6">
       <c r="B275" s="4"/>
       <c r="C275" s="3"/>
-      <c r="D275" s="13"/>
+      <c r="D275" s="3"/>
       <c r="E275" s="13"/>
-    </row>
-    <row r="276" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F275" s="13"/>
+    </row>
+    <row r="276" spans="2:6">
       <c r="B276" s="4"/>
       <c r="C276" s="3"/>
-      <c r="D276" s="14"/>
+      <c r="D276" s="3"/>
       <c r="E276" s="14"/>
-    </row>
-    <row r="277" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F276" s="14"/>
+    </row>
+    <row r="277" spans="2:6">
       <c r="B277" s="4"/>
       <c r="C277" s="3"/>
-      <c r="D277" s="14"/>
+      <c r="D277" s="3"/>
       <c r="E277" s="14"/>
-    </row>
-    <row r="278" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F277" s="14"/>
+    </row>
+    <row r="278" spans="2:6">
       <c r="B278" s="4"/>
       <c r="C278" s="3"/>
-      <c r="D278" s="14"/>
+      <c r="D278" s="3"/>
       <c r="E278" s="14"/>
-    </row>
-    <row r="279" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F278" s="14"/>
+    </row>
+    <row r="279" spans="2:6">
       <c r="B279" s="4"/>
       <c r="C279" s="3"/>
-      <c r="D279" s="14"/>
+      <c r="D279" s="3"/>
       <c r="E279" s="14"/>
-    </row>
-    <row r="280" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F279" s="14"/>
+    </row>
+    <row r="280" spans="2:6">
       <c r="B280" s="4"/>
       <c r="C280" s="3"/>
-      <c r="D280" s="14"/>
+      <c r="D280" s="3"/>
       <c r="E280" s="14"/>
-    </row>
-    <row r="281" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F280" s="14"/>
+    </row>
+    <row r="281" spans="2:6">
       <c r="B281" s="4"/>
       <c r="C281" s="3"/>
-      <c r="D281" s="14"/>
+      <c r="D281" s="3"/>
       <c r="E281" s="14"/>
-    </row>
-    <row r="282" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F281" s="14"/>
+    </row>
+    <row r="282" spans="2:6">
       <c r="B282" s="4"/>
       <c r="C282" s="3"/>
-      <c r="D282" s="14"/>
+      <c r="D282" s="3"/>
       <c r="E282" s="14"/>
-    </row>
-    <row r="283" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F282" s="14"/>
+    </row>
+    <row r="283" spans="2:6">
       <c r="B283" s="4"/>
       <c r="C283" s="3"/>
-      <c r="D283" s="14"/>
+      <c r="D283" s="3"/>
       <c r="E283" s="14"/>
-    </row>
-    <row r="284" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F283" s="14"/>
+    </row>
+    <row r="284" spans="2:6">
       <c r="B284" s="4"/>
       <c r="C284" s="3"/>
-      <c r="D284" s="14"/>
+      <c r="D284" s="3"/>
       <c r="E284" s="14"/>
-    </row>
-    <row r="285" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F284" s="14"/>
+    </row>
+    <row r="285" spans="2:6">
       <c r="B285" s="5"/>
       <c r="C285" s="17"/>
-      <c r="D285" s="14"/>
+      <c r="D285" s="3"/>
       <c r="E285" s="14"/>
-    </row>
-    <row r="286" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F285" s="14"/>
+    </row>
+    <row r="286" spans="2:6">
       <c r="B286" s="4"/>
       <c r="C286" s="3"/>
-      <c r="D286" s="14"/>
+      <c r="D286" s="3"/>
       <c r="E286" s="14"/>
-    </row>
-    <row r="287" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F286" s="14"/>
+    </row>
+    <row r="287" spans="2:6">
       <c r="B287" s="5"/>
       <c r="C287" s="17"/>
-      <c r="D287" s="14"/>
+      <c r="D287" s="3"/>
       <c r="E287" s="14"/>
-    </row>
-    <row r="288" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F287" s="14"/>
+    </row>
+    <row r="288" spans="2:6">
       <c r="B288" s="5"/>
       <c r="C288" s="17"/>
-      <c r="D288" s="14"/>
+      <c r="D288" s="3"/>
       <c r="E288" s="14"/>
-    </row>
-    <row r="289" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F288" s="14"/>
+    </row>
+    <row r="289" spans="2:6">
       <c r="B289" s="4"/>
       <c r="C289" s="3"/>
-      <c r="D289" s="14"/>
+      <c r="D289" s="3"/>
       <c r="E289" s="14"/>
-    </row>
-    <row r="290" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F289" s="14"/>
+    </row>
+    <row r="290" spans="2:6">
       <c r="B290" s="4"/>
       <c r="C290" s="3"/>
-      <c r="D290" s="14"/>
+      <c r="D290" s="3"/>
       <c r="E290" s="14"/>
-    </row>
-    <row r="291" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F290" s="14"/>
+    </row>
+    <row r="291" spans="2:6">
       <c r="B291" s="4"/>
       <c r="C291" s="3"/>
-      <c r="D291" s="14"/>
+      <c r="D291" s="3"/>
       <c r="E291" s="14"/>
-    </row>
-    <row r="292" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F291" s="14"/>
+    </row>
+    <row r="292" spans="2:6">
       <c r="B292" s="4"/>
       <c r="C292" s="3"/>
-      <c r="D292" s="13"/>
+      <c r="D292" s="3"/>
       <c r="E292" s="13"/>
-    </row>
-    <row r="293" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F292" s="13"/>
+    </row>
+    <row r="293" spans="2:6">
       <c r="B293" s="4"/>
       <c r="C293" s="3"/>
-      <c r="D293" s="14"/>
+      <c r="D293" s="3"/>
       <c r="E293" s="14"/>
-    </row>
-    <row r="294" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F293" s="14"/>
+    </row>
+    <row r="294" spans="2:6">
       <c r="B294" s="4"/>
       <c r="C294" s="3"/>
-      <c r="D294" s="14"/>
+      <c r="D294" s="3"/>
       <c r="E294" s="14"/>
-    </row>
-    <row r="295" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F294" s="14"/>
+    </row>
+    <row r="295" spans="2:6">
       <c r="B295" s="4"/>
       <c r="C295" s="3"/>
-      <c r="D295" s="14"/>
+      <c r="D295" s="3"/>
       <c r="E295" s="14"/>
-    </row>
-    <row r="296" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F295" s="14"/>
+    </row>
+    <row r="296" spans="2:6">
       <c r="B296" s="4"/>
       <c r="C296" s="3"/>
-      <c r="D296" s="14"/>
+      <c r="D296" s="3"/>
       <c r="E296" s="14"/>
-    </row>
-    <row r="297" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F296" s="14"/>
+    </row>
+    <row r="297" spans="2:6">
       <c r="B297" s="4"/>
       <c r="C297" s="3"/>
-      <c r="D297" s="14"/>
+      <c r="D297" s="3"/>
       <c r="E297" s="14"/>
-    </row>
-    <row r="298" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F297" s="14"/>
+    </row>
+    <row r="298" spans="2:6">
       <c r="B298" s="4"/>
       <c r="C298" s="3"/>
-      <c r="D298" s="14"/>
+      <c r="D298" s="3"/>
       <c r="E298" s="14"/>
-    </row>
-    <row r="299" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F298" s="14"/>
+    </row>
+    <row r="299" spans="2:6">
       <c r="B299" s="4"/>
       <c r="C299" s="3"/>
-      <c r="D299" s="14"/>
+      <c r="D299" s="3"/>
       <c r="E299" s="14"/>
-    </row>
-    <row r="300" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F299" s="14"/>
+    </row>
+    <row r="300" spans="2:6">
       <c r="B300" s="4"/>
       <c r="C300" s="3"/>
-      <c r="D300" s="14"/>
+      <c r="D300" s="3"/>
       <c r="E300" s="14"/>
-    </row>
-    <row r="301" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F300" s="14"/>
+    </row>
+    <row r="301" spans="2:6">
       <c r="B301" s="4"/>
       <c r="C301" s="3"/>
-      <c r="D301" s="14"/>
+      <c r="D301" s="3"/>
       <c r="E301" s="14"/>
-    </row>
-    <row r="302" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F301" s="14"/>
+    </row>
+    <row r="302" spans="2:6">
       <c r="B302" s="5"/>
       <c r="C302" s="3"/>
-      <c r="D302" s="14"/>
+      <c r="D302" s="3"/>
       <c r="E302" s="14"/>
-    </row>
-    <row r="303" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F302" s="14"/>
+    </row>
+    <row r="303" spans="2:6">
       <c r="B303" s="4"/>
       <c r="C303" s="3"/>
-      <c r="D303" s="14"/>
+      <c r="D303" s="3"/>
       <c r="E303" s="14"/>
-    </row>
-    <row r="304" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F303" s="14"/>
+    </row>
+    <row r="304" spans="2:6">
       <c r="B304" s="5"/>
       <c r="C304" s="3"/>
-      <c r="D304" s="14"/>
+      <c r="D304" s="3"/>
       <c r="E304" s="14"/>
-    </row>
-    <row r="305" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F304" s="14"/>
+    </row>
+    <row r="305" spans="2:6">
       <c r="B305" s="5"/>
       <c r="C305" s="3"/>
-      <c r="D305" s="14"/>
+      <c r="D305" s="3"/>
       <c r="E305" s="14"/>
-    </row>
-    <row r="306" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F305" s="14"/>
+    </row>
+    <row r="306" spans="2:6">
       <c r="B306" s="4"/>
       <c r="C306" s="3"/>
-      <c r="D306" s="14"/>
+      <c r="D306" s="3"/>
       <c r="E306" s="14"/>
-    </row>
-    <row r="307" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F306" s="14"/>
+    </row>
+    <row r="307" spans="2:6">
       <c r="B307" s="4"/>
       <c r="C307" s="3"/>
-      <c r="D307" s="14"/>
+      <c r="D307" s="3"/>
       <c r="E307" s="14"/>
-    </row>
-    <row r="308" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F307" s="14"/>
+    </row>
+    <row r="308" spans="2:6">
       <c r="B308" s="4"/>
       <c r="C308" s="3"/>
-      <c r="D308" s="14"/>
+      <c r="D308" s="3"/>
       <c r="E308" s="14"/>
-    </row>
-    <row r="309" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F308" s="14"/>
+    </row>
+    <row r="309" spans="2:6">
       <c r="B309" s="4"/>
       <c r="C309" s="3"/>
-      <c r="D309" s="13"/>
+      <c r="D309" s="3"/>
       <c r="E309" s="13"/>
-    </row>
-    <row r="310" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F309" s="13"/>
+    </row>
+    <row r="310" spans="2:6">
       <c r="B310" s="4"/>
       <c r="C310" s="3"/>
-      <c r="D310" s="14"/>
+      <c r="D310" s="3"/>
       <c r="E310" s="14"/>
-    </row>
-    <row r="311" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F310" s="14"/>
+    </row>
+    <row r="311" spans="2:6">
       <c r="B311" s="4"/>
       <c r="C311" s="3"/>
-      <c r="D311" s="14"/>
+      <c r="D311" s="3"/>
       <c r="E311" s="14"/>
-    </row>
-    <row r="312" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F311" s="14"/>
+    </row>
+    <row r="312" spans="2:6">
       <c r="B312" s="4"/>
       <c r="C312" s="3"/>
-      <c r="D312" s="14"/>
+      <c r="D312" s="3"/>
       <c r="E312" s="14"/>
-    </row>
-    <row r="313" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F312" s="14"/>
+    </row>
+    <row r="313" spans="2:6">
       <c r="B313" s="4"/>
       <c r="C313" s="3"/>
-      <c r="D313" s="14"/>
+      <c r="D313" s="3"/>
       <c r="E313" s="14"/>
-    </row>
-    <row r="314" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F313" s="14"/>
+    </row>
+    <row r="314" spans="2:6">
       <c r="B314" s="4"/>
       <c r="C314" s="3"/>
-      <c r="D314" s="14"/>
+      <c r="D314" s="3"/>
       <c r="E314" s="14"/>
-    </row>
-    <row r="315" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F314" s="14"/>
+    </row>
+    <row r="315" spans="2:6">
       <c r="B315" s="4"/>
       <c r="C315" s="3"/>
-      <c r="D315" s="14"/>
+      <c r="D315" s="3"/>
       <c r="E315" s="14"/>
-    </row>
-    <row r="316" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F315" s="14"/>
+    </row>
+    <row r="316" spans="2:6">
       <c r="B316" s="4"/>
       <c r="C316" s="3"/>
-      <c r="D316" s="14"/>
+      <c r="D316" s="3"/>
       <c r="E316" s="14"/>
-    </row>
-    <row r="317" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F316" s="14"/>
+    </row>
+    <row r="317" spans="2:6">
       <c r="B317" s="4"/>
       <c r="C317" s="3"/>
-      <c r="D317" s="14"/>
+      <c r="D317" s="3"/>
       <c r="E317" s="14"/>
-    </row>
-    <row r="318" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F317" s="14"/>
+    </row>
+    <row r="318" spans="2:6">
       <c r="B318" s="4"/>
       <c r="C318" s="3"/>
-      <c r="D318" s="14"/>
+      <c r="D318" s="3"/>
       <c r="E318" s="14"/>
-    </row>
-    <row r="319" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F318" s="14"/>
+    </row>
+    <row r="319" spans="2:6">
       <c r="B319" s="5"/>
       <c r="C319" s="3"/>
-      <c r="D319" s="14"/>
+      <c r="D319" s="3"/>
       <c r="E319" s="14"/>
-    </row>
-    <row r="320" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F319" s="14"/>
+    </row>
+    <row r="320" spans="2:6">
       <c r="B320" s="4"/>
       <c r="C320" s="3"/>
-      <c r="D320" s="14"/>
+      <c r="D320" s="3"/>
       <c r="E320" s="14"/>
-    </row>
-    <row r="321" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F320" s="14"/>
+    </row>
+    <row r="321" spans="2:6">
       <c r="B321" s="5"/>
       <c r="C321" s="3"/>
-      <c r="D321" s="14"/>
+      <c r="D321" s="3"/>
       <c r="E321" s="14"/>
-    </row>
-    <row r="322" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F321" s="14"/>
+    </row>
+    <row r="322" spans="2:6">
       <c r="B322" s="5"/>
       <c r="C322" s="3"/>
-      <c r="D322" s="14"/>
+      <c r="D322" s="3"/>
       <c r="E322" s="14"/>
-    </row>
-    <row r="323" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F322" s="14"/>
+    </row>
+    <row r="323" spans="2:6">
       <c r="B323" s="4"/>
       <c r="C323" s="3"/>
-      <c r="D323" s="14"/>
+      <c r="D323" s="3"/>
       <c r="E323" s="14"/>
-    </row>
-    <row r="324" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F323" s="14"/>
+    </row>
+    <row r="324" spans="2:6">
       <c r="B324" s="4"/>
       <c r="C324" s="3"/>
-      <c r="D324" s="14"/>
+      <c r="D324" s="3"/>
       <c r="E324" s="14"/>
-    </row>
-    <row r="325" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F324" s="14"/>
+    </row>
+    <row r="325" spans="2:6">
       <c r="B325" s="4"/>
       <c r="C325" s="3"/>
-      <c r="D325" s="14"/>
+      <c r="D325" s="3"/>
       <c r="E325" s="14"/>
-    </row>
-    <row r="326" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F325" s="14"/>
+    </row>
+    <row r="326" spans="2:6">
       <c r="B326" s="4"/>
       <c r="C326" s="19"/>
-      <c r="D326" s="13"/>
+      <c r="D326" s="19"/>
       <c r="E326" s="13"/>
-    </row>
-    <row r="327" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F326" s="13"/>
+    </row>
+    <row r="327" spans="2:6">
       <c r="B327" s="4"/>
       <c r="C327" s="3"/>
-      <c r="D327" s="14"/>
+      <c r="D327" s="3"/>
       <c r="E327" s="14"/>
-    </row>
-    <row r="328" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F327" s="14"/>
+    </row>
+    <row r="328" spans="2:6">
       <c r="B328" s="4"/>
       <c r="C328" s="3"/>
-      <c r="D328" s="14"/>
+      <c r="D328" s="3"/>
       <c r="E328" s="14"/>
-    </row>
-    <row r="329" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F328" s="14"/>
+    </row>
+    <row r="329" spans="2:6">
       <c r="B329" s="4"/>
       <c r="C329" s="3"/>
-      <c r="D329" s="14"/>
+      <c r="D329" s="3"/>
       <c r="E329" s="14"/>
-    </row>
-    <row r="330" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F329" s="14"/>
+    </row>
+    <row r="330" spans="2:6">
       <c r="B330" s="4"/>
       <c r="C330" s="3"/>
-      <c r="D330" s="14"/>
+      <c r="D330" s="3"/>
       <c r="E330" s="14"/>
-    </row>
-    <row r="331" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F330" s="14"/>
+    </row>
+    <row r="331" spans="2:6">
       <c r="B331" s="4"/>
       <c r="C331" s="3"/>
-      <c r="D331" s="14"/>
+      <c r="D331" s="3"/>
       <c r="E331" s="14"/>
-    </row>
-    <row r="332" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F331" s="14"/>
+    </row>
+    <row r="332" spans="2:6">
       <c r="B332" s="4"/>
       <c r="C332" s="3"/>
-      <c r="D332" s="14"/>
+      <c r="D332" s="3"/>
       <c r="E332" s="14"/>
-    </row>
-    <row r="333" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F332" s="14"/>
+    </row>
+    <row r="333" spans="2:6">
       <c r="B333" s="4"/>
       <c r="C333" s="3"/>
-      <c r="D333" s="14"/>
+      <c r="D333" s="3"/>
       <c r="E333" s="14"/>
-    </row>
-    <row r="334" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F333" s="14"/>
+    </row>
+    <row r="334" spans="2:6">
       <c r="B334" s="4"/>
       <c r="C334" s="3"/>
-      <c r="D334" s="14"/>
+      <c r="D334" s="3"/>
       <c r="E334" s="14"/>
-    </row>
-    <row r="335" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F334" s="14"/>
+    </row>
+    <row r="335" spans="2:6">
       <c r="B335" s="4"/>
       <c r="C335" s="3"/>
-      <c r="D335" s="14"/>
+      <c r="D335" s="3"/>
       <c r="E335" s="14"/>
-    </row>
-    <row r="336" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F335" s="14"/>
+    </row>
+    <row r="336" spans="2:6">
       <c r="B336" s="5"/>
       <c r="C336" s="3"/>
-      <c r="D336" s="14"/>
+      <c r="D336" s="3"/>
       <c r="E336" s="14"/>
-    </row>
-    <row r="337" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F336" s="14"/>
+    </row>
+    <row r="337" spans="2:6">
       <c r="B337" s="4"/>
       <c r="C337" s="3"/>
-      <c r="D337" s="14"/>
+      <c r="D337" s="3"/>
       <c r="E337" s="14"/>
-    </row>
-    <row r="338" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F337" s="14"/>
+    </row>
+    <row r="338" spans="2:6">
       <c r="B338" s="5"/>
       <c r="C338" s="3"/>
-      <c r="D338" s="14"/>
+      <c r="D338" s="3"/>
       <c r="E338" s="14"/>
-    </row>
-    <row r="339" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F338" s="14"/>
+    </row>
+    <row r="339" spans="2:6">
       <c r="B339" s="5"/>
       <c r="C339" s="3"/>
-      <c r="D339" s="14"/>
+      <c r="D339" s="3"/>
       <c r="E339" s="14"/>
-    </row>
-    <row r="340" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F339" s="14"/>
+    </row>
+    <row r="340" spans="2:6">
       <c r="B340" s="4"/>
       <c r="C340" s="3"/>
-      <c r="D340" s="14"/>
+      <c r="D340" s="3"/>
       <c r="E340" s="14"/>
-    </row>
-    <row r="341" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F340" s="14"/>
+    </row>
+    <row r="341" spans="2:6">
       <c r="B341" s="4"/>
       <c r="C341" s="3"/>
-      <c r="D341" s="14"/>
+      <c r="D341" s="3"/>
       <c r="E341" s="14"/>
-    </row>
-    <row r="342" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F341" s="14"/>
+    </row>
+    <row r="342" spans="2:6">
       <c r="B342" s="4"/>
       <c r="C342" s="3"/>
-      <c r="D342" s="14"/>
+      <c r="D342" s="3"/>
       <c r="E342" s="14"/>
-    </row>
-    <row r="343" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F342" s="14"/>
+    </row>
+    <row r="343" spans="2:6">
       <c r="B343" s="4"/>
       <c r="C343" s="3"/>
-      <c r="D343" s="14"/>
+      <c r="D343" s="3"/>
       <c r="E343" s="14"/>
-    </row>
-    <row r="344" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F343" s="14"/>
+    </row>
+    <row r="344" spans="2:6">
       <c r="B344" s="4"/>
       <c r="C344" s="3"/>
-      <c r="D344" s="14"/>
+      <c r="D344" s="3"/>
       <c r="E344" s="14"/>
-    </row>
-    <row r="345" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F344" s="14"/>
+    </row>
+    <row r="345" spans="2:6">
       <c r="B345" s="4"/>
       <c r="C345" s="3"/>
-      <c r="D345" s="14"/>
+      <c r="D345" s="3"/>
       <c r="E345" s="14"/>
-    </row>
-    <row r="346" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F345" s="14"/>
+    </row>
+    <row r="346" spans="2:6">
       <c r="B346" s="4"/>
       <c r="C346" s="3"/>
-      <c r="D346" s="14"/>
+      <c r="D346" s="3"/>
       <c r="E346" s="14"/>
-    </row>
-    <row r="347" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F346" s="14"/>
+    </row>
+    <row r="347" spans="2:6">
       <c r="B347" s="4"/>
       <c r="C347" s="3"/>
-      <c r="D347" s="14"/>
+      <c r="D347" s="3"/>
       <c r="E347" s="14"/>
-    </row>
-    <row r="348" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F347" s="14"/>
+    </row>
+    <row r="348" spans="2:6">
       <c r="B348" s="4"/>
       <c r="C348" s="3"/>
-      <c r="D348" s="14"/>
+      <c r="D348" s="3"/>
       <c r="E348" s="14"/>
-    </row>
-    <row r="349" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F348" s="14"/>
+    </row>
+    <row r="349" spans="2:6">
       <c r="B349" s="4"/>
       <c r="C349" s="3"/>
-      <c r="D349" s="14"/>
+      <c r="D349" s="3"/>
       <c r="E349" s="14"/>
-    </row>
-    <row r="350" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F349" s="14"/>
+    </row>
+    <row r="350" spans="2:6">
       <c r="B350" s="4"/>
       <c r="C350" s="3"/>
-      <c r="D350" s="14"/>
+      <c r="D350" s="3"/>
       <c r="E350" s="14"/>
-    </row>
-    <row r="351" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F350" s="14"/>
+    </row>
+    <row r="351" spans="2:6">
       <c r="B351" s="4"/>
       <c r="C351" s="19"/>
-      <c r="D351" s="13"/>
+      <c r="D351" s="19"/>
       <c r="E351" s="13"/>
-    </row>
-    <row r="352" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F351" s="13"/>
+    </row>
+    <row r="352" spans="2:6">
       <c r="B352" s="4" t="s">
         <v>49</v>
       </c>
       <c r="C352" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="D352" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="D352" s="3"/>
       <c r="E352" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="353" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F352" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="353" spans="2:6">
       <c r="B353" s="4" t="s">
         <v>50</v>
       </c>
       <c r="C353" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="D353" s="13" t="s">
-        <v>141</v>
+      <c r="D353" s="3" t="s">
+        <v>266</v>
       </c>
       <c r="E353" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="354" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F353" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="354" spans="2:6">
       <c r="B354" s="4" t="s">
         <v>129</v>
       </c>
       <c r="C354" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="D354" s="13" t="s">
-        <v>141</v>
-      </c>
+      <c r="D354" s="3"/>
       <c r="E354" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="355" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F354" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="355" spans="2:6">
       <c r="B355" s="4" t="s">
         <v>130</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="D355" s="13"/>
+      <c r="D355" s="3" t="s">
+        <v>265</v>
+      </c>
       <c r="E355" s="13"/>
-    </row>
-    <row r="356" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F355" s="13"/>
+    </row>
+    <row r="356" spans="2:6">
       <c r="B356" s="4"/>
       <c r="C356" s="3"/>
-      <c r="D356" s="13"/>
+      <c r="D356" s="3"/>
       <c r="E356" s="13"/>
-    </row>
-    <row r="357" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F356" s="13"/>
+    </row>
+    <row r="357" spans="2:6">
       <c r="B357" s="4" t="s">
         <v>131</v>
       </c>
       <c r="C357" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D357" s="13"/>
+      <c r="D357" s="3"/>
       <c r="E357" s="13"/>
-    </row>
-    <row r="358" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F357" s="13"/>
+    </row>
+    <row r="358" spans="2:6">
       <c r="B358" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C358" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D358" s="13"/>
+      <c r="D358" s="3"/>
       <c r="E358" s="13"/>
-    </row>
-    <row r="359" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F358" s="13"/>
+    </row>
+    <row r="359" spans="2:6">
       <c r="B359" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C359" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D359" s="13"/>
+      <c r="D359" s="3"/>
       <c r="E359" s="13"/>
-    </row>
-    <row r="360" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F359" s="13"/>
+    </row>
+    <row r="360" spans="2:6">
       <c r="B360" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C360" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D360" s="13"/>
+      <c r="D360" s="3"/>
       <c r="E360" s="13"/>
-    </row>
-    <row r="361" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F360" s="13"/>
+    </row>
+    <row r="361" spans="2:6">
       <c r="B361" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C361" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D361" s="13"/>
+      <c r="D361" s="3"/>
       <c r="E361" s="13"/>
-    </row>
-    <row r="362" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F361" s="13"/>
+    </row>
+    <row r="362" spans="2:6">
       <c r="B362" s="4"/>
       <c r="C362" s="3"/>
-      <c r="D362" s="13"/>
+      <c r="D362" s="3"/>
       <c r="E362" s="13"/>
-    </row>
-    <row r="363" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F362" s="13"/>
+    </row>
+    <row r="363" spans="2:6">
       <c r="B363" s="4" t="s">
         <v>131</v>
       </c>
       <c r="C363" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D363" s="13"/>
+      <c r="D363" s="3"/>
       <c r="E363" s="13"/>
-    </row>
-    <row r="364" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F363" s="13"/>
+    </row>
+    <row r="364" spans="2:6">
       <c r="B364" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C364" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D364" s="13"/>
+      <c r="D364" s="3"/>
       <c r="E364" s="13"/>
-    </row>
-    <row r="365" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F364" s="13"/>
+    </row>
+    <row r="365" spans="2:6">
       <c r="B365" s="4" t="s">
         <v>133</v>
       </c>
       <c r="C365" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D365" s="13"/>
+      <c r="D365" s="3"/>
       <c r="E365" s="13"/>
-    </row>
-    <row r="366" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F365" s="13"/>
+    </row>
+    <row r="366" spans="2:6">
       <c r="B366" s="4" t="s">
         <v>134</v>
       </c>
       <c r="C366" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D366" s="13"/>
+      <c r="D366" s="3"/>
       <c r="E366" s="13"/>
-    </row>
-    <row r="367" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F366" s="13"/>
+    </row>
+    <row r="367" spans="2:6">
       <c r="B367" s="4" t="s">
         <v>135</v>
       </c>
       <c r="C367" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D367" s="13"/>
+      <c r="D367" s="3"/>
       <c r="E367" s="13"/>
-    </row>
-    <row r="368" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F367" s="13"/>
+    </row>
+    <row r="368" spans="2:6">
       <c r="B368" s="4"/>
       <c r="C368" s="3"/>
-      <c r="D368" s="13"/>
+      <c r="D368" s="3"/>
       <c r="E368" s="13"/>
-    </row>
-    <row r="369" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F368" s="13"/>
+    </row>
+    <row r="369" spans="2:6">
       <c r="B369" s="4" t="s">
         <v>136</v>
       </c>
       <c r="C369" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D369" s="13"/>
+      <c r="D369" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="E369" s="13"/>
-    </row>
-    <row r="370" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F369" s="13"/>
+    </row>
+    <row r="370" spans="2:6">
       <c r="B370" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C370" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D370" s="13"/>
+      <c r="D370" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="E370" s="13"/>
-    </row>
-    <row r="371" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F370" s="13"/>
+    </row>
+    <row r="371" spans="2:6">
       <c r="B371" s="4" t="s">
         <v>138</v>
       </c>
       <c r="C371" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D371" s="13"/>
+      <c r="D371" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="E371" s="13"/>
-    </row>
-    <row r="372" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F371" s="13"/>
+    </row>
+    <row r="372" spans="2:6">
       <c r="B372" s="4"/>
       <c r="C372" s="3"/>
-      <c r="D372" s="13"/>
+      <c r="D372" s="3"/>
       <c r="E372" s="13"/>
-    </row>
-    <row r="373" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F372" s="13"/>
+    </row>
+    <row r="373" spans="2:6">
       <c r="B373" s="4" t="s">
         <v>136</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="D373" s="13"/>
+      <c r="D373" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="E373" s="13"/>
-    </row>
-    <row r="374" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F373" s="13"/>
+    </row>
+    <row r="374" spans="2:6">
       <c r="B374" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D374" s="13"/>
+      <c r="D374" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="E374" s="13"/>
-    </row>
-    <row r="375" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F374" s="13"/>
+    </row>
+    <row r="375" spans="2:6">
       <c r="B375" s="4" t="s">
         <v>138</v>
       </c>
       <c r="C375" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="D375" s="13"/>
+      <c r="D375" s="3" t="s">
+        <v>273</v>
+      </c>
       <c r="E375" s="13"/>
-    </row>
-    <row r="376" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F375" s="13"/>
+    </row>
+    <row r="376" spans="2:6">
       <c r="B376" s="4"/>
       <c r="C376" s="3"/>
-      <c r="D376" s="13"/>
+      <c r="D376" s="3"/>
       <c r="E376" s="13"/>
-    </row>
-    <row r="377" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F376" s="13"/>
+    </row>
+    <row r="377" spans="2:6">
       <c r="B377" s="4"/>
       <c r="C377" s="3"/>
-      <c r="D377" s="13"/>
+      <c r="D377" s="3"/>
       <c r="E377" s="13"/>
-    </row>
-    <row r="378" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F377" s="13"/>
+    </row>
+    <row r="378" spans="2:6">
       <c r="B378" s="4"/>
       <c r="C378" s="3"/>
-      <c r="D378" s="13"/>
+      <c r="D378" s="3"/>
       <c r="E378" s="13"/>
-    </row>
-    <row r="379" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F378" s="13"/>
+    </row>
+    <row r="379" spans="2:6">
       <c r="B379" s="4"/>
       <c r="C379" s="3"/>
-      <c r="D379" s="13"/>
+      <c r="D379" s="3"/>
       <c r="E379" s="13"/>
-    </row>
-    <row r="380" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F379" s="13"/>
+    </row>
+    <row r="380" spans="2:6">
       <c r="B380" s="4"/>
       <c r="C380" s="3"/>
-      <c r="D380" s="13"/>
+      <c r="D380" s="3"/>
       <c r="E380" s="13"/>
-    </row>
-    <row r="381" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F380" s="13"/>
+    </row>
+    <row r="381" spans="2:6">
       <c r="B381" s="4"/>
       <c r="C381" s="3"/>
-      <c r="D381" s="13"/>
+      <c r="D381" s="3"/>
       <c r="E381" s="13"/>
-    </row>
-    <row r="382" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F381" s="13"/>
+    </row>
+    <row r="382" spans="2:6">
       <c r="B382" s="4"/>
       <c r="C382" s="3"/>
-      <c r="D382" s="13"/>
+      <c r="D382" s="3"/>
       <c r="E382" s="13"/>
-    </row>
-    <row r="383" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F382" s="13"/>
+    </row>
+    <row r="383" spans="2:6">
       <c r="B383" s="4"/>
       <c r="C383" s="3"/>
-      <c r="D383" s="13"/>
+      <c r="D383" s="3"/>
       <c r="E383" s="13"/>
-    </row>
-    <row r="384" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F383" s="13"/>
+    </row>
+    <row r="384" spans="2:6">
       <c r="B384" s="4"/>
       <c r="C384" s="3"/>
-      <c r="D384" s="13"/>
+      <c r="D384" s="3"/>
       <c r="E384" s="13"/>
-    </row>
-    <row r="385" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F384" s="13"/>
+    </row>
+    <row r="385" spans="2:6">
       <c r="B385" s="4"/>
       <c r="C385" s="3"/>
-      <c r="D385" s="13"/>
+      <c r="D385" s="3"/>
       <c r="E385" s="13"/>
-    </row>
-    <row r="386" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F385" s="13"/>
+    </row>
+    <row r="386" spans="2:6">
       <c r="B386" s="4"/>
       <c r="C386" s="3"/>
-      <c r="D386" s="13"/>
+      <c r="D386" s="3"/>
       <c r="E386" s="13"/>
-    </row>
-    <row r="387" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F386" s="13"/>
+    </row>
+    <row r="387" spans="2:6">
       <c r="B387" s="4"/>
       <c r="C387" s="3"/>
-      <c r="D387" s="13"/>
+      <c r="D387" s="3"/>
       <c r="E387" s="13"/>
-    </row>
-    <row r="388" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F387" s="13"/>
+    </row>
+    <row r="388" spans="2:6">
       <c r="B388" s="4"/>
       <c r="C388" s="3"/>
-      <c r="D388" s="13"/>
+      <c r="D388" s="3"/>
       <c r="E388" s="13"/>
-    </row>
-    <row r="389" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F388" s="13"/>
+    </row>
+    <row r="389" spans="2:6">
       <c r="B389" s="4"/>
       <c r="C389" s="3"/>
-      <c r="D389" s="13"/>
+      <c r="D389" s="3"/>
       <c r="E389" s="13"/>
-    </row>
-    <row r="390" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F389" s="13"/>
+    </row>
+    <row r="390" spans="2:6">
       <c r="B390" s="4"/>
       <c r="C390" s="3"/>
-      <c r="D390" s="13"/>
+      <c r="D390" s="3"/>
       <c r="E390" s="13"/>
-    </row>
-    <row r="391" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F390" s="13"/>
+    </row>
+    <row r="391" spans="2:6">
       <c r="B391" s="4"/>
       <c r="C391" s="3"/>
-      <c r="D391" s="13"/>
+      <c r="D391" s="3"/>
       <c r="E391" s="13"/>
-    </row>
-    <row r="392" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F391" s="13"/>
+    </row>
+    <row r="392" spans="2:6">
       <c r="B392" s="4"/>
       <c r="C392" s="3"/>
-      <c r="D392" s="13"/>
+      <c r="D392" s="3"/>
       <c r="E392" s="13"/>
-    </row>
-    <row r="393" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F392" s="13"/>
+    </row>
+    <row r="393" spans="2:6">
       <c r="B393" s="4"/>
       <c r="C393" s="3"/>
-      <c r="D393" s="13"/>
+      <c r="D393" s="3"/>
       <c r="E393" s="13"/>
-    </row>
-    <row r="394" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F393" s="13"/>
+    </row>
+    <row r="394" spans="2:6">
       <c r="B394" s="4"/>
       <c r="C394" s="3"/>
-      <c r="D394" s="13"/>
+      <c r="D394" s="3"/>
       <c r="E394" s="13"/>
-    </row>
-    <row r="395" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F394" s="13"/>
+    </row>
+    <row r="395" spans="2:6">
       <c r="B395" s="4"/>
       <c r="C395" s="3"/>
-      <c r="D395" s="13"/>
+      <c r="D395" s="3"/>
       <c r="E395" s="13"/>
-    </row>
-    <row r="396" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F395" s="13"/>
+    </row>
+    <row r="396" spans="2:6">
       <c r="B396" s="4"/>
       <c r="C396" s="3"/>
-      <c r="D396" s="13"/>
+      <c r="D396" s="3"/>
       <c r="E396" s="13"/>
-    </row>
-    <row r="397" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F396" s="13"/>
+    </row>
+    <row r="397" spans="2:6">
       <c r="B397" s="9"/>
       <c r="C397" s="3"/>
-      <c r="D397" s="13"/>
+      <c r="D397" s="3"/>
       <c r="E397" s="13"/>
-    </row>
-    <row r="398" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F397" s="13"/>
+    </row>
+    <row r="398" spans="2:6">
       <c r="B398" s="9"/>
       <c r="C398" s="3"/>
-      <c r="D398" s="13"/>
+      <c r="D398" s="3"/>
       <c r="E398" s="13"/>
-    </row>
-    <row r="399" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F398" s="13"/>
+    </row>
+    <row r="399" spans="2:6">
       <c r="B399" s="9"/>
       <c r="C399" s="3"/>
-      <c r="D399" s="13"/>
+      <c r="D399" s="3"/>
       <c r="E399" s="13"/>
-    </row>
-    <row r="400" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F399" s="13"/>
+    </row>
+    <row r="400" spans="2:6">
       <c r="B400" s="9"/>
       <c r="C400" s="3"/>
-      <c r="D400" s="13"/>
+      <c r="D400" s="3"/>
       <c r="E400" s="13"/>
-    </row>
-    <row r="401" spans="2:5" x14ac:dyDescent="0.4">
+      <c r="F400" s="13"/>
+    </row>
+    <row r="401" spans="2:6">
       <c r="B401" s="4"/>
       <c r="C401" s="3"/>
-      <c r="D401" s="13"/>
+      <c r="D401" s="3"/>
       <c r="E401" s="13"/>
+      <c r="F401" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:E401" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}"/>
+  <autoFilter ref="B2:F401" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Arial"&amp;8&amp;K737373 Classified by Alfa Laval as: Business</oddFooter>

--- a/testBrew.xlsx
+++ b/testBrew.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Agentic World\TestDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84C73474-4993-41AD-8BA3-F16422125108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2AAB84-AC99-4A8C-A5EB-F74211546327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$2:$F$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$G$401</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,6 +50,7 @@
     <author>tc={932F2D4C-D793-48A0-8BED-5F38FC3D7DAF}</author>
     <author>tc={E1E2F944-CF9F-4061-9330-99AC06440908}</author>
     <author>tc={F8073023-E3D6-437F-A368-4B60DA804058}</author>
+    <author>tc={DA4D74A7-C735-4500-AC22-C9E4A5C304D0}</author>
     <author>tc={FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}</author>
     <author>tc={C29E9803-A59F-4197-99DC-10131D1A8691}</author>
     <author>tc={F05B5C03-D80C-44EE-911F-FD4F08369CD1}</author>
@@ -89,6 +90,20 @@
       </text>
     </comment>
     <comment ref="F110" authorId="1" shapeId="0" xr:uid="{A7EDFD00-73D4-4924-B708-E4D643A140C2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G110" authorId="1" shapeId="0" xr:uid="{5C433F4A-7D9B-45D8-B24B-18AE78249403}">
       <text>
         <r>
           <rPr>
@@ -164,6 +179,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="G130" authorId="1" shapeId="0" xr:uid="{B13A63A5-9509-42B4-BA99-580BB0EBC210}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PCV220-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B132" authorId="4" shapeId="0" xr:uid="{330CC50C-0FF1-4C20-92A7-B1A460F72FE0}">
       <text>
         <r>
@@ -223,6 +252,20 @@
             <family val="2"/>
           </rPr>
           <t>ST740</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G139" authorId="1" shapeId="0" xr:uid="{DE12BDB5-71C1-4CAB-99EE-1B18B4AFE875}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ST741</t>
         </r>
       </text>
     </comment>
@@ -288,6 +331,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="G212" authorId="1" shapeId="0" xr:uid="{6A100EDB-F0FD-443B-AC82-6F4F1F5090D0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>YT750</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B214" authorId="8" shapeId="0" xr:uid="{932F2D4C-D793-48A0-8BED-5F38FC3D7DAF}">
       <text>
         <r>
@@ -306,6 +363,20 @@
       </text>
     </comment>
     <comment ref="F214" authorId="1" shapeId="0" xr:uid="{A7A9E8D1-727E-4B93-BDEB-E67DFF623450}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PT376-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G214" authorId="1" shapeId="0" xr:uid="{C45EBACB-06C0-4C27-B60E-9BCCFB34E699}">
       <text>
         <r>
           <rPr>
@@ -352,7 +423,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="B223" authorId="11" shapeId="0" xr:uid="{FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}">
+    <comment ref="G218" authorId="11" shapeId="0" xr:uid="{A9D86EE3-DF9D-4BE8-AB28-2DFBCAEFC0D2}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="MS Sans Serif"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sensor: TT733</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B223" authorId="12" shapeId="0" xr:uid="{FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}">
       <text>
         <r>
           <rPr>
@@ -397,7 +482,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="B243" authorId="12" shapeId="0" xr:uid="{C29E9803-A59F-4197-99DC-10131D1A8691}">
+    <comment ref="G223" authorId="1" shapeId="0" xr:uid="{D86C5B0B-7016-4D4A-9B19-F87768621E9D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT410-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B243" authorId="13" shapeId="0" xr:uid="{C29E9803-A59F-4197-99DC-10131D1A8691}">
       <text>
         <r>
           <rPr>
@@ -413,7 +512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B248" authorId="13" shapeId="0" xr:uid="{F05B5C03-D80C-44EE-911F-FD4F08369CD1}">
+    <comment ref="B248" authorId="14" shapeId="0" xr:uid="{F05B5C03-D80C-44EE-911F-FD4F08369CD1}">
       <text>
         <r>
           <rPr>
@@ -458,7 +557,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="B252" authorId="14" shapeId="0" xr:uid="{6BE60107-F28C-41F1-A623-84DD5A6A045C}">
+    <comment ref="G248" authorId="1" shapeId="0" xr:uid="{6C67152D-C75F-4312-9E59-CD88F97F35D0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>AV375-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B252" authorId="15" shapeId="0" xr:uid="{6BE60107-F28C-41F1-A623-84DD5A6A045C}">
       <text>
         <r>
           <rPr>
@@ -475,7 +588,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B253" authorId="15" shapeId="0" xr:uid="{573F35F3-86C4-417F-BDB5-9F88836E09BB}">
+    <comment ref="B253" authorId="16" shapeId="0" xr:uid="{573F35F3-86C4-417F-BDB5-9F88836E09BB}">
       <text>
         <r>
           <rPr>
@@ -520,6 +633,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="G253" authorId="1" shapeId="0" xr:uid="{66A2BB66-877D-4282-BBED-424E278600FF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>506c</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E354" authorId="1" shapeId="0" xr:uid="{C0B47CE5-D73E-476B-A5B9-42559C542AEB}">
       <text>
         <r>
@@ -548,12 +675,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="G354" authorId="1" shapeId="0" xr:uid="{E1FDF170-EC3C-4C3E-9D47-490D5F042A9C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIT220-1</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="277">
   <si>
     <t>Tag Label</t>
   </si>
@@ -1381,13 +1522,16 @@
   </si>
   <si>
     <t>E/L-DRIVE</t>
+  </si>
+  <si>
+    <t>BREW 600</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1434,6 +1578,10 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="MS Sans Serif"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2079,16 +2227,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}">
-  <dimension ref="B2:F401"/>
+  <dimension ref="B2:G401"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.25" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.75" style="1" customWidth="1"/>
     <col min="5" max="6" width="2.25" style="10" customWidth="1"/>
+    <col min="7" max="7" width="2.875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="49.5">
+    <row r="2" spans="2:7" ht="49.5">
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
@@ -2098,8 +2247,11 @@
       <c r="F2" s="11" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="3" spans="2:6">
+      <c r="G2" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2111,29 +2263,33 @@
       </c>
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="2:6">
+      <c r="G3" s="12"/>
+    </row>
+    <row r="4" spans="2:7">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
-    </row>
-    <row r="5" spans="2:6">
+      <c r="G4" s="13"/>
+    </row>
+    <row r="5" spans="2:7">
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
-    </row>
-    <row r="6" spans="2:6">
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="2:7">
       <c r="B6" s="4"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
-    </row>
-    <row r="7" spans="2:6">
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" spans="2:7">
       <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
@@ -2147,8 +2303,11 @@
       <c r="F7" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="2:6">
+      <c r="G7" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7">
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
@@ -2162,8 +2321,11 @@
       <c r="F8" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="9" spans="2:6">
+      <c r="G8" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7">
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
@@ -2177,8 +2339,11 @@
       <c r="F9" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="10" spans="2:6">
+      <c r="G9" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -2190,8 +2355,9 @@
       </c>
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
-    </row>
-    <row r="11" spans="2:6">
+      <c r="G10" s="13"/>
+    </row>
+    <row r="11" spans="2:7">
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
@@ -2205,8 +2371,11 @@
       <c r="F11" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="12" spans="2:6">
+      <c r="G11" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
       <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
@@ -2220,8 +2389,11 @@
       <c r="F12" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="13" spans="2:6">
+      <c r="G12" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7">
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
@@ -2235,8 +2407,11 @@
       <c r="F13" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="2:6">
+      <c r="G13" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7">
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
@@ -2246,8 +2421,9 @@
       <c r="D14" s="3"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="2:6">
+      <c r="G14" s="13"/>
+    </row>
+    <row r="15" spans="2:7">
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
@@ -2257,8 +2433,9 @@
       <c r="D15" s="3"/>
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="2:6">
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" spans="2:7">
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
@@ -2272,8 +2449,11 @@
       <c r="F16" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="2:6">
+      <c r="G16" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7">
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
@@ -2287,8 +2467,11 @@
       <c r="F17" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="18" spans="2:6">
+      <c r="G17" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
@@ -2304,8 +2487,11 @@
       <c r="F18" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="19" spans="2:6">
+      <c r="G18" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7">
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
@@ -2315,8 +2501,9 @@
       <c r="D19" s="3"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="G19" s="13"/>
+    </row>
+    <row r="20" spans="2:7">
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
@@ -2326,8 +2513,9 @@
       <c r="D20" s="3"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="2:6">
+      <c r="G20" s="13"/>
+    </row>
+    <row r="21" spans="2:7">
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
@@ -2337,8 +2525,9 @@
       <c r="D21" s="3"/>
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="2:6">
+      <c r="G21" s="13"/>
+    </row>
+    <row r="22" spans="2:7">
       <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
@@ -2354,15 +2543,19 @@
       <c r="F22" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="23" spans="2:6">
+      <c r="G22" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="2:6">
+      <c r="G23" s="13"/>
+    </row>
+    <row r="24" spans="2:7">
       <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
@@ -2376,8 +2569,11 @@
       <c r="F24" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="25" spans="2:6">
+      <c r="G24" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7">
       <c r="B25" s="6" t="s">
         <v>13</v>
       </c>
@@ -2391,8 +2587,11 @@
       <c r="F25" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="26" spans="2:6">
+      <c r="G25" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7">
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
@@ -2408,8 +2607,11 @@
       <c r="F26" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="27" spans="2:6">
+      <c r="G26" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
@@ -2425,8 +2627,11 @@
       <c r="F27" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="28" spans="2:6">
+      <c r="G27" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
       <c r="B28" s="6" t="s">
         <v>15</v>
       </c>
@@ -2442,8 +2647,11 @@
       <c r="F28" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="29" spans="2:6">
+      <c r="G28" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
       <c r="B29" s="6" t="s">
         <v>15</v>
       </c>
@@ -2459,8 +2667,11 @@
       <c r="F29" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="30" spans="2:6">
+      <c r="G29" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
       <c r="B30" s="6" t="s">
         <v>16</v>
       </c>
@@ -2474,8 +2685,11 @@
       <c r="F30" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="31" spans="2:6">
+      <c r="G30" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7">
       <c r="B31" s="6" t="s">
         <v>16</v>
       </c>
@@ -2489,8 +2703,11 @@
       <c r="F31" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="32" spans="2:6">
+      <c r="G31" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7">
       <c r="B32" s="6" t="s">
         <v>17</v>
       </c>
@@ -2504,8 +2721,11 @@
       <c r="F32" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="2:6">
+      <c r="G32" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
       <c r="B33" s="6" t="s">
         <v>17</v>
       </c>
@@ -2519,8 +2739,11 @@
       <c r="F33" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="34" spans="2:6">
+      <c r="G33" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7">
       <c r="B34" s="6" t="s">
         <v>18</v>
       </c>
@@ -2532,8 +2755,9 @@
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
-    </row>
-    <row r="35" spans="2:6">
+      <c r="G34" s="13"/>
+    </row>
+    <row r="35" spans="2:7">
       <c r="B35" s="6" t="s">
         <v>18</v>
       </c>
@@ -2545,8 +2769,9 @@
       </c>
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
-    </row>
-    <row r="36" spans="2:6">
+      <c r="G35" s="13"/>
+    </row>
+    <row r="36" spans="2:7">
       <c r="B36" s="6" t="s">
         <v>19</v>
       </c>
@@ -2560,8 +2785,11 @@
       <c r="F36" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="37" spans="2:6">
+      <c r="G36" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7">
       <c r="B37" s="7" t="s">
         <v>19</v>
       </c>
@@ -2575,8 +2803,11 @@
       <c r="F37" s="15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="38" spans="2:6">
+      <c r="G37" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
@@ -2586,8 +2817,9 @@
       <c r="D38" s="3"/>
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
-    </row>
-    <row r="39" spans="2:6">
+      <c r="G38" s="13"/>
+    </row>
+    <row r="39" spans="2:7">
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
@@ -2597,15 +2829,17 @@
       <c r="D39" s="3"/>
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
-    </row>
-    <row r="40" spans="2:6">
+      <c r="G39" s="13"/>
+    </row>
+    <row r="40" spans="2:7">
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="G40" s="13"/>
+    </row>
+    <row r="41" spans="2:7">
       <c r="B41" s="7" t="s">
         <v>20</v>
       </c>
@@ -2619,8 +2853,11 @@
       <c r="F41" s="15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="42" spans="2:6">
+      <c r="G41" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
       <c r="B42" s="6" t="s">
         <v>20</v>
       </c>
@@ -2634,8 +2871,11 @@
       <c r="F42" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="2:6">
+      <c r="G42" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7">
       <c r="B43" s="6" t="s">
         <v>21</v>
       </c>
@@ -2649,8 +2889,11 @@
       <c r="F43" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="G43" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7">
       <c r="B44" s="6" t="s">
         <v>21</v>
       </c>
@@ -2664,8 +2907,11 @@
       <c r="F44" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="45" spans="2:6">
+      <c r="G44" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7">
       <c r="B45" s="6" t="s">
         <v>22</v>
       </c>
@@ -2679,8 +2925,11 @@
       <c r="F45" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="46" spans="2:6">
+      <c r="G45" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7">
       <c r="B46" s="6" t="s">
         <v>22</v>
       </c>
@@ -2694,8 +2943,11 @@
       <c r="F46" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="47" spans="2:6">
+      <c r="G46" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7">
       <c r="B47" s="6" t="s">
         <v>23</v>
       </c>
@@ -2709,8 +2961,11 @@
       <c r="F47" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="48" spans="2:6">
+      <c r="G47" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7">
       <c r="B48" s="6" t="s">
         <v>23</v>
       </c>
@@ -2724,8 +2979,11 @@
       <c r="F48" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="49" spans="2:6">
+      <c r="G48" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7">
       <c r="B49" s="6" t="s">
         <v>24</v>
       </c>
@@ -2739,8 +2997,11 @@
       <c r="F49" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="50" spans="2:6">
+      <c r="G49" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7">
       <c r="B50" s="6" t="s">
         <v>24</v>
       </c>
@@ -2754,8 +3015,11 @@
       <c r="F50" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="G50" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7">
       <c r="B51" s="6" t="s">
         <v>25</v>
       </c>
@@ -2769,8 +3033,11 @@
       <c r="F51" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="52" spans="2:6">
+      <c r="G51" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="2:7">
       <c r="B52" s="6" t="s">
         <v>25</v>
       </c>
@@ -2784,8 +3051,11 @@
       <c r="F52" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="53" spans="2:6">
+      <c r="G52" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7">
       <c r="B53" s="6" t="s">
         <v>26</v>
       </c>
@@ -2797,8 +3067,11 @@
       <c r="F53" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="54" spans="2:6">
+      <c r="G53" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7">
       <c r="B54" s="6" t="s">
         <v>26</v>
       </c>
@@ -2810,8 +3083,11 @@
       <c r="F54" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="55" spans="2:6">
+      <c r="G54" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7">
       <c r="B55" s="5" t="s">
         <v>8</v>
       </c>
@@ -2821,8 +3097,9 @@
       <c r="D55" s="3"/>
       <c r="E55" s="13"/>
       <c r="F55" s="13"/>
-    </row>
-    <row r="56" spans="2:6">
+      <c r="G55" s="13"/>
+    </row>
+    <row r="56" spans="2:7">
       <c r="B56" s="5" t="s">
         <v>8</v>
       </c>
@@ -2832,15 +3109,17 @@
       <c r="D56" s="3"/>
       <c r="E56" s="13"/>
       <c r="F56" s="13"/>
-    </row>
-    <row r="57" spans="2:6">
+      <c r="G56" s="13"/>
+    </row>
+    <row r="57" spans="2:7">
       <c r="B57" s="6"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="13"/>
       <c r="F57" s="13"/>
-    </row>
-    <row r="58" spans="2:6">
+      <c r="G57" s="13"/>
+    </row>
+    <row r="58" spans="2:7">
       <c r="B58" s="6" t="s">
         <v>27</v>
       </c>
@@ -2854,8 +3133,11 @@
       <c r="F58" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="G58" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7">
       <c r="B59" s="6" t="s">
         <v>27</v>
       </c>
@@ -2869,8 +3151,11 @@
       <c r="F59" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="60" spans="2:6">
+      <c r="G59" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7">
       <c r="B60" s="5" t="s">
         <v>8</v>
       </c>
@@ -2880,8 +3165,9 @@
       <c r="D60" s="3"/>
       <c r="E60" s="13"/>
       <c r="F60" s="13"/>
-    </row>
-    <row r="61" spans="2:6">
+      <c r="G60" s="13"/>
+    </row>
+    <row r="61" spans="2:7">
       <c r="B61" s="5" t="s">
         <v>8</v>
       </c>
@@ -2891,8 +3177,9 @@
       <c r="D61" s="3"/>
       <c r="E61" s="13"/>
       <c r="F61" s="13"/>
-    </row>
-    <row r="62" spans="2:6">
+      <c r="G61" s="13"/>
+    </row>
+    <row r="62" spans="2:7">
       <c r="B62" s="6" t="s">
         <v>28</v>
       </c>
@@ -2906,8 +3193,11 @@
       <c r="F62" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="63" spans="2:6">
+      <c r="G62" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7">
       <c r="B63" s="6" t="s">
         <v>28</v>
       </c>
@@ -2921,8 +3211,11 @@
       <c r="F63" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="64" spans="2:6">
+      <c r="G63" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7">
       <c r="B64" s="6" t="s">
         <v>29</v>
       </c>
@@ -2936,8 +3229,11 @@
       <c r="F64" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="65" spans="2:6">
+      <c r="G64" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7">
       <c r="B65" s="6" t="s">
         <v>29</v>
       </c>
@@ -2951,8 +3247,11 @@
       <c r="F65" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="66" spans="2:6">
+      <c r="G65" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="2:7">
       <c r="B66" s="6" t="s">
         <v>30</v>
       </c>
@@ -2964,8 +3263,9 @@
       </c>
       <c r="E66" s="13"/>
       <c r="F66" s="13"/>
-    </row>
-    <row r="67" spans="2:6">
+      <c r="G66" s="13"/>
+    </row>
+    <row r="67" spans="2:7">
       <c r="B67" s="6" t="s">
         <v>30</v>
       </c>
@@ -2977,8 +3277,9 @@
       </c>
       <c r="E67" s="13"/>
       <c r="F67" s="13"/>
-    </row>
-    <row r="68" spans="2:6">
+      <c r="G67" s="13"/>
+    </row>
+    <row r="68" spans="2:7">
       <c r="B68" s="5" t="s">
         <v>8</v>
       </c>
@@ -2988,8 +3289,9 @@
       <c r="D68" s="3"/>
       <c r="E68" s="13"/>
       <c r="F68" s="13"/>
-    </row>
-    <row r="69" spans="2:6">
+      <c r="G68" s="13"/>
+    </row>
+    <row r="69" spans="2:7">
       <c r="B69" s="5" t="s">
         <v>8</v>
       </c>
@@ -2999,8 +3301,9 @@
       <c r="D69" s="3"/>
       <c r="E69" s="13"/>
       <c r="F69" s="13"/>
-    </row>
-    <row r="70" spans="2:6">
+      <c r="G69" s="13"/>
+    </row>
+    <row r="70" spans="2:7">
       <c r="B70" s="5" t="s">
         <v>8</v>
       </c>
@@ -3010,8 +3313,9 @@
       <c r="D70" s="3"/>
       <c r="E70" s="13"/>
       <c r="F70" s="13"/>
-    </row>
-    <row r="71" spans="2:6">
+      <c r="G70" s="13"/>
+    </row>
+    <row r="71" spans="2:7">
       <c r="B71" s="5" t="s">
         <v>8</v>
       </c>
@@ -3021,8 +3325,9 @@
       <c r="D71" s="3"/>
       <c r="E71" s="13"/>
       <c r="F71" s="13"/>
-    </row>
-    <row r="72" spans="2:6">
+      <c r="G71" s="13"/>
+    </row>
+    <row r="72" spans="2:7">
       <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
@@ -3032,8 +3337,9 @@
       <c r="D72" s="3"/>
       <c r="E72" s="13"/>
       <c r="F72" s="13"/>
-    </row>
-    <row r="73" spans="2:6">
+      <c r="G72" s="13"/>
+    </row>
+    <row r="73" spans="2:7">
       <c r="B73" s="5" t="s">
         <v>8</v>
       </c>
@@ -3043,15 +3349,17 @@
       <c r="D73" s="3"/>
       <c r="E73" s="13"/>
       <c r="F73" s="13"/>
-    </row>
-    <row r="74" spans="2:6">
+      <c r="G73" s="13"/>
+    </row>
+    <row r="74" spans="2:7">
       <c r="B74" s="6"/>
       <c r="C74" s="3"/>
       <c r="D74" s="20"/>
       <c r="E74" s="13"/>
       <c r="F74" s="13"/>
-    </row>
-    <row r="75" spans="2:6">
+      <c r="G74" s="13"/>
+    </row>
+    <row r="75" spans="2:7">
       <c r="B75" s="6" t="s">
         <v>13</v>
       </c>
@@ -3065,8 +3373,11 @@
       <c r="F75" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="76" spans="2:6">
+      <c r="G75" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7">
       <c r="B76" s="6" t="s">
         <v>14</v>
       </c>
@@ -3082,8 +3393,11 @@
       <c r="F76" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="77" spans="2:6">
+      <c r="G76" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7">
       <c r="B77" s="6" t="s">
         <v>15</v>
       </c>
@@ -3099,8 +3413,11 @@
       <c r="F77" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="78" spans="2:6">
+      <c r="G77" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7">
       <c r="B78" s="6" t="s">
         <v>16</v>
       </c>
@@ -3114,8 +3431,11 @@
       <c r="F78" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="79" spans="2:6">
+      <c r="G78" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7">
       <c r="B79" s="6" t="s">
         <v>17</v>
       </c>
@@ -3129,8 +3449,11 @@
       <c r="F79" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="80" spans="2:6">
+      <c r="G79" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7">
       <c r="B80" s="6" t="s">
         <v>18</v>
       </c>
@@ -3142,8 +3465,9 @@
       </c>
       <c r="E80" s="13"/>
       <c r="F80" s="13"/>
-    </row>
-    <row r="81" spans="2:6">
+      <c r="G80" s="13"/>
+    </row>
+    <row r="81" spans="2:7">
       <c r="B81" s="6" t="s">
         <v>19</v>
       </c>
@@ -3157,8 +3481,11 @@
       <c r="F81" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="82" spans="2:6">
+      <c r="G81" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="82" spans="2:7">
       <c r="B82" s="5" t="s">
         <v>8</v>
       </c>
@@ -3168,8 +3495,9 @@
       <c r="D82" s="3"/>
       <c r="E82" s="13"/>
       <c r="F82" s="13"/>
-    </row>
-    <row r="83" spans="2:6">
+      <c r="G82" s="13"/>
+    </row>
+    <row r="83" spans="2:7">
       <c r="B83" s="6" t="s">
         <v>20</v>
       </c>
@@ -3183,8 +3511,11 @@
       <c r="F83" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="84" spans="2:6">
+      <c r="G83" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7">
       <c r="B84" s="6" t="s">
         <v>21</v>
       </c>
@@ -3198,8 +3529,11 @@
       <c r="F84" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="85" spans="2:6">
+      <c r="G84" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7">
       <c r="B85" s="6" t="s">
         <v>22</v>
       </c>
@@ -3213,8 +3547,11 @@
       <c r="F85" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="86" spans="2:6">
+      <c r="G85" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" spans="2:7">
       <c r="B86" s="6" t="s">
         <v>23</v>
       </c>
@@ -3228,8 +3565,11 @@
       <c r="F86" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="87" spans="2:6">
+      <c r="G86" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="87" spans="2:7">
       <c r="B87" s="6" t="s">
         <v>24</v>
       </c>
@@ -3243,8 +3583,11 @@
       <c r="F87" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="88" spans="2:6">
+      <c r="G87" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7">
       <c r="B88" s="6" t="s">
         <v>25</v>
       </c>
@@ -3258,8 +3601,11 @@
       <c r="F88" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="89" spans="2:6">
+      <c r="G88" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="89" spans="2:7">
       <c r="B89" s="6" t="s">
         <v>26</v>
       </c>
@@ -3271,8 +3617,11 @@
       <c r="F89" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="90" spans="2:6">
+      <c r="G89" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7">
       <c r="B90" s="5" t="s">
         <v>8</v>
       </c>
@@ -3282,15 +3631,17 @@
       <c r="D90" s="3"/>
       <c r="E90" s="13"/>
       <c r="F90" s="13"/>
-    </row>
-    <row r="91" spans="2:6">
+      <c r="G90" s="13"/>
+    </row>
+    <row r="91" spans="2:7">
       <c r="B91" s="6"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="13"/>
       <c r="F91" s="13"/>
-    </row>
-    <row r="92" spans="2:6">
+      <c r="G91" s="13"/>
+    </row>
+    <row r="92" spans="2:7">
       <c r="B92" s="6" t="s">
         <v>27</v>
       </c>
@@ -3304,8 +3655,11 @@
       <c r="F92" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="93" spans="2:6">
+      <c r="G92" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="93" spans="2:7">
       <c r="B93" s="5" t="s">
         <v>8</v>
       </c>
@@ -3317,8 +3671,9 @@
       </c>
       <c r="E93" s="13"/>
       <c r="F93" s="13"/>
-    </row>
-    <row r="94" spans="2:6">
+      <c r="G93" s="13"/>
+    </row>
+    <row r="94" spans="2:7">
       <c r="B94" s="6" t="s">
         <v>28</v>
       </c>
@@ -3332,8 +3687,11 @@
       <c r="F94" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="95" spans="2:6">
+      <c r="G94" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="2:7">
       <c r="B95" s="6" t="s">
         <v>29</v>
       </c>
@@ -3347,8 +3705,11 @@
       <c r="F95" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="96" spans="2:6">
+      <c r="G95" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="96" spans="2:7">
       <c r="B96" s="6" t="s">
         <v>30</v>
       </c>
@@ -3360,8 +3721,9 @@
       </c>
       <c r="E96" s="13"/>
       <c r="F96" s="13"/>
-    </row>
-    <row r="97" spans="2:6">
+      <c r="G96" s="13"/>
+    </row>
+    <row r="97" spans="2:7">
       <c r="B97" s="5" t="s">
         <v>8</v>
       </c>
@@ -3371,8 +3733,9 @@
       <c r="D97" s="3"/>
       <c r="E97" s="13"/>
       <c r="F97" s="13"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="G97" s="13"/>
+    </row>
+    <row r="98" spans="2:7">
       <c r="B98" s="5" t="s">
         <v>8</v>
       </c>
@@ -3382,8 +3745,9 @@
       <c r="D98" s="3"/>
       <c r="E98" s="13"/>
       <c r="F98" s="13"/>
-    </row>
-    <row r="99" spans="2:6">
+      <c r="G98" s="13"/>
+    </row>
+    <row r="99" spans="2:7">
       <c r="B99" s="5" t="s">
         <v>8</v>
       </c>
@@ -3393,8 +3757,9 @@
       <c r="D99" s="3"/>
       <c r="E99" s="13"/>
       <c r="F99" s="13"/>
-    </row>
-    <row r="100" spans="2:6">
+      <c r="G99" s="13"/>
+    </row>
+    <row r="100" spans="2:7">
       <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
@@ -3404,8 +3769,9 @@
       <c r="D100" s="3"/>
       <c r="E100" s="13"/>
       <c r="F100" s="13"/>
-    </row>
-    <row r="101" spans="2:6">
+      <c r="G100" s="13"/>
+    </row>
+    <row r="101" spans="2:7">
       <c r="B101" s="4" t="s">
         <v>31</v>
       </c>
@@ -3419,8 +3785,11 @@
       <c r="F101" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="G101" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" spans="2:7">
       <c r="B102" s="8" t="s">
         <v>32</v>
       </c>
@@ -3434,8 +3803,11 @@
       <c r="F102" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="103" spans="2:6">
+      <c r="G102" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="2:7">
       <c r="B103" s="4" t="s">
         <v>33</v>
       </c>
@@ -3449,8 +3821,11 @@
       <c r="F103" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="104" spans="2:6">
+      <c r="G103" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
       <c r="B104" s="4" t="s">
         <v>34</v>
       </c>
@@ -3464,8 +3839,11 @@
       <c r="F104" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="105" spans="2:6">
+      <c r="G104" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="105" spans="2:7">
       <c r="B105" s="4" t="s">
         <v>35</v>
       </c>
@@ -3479,8 +3857,11 @@
       <c r="F105" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="106" spans="2:6">
+      <c r="G105" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7">
       <c r="B106" s="4" t="s">
         <v>36</v>
       </c>
@@ -3494,8 +3875,11 @@
       <c r="F106" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="107" spans="2:6">
+      <c r="G106" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="107" spans="2:7">
       <c r="B107" s="4" t="s">
         <v>37</v>
       </c>
@@ -3505,15 +3889,17 @@
       <c r="D107" s="3"/>
       <c r="E107" s="13"/>
       <c r="F107" s="13"/>
-    </row>
-    <row r="108" spans="2:6">
+      <c r="G107" s="13"/>
+    </row>
+    <row r="108" spans="2:7">
       <c r="B108" s="4"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="13"/>
       <c r="F108" s="13"/>
-    </row>
-    <row r="109" spans="2:6">
+      <c r="G108" s="13"/>
+    </row>
+    <row r="109" spans="2:7">
       <c r="B109" s="4" t="s">
         <v>38</v>
       </c>
@@ -3527,8 +3913,11 @@
       <c r="F109" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="110" spans="2:6">
+      <c r="G109" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7">
       <c r="B110" s="4" t="s">
         <v>39</v>
       </c>
@@ -3542,8 +3931,11 @@
       <c r="F110" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="111" spans="2:6">
+      <c r="G110" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="111" spans="2:7">
       <c r="B111" s="4" t="s">
         <v>40</v>
       </c>
@@ -3557,8 +3949,11 @@
       <c r="F111" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="112" spans="2:6">
+      <c r="G111" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="2:7">
       <c r="B112" s="4" t="s">
         <v>41</v>
       </c>
@@ -3572,15 +3967,19 @@
       <c r="F112" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="113" spans="2:6">
+      <c r="G112" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="113" spans="2:7">
       <c r="B113" s="4"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="13"/>
       <c r="F113" s="13"/>
-    </row>
-    <row r="114" spans="2:6">
+      <c r="G113" s="13"/>
+    </row>
+    <row r="114" spans="2:7">
       <c r="B114" s="4" t="s">
         <v>42</v>
       </c>
@@ -3596,8 +3995,11 @@
       <c r="F114" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="115" spans="2:6">
+      <c r="G114" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="115" spans="2:7">
       <c r="B115" s="5" t="s">
         <v>8</v>
       </c>
@@ -3607,8 +4009,9 @@
       <c r="D115" s="19"/>
       <c r="E115" s="13"/>
       <c r="F115" s="13"/>
-    </row>
-    <row r="116" spans="2:6">
+      <c r="G115" s="13"/>
+    </row>
+    <row r="116" spans="2:7">
       <c r="B116" s="4" t="s">
         <v>43</v>
       </c>
@@ -3620,8 +4023,9 @@
       </c>
       <c r="E116" s="13"/>
       <c r="F116" s="13"/>
-    </row>
-    <row r="117" spans="2:6">
+      <c r="G116" s="13"/>
+    </row>
+    <row r="117" spans="2:7">
       <c r="B117" s="4" t="s">
         <v>44</v>
       </c>
@@ -3631,15 +4035,17 @@
       <c r="D117" s="19"/>
       <c r="E117" s="13"/>
       <c r="F117" s="13"/>
-    </row>
-    <row r="118" spans="2:6">
+      <c r="G117" s="13"/>
+    </row>
+    <row r="118" spans="2:7">
       <c r="B118" s="4"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="13"/>
       <c r="F118" s="13"/>
-    </row>
-    <row r="119" spans="2:6">
+      <c r="G118" s="13"/>
+    </row>
+    <row r="119" spans="2:7">
       <c r="B119" s="4" t="s">
         <v>45</v>
       </c>
@@ -3653,8 +4059,11 @@
       <c r="F119" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="120" spans="2:6">
+      <c r="G119" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="2:7">
       <c r="B120" s="4" t="s">
         <v>46</v>
       </c>
@@ -3668,8 +4077,11 @@
       <c r="F120" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="121" spans="2:6">
+      <c r="G120" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7">
       <c r="B121" s="4" t="s">
         <v>47</v>
       </c>
@@ -3683,8 +4095,11 @@
       <c r="F121" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="122" spans="2:6">
+      <c r="G121" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="122" spans="2:7">
       <c r="B122" s="4" t="s">
         <v>48</v>
       </c>
@@ -3700,15 +4115,19 @@
       <c r="F122" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="123" spans="2:6">
+      <c r="G122" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7">
       <c r="B123" s="4"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="13"/>
       <c r="F123" s="13"/>
-    </row>
-    <row r="124" spans="2:6">
+      <c r="G123" s="13"/>
+    </row>
+    <row r="124" spans="2:7">
       <c r="B124" s="4" t="s">
         <v>49</v>
       </c>
@@ -3718,8 +4137,9 @@
       <c r="D124" s="3"/>
       <c r="E124" s="13"/>
       <c r="F124" s="13"/>
-    </row>
-    <row r="125" spans="2:6">
+      <c r="G124" s="13"/>
+    </row>
+    <row r="125" spans="2:7">
       <c r="B125" s="4" t="s">
         <v>50</v>
       </c>
@@ -3731,8 +4151,9 @@
       </c>
       <c r="E125" s="13"/>
       <c r="F125" s="13"/>
-    </row>
-    <row r="126" spans="2:6">
+      <c r="G125" s="13"/>
+    </row>
+    <row r="126" spans="2:7">
       <c r="B126" s="4" t="s">
         <v>51</v>
       </c>
@@ -3748,8 +4169,11 @@
       <c r="F126" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="127" spans="2:6">
+      <c r="G126" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" spans="2:7">
       <c r="B127" s="5" t="s">
         <v>8</v>
       </c>
@@ -3759,15 +4183,17 @@
       <c r="D127" s="19"/>
       <c r="E127" s="13"/>
       <c r="F127" s="13"/>
-    </row>
-    <row r="128" spans="2:6">
+      <c r="G127" s="13"/>
+    </row>
+    <row r="128" spans="2:7">
       <c r="B128" s="4"/>
       <c r="C128" s="3"/>
       <c r="D128" s="19"/>
       <c r="E128" s="13"/>
       <c r="F128" s="13"/>
-    </row>
-    <row r="129" spans="2:6">
+      <c r="G128" s="13"/>
+    </row>
+    <row r="129" spans="2:7">
       <c r="B129" s="4" t="s">
         <v>52</v>
       </c>
@@ -3781,8 +4207,11 @@
       <c r="F129" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="130" spans="2:6">
+      <c r="G129" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130" spans="2:7">
       <c r="B130" s="4" t="s">
         <v>53</v>
       </c>
@@ -3796,8 +4225,11 @@
       <c r="F130" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="131" spans="2:6">
+      <c r="G130" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7">
       <c r="B131" s="4" t="s">
         <v>54</v>
       </c>
@@ -3811,8 +4243,11 @@
       <c r="F131" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="132" spans="2:6">
+      <c r="G131" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="132" spans="2:7">
       <c r="B132" s="4" t="s">
         <v>55</v>
       </c>
@@ -3822,15 +4257,17 @@
       <c r="D132" s="3"/>
       <c r="E132" s="13"/>
       <c r="F132" s="13"/>
-    </row>
-    <row r="133" spans="2:6">
+      <c r="G132" s="13"/>
+    </row>
+    <row r="133" spans="2:7">
       <c r="B133" s="4"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="13"/>
       <c r="F133" s="13"/>
-    </row>
-    <row r="134" spans="2:6">
+      <c r="G133" s="13"/>
+    </row>
+    <row r="134" spans="2:7">
       <c r="B134" s="4" t="s">
         <v>56</v>
       </c>
@@ -3846,8 +4283,11 @@
       <c r="F134" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="135" spans="2:6">
+      <c r="G134" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="135" spans="2:7">
       <c r="B135" s="4" t="s">
         <v>57</v>
       </c>
@@ -3863,8 +4303,11 @@
       <c r="F135" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="136" spans="2:6">
+      <c r="G135" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="136" spans="2:7">
       <c r="B136" s="4" t="s">
         <v>58</v>
       </c>
@@ -3880,8 +4323,11 @@
       <c r="F136" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="137" spans="2:6">
+      <c r="G136" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7">
       <c r="B137" s="4" t="s">
         <v>59</v>
       </c>
@@ -3897,15 +4343,19 @@
       <c r="F137" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="138" spans="2:6">
+      <c r="G137" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="138" spans="2:7">
       <c r="B138" s="4"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="13"/>
       <c r="F138" s="13"/>
-    </row>
-    <row r="139" spans="2:6">
+      <c r="G138" s="13"/>
+    </row>
+    <row r="139" spans="2:7">
       <c r="B139" s="4" t="s">
         <v>60</v>
       </c>
@@ -3919,15 +4369,19 @@
       <c r="F139" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="140" spans="2:6">
+      <c r="G139" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="140" spans="2:7">
       <c r="B140" s="4"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="13"/>
       <c r="F140" s="13"/>
-    </row>
-    <row r="141" spans="2:6">
+      <c r="G140" s="13"/>
+    </row>
+    <row r="141" spans="2:7">
       <c r="B141" s="4" t="s">
         <v>61</v>
       </c>
@@ -3939,15 +4393,17 @@
       </c>
       <c r="E141" s="14"/>
       <c r="F141" s="14"/>
-    </row>
-    <row r="142" spans="2:6">
+      <c r="G141" s="14"/>
+    </row>
+    <row r="142" spans="2:7">
       <c r="B142" s="4"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="13"/>
       <c r="F142" s="13"/>
-    </row>
-    <row r="143" spans="2:6">
+      <c r="G142" s="13"/>
+    </row>
+    <row r="143" spans="2:7">
       <c r="B143" s="4" t="s">
         <v>62</v>
       </c>
@@ -3961,8 +4417,11 @@
       <c r="F143" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="144" spans="2:6">
+      <c r="G143" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="144" spans="2:7">
       <c r="B144" s="4" t="s">
         <v>63</v>
       </c>
@@ -3976,8 +4435,11 @@
       <c r="F144" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="145" spans="2:6">
+      <c r="G144" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="2:7">
       <c r="B145" s="4" t="s">
         <v>64</v>
       </c>
@@ -3991,8 +4453,11 @@
       <c r="F145" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="146" spans="2:6">
+      <c r="G145" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="146" spans="2:7">
       <c r="B146" s="4" t="s">
         <v>65</v>
       </c>
@@ -4006,8 +4471,11 @@
       <c r="F146" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="147" spans="2:6">
+      <c r="G146" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="147" spans="2:7">
       <c r="B147" s="4" t="s">
         <v>66</v>
       </c>
@@ -4021,8 +4489,11 @@
       <c r="F147" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="148" spans="2:6">
+      <c r="G147" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" spans="2:7">
       <c r="B148" s="4" t="s">
         <v>67</v>
       </c>
@@ -4036,8 +4507,11 @@
       <c r="F148" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="149" spans="2:6">
+      <c r="G148" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="149" spans="2:7">
       <c r="B149" s="4" t="s">
         <v>68</v>
       </c>
@@ -4053,8 +4527,11 @@
       <c r="F149" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="150" spans="2:6">
+      <c r="G149" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7">
       <c r="B150" s="4" t="s">
         <v>69</v>
       </c>
@@ -4066,8 +4543,9 @@
       </c>
       <c r="E150" s="13"/>
       <c r="F150" s="13"/>
-    </row>
-    <row r="151" spans="2:6">
+      <c r="G150" s="13"/>
+    </row>
+    <row r="151" spans="2:7">
       <c r="B151" s="4" t="s">
         <v>70</v>
       </c>
@@ -4079,8 +4557,9 @@
       </c>
       <c r="E151" s="13"/>
       <c r="F151" s="13"/>
-    </row>
-    <row r="152" spans="2:6">
+      <c r="G151" s="13"/>
+    </row>
+    <row r="152" spans="2:7">
       <c r="B152" s="5" t="s">
         <v>8</v>
       </c>
@@ -4090,8 +4569,9 @@
       <c r="D152" s="3"/>
       <c r="E152" s="13"/>
       <c r="F152" s="13"/>
-    </row>
-    <row r="153" spans="2:6">
+      <c r="G152" s="13"/>
+    </row>
+    <row r="153" spans="2:7">
       <c r="B153" s="4" t="s">
         <v>71</v>
       </c>
@@ -4105,8 +4585,11 @@
       <c r="F153" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="154" spans="2:6">
+      <c r="G153" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="154" spans="2:7">
       <c r="B154" s="4" t="s">
         <v>71</v>
       </c>
@@ -4120,8 +4603,11 @@
       <c r="F154" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="155" spans="2:6">
+      <c r="G154" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="2:7">
       <c r="B155" s="4" t="s">
         <v>72</v>
       </c>
@@ -4137,8 +4623,11 @@
       <c r="F155" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="156" spans="2:6">
+      <c r="G155" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="156" spans="2:7">
       <c r="B156" s="4" t="s">
         <v>72</v>
       </c>
@@ -4154,8 +4643,11 @@
       <c r="F156" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="157" spans="2:6">
+      <c r="G156" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="157" spans="2:7">
       <c r="B157" s="5" t="s">
         <v>8</v>
       </c>
@@ -4165,8 +4657,9 @@
       <c r="D157" s="3"/>
       <c r="E157" s="13"/>
       <c r="F157" s="13"/>
-    </row>
-    <row r="158" spans="2:6">
+      <c r="G157" s="13"/>
+    </row>
+    <row r="158" spans="2:7">
       <c r="B158" s="5" t="s">
         <v>8</v>
       </c>
@@ -4176,15 +4669,17 @@
       <c r="D158" s="3"/>
       <c r="E158" s="13"/>
       <c r="F158" s="13"/>
-    </row>
-    <row r="159" spans="2:6">
+      <c r="G158" s="13"/>
+    </row>
+    <row r="159" spans="2:7">
       <c r="B159" s="4"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="13"/>
       <c r="F159" s="13"/>
-    </row>
-    <row r="160" spans="2:6">
+      <c r="G159" s="13"/>
+    </row>
+    <row r="160" spans="2:7">
       <c r="B160" s="4" t="s">
         <v>73</v>
       </c>
@@ -4196,8 +4691,9 @@
       </c>
       <c r="E160" s="13"/>
       <c r="F160" s="13"/>
-    </row>
-    <row r="161" spans="2:6">
+      <c r="G160" s="13"/>
+    </row>
+    <row r="161" spans="2:7">
       <c r="B161" s="4" t="s">
         <v>73</v>
       </c>
@@ -4209,8 +4705,9 @@
       </c>
       <c r="E161" s="13"/>
       <c r="F161" s="13"/>
-    </row>
-    <row r="162" spans="2:6">
+      <c r="G161" s="13"/>
+    </row>
+    <row r="162" spans="2:7">
       <c r="B162" s="4" t="s">
         <v>74</v>
       </c>
@@ -4226,8 +4723,11 @@
       <c r="F162" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="163" spans="2:6">
+      <c r="G162" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="163" spans="2:7">
       <c r="B163" s="4" t="s">
         <v>74</v>
       </c>
@@ -4243,8 +4743,11 @@
       <c r="F163" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="164" spans="2:6">
+      <c r="G163" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="164" spans="2:7">
       <c r="B164" s="4" t="s">
         <v>75</v>
       </c>
@@ -4258,8 +4761,11 @@
       <c r="F164" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="165" spans="2:6">
+      <c r="G164" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="165" spans="2:7">
       <c r="B165" s="4" t="s">
         <v>75</v>
       </c>
@@ -4273,8 +4779,11 @@
       <c r="F165" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="166" spans="2:6">
+      <c r="G165" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="166" spans="2:7">
       <c r="B166" s="4" t="s">
         <v>76</v>
       </c>
@@ -4290,8 +4799,11 @@
       <c r="F166" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="167" spans="2:6">
+      <c r="G166" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="167" spans="2:7">
       <c r="B167" s="4" t="s">
         <v>76</v>
       </c>
@@ -4307,8 +4819,11 @@
       <c r="F167" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="168" spans="2:6">
+      <c r="G167" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="168" spans="2:7">
       <c r="B168" s="4" t="s">
         <v>77</v>
       </c>
@@ -4324,8 +4839,11 @@
       <c r="F168" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="169" spans="2:6">
+      <c r="G168" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="169" spans="2:7">
       <c r="B169" s="4" t="s">
         <v>77</v>
       </c>
@@ -4341,8 +4859,11 @@
       <c r="F169" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="170" spans="2:6">
+      <c r="G169" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="170" spans="2:7">
       <c r="B170" s="5" t="s">
         <v>8</v>
       </c>
@@ -4352,8 +4873,9 @@
       <c r="D170" s="3"/>
       <c r="E170" s="13"/>
       <c r="F170" s="13"/>
-    </row>
-    <row r="171" spans="2:6">
+      <c r="G170" s="13"/>
+    </row>
+    <row r="171" spans="2:7">
       <c r="B171" s="5" t="s">
         <v>8</v>
       </c>
@@ -4363,8 +4885,9 @@
       <c r="D171" s="3"/>
       <c r="E171" s="13"/>
       <c r="F171" s="13"/>
-    </row>
-    <row r="172" spans="2:6">
+      <c r="G171" s="13"/>
+    </row>
+    <row r="172" spans="2:7">
       <c r="B172" s="5" t="s">
         <v>8</v>
       </c>
@@ -4374,8 +4897,9 @@
       <c r="D172" s="3"/>
       <c r="E172" s="13"/>
       <c r="F172" s="13"/>
-    </row>
-    <row r="173" spans="2:6">
+      <c r="G172" s="13"/>
+    </row>
+    <row r="173" spans="2:7">
       <c r="B173" s="5" t="s">
         <v>8</v>
       </c>
@@ -4385,8 +4909,9 @@
       <c r="D173" s="3"/>
       <c r="E173" s="13"/>
       <c r="F173" s="13"/>
-    </row>
-    <row r="174" spans="2:6">
+      <c r="G173" s="13"/>
+    </row>
+    <row r="174" spans="2:7">
       <c r="B174" s="5" t="s">
         <v>8</v>
       </c>
@@ -4396,8 +4921,9 @@
       <c r="D174" s="3"/>
       <c r="E174" s="13"/>
       <c r="F174" s="13"/>
-    </row>
-    <row r="175" spans="2:6">
+      <c r="G174" s="13"/>
+    </row>
+    <row r="175" spans="2:7">
       <c r="B175" s="5" t="s">
         <v>8</v>
       </c>
@@ -4407,15 +4933,17 @@
       <c r="D175" s="3"/>
       <c r="E175" s="13"/>
       <c r="F175" s="13"/>
-    </row>
-    <row r="176" spans="2:6">
+      <c r="G175" s="13"/>
+    </row>
+    <row r="176" spans="2:7">
       <c r="B176" s="4"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="13"/>
       <c r="F176" s="13"/>
-    </row>
-    <row r="177" spans="2:6">
+      <c r="G176" s="13"/>
+    </row>
+    <row r="177" spans="2:7">
       <c r="B177" s="4" t="s">
         <v>78</v>
       </c>
@@ -4427,8 +4955,11 @@
       </c>
       <c r="E177" s="13"/>
       <c r="F177" s="13"/>
-    </row>
-    <row r="178" spans="2:6">
+      <c r="G177" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="178" spans="2:7">
       <c r="B178" s="4" t="s">
         <v>79</v>
       </c>
@@ -4440,8 +4971,11 @@
       </c>
       <c r="E178" s="13"/>
       <c r="F178" s="13"/>
-    </row>
-    <row r="179" spans="2:6">
+      <c r="G178" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="179" spans="2:7">
       <c r="B179" s="4" t="s">
         <v>80</v>
       </c>
@@ -4453,8 +4987,11 @@
       </c>
       <c r="E179" s="13"/>
       <c r="F179" s="13"/>
-    </row>
-    <row r="180" spans="2:6">
+      <c r="G179" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="180" spans="2:7">
       <c r="B180" s="4" t="s">
         <v>81</v>
       </c>
@@ -4466,8 +5003,11 @@
       </c>
       <c r="E180" s="13"/>
       <c r="F180" s="13"/>
-    </row>
-    <row r="181" spans="2:6">
+      <c r="G180" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="181" spans="2:7">
       <c r="B181" s="5" t="s">
         <v>8</v>
       </c>
@@ -4477,8 +5017,9 @@
       <c r="D181" s="3"/>
       <c r="E181" s="13"/>
       <c r="F181" s="13"/>
-    </row>
-    <row r="182" spans="2:6">
+      <c r="G181" s="13"/>
+    </row>
+    <row r="182" spans="2:7">
       <c r="B182" s="5" t="s">
         <v>8</v>
       </c>
@@ -4488,8 +5029,9 @@
       <c r="D182" s="3"/>
       <c r="E182" s="13"/>
       <c r="F182" s="13"/>
-    </row>
-    <row r="183" spans="2:6">
+      <c r="G182" s="13"/>
+    </row>
+    <row r="183" spans="2:7">
       <c r="B183" s="4" t="s">
         <v>82</v>
       </c>
@@ -4501,8 +5043,9 @@
       </c>
       <c r="E183" s="13"/>
       <c r="F183" s="13"/>
-    </row>
-    <row r="184" spans="2:6">
+      <c r="G183" s="13"/>
+    </row>
+    <row r="184" spans="2:7">
       <c r="B184" s="4" t="s">
         <v>83</v>
       </c>
@@ -4514,8 +5057,9 @@
       </c>
       <c r="E184" s="13"/>
       <c r="F184" s="13"/>
-    </row>
-    <row r="185" spans="2:6">
+      <c r="G184" s="13"/>
+    </row>
+    <row r="185" spans="2:7">
       <c r="B185" s="4" t="s">
         <v>84</v>
       </c>
@@ -4527,8 +5071,9 @@
       </c>
       <c r="E185" s="13"/>
       <c r="F185" s="13"/>
-    </row>
-    <row r="186" spans="2:6">
+      <c r="G185" s="13"/>
+    </row>
+    <row r="186" spans="2:7">
       <c r="B186" s="4" t="s">
         <v>85</v>
       </c>
@@ -4540,8 +5085,9 @@
       </c>
       <c r="E186" s="13"/>
       <c r="F186" s="13"/>
-    </row>
-    <row r="187" spans="2:6">
+      <c r="G186" s="13"/>
+    </row>
+    <row r="187" spans="2:7">
       <c r="B187" s="4" t="s">
         <v>86</v>
       </c>
@@ -4553,8 +5099,9 @@
       </c>
       <c r="E187" s="13"/>
       <c r="F187" s="13"/>
-    </row>
-    <row r="188" spans="2:6">
+      <c r="G187" s="13"/>
+    </row>
+    <row r="188" spans="2:7">
       <c r="B188" s="4" t="s">
         <v>87</v>
       </c>
@@ -4566,8 +5113,9 @@
       </c>
       <c r="E188" s="13"/>
       <c r="F188" s="13"/>
-    </row>
-    <row r="189" spans="2:6">
+      <c r="G188" s="13"/>
+    </row>
+    <row r="189" spans="2:7">
       <c r="B189" s="4" t="s">
         <v>88</v>
       </c>
@@ -4579,8 +5127,9 @@
       </c>
       <c r="E189" s="13"/>
       <c r="F189" s="13"/>
-    </row>
-    <row r="190" spans="2:6">
+      <c r="G189" s="13"/>
+    </row>
+    <row r="190" spans="2:7">
       <c r="B190" s="5" t="s">
         <v>8</v>
       </c>
@@ -4590,8 +5139,9 @@
       <c r="D190" s="3"/>
       <c r="E190" s="13"/>
       <c r="F190" s="13"/>
-    </row>
-    <row r="191" spans="2:6">
+      <c r="G190" s="13"/>
+    </row>
+    <row r="191" spans="2:7">
       <c r="B191" s="5" t="s">
         <v>8</v>
       </c>
@@ -4601,8 +5151,9 @@
       <c r="D191" s="3"/>
       <c r="E191" s="13"/>
       <c r="F191" s="13"/>
-    </row>
-    <row r="192" spans="2:6">
+      <c r="G191" s="13"/>
+    </row>
+    <row r="192" spans="2:7">
       <c r="B192" s="5" t="s">
         <v>8</v>
       </c>
@@ -4612,15 +5163,17 @@
       <c r="D192" s="3"/>
       <c r="E192" s="13"/>
       <c r="F192" s="13"/>
-    </row>
-    <row r="193" spans="2:6">
+      <c r="G192" s="13"/>
+    </row>
+    <row r="193" spans="2:7">
       <c r="B193" s="4"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="13"/>
       <c r="F193" s="13"/>
-    </row>
-    <row r="194" spans="2:6">
+      <c r="G193" s="13"/>
+    </row>
+    <row r="194" spans="2:7">
       <c r="B194" s="4" t="s">
         <v>71</v>
       </c>
@@ -4634,8 +5187,11 @@
       <c r="F194" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="195" spans="2:6">
+      <c r="G194" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="195" spans="2:7">
       <c r="B195" s="4" t="s">
         <v>71</v>
       </c>
@@ -4649,8 +5205,11 @@
       <c r="F195" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="196" spans="2:6">
+      <c r="G195" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="196" spans="2:7">
       <c r="B196" s="4" t="s">
         <v>72</v>
       </c>
@@ -4666,8 +5225,11 @@
       <c r="F196" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="197" spans="2:6">
+      <c r="G196" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="197" spans="2:7">
       <c r="B197" s="4" t="s">
         <v>73</v>
       </c>
@@ -4679,8 +5241,9 @@
       </c>
       <c r="E197" s="13"/>
       <c r="F197" s="13"/>
-    </row>
-    <row r="198" spans="2:6">
+      <c r="G197" s="13"/>
+    </row>
+    <row r="198" spans="2:7">
       <c r="B198" s="4" t="s">
         <v>74</v>
       </c>
@@ -4696,8 +5259,11 @@
       <c r="F198" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="199" spans="2:6">
+      <c r="G198" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="199" spans="2:7">
       <c r="B199" s="4" t="s">
         <v>75</v>
       </c>
@@ -4711,8 +5277,11 @@
       <c r="F199" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="200" spans="2:6">
+      <c r="G199" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="200" spans="2:7">
       <c r="B200" s="4" t="s">
         <v>76</v>
       </c>
@@ -4728,8 +5297,11 @@
       <c r="F200" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="201" spans="2:6">
+      <c r="G200" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="201" spans="2:7">
       <c r="B201" s="4" t="s">
         <v>76</v>
       </c>
@@ -4745,8 +5317,11 @@
       <c r="F201" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="202" spans="2:6">
+      <c r="G201" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="202" spans="2:7">
       <c r="B202" s="4" t="s">
         <v>77</v>
       </c>
@@ -4762,8 +5337,11 @@
       <c r="F202" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="203" spans="2:6">
+      <c r="G202" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="203" spans="2:7">
       <c r="B203" s="5" t="s">
         <v>8</v>
       </c>
@@ -4773,8 +5351,9 @@
       <c r="D203" s="3"/>
       <c r="E203" s="13"/>
       <c r="F203" s="13"/>
-    </row>
-    <row r="204" spans="2:6">
+      <c r="G203" s="13"/>
+    </row>
+    <row r="204" spans="2:7">
       <c r="B204" s="4" t="s">
         <v>89</v>
       </c>
@@ -4788,8 +5367,11 @@
       <c r="F204" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="205" spans="2:6">
+      <c r="G204" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="205" spans="2:7">
       <c r="B205" s="5" t="s">
         <v>8</v>
       </c>
@@ -4799,8 +5381,9 @@
       <c r="D205" s="3"/>
       <c r="E205" s="13"/>
       <c r="F205" s="13"/>
-    </row>
-    <row r="206" spans="2:6">
+      <c r="G205" s="13"/>
+    </row>
+    <row r="206" spans="2:7">
       <c r="B206" s="5" t="s">
         <v>8</v>
       </c>
@@ -4810,8 +5393,9 @@
       <c r="D206" s="3"/>
       <c r="E206" s="13"/>
       <c r="F206" s="13"/>
-    </row>
-    <row r="207" spans="2:6">
+      <c r="G206" s="13"/>
+    </row>
+    <row r="207" spans="2:7">
       <c r="B207" s="5" t="s">
         <v>8</v>
       </c>
@@ -4821,8 +5405,9 @@
       <c r="D207" s="3"/>
       <c r="E207" s="13"/>
       <c r="F207" s="13"/>
-    </row>
-    <row r="208" spans="2:6">
+      <c r="G207" s="13"/>
+    </row>
+    <row r="208" spans="2:7">
       <c r="B208" s="5" t="s">
         <v>8</v>
       </c>
@@ -4832,8 +5417,9 @@
       <c r="D208" s="3"/>
       <c r="E208" s="13"/>
       <c r="F208" s="13"/>
-    </row>
-    <row r="209" spans="2:6">
+      <c r="G208" s="13"/>
+    </row>
+    <row r="209" spans="2:7">
       <c r="B209" s="5" t="s">
         <v>8</v>
       </c>
@@ -4843,15 +5429,17 @@
       <c r="D209" s="3"/>
       <c r="E209" s="13"/>
       <c r="F209" s="13"/>
-    </row>
-    <row r="210" spans="2:6">
+      <c r="G209" s="13"/>
+    </row>
+    <row r="210" spans="2:7">
       <c r="B210" s="4"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="13"/>
       <c r="F210" s="13"/>
-    </row>
-    <row r="211" spans="2:6">
+      <c r="G210" s="13"/>
+    </row>
+    <row r="211" spans="2:7">
       <c r="B211" s="4" t="s">
         <v>90</v>
       </c>
@@ -4865,8 +5453,11 @@
       <c r="F211" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="212" spans="2:6">
+      <c r="G211" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="212" spans="2:7">
       <c r="B212" s="4" t="s">
         <v>91</v>
       </c>
@@ -4880,8 +5471,11 @@
       <c r="F212" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="213" spans="2:6">
+      <c r="G212" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="213" spans="2:7">
       <c r="B213" s="4" t="s">
         <v>92</v>
       </c>
@@ -4893,8 +5487,9 @@
       </c>
       <c r="E213" s="13"/>
       <c r="F213" s="13"/>
-    </row>
-    <row r="214" spans="2:6">
+      <c r="G213" s="13"/>
+    </row>
+    <row r="214" spans="2:7">
       <c r="B214" s="4" t="s">
         <v>93</v>
       </c>
@@ -4908,15 +5503,19 @@
       <c r="F214" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="215" spans="2:6">
+      <c r="G214" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="215" spans="2:7">
       <c r="B215" s="4"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="13"/>
       <c r="F215" s="13"/>
-    </row>
-    <row r="216" spans="2:6">
+      <c r="G215" s="13"/>
+    </row>
+    <row r="216" spans="2:7">
       <c r="B216" s="4" t="s">
         <v>94</v>
       </c>
@@ -4926,8 +5525,9 @@
       <c r="D216" s="3"/>
       <c r="E216" s="13"/>
       <c r="F216" s="13"/>
-    </row>
-    <row r="217" spans="2:6">
+      <c r="G216" s="13"/>
+    </row>
+    <row r="217" spans="2:7">
       <c r="B217" s="4" t="s">
         <v>95</v>
       </c>
@@ -4939,8 +5539,11 @@
       <c r="F217" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="218" spans="2:6">
+      <c r="G217" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="218" spans="2:7">
       <c r="B218" s="4" t="s">
         <v>96</v>
       </c>
@@ -4952,8 +5555,11 @@
       <c r="F218" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="219" spans="2:6">
+      <c r="G218" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="219" spans="2:7">
       <c r="B219" s="4" t="s">
         <v>97</v>
       </c>
@@ -4967,8 +5573,11 @@
       <c r="F219" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="220" spans="2:6">
+      <c r="G219" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="220" spans="2:7">
       <c r="B220" s="4" t="s">
         <v>98</v>
       </c>
@@ -4980,8 +5589,9 @@
       </c>
       <c r="E220" s="13"/>
       <c r="F220" s="13"/>
-    </row>
-    <row r="221" spans="2:6">
+      <c r="G220" s="13"/>
+    </row>
+    <row r="221" spans="2:7">
       <c r="B221" s="4" t="s">
         <v>99</v>
       </c>
@@ -4993,8 +5603,9 @@
       </c>
       <c r="E221" s="13"/>
       <c r="F221" s="13"/>
-    </row>
-    <row r="222" spans="2:6">
+      <c r="G221" s="13"/>
+    </row>
+    <row r="222" spans="2:7">
       <c r="B222" s="4" t="s">
         <v>100</v>
       </c>
@@ -5006,8 +5617,9 @@
       </c>
       <c r="E222" s="13"/>
       <c r="F222" s="13"/>
-    </row>
-    <row r="223" spans="2:6">
+      <c r="G222" s="13"/>
+    </row>
+    <row r="223" spans="2:7">
       <c r="B223" s="4" t="s">
         <v>101</v>
       </c>
@@ -5023,15 +5635,19 @@
       <c r="F223" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="224" spans="2:6">
+      <c r="G223" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="224" spans="2:7">
       <c r="B224" s="4"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="13"/>
       <c r="F224" s="13"/>
-    </row>
-    <row r="225" spans="2:6">
+      <c r="G224" s="13"/>
+    </row>
+    <row r="225" spans="2:7">
       <c r="B225" s="4" t="s">
         <v>71</v>
       </c>
@@ -5045,8 +5661,11 @@
       <c r="F225" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="226" spans="2:6">
+      <c r="G225" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="226" spans="2:7">
       <c r="B226" s="4" t="s">
         <v>76</v>
       </c>
@@ -5062,8 +5681,11 @@
       <c r="F226" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="227" spans="2:6">
+      <c r="G226" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="227" spans="2:7">
       <c r="B227" s="5" t="s">
         <v>8</v>
       </c>
@@ -5073,8 +5695,9 @@
       <c r="D227" s="3"/>
       <c r="E227" s="13"/>
       <c r="F227" s="13"/>
-    </row>
-    <row r="228" spans="2:6">
+      <c r="G227" s="13"/>
+    </row>
+    <row r="228" spans="2:7">
       <c r="B228" s="5" t="s">
         <v>8</v>
       </c>
@@ -5084,15 +5707,17 @@
       <c r="D228" s="3"/>
       <c r="E228" s="13"/>
       <c r="F228" s="13"/>
-    </row>
-    <row r="229" spans="2:6">
+      <c r="G228" s="13"/>
+    </row>
+    <row r="229" spans="2:7">
       <c r="B229" s="4"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="13"/>
       <c r="F229" s="13"/>
-    </row>
-    <row r="230" spans="2:6">
+      <c r="G229" s="13"/>
+    </row>
+    <row r="230" spans="2:7">
       <c r="B230" s="4"/>
       <c r="C230" s="3" t="s">
         <v>234</v>
@@ -5102,8 +5727,11 @@
       </c>
       <c r="E230" s="13"/>
       <c r="F230" s="13"/>
-    </row>
-    <row r="231" spans="2:6">
+      <c r="G230" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="231" spans="2:7">
       <c r="B231" s="4"/>
       <c r="C231" s="3" t="s">
         <v>235</v>
@@ -5113,15 +5741,19 @@
       </c>
       <c r="E231" s="13"/>
       <c r="F231" s="13"/>
-    </row>
-    <row r="232" spans="2:6">
+      <c r="G231" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="232" spans="2:7">
       <c r="B232" s="4"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="13"/>
       <c r="F232" s="13"/>
-    </row>
-    <row r="233" spans="2:6">
+      <c r="G232" s="13"/>
+    </row>
+    <row r="233" spans="2:7">
       <c r="B233" s="4" t="s">
         <v>102</v>
       </c>
@@ -5133,8 +5765,11 @@
       </c>
       <c r="E233" s="13"/>
       <c r="F233" s="13"/>
-    </row>
-    <row r="234" spans="2:6">
+      <c r="G233" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="234" spans="2:7">
       <c r="B234" s="4" t="s">
         <v>103</v>
       </c>
@@ -5146,8 +5781,11 @@
       </c>
       <c r="E234" s="13"/>
       <c r="F234" s="13"/>
-    </row>
-    <row r="235" spans="2:6">
+      <c r="G234" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="235" spans="2:7">
       <c r="B235" s="4" t="s">
         <v>104</v>
       </c>
@@ -5159,8 +5797,11 @@
       </c>
       <c r="E235" s="13"/>
       <c r="F235" s="13"/>
-    </row>
-    <row r="236" spans="2:6">
+      <c r="G235" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="236" spans="2:7">
       <c r="B236" s="5" t="s">
         <v>8</v>
       </c>
@@ -5172,15 +5813,19 @@
       </c>
       <c r="E236" s="13"/>
       <c r="F236" s="13"/>
-    </row>
-    <row r="237" spans="2:6">
+      <c r="G236" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="237" spans="2:7">
       <c r="B237" s="4"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="13"/>
       <c r="F237" s="13"/>
-    </row>
-    <row r="238" spans="2:6">
+      <c r="G237" s="13"/>
+    </row>
+    <row r="238" spans="2:7">
       <c r="B238" s="4" t="s">
         <v>105</v>
       </c>
@@ -5192,8 +5837,11 @@
       </c>
       <c r="E238" s="13"/>
       <c r="F238" s="13"/>
-    </row>
-    <row r="239" spans="2:6">
+      <c r="G238" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="239" spans="2:7">
       <c r="B239" s="4" t="s">
         <v>80</v>
       </c>
@@ -5205,8 +5853,11 @@
       </c>
       <c r="E239" s="13"/>
       <c r="F239" s="13"/>
-    </row>
-    <row r="240" spans="2:6">
+      <c r="G239" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="240" spans="2:7">
       <c r="B240" s="4" t="s">
         <v>106</v>
       </c>
@@ -5218,8 +5869,11 @@
       </c>
       <c r="E240" s="13"/>
       <c r="F240" s="13"/>
-    </row>
-    <row r="241" spans="2:6">
+      <c r="G240" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="241" spans="2:7">
       <c r="B241" s="4" t="s">
         <v>81</v>
       </c>
@@ -5231,15 +5885,19 @@
       </c>
       <c r="E241" s="13"/>
       <c r="F241" s="13"/>
-    </row>
-    <row r="242" spans="2:6">
+      <c r="G241" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="242" spans="2:7">
       <c r="B242" s="4"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="13"/>
       <c r="F242" s="13"/>
-    </row>
-    <row r="243" spans="2:6">
+      <c r="G242" s="13"/>
+    </row>
+    <row r="243" spans="2:7">
       <c r="B243" s="4" t="s">
         <v>107</v>
       </c>
@@ -5251,8 +5909,11 @@
         <v>140</v>
       </c>
       <c r="F243" s="13"/>
-    </row>
-    <row r="244" spans="2:6">
+      <c r="G243" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="244" spans="2:7">
       <c r="B244" s="4" t="s">
         <v>108</v>
       </c>
@@ -5266,8 +5927,11 @@
       <c r="F244" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="245" spans="2:6">
+      <c r="G244" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="245" spans="2:7">
       <c r="B245" s="4" t="s">
         <v>109</v>
       </c>
@@ -5281,8 +5945,11 @@
       <c r="F245" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="246" spans="2:6">
+      <c r="G245" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="246" spans="2:7">
       <c r="B246" s="4" t="s">
         <v>110</v>
       </c>
@@ -5296,8 +5963,11 @@
       <c r="F246" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="247" spans="2:6">
+      <c r="G246" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="247" spans="2:7">
       <c r="B247" s="4" t="s">
         <v>111</v>
       </c>
@@ -5311,8 +5981,11 @@
       <c r="F247" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="248" spans="2:6">
+      <c r="G247" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="248" spans="2:7">
       <c r="B248" s="4" t="s">
         <v>112</v>
       </c>
@@ -5326,8 +5999,11 @@
       <c r="F248" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="249" spans="2:6">
+      <c r="G248" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="249" spans="2:7">
       <c r="B249" s="4" t="s">
         <v>113</v>
       </c>
@@ -5341,8 +6017,11 @@
       <c r="F249" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="250" spans="2:6">
+      <c r="G249" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="250" spans="2:7">
       <c r="B250" s="4" t="s">
         <v>114</v>
       </c>
@@ -5356,8 +6035,11 @@
       <c r="F250" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="251" spans="2:6">
+      <c r="G250" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="251" spans="2:7">
       <c r="B251" s="4" t="s">
         <v>115</v>
       </c>
@@ -5371,8 +6053,11 @@
       <c r="F251" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="252" spans="2:6">
+      <c r="G251" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="252" spans="2:7">
       <c r="B252" s="4" t="s">
         <v>116</v>
       </c>
@@ -5382,8 +6067,9 @@
       <c r="D252" s="3"/>
       <c r="E252" s="13"/>
       <c r="F252" s="13"/>
-    </row>
-    <row r="253" spans="2:6">
+      <c r="G252" s="13"/>
+    </row>
+    <row r="253" spans="2:7">
       <c r="B253" s="4" t="s">
         <v>117</v>
       </c>
@@ -5397,8 +6083,11 @@
       <c r="F253" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="254" spans="2:6">
+      <c r="G253" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="254" spans="2:7">
       <c r="B254" s="5" t="s">
         <v>8</v>
       </c>
@@ -5408,8 +6097,9 @@
       <c r="D254" s="3"/>
       <c r="E254" s="13"/>
       <c r="F254" s="13"/>
-    </row>
-    <row r="255" spans="2:6">
+      <c r="G254" s="13"/>
+    </row>
+    <row r="255" spans="2:7">
       <c r="B255" s="4" t="s">
         <v>118</v>
       </c>
@@ -5419,8 +6109,9 @@
       <c r="D255" s="3"/>
       <c r="E255" s="13"/>
       <c r="F255" s="13"/>
-    </row>
-    <row r="256" spans="2:6">
+      <c r="G255" s="13"/>
+    </row>
+    <row r="256" spans="2:7">
       <c r="B256" s="4" t="s">
         <v>119</v>
       </c>
@@ -5432,8 +6123,9 @@
       </c>
       <c r="E256" s="13"/>
       <c r="F256" s="13"/>
-    </row>
-    <row r="257" spans="2:6">
+      <c r="G256" s="13"/>
+    </row>
+    <row r="257" spans="2:7">
       <c r="B257" s="4" t="s">
         <v>120</v>
       </c>
@@ -5445,8 +6137,9 @@
       </c>
       <c r="E257" s="13"/>
       <c r="F257" s="13"/>
-    </row>
-    <row r="258" spans="2:6">
+      <c r="G257" s="13"/>
+    </row>
+    <row r="258" spans="2:7">
       <c r="B258" s="4" t="s">
         <v>121</v>
       </c>
@@ -5460,8 +6153,11 @@
       <c r="F258" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="259" spans="2:6">
+      <c r="G258" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="259" spans="2:7">
       <c r="B259" s="4" t="s">
         <v>122</v>
       </c>
@@ -5475,8 +6171,11 @@
       <c r="F259" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="260" spans="2:6">
+      <c r="G259" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="260" spans="2:7">
       <c r="B260" s="4" t="s">
         <v>123</v>
       </c>
@@ -5490,8 +6189,11 @@
       <c r="F260" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="261" spans="2:6">
+      <c r="G260" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="261" spans="2:7">
       <c r="B261" s="4" t="s">
         <v>124</v>
       </c>
@@ -5505,8 +6207,11 @@
       <c r="F261" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="262" spans="2:6">
+      <c r="G261" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="262" spans="2:7">
       <c r="B262" s="4" t="s">
         <v>125</v>
       </c>
@@ -5522,8 +6227,11 @@
       <c r="F262" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="263" spans="2:6">
+      <c r="G262" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="263" spans="2:7">
       <c r="B263" s="5" t="s">
         <v>8</v>
       </c>
@@ -5533,8 +6241,9 @@
       <c r="D263" s="3"/>
       <c r="E263" s="13"/>
       <c r="F263" s="13"/>
-    </row>
-    <row r="264" spans="2:6">
+      <c r="G263" s="13"/>
+    </row>
+    <row r="264" spans="2:7">
       <c r="B264" s="4" t="s">
         <v>126</v>
       </c>
@@ -5548,8 +6257,11 @@
       <c r="F264" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="265" spans="2:6">
+      <c r="G264" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="265" spans="2:7">
       <c r="B265" s="4" t="s">
         <v>127</v>
       </c>
@@ -5563,8 +6275,11 @@
       <c r="F265" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="266" spans="2:6">
+      <c r="G265" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="266" spans="2:7">
       <c r="B266" s="5" t="s">
         <v>8</v>
       </c>
@@ -5574,8 +6289,9 @@
       <c r="D266" s="19"/>
       <c r="E266" s="13"/>
       <c r="F266" s="13"/>
-    </row>
-    <row r="267" spans="2:6">
+      <c r="G266" s="13"/>
+    </row>
+    <row r="267" spans="2:7">
       <c r="B267" s="5" t="s">
         <v>128</v>
       </c>
@@ -5585,8 +6301,9 @@
       <c r="D267" s="19"/>
       <c r="E267" s="13"/>
       <c r="F267" s="13"/>
-    </row>
-    <row r="268" spans="2:6">
+      <c r="G267" s="13"/>
+    </row>
+    <row r="268" spans="2:7">
       <c r="B268" s="5" t="s">
         <v>128</v>
       </c>
@@ -5596,8 +6313,9 @@
       <c r="D268" s="19"/>
       <c r="E268" s="13"/>
       <c r="F268" s="13"/>
-    </row>
-    <row r="269" spans="2:6">
+      <c r="G268" s="13"/>
+    </row>
+    <row r="269" spans="2:7">
       <c r="B269" s="5" t="s">
         <v>128</v>
       </c>
@@ -5607,8 +6325,9 @@
       <c r="D269" s="19"/>
       <c r="E269" s="13"/>
       <c r="F269" s="13"/>
-    </row>
-    <row r="270" spans="2:6">
+      <c r="G269" s="13"/>
+    </row>
+    <row r="270" spans="2:7">
       <c r="B270" s="5" t="s">
         <v>128</v>
       </c>
@@ -5618,8 +6337,9 @@
       <c r="D270" s="19"/>
       <c r="E270" s="13"/>
       <c r="F270" s="13"/>
-    </row>
-    <row r="271" spans="2:6">
+      <c r="G270" s="13"/>
+    </row>
+    <row r="271" spans="2:7">
       <c r="B271" s="5" t="s">
         <v>128</v>
       </c>
@@ -5629,8 +6349,9 @@
       <c r="D271" s="19"/>
       <c r="E271" s="13"/>
       <c r="F271" s="13"/>
-    </row>
-    <row r="272" spans="2:6">
+      <c r="G271" s="13"/>
+    </row>
+    <row r="272" spans="2:7">
       <c r="B272" s="5" t="s">
         <v>128</v>
       </c>
@@ -5640,8 +6361,9 @@
       <c r="D272" s="19"/>
       <c r="E272" s="13"/>
       <c r="F272" s="13"/>
-    </row>
-    <row r="273" spans="2:6">
+      <c r="G272" s="13"/>
+    </row>
+    <row r="273" spans="2:7">
       <c r="B273" s="5" t="s">
         <v>128</v>
       </c>
@@ -5651,8 +6373,9 @@
       <c r="D273" s="19"/>
       <c r="E273" s="13"/>
       <c r="F273" s="13"/>
-    </row>
-    <row r="274" spans="2:6">
+      <c r="G273" s="13"/>
+    </row>
+    <row r="274" spans="2:7">
       <c r="B274" s="5" t="s">
         <v>128</v>
       </c>
@@ -5662,547 +6385,625 @@
       <c r="D274" s="19"/>
       <c r="E274" s="13"/>
       <c r="F274" s="13"/>
-    </row>
-    <row r="275" spans="2:6">
+      <c r="G274" s="13"/>
+    </row>
+    <row r="275" spans="2:7">
       <c r="B275" s="4"/>
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="13"/>
       <c r="F275" s="13"/>
-    </row>
-    <row r="276" spans="2:6">
+      <c r="G275" s="13"/>
+    </row>
+    <row r="276" spans="2:7">
       <c r="B276" s="4"/>
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="14"/>
       <c r="F276" s="14"/>
-    </row>
-    <row r="277" spans="2:6">
+      <c r="G276" s="14"/>
+    </row>
+    <row r="277" spans="2:7">
       <c r="B277" s="4"/>
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="14"/>
       <c r="F277" s="14"/>
-    </row>
-    <row r="278" spans="2:6">
+      <c r="G277" s="14"/>
+    </row>
+    <row r="278" spans="2:7">
       <c r="B278" s="4"/>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="14"/>
       <c r="F278" s="14"/>
-    </row>
-    <row r="279" spans="2:6">
+      <c r="G278" s="14"/>
+    </row>
+    <row r="279" spans="2:7">
       <c r="B279" s="4"/>
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="14"/>
       <c r="F279" s="14"/>
-    </row>
-    <row r="280" spans="2:6">
+      <c r="G279" s="14"/>
+    </row>
+    <row r="280" spans="2:7">
       <c r="B280" s="4"/>
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="14"/>
       <c r="F280" s="14"/>
-    </row>
-    <row r="281" spans="2:6">
+      <c r="G280" s="14"/>
+    </row>
+    <row r="281" spans="2:7">
       <c r="B281" s="4"/>
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="14"/>
       <c r="F281" s="14"/>
-    </row>
-    <row r="282" spans="2:6">
+      <c r="G281" s="14"/>
+    </row>
+    <row r="282" spans="2:7">
       <c r="B282" s="4"/>
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="14"/>
       <c r="F282" s="14"/>
-    </row>
-    <row r="283" spans="2:6">
+      <c r="G282" s="14"/>
+    </row>
+    <row r="283" spans="2:7">
       <c r="B283" s="4"/>
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="14"/>
       <c r="F283" s="14"/>
-    </row>
-    <row r="284" spans="2:6">
+      <c r="G283" s="14"/>
+    </row>
+    <row r="284" spans="2:7">
       <c r="B284" s="4"/>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="14"/>
       <c r="F284" s="14"/>
-    </row>
-    <row r="285" spans="2:6">
+      <c r="G284" s="14"/>
+    </row>
+    <row r="285" spans="2:7">
       <c r="B285" s="5"/>
       <c r="C285" s="17"/>
       <c r="D285" s="3"/>
       <c r="E285" s="14"/>
       <c r="F285" s="14"/>
-    </row>
-    <row r="286" spans="2:6">
+      <c r="G285" s="14"/>
+    </row>
+    <row r="286" spans="2:7">
       <c r="B286" s="4"/>
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="14"/>
       <c r="F286" s="14"/>
-    </row>
-    <row r="287" spans="2:6">
+      <c r="G286" s="14"/>
+    </row>
+    <row r="287" spans="2:7">
       <c r="B287" s="5"/>
       <c r="C287" s="17"/>
       <c r="D287" s="3"/>
       <c r="E287" s="14"/>
       <c r="F287" s="14"/>
-    </row>
-    <row r="288" spans="2:6">
+      <c r="G287" s="14"/>
+    </row>
+    <row r="288" spans="2:7">
       <c r="B288" s="5"/>
       <c r="C288" s="17"/>
       <c r="D288" s="3"/>
       <c r="E288" s="14"/>
       <c r="F288" s="14"/>
-    </row>
-    <row r="289" spans="2:6">
+      <c r="G288" s="14"/>
+    </row>
+    <row r="289" spans="2:7">
       <c r="B289" s="4"/>
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="14"/>
       <c r="F289" s="14"/>
-    </row>
-    <row r="290" spans="2:6">
+      <c r="G289" s="14"/>
+    </row>
+    <row r="290" spans="2:7">
       <c r="B290" s="4"/>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="14"/>
       <c r="F290" s="14"/>
-    </row>
-    <row r="291" spans="2:6">
+      <c r="G290" s="14"/>
+    </row>
+    <row r="291" spans="2:7">
       <c r="B291" s="4"/>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="14"/>
       <c r="F291" s="14"/>
-    </row>
-    <row r="292" spans="2:6">
+      <c r="G291" s="14"/>
+    </row>
+    <row r="292" spans="2:7">
       <c r="B292" s="4"/>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="13"/>
       <c r="F292" s="13"/>
-    </row>
-    <row r="293" spans="2:6">
+      <c r="G292" s="13"/>
+    </row>
+    <row r="293" spans="2:7">
       <c r="B293" s="4"/>
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="14"/>
       <c r="F293" s="14"/>
-    </row>
-    <row r="294" spans="2:6">
+      <c r="G293" s="14"/>
+    </row>
+    <row r="294" spans="2:7">
       <c r="B294" s="4"/>
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="14"/>
       <c r="F294" s="14"/>
-    </row>
-    <row r="295" spans="2:6">
+      <c r="G294" s="14"/>
+    </row>
+    <row r="295" spans="2:7">
       <c r="B295" s="4"/>
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="14"/>
       <c r="F295" s="14"/>
-    </row>
-    <row r="296" spans="2:6">
+      <c r="G295" s="14"/>
+    </row>
+    <row r="296" spans="2:7">
       <c r="B296" s="4"/>
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="14"/>
       <c r="F296" s="14"/>
-    </row>
-    <row r="297" spans="2:6">
+      <c r="G296" s="14"/>
+    </row>
+    <row r="297" spans="2:7">
       <c r="B297" s="4"/>
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="14"/>
       <c r="F297" s="14"/>
-    </row>
-    <row r="298" spans="2:6">
+      <c r="G297" s="14"/>
+    </row>
+    <row r="298" spans="2:7">
       <c r="B298" s="4"/>
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="14"/>
       <c r="F298" s="14"/>
-    </row>
-    <row r="299" spans="2:6">
+      <c r="G298" s="14"/>
+    </row>
+    <row r="299" spans="2:7">
       <c r="B299" s="4"/>
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="14"/>
       <c r="F299" s="14"/>
-    </row>
-    <row r="300" spans="2:6">
+      <c r="G299" s="14"/>
+    </row>
+    <row r="300" spans="2:7">
       <c r="B300" s="4"/>
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="14"/>
       <c r="F300" s="14"/>
-    </row>
-    <row r="301" spans="2:6">
+      <c r="G300" s="14"/>
+    </row>
+    <row r="301" spans="2:7">
       <c r="B301" s="4"/>
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="14"/>
       <c r="F301" s="14"/>
-    </row>
-    <row r="302" spans="2:6">
+      <c r="G301" s="14"/>
+    </row>
+    <row r="302" spans="2:7">
       <c r="B302" s="5"/>
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="14"/>
       <c r="F302" s="14"/>
-    </row>
-    <row r="303" spans="2:6">
+      <c r="G302" s="14"/>
+    </row>
+    <row r="303" spans="2:7">
       <c r="B303" s="4"/>
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="14"/>
       <c r="F303" s="14"/>
-    </row>
-    <row r="304" spans="2:6">
+      <c r="G303" s="14"/>
+    </row>
+    <row r="304" spans="2:7">
       <c r="B304" s="5"/>
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="14"/>
       <c r="F304" s="14"/>
-    </row>
-    <row r="305" spans="2:6">
+      <c r="G304" s="14"/>
+    </row>
+    <row r="305" spans="2:7">
       <c r="B305" s="5"/>
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="14"/>
       <c r="F305" s="14"/>
-    </row>
-    <row r="306" spans="2:6">
+      <c r="G305" s="14"/>
+    </row>
+    <row r="306" spans="2:7">
       <c r="B306" s="4"/>
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="14"/>
       <c r="F306" s="14"/>
-    </row>
-    <row r="307" spans="2:6">
+      <c r="G306" s="14"/>
+    </row>
+    <row r="307" spans="2:7">
       <c r="B307" s="4"/>
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="14"/>
       <c r="F307" s="14"/>
-    </row>
-    <row r="308" spans="2:6">
+      <c r="G307" s="14"/>
+    </row>
+    <row r="308" spans="2:7">
       <c r="B308" s="4"/>
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="14"/>
       <c r="F308" s="14"/>
-    </row>
-    <row r="309" spans="2:6">
+      <c r="G308" s="14"/>
+    </row>
+    <row r="309" spans="2:7">
       <c r="B309" s="4"/>
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="13"/>
       <c r="F309" s="13"/>
-    </row>
-    <row r="310" spans="2:6">
+      <c r="G309" s="13"/>
+    </row>
+    <row r="310" spans="2:7">
       <c r="B310" s="4"/>
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="14"/>
       <c r="F310" s="14"/>
-    </row>
-    <row r="311" spans="2:6">
+      <c r="G310" s="14"/>
+    </row>
+    <row r="311" spans="2:7">
       <c r="B311" s="4"/>
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="14"/>
       <c r="F311" s="14"/>
-    </row>
-    <row r="312" spans="2:6">
+      <c r="G311" s="14"/>
+    </row>
+    <row r="312" spans="2:7">
       <c r="B312" s="4"/>
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="14"/>
       <c r="F312" s="14"/>
-    </row>
-    <row r="313" spans="2:6">
+      <c r="G312" s="14"/>
+    </row>
+    <row r="313" spans="2:7">
       <c r="B313" s="4"/>
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="14"/>
       <c r="F313" s="14"/>
-    </row>
-    <row r="314" spans="2:6">
+      <c r="G313" s="14"/>
+    </row>
+    <row r="314" spans="2:7">
       <c r="B314" s="4"/>
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="14"/>
       <c r="F314" s="14"/>
-    </row>
-    <row r="315" spans="2:6">
+      <c r="G314" s="14"/>
+    </row>
+    <row r="315" spans="2:7">
       <c r="B315" s="4"/>
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="14"/>
       <c r="F315" s="14"/>
-    </row>
-    <row r="316" spans="2:6">
+      <c r="G315" s="14"/>
+    </row>
+    <row r="316" spans="2:7">
       <c r="B316" s="4"/>
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="14"/>
       <c r="F316" s="14"/>
-    </row>
-    <row r="317" spans="2:6">
+      <c r="G316" s="14"/>
+    </row>
+    <row r="317" spans="2:7">
       <c r="B317" s="4"/>
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="14"/>
       <c r="F317" s="14"/>
-    </row>
-    <row r="318" spans="2:6">
+      <c r="G317" s="14"/>
+    </row>
+    <row r="318" spans="2:7">
       <c r="B318" s="4"/>
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="14"/>
       <c r="F318" s="14"/>
-    </row>
-    <row r="319" spans="2:6">
+      <c r="G318" s="14"/>
+    </row>
+    <row r="319" spans="2:7">
       <c r="B319" s="5"/>
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="14"/>
       <c r="F319" s="14"/>
-    </row>
-    <row r="320" spans="2:6">
+      <c r="G319" s="14"/>
+    </row>
+    <row r="320" spans="2:7">
       <c r="B320" s="4"/>
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="14"/>
       <c r="F320" s="14"/>
-    </row>
-    <row r="321" spans="2:6">
+      <c r="G320" s="14"/>
+    </row>
+    <row r="321" spans="2:7">
       <c r="B321" s="5"/>
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="14"/>
       <c r="F321" s="14"/>
-    </row>
-    <row r="322" spans="2:6">
+      <c r="G321" s="14"/>
+    </row>
+    <row r="322" spans="2:7">
       <c r="B322" s="5"/>
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="14"/>
       <c r="F322" s="14"/>
-    </row>
-    <row r="323" spans="2:6">
+      <c r="G322" s="14"/>
+    </row>
+    <row r="323" spans="2:7">
       <c r="B323" s="4"/>
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="14"/>
       <c r="F323" s="14"/>
-    </row>
-    <row r="324" spans="2:6">
+      <c r="G323" s="14"/>
+    </row>
+    <row r="324" spans="2:7">
       <c r="B324" s="4"/>
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="14"/>
       <c r="F324" s="14"/>
-    </row>
-    <row r="325" spans="2:6">
+      <c r="G324" s="14"/>
+    </row>
+    <row r="325" spans="2:7">
       <c r="B325" s="4"/>
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="14"/>
       <c r="F325" s="14"/>
-    </row>
-    <row r="326" spans="2:6">
+      <c r="G325" s="14"/>
+    </row>
+    <row r="326" spans="2:7">
       <c r="B326" s="4"/>
       <c r="C326" s="19"/>
       <c r="D326" s="19"/>
       <c r="E326" s="13"/>
       <c r="F326" s="13"/>
-    </row>
-    <row r="327" spans="2:6">
+      <c r="G326" s="13"/>
+    </row>
+    <row r="327" spans="2:7">
       <c r="B327" s="4"/>
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="14"/>
       <c r="F327" s="14"/>
-    </row>
-    <row r="328" spans="2:6">
+      <c r="G327" s="14"/>
+    </row>
+    <row r="328" spans="2:7">
       <c r="B328" s="4"/>
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="14"/>
       <c r="F328" s="14"/>
-    </row>
-    <row r="329" spans="2:6">
+      <c r="G328" s="14"/>
+    </row>
+    <row r="329" spans="2:7">
       <c r="B329" s="4"/>
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="14"/>
       <c r="F329" s="14"/>
-    </row>
-    <row r="330" spans="2:6">
+      <c r="G329" s="14"/>
+    </row>
+    <row r="330" spans="2:7">
       <c r="B330" s="4"/>
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="14"/>
       <c r="F330" s="14"/>
-    </row>
-    <row r="331" spans="2:6">
+      <c r="G330" s="14"/>
+    </row>
+    <row r="331" spans="2:7">
       <c r="B331" s="4"/>
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="14"/>
       <c r="F331" s="14"/>
-    </row>
-    <row r="332" spans="2:6">
+      <c r="G331" s="14"/>
+    </row>
+    <row r="332" spans="2:7">
       <c r="B332" s="4"/>
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="14"/>
       <c r="F332" s="14"/>
-    </row>
-    <row r="333" spans="2:6">
+      <c r="G332" s="14"/>
+    </row>
+    <row r="333" spans="2:7">
       <c r="B333" s="4"/>
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
       <c r="E333" s="14"/>
       <c r="F333" s="14"/>
-    </row>
-    <row r="334" spans="2:6">
+      <c r="G333" s="14"/>
+    </row>
+    <row r="334" spans="2:7">
       <c r="B334" s="4"/>
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
       <c r="E334" s="14"/>
       <c r="F334" s="14"/>
-    </row>
-    <row r="335" spans="2:6">
+      <c r="G334" s="14"/>
+    </row>
+    <row r="335" spans="2:7">
       <c r="B335" s="4"/>
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="14"/>
       <c r="F335" s="14"/>
-    </row>
-    <row r="336" spans="2:6">
+      <c r="G335" s="14"/>
+    </row>
+    <row r="336" spans="2:7">
       <c r="B336" s="5"/>
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
       <c r="E336" s="14"/>
       <c r="F336" s="14"/>
-    </row>
-    <row r="337" spans="2:6">
+      <c r="G336" s="14"/>
+    </row>
+    <row r="337" spans="2:7">
       <c r="B337" s="4"/>
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
       <c r="E337" s="14"/>
       <c r="F337" s="14"/>
-    </row>
-    <row r="338" spans="2:6">
+      <c r="G337" s="14"/>
+    </row>
+    <row r="338" spans="2:7">
       <c r="B338" s="5"/>
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
       <c r="E338" s="14"/>
       <c r="F338" s="14"/>
-    </row>
-    <row r="339" spans="2:6">
+      <c r="G338" s="14"/>
+    </row>
+    <row r="339" spans="2:7">
       <c r="B339" s="5"/>
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
       <c r="E339" s="14"/>
       <c r="F339" s="14"/>
-    </row>
-    <row r="340" spans="2:6">
+      <c r="G339" s="14"/>
+    </row>
+    <row r="340" spans="2:7">
       <c r="B340" s="4"/>
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
       <c r="E340" s="14"/>
       <c r="F340" s="14"/>
-    </row>
-    <row r="341" spans="2:6">
+      <c r="G340" s="14"/>
+    </row>
+    <row r="341" spans="2:7">
       <c r="B341" s="4"/>
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
       <c r="E341" s="14"/>
       <c r="F341" s="14"/>
-    </row>
-    <row r="342" spans="2:6">
+      <c r="G341" s="14"/>
+    </row>
+    <row r="342" spans="2:7">
       <c r="B342" s="4"/>
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
       <c r="E342" s="14"/>
       <c r="F342" s="14"/>
-    </row>
-    <row r="343" spans="2:6">
+      <c r="G342" s="14"/>
+    </row>
+    <row r="343" spans="2:7">
       <c r="B343" s="4"/>
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="14"/>
       <c r="F343" s="14"/>
-    </row>
-    <row r="344" spans="2:6">
+      <c r="G343" s="14"/>
+    </row>
+    <row r="344" spans="2:7">
       <c r="B344" s="4"/>
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="14"/>
       <c r="F344" s="14"/>
-    </row>
-    <row r="345" spans="2:6">
+      <c r="G344" s="14"/>
+    </row>
+    <row r="345" spans="2:7">
       <c r="B345" s="4"/>
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="14"/>
       <c r="F345" s="14"/>
-    </row>
-    <row r="346" spans="2:6">
+      <c r="G345" s="14"/>
+    </row>
+    <row r="346" spans="2:7">
       <c r="B346" s="4"/>
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="14"/>
       <c r="F346" s="14"/>
-    </row>
-    <row r="347" spans="2:6">
+      <c r="G346" s="14"/>
+    </row>
+    <row r="347" spans="2:7">
       <c r="B347" s="4"/>
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="14"/>
       <c r="F347" s="14"/>
-    </row>
-    <row r="348" spans="2:6">
+      <c r="G347" s="14"/>
+    </row>
+    <row r="348" spans="2:7">
       <c r="B348" s="4"/>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="14"/>
       <c r="F348" s="14"/>
-    </row>
-    <row r="349" spans="2:6">
+      <c r="G348" s="14"/>
+    </row>
+    <row r="349" spans="2:7">
       <c r="B349" s="4"/>
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
       <c r="E349" s="14"/>
       <c r="F349" s="14"/>
-    </row>
-    <row r="350" spans="2:6">
+      <c r="G349" s="14"/>
+    </row>
+    <row r="350" spans="2:7">
       <c r="B350" s="4"/>
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
       <c r="E350" s="14"/>
       <c r="F350" s="14"/>
-    </row>
-    <row r="351" spans="2:6">
+      <c r="G350" s="14"/>
+    </row>
+    <row r="351" spans="2:7">
       <c r="B351" s="4"/>
       <c r="C351" s="19"/>
       <c r="D351" s="19"/>
       <c r="E351" s="13"/>
       <c r="F351" s="13"/>
-    </row>
-    <row r="352" spans="2:6">
+      <c r="G351" s="13"/>
+    </row>
+    <row r="352" spans="2:7">
       <c r="B352" s="4" t="s">
         <v>49</v>
       </c>
@@ -6216,8 +7017,11 @@
       <c r="F352" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="353" spans="2:6">
+      <c r="G352" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="353" spans="2:7">
       <c r="B353" s="4" t="s">
         <v>50</v>
       </c>
@@ -6233,8 +7037,11 @@
       <c r="F353" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="354" spans="2:6">
+      <c r="G353" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="354" spans="2:7">
       <c r="B354" s="4" t="s">
         <v>129</v>
       </c>
@@ -6248,8 +7055,11 @@
       <c r="F354" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="355" spans="2:6">
+      <c r="G354" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="355" spans="2:7">
       <c r="B355" s="4" t="s">
         <v>130</v>
       </c>
@@ -6261,15 +7071,17 @@
       </c>
       <c r="E355" s="13"/>
       <c r="F355" s="13"/>
-    </row>
-    <row r="356" spans="2:6">
+      <c r="G355" s="13"/>
+    </row>
+    <row r="356" spans="2:7">
       <c r="B356" s="4"/>
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
       <c r="E356" s="13"/>
       <c r="F356" s="13"/>
-    </row>
-    <row r="357" spans="2:6">
+      <c r="G356" s="13"/>
+    </row>
+    <row r="357" spans="2:7">
       <c r="B357" s="4" t="s">
         <v>131</v>
       </c>
@@ -6279,8 +7091,9 @@
       <c r="D357" s="3"/>
       <c r="E357" s="13"/>
       <c r="F357" s="13"/>
-    </row>
-    <row r="358" spans="2:6">
+      <c r="G357" s="13"/>
+    </row>
+    <row r="358" spans="2:7">
       <c r="B358" s="4" t="s">
         <v>132</v>
       </c>
@@ -6290,8 +7103,9 @@
       <c r="D358" s="3"/>
       <c r="E358" s="13"/>
       <c r="F358" s="13"/>
-    </row>
-    <row r="359" spans="2:6">
+      <c r="G358" s="13"/>
+    </row>
+    <row r="359" spans="2:7">
       <c r="B359" s="4" t="s">
         <v>133</v>
       </c>
@@ -6301,8 +7115,9 @@
       <c r="D359" s="3"/>
       <c r="E359" s="13"/>
       <c r="F359" s="13"/>
-    </row>
-    <row r="360" spans="2:6">
+      <c r="G359" s="13"/>
+    </row>
+    <row r="360" spans="2:7">
       <c r="B360" s="4" t="s">
         <v>134</v>
       </c>
@@ -6312,8 +7127,9 @@
       <c r="D360" s="3"/>
       <c r="E360" s="13"/>
       <c r="F360" s="13"/>
-    </row>
-    <row r="361" spans="2:6">
+      <c r="G360" s="13"/>
+    </row>
+    <row r="361" spans="2:7">
       <c r="B361" s="4" t="s">
         <v>135</v>
       </c>
@@ -6323,15 +7139,17 @@
       <c r="D361" s="3"/>
       <c r="E361" s="13"/>
       <c r="F361" s="13"/>
-    </row>
-    <row r="362" spans="2:6">
+      <c r="G361" s="13"/>
+    </row>
+    <row r="362" spans="2:7">
       <c r="B362" s="4"/>
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
       <c r="E362" s="13"/>
       <c r="F362" s="13"/>
-    </row>
-    <row r="363" spans="2:6">
+      <c r="G362" s="13"/>
+    </row>
+    <row r="363" spans="2:7">
       <c r="B363" s="4" t="s">
         <v>131</v>
       </c>
@@ -6341,8 +7159,9 @@
       <c r="D363" s="3"/>
       <c r="E363" s="13"/>
       <c r="F363" s="13"/>
-    </row>
-    <row r="364" spans="2:6">
+      <c r="G363" s="13"/>
+    </row>
+    <row r="364" spans="2:7">
       <c r="B364" s="4" t="s">
         <v>132</v>
       </c>
@@ -6352,8 +7171,9 @@
       <c r="D364" s="3"/>
       <c r="E364" s="13"/>
       <c r="F364" s="13"/>
-    </row>
-    <row r="365" spans="2:6">
+      <c r="G364" s="13"/>
+    </row>
+    <row r="365" spans="2:7">
       <c r="B365" s="4" t="s">
         <v>133</v>
       </c>
@@ -6363,8 +7183,9 @@
       <c r="D365" s="3"/>
       <c r="E365" s="13"/>
       <c r="F365" s="13"/>
-    </row>
-    <row r="366" spans="2:6">
+      <c r="G365" s="13"/>
+    </row>
+    <row r="366" spans="2:7">
       <c r="B366" s="4" t="s">
         <v>134</v>
       </c>
@@ -6374,8 +7195,9 @@
       <c r="D366" s="3"/>
       <c r="E366" s="13"/>
       <c r="F366" s="13"/>
-    </row>
-    <row r="367" spans="2:6">
+      <c r="G366" s="13"/>
+    </row>
+    <row r="367" spans="2:7">
       <c r="B367" s="4" t="s">
         <v>135</v>
       </c>
@@ -6385,15 +7207,17 @@
       <c r="D367" s="3"/>
       <c r="E367" s="13"/>
       <c r="F367" s="13"/>
-    </row>
-    <row r="368" spans="2:6">
+      <c r="G367" s="13"/>
+    </row>
+    <row r="368" spans="2:7">
       <c r="B368" s="4"/>
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
       <c r="E368" s="13"/>
       <c r="F368" s="13"/>
-    </row>
-    <row r="369" spans="2:6">
+      <c r="G368" s="13"/>
+    </row>
+    <row r="369" spans="2:7">
       <c r="B369" s="4" t="s">
         <v>136</v>
       </c>
@@ -6405,8 +7229,9 @@
       </c>
       <c r="E369" s="13"/>
       <c r="F369" s="13"/>
-    </row>
-    <row r="370" spans="2:6">
+      <c r="G369" s="13"/>
+    </row>
+    <row r="370" spans="2:7">
       <c r="B370" s="4" t="s">
         <v>137</v>
       </c>
@@ -6418,8 +7243,9 @@
       </c>
       <c r="E370" s="13"/>
       <c r="F370" s="13"/>
-    </row>
-    <row r="371" spans="2:6">
+      <c r="G370" s="13"/>
+    </row>
+    <row r="371" spans="2:7">
       <c r="B371" s="4" t="s">
         <v>138</v>
       </c>
@@ -6431,15 +7257,17 @@
       </c>
       <c r="E371" s="13"/>
       <c r="F371" s="13"/>
-    </row>
-    <row r="372" spans="2:6">
+      <c r="G371" s="13"/>
+    </row>
+    <row r="372" spans="2:7">
       <c r="B372" s="4"/>
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
       <c r="E372" s="13"/>
       <c r="F372" s="13"/>
-    </row>
-    <row r="373" spans="2:6">
+      <c r="G372" s="13"/>
+    </row>
+    <row r="373" spans="2:7">
       <c r="B373" s="4" t="s">
         <v>136</v>
       </c>
@@ -6451,8 +7279,9 @@
       </c>
       <c r="E373" s="13"/>
       <c r="F373" s="13"/>
-    </row>
-    <row r="374" spans="2:6">
+      <c r="G373" s="13"/>
+    </row>
+    <row r="374" spans="2:7">
       <c r="B374" s="4" t="s">
         <v>137</v>
       </c>
@@ -6464,8 +7293,9 @@
       </c>
       <c r="E374" s="13"/>
       <c r="F374" s="13"/>
-    </row>
-    <row r="375" spans="2:6">
+      <c r="G374" s="13"/>
+    </row>
+    <row r="375" spans="2:7">
       <c r="B375" s="4" t="s">
         <v>138</v>
       </c>
@@ -6477,191 +7307,218 @@
       </c>
       <c r="E375" s="13"/>
       <c r="F375" s="13"/>
-    </row>
-    <row r="376" spans="2:6">
+      <c r="G375" s="13"/>
+    </row>
+    <row r="376" spans="2:7">
       <c r="B376" s="4"/>
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
       <c r="E376" s="13"/>
       <c r="F376" s="13"/>
-    </row>
-    <row r="377" spans="2:6">
+      <c r="G376" s="13"/>
+    </row>
+    <row r="377" spans="2:7">
       <c r="B377" s="4"/>
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
       <c r="E377" s="13"/>
       <c r="F377" s="13"/>
-    </row>
-    <row r="378" spans="2:6">
+      <c r="G377" s="13"/>
+    </row>
+    <row r="378" spans="2:7">
       <c r="B378" s="4"/>
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
       <c r="E378" s="13"/>
       <c r="F378" s="13"/>
-    </row>
-    <row r="379" spans="2:6">
+      <c r="G378" s="13"/>
+    </row>
+    <row r="379" spans="2:7">
       <c r="B379" s="4"/>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
       <c r="E379" s="13"/>
       <c r="F379" s="13"/>
-    </row>
-    <row r="380" spans="2:6">
+      <c r="G379" s="13"/>
+    </row>
+    <row r="380" spans="2:7">
       <c r="B380" s="4"/>
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
       <c r="E380" s="13"/>
       <c r="F380" s="13"/>
-    </row>
-    <row r="381" spans="2:6">
+      <c r="G380" s="13"/>
+    </row>
+    <row r="381" spans="2:7">
       <c r="B381" s="4"/>
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
       <c r="E381" s="13"/>
       <c r="F381" s="13"/>
-    </row>
-    <row r="382" spans="2:6">
+      <c r="G381" s="13"/>
+    </row>
+    <row r="382" spans="2:7">
       <c r="B382" s="4"/>
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
       <c r="E382" s="13"/>
       <c r="F382" s="13"/>
-    </row>
-    <row r="383" spans="2:6">
+      <c r="G382" s="13"/>
+    </row>
+    <row r="383" spans="2:7">
       <c r="B383" s="4"/>
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
       <c r="E383" s="13"/>
       <c r="F383" s="13"/>
-    </row>
-    <row r="384" spans="2:6">
+      <c r="G383" s="13"/>
+    </row>
+    <row r="384" spans="2:7">
       <c r="B384" s="4"/>
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
       <c r="E384" s="13"/>
       <c r="F384" s="13"/>
-    </row>
-    <row r="385" spans="2:6">
+      <c r="G384" s="13"/>
+    </row>
+    <row r="385" spans="2:7">
       <c r="B385" s="4"/>
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
       <c r="E385" s="13"/>
       <c r="F385" s="13"/>
-    </row>
-    <row r="386" spans="2:6">
+      <c r="G385" s="13"/>
+    </row>
+    <row r="386" spans="2:7">
       <c r="B386" s="4"/>
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
       <c r="E386" s="13"/>
       <c r="F386" s="13"/>
-    </row>
-    <row r="387" spans="2:6">
+      <c r="G386" s="13"/>
+    </row>
+    <row r="387" spans="2:7">
       <c r="B387" s="4"/>
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
       <c r="E387" s="13"/>
       <c r="F387" s="13"/>
-    </row>
-    <row r="388" spans="2:6">
+      <c r="G387" s="13"/>
+    </row>
+    <row r="388" spans="2:7">
       <c r="B388" s="4"/>
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
       <c r="E388" s="13"/>
       <c r="F388" s="13"/>
-    </row>
-    <row r="389" spans="2:6">
+      <c r="G388" s="13"/>
+    </row>
+    <row r="389" spans="2:7">
       <c r="B389" s="4"/>
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
       <c r="E389" s="13"/>
       <c r="F389" s="13"/>
-    </row>
-    <row r="390" spans="2:6">
+      <c r="G389" s="13"/>
+    </row>
+    <row r="390" spans="2:7">
       <c r="B390" s="4"/>
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
       <c r="E390" s="13"/>
       <c r="F390" s="13"/>
-    </row>
-    <row r="391" spans="2:6">
+      <c r="G390" s="13"/>
+    </row>
+    <row r="391" spans="2:7">
       <c r="B391" s="4"/>
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
       <c r="E391" s="13"/>
       <c r="F391" s="13"/>
-    </row>
-    <row r="392" spans="2:6">
+      <c r="G391" s="13"/>
+    </row>
+    <row r="392" spans="2:7">
       <c r="B392" s="4"/>
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
       <c r="E392" s="13"/>
       <c r="F392" s="13"/>
-    </row>
-    <row r="393" spans="2:6">
+      <c r="G392" s="13"/>
+    </row>
+    <row r="393" spans="2:7">
       <c r="B393" s="4"/>
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
       <c r="E393" s="13"/>
       <c r="F393" s="13"/>
-    </row>
-    <row r="394" spans="2:6">
+      <c r="G393" s="13"/>
+    </row>
+    <row r="394" spans="2:7">
       <c r="B394" s="4"/>
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
       <c r="E394" s="13"/>
       <c r="F394" s="13"/>
-    </row>
-    <row r="395" spans="2:6">
+      <c r="G394" s="13"/>
+    </row>
+    <row r="395" spans="2:7">
       <c r="B395" s="4"/>
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
       <c r="E395" s="13"/>
       <c r="F395" s="13"/>
-    </row>
-    <row r="396" spans="2:6">
+      <c r="G395" s="13"/>
+    </row>
+    <row r="396" spans="2:7">
       <c r="B396" s="4"/>
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
       <c r="E396" s="13"/>
       <c r="F396" s="13"/>
-    </row>
-    <row r="397" spans="2:6">
+      <c r="G396" s="13"/>
+    </row>
+    <row r="397" spans="2:7">
       <c r="B397" s="9"/>
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
       <c r="E397" s="13"/>
       <c r="F397" s="13"/>
-    </row>
-    <row r="398" spans="2:6">
+      <c r="G397" s="13"/>
+    </row>
+    <row r="398" spans="2:7">
       <c r="B398" s="9"/>
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
       <c r="E398" s="13"/>
       <c r="F398" s="13"/>
-    </row>
-    <row r="399" spans="2:6">
+      <c r="G398" s="13"/>
+    </row>
+    <row r="399" spans="2:7">
       <c r="B399" s="9"/>
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
       <c r="E399" s="13"/>
       <c r="F399" s="13"/>
-    </row>
-    <row r="400" spans="2:6">
+      <c r="G399" s="13"/>
+    </row>
+    <row r="400" spans="2:7">
       <c r="B400" s="9"/>
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
       <c r="E400" s="13"/>
       <c r="F400" s="13"/>
-    </row>
-    <row r="401" spans="2:6">
+      <c r="G400" s="13"/>
+    </row>
+    <row r="401" spans="2:7">
       <c r="B401" s="4"/>
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
       <c r="E401" s="13"/>
       <c r="F401" s="13"/>
+      <c r="G401" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:F401" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}"/>
+  <autoFilter ref="E1:G401" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Arial"&amp;8&amp;K737373 Classified by Alfa Laval as: Business</oddFooter>

--- a/testBrew.xlsx
+++ b/testBrew.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Agentic World\TestDB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E2AAB84-AC99-4A8C-A5EB-F74211546327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F535A0A9-3B48-4134-A4A9-548BA04D1965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
+    <workbookView xWindow="585" yWindow="15" windowWidth="27870" windowHeight="16440" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -51,6 +51,7 @@
     <author>tc={E1E2F944-CF9F-4061-9330-99AC06440908}</author>
     <author>tc={F8073023-E3D6-437F-A368-4B60DA804058}</author>
     <author>tc={DA4D74A7-C735-4500-AC22-C9E4A5C304D0}</author>
+    <author>tc={72ED2E73-21B1-4D03-AEDB-85B3EA8C35E8}</author>
     <author>tc={FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}</author>
     <author>tc={C29E9803-A59F-4197-99DC-10131D1A8691}</author>
     <author>tc={F05B5C03-D80C-44EE-911F-FD4F08369CD1}</author>
@@ -104,6 +105,20 @@
       </text>
     </comment>
     <comment ref="G110" authorId="1" shapeId="0" xr:uid="{5C433F4A-7D9B-45D8-B24B-18AE78249403}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H110" authorId="1" shapeId="0" xr:uid="{D6A598F2-5142-4444-BCA7-F0CB1C4F6B7C}">
       <text>
         <r>
           <rPr>
@@ -193,6 +208,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="H130" authorId="1" shapeId="0" xr:uid="{6DA77B57-5F6A-4CD0-8E7A-6EAE748BAFB2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PCV220-1</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B132" authorId="4" shapeId="0" xr:uid="{330CC50C-0FF1-4C20-92A7-B1A460F72FE0}">
       <text>
         <r>
@@ -256,6 +285,20 @@
       </text>
     </comment>
     <comment ref="G139" authorId="1" shapeId="0" xr:uid="{DE12BDB5-71C1-4CAB-99EE-1B18B4AFE875}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ST741</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H139" authorId="1" shapeId="0" xr:uid="{6E31F1C5-7063-4F02-BBEA-7D50276E92A1}">
       <text>
         <r>
           <rPr>
@@ -345,6 +388,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="H212" authorId="1" shapeId="0" xr:uid="{3B6DE3E5-1411-44CF-B4D7-2C9B13130891}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>YT750</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="B214" authorId="8" shapeId="0" xr:uid="{932F2D4C-D793-48A0-8BED-5F38FC3D7DAF}">
       <text>
         <r>
@@ -377,6 +434,20 @@
       </text>
     </comment>
     <comment ref="G214" authorId="1" shapeId="0" xr:uid="{C45EBACB-06C0-4C27-B60E-9BCCFB34E699}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PT376-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H214" authorId="1" shapeId="0" xr:uid="{8DDAC368-25C5-440F-A8A5-CC0AC2E51B07}">
       <text>
         <r>
           <rPr>
@@ -437,7 +508,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="B223" authorId="12" shapeId="0" xr:uid="{FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}">
+    <comment ref="H218" authorId="12" shapeId="0" xr:uid="{FAD37F86-ED48-4D18-BA32-262C45C29066}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="MS Sans Serif"/>
+          </rPr>
+          <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Sensor: TT733</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B223" authorId="13" shapeId="0" xr:uid="{FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}">
       <text>
         <r>
           <rPr>
@@ -496,7 +581,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="B243" authorId="13" shapeId="0" xr:uid="{C29E9803-A59F-4197-99DC-10131D1A8691}">
+    <comment ref="H223" authorId="1" shapeId="0" xr:uid="{E3641417-7095-4B2A-951B-2A86224832D4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT410-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B243" authorId="14" shapeId="0" xr:uid="{C29E9803-A59F-4197-99DC-10131D1A8691}">
       <text>
         <r>
           <rPr>
@@ -512,7 +611,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B248" authorId="14" shapeId="0" xr:uid="{F05B5C03-D80C-44EE-911F-FD4F08369CD1}">
+    <comment ref="B248" authorId="15" shapeId="0" xr:uid="{F05B5C03-D80C-44EE-911F-FD4F08369CD1}">
       <text>
         <r>
           <rPr>
@@ -571,7 +670,21 @@
         </r>
       </text>
     </comment>
-    <comment ref="B252" authorId="15" shapeId="0" xr:uid="{6BE60107-F28C-41F1-A623-84DD5A6A045C}">
+    <comment ref="H248" authorId="1" shapeId="0" xr:uid="{66512256-8DA0-45B0-A1AC-DC3507E2A268}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>AV375-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B252" authorId="16" shapeId="0" xr:uid="{6BE60107-F28C-41F1-A623-84DD5A6A045C}">
       <text>
         <r>
           <rPr>
@@ -588,7 +701,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B253" authorId="16" shapeId="0" xr:uid="{573F35F3-86C4-417F-BDB5-9F88836E09BB}">
+    <comment ref="B253" authorId="17" shapeId="0" xr:uid="{573F35F3-86C4-417F-BDB5-9F88836E09BB}">
       <text>
         <r>
           <rPr>
@@ -647,6 +760,20 @@
         </r>
       </text>
     </comment>
+    <comment ref="H253" authorId="1" shapeId="0" xr:uid="{ACAA1C35-1FC5-42CD-8B5D-94E43FB3E701}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>506c</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="E354" authorId="1" shapeId="0" xr:uid="{C0B47CE5-D73E-476B-A5B9-42559C542AEB}">
       <text>
         <r>
@@ -689,12 +816,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="H354" authorId="1" shapeId="0" xr:uid="{712E4485-1474-4A27-BA32-2C9EB831D78F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIT220-1</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="278">
   <si>
     <t>Tag Label</t>
   </si>
@@ -1525,6 +1666,9 @@
   </si>
   <si>
     <t>BREW 600</t>
+  </si>
+  <si>
+    <t>BREW 750H</t>
   </si>
 </sst>
 </file>
@@ -2227,17 +2371,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}">
-  <dimension ref="B2:G401"/>
+  <dimension ref="B2:H401"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="10.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="31.25" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.75" style="1" customWidth="1"/>
     <col min="5" max="6" width="2.25" style="10" customWidth="1"/>
-    <col min="7" max="7" width="2.875" style="10" customWidth="1"/>
+    <col min="7" max="8" width="2.875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" ht="49.5">
+    <row r="2" spans="2:8" ht="55.5">
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
@@ -2250,8 +2394,11 @@
       <c r="G2" s="11" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="3" spans="2:7">
+      <c r="H2" s="11" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2264,32 +2411,36 @@
       <c r="E3" s="12"/>
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
-    </row>
-    <row r="4" spans="2:7">
+      <c r="H3" s="12"/>
+    </row>
+    <row r="4" spans="2:8">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-    </row>
-    <row r="5" spans="2:7">
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5" spans="2:8">
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="14"/>
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="2:7">
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="2:8">
       <c r="B6" s="4"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
-    </row>
-    <row r="7" spans="2:7">
+      <c r="H6" s="13"/>
+    </row>
+    <row r="7" spans="2:8">
       <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
@@ -2306,8 +2457,11 @@
       <c r="G7" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="2:7">
+      <c r="H7" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8">
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
@@ -2324,8 +2478,11 @@
       <c r="G8" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="9" spans="2:7">
+      <c r="H8" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8">
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
@@ -2342,8 +2499,11 @@
       <c r="G9" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="10" spans="2:7">
+      <c r="H9" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -2356,8 +2516,9 @@
       <c r="E10" s="13"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
-    </row>
-    <row r="11" spans="2:7">
+      <c r="H10" s="13"/>
+    </row>
+    <row r="11" spans="2:8">
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
@@ -2374,8 +2535,11 @@
       <c r="G11" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="12" spans="2:7">
+      <c r="H11" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8">
       <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
@@ -2392,8 +2556,11 @@
       <c r="G12" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="13" spans="2:7">
+      <c r="H12" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8">
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
@@ -2410,8 +2577,11 @@
       <c r="G13" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="2:7">
+      <c r="H13" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="2:8">
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
@@ -2422,8 +2592,9 @@
       <c r="E14" s="13"/>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
-    </row>
-    <row r="15" spans="2:7">
+      <c r="H14" s="13"/>
+    </row>
+    <row r="15" spans="2:8">
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
@@ -2434,8 +2605,9 @@
       <c r="E15" s="13"/>
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
-    </row>
-    <row r="16" spans="2:7">
+      <c r="H15" s="13"/>
+    </row>
+    <row r="16" spans="2:8">
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
@@ -2452,8 +2624,11 @@
       <c r="G16" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="2:7">
+      <c r="H16" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8">
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
@@ -2470,8 +2645,11 @@
       <c r="G17" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="18" spans="2:7">
+      <c r="H17" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
@@ -2490,8 +2668,11 @@
       <c r="G18" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="19" spans="2:7">
+      <c r="H18" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
@@ -2502,8 +2683,9 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-    </row>
-    <row r="20" spans="2:7">
+      <c r="H19" s="13"/>
+    </row>
+    <row r="20" spans="2:8">
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
@@ -2514,8 +2696,9 @@
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
-    </row>
-    <row r="21" spans="2:7">
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" spans="2:8">
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
@@ -2526,8 +2709,9 @@
       <c r="E21" s="13"/>
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
-    </row>
-    <row r="22" spans="2:7">
+      <c r="H21" s="13"/>
+    </row>
+    <row r="22" spans="2:8">
       <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
@@ -2546,16 +2730,20 @@
       <c r="G22" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="23" spans="2:7">
+      <c r="H22" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="2:8">
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="13"/>
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
-    </row>
-    <row r="24" spans="2:7">
+      <c r="H23" s="13"/>
+    </row>
+    <row r="24" spans="2:8">
       <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
@@ -2572,8 +2760,11 @@
       <c r="G24" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="25" spans="2:7">
+      <c r="H24" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8">
       <c r="B25" s="6" t="s">
         <v>13</v>
       </c>
@@ -2590,8 +2781,11 @@
       <c r="G25" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="26" spans="2:7">
+      <c r="H25" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8">
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
@@ -2610,8 +2804,11 @@
       <c r="G26" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="27" spans="2:7">
+      <c r="H26" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8">
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
@@ -2630,8 +2827,11 @@
       <c r="G27" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="28" spans="2:7">
+      <c r="H27" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="2:8">
       <c r="B28" s="6" t="s">
         <v>15</v>
       </c>
@@ -2650,8 +2850,11 @@
       <c r="G28" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="29" spans="2:7">
+      <c r="H28" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8">
       <c r="B29" s="6" t="s">
         <v>15</v>
       </c>
@@ -2670,8 +2873,11 @@
       <c r="G29" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="30" spans="2:7">
+      <c r="H29" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
       <c r="B30" s="6" t="s">
         <v>16</v>
       </c>
@@ -2688,8 +2894,11 @@
       <c r="G30" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="31" spans="2:7">
+      <c r="H30" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
       <c r="B31" s="6" t="s">
         <v>16</v>
       </c>
@@ -2706,8 +2915,11 @@
       <c r="G31" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="32" spans="2:7">
+      <c r="H31" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
       <c r="B32" s="6" t="s">
         <v>17</v>
       </c>
@@ -2724,8 +2936,11 @@
       <c r="G32" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="2:7">
+      <c r="H32" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
       <c r="B33" s="6" t="s">
         <v>17</v>
       </c>
@@ -2742,8 +2957,11 @@
       <c r="G33" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="34" spans="2:7">
+      <c r="H33" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
       <c r="B34" s="6" t="s">
         <v>18</v>
       </c>
@@ -2756,8 +2974,9 @@
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
-    </row>
-    <row r="35" spans="2:7">
+      <c r="H34" s="13"/>
+    </row>
+    <row r="35" spans="2:8">
       <c r="B35" s="6" t="s">
         <v>18</v>
       </c>
@@ -2770,8 +2989,9 @@
       <c r="E35" s="13"/>
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
-    </row>
-    <row r="36" spans="2:7">
+      <c r="H35" s="13"/>
+    </row>
+    <row r="36" spans="2:8">
       <c r="B36" s="6" t="s">
         <v>19</v>
       </c>
@@ -2788,8 +3008,11 @@
       <c r="G36" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="37" spans="2:7">
+      <c r="H36" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8">
       <c r="B37" s="7" t="s">
         <v>19</v>
       </c>
@@ -2806,8 +3029,11 @@
       <c r="G37" s="15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="38" spans="2:7">
+      <c r="H37" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8">
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
@@ -2818,8 +3044,9 @@
       <c r="E38" s="13"/>
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
-    </row>
-    <row r="39" spans="2:7">
+      <c r="H38" s="13"/>
+    </row>
+    <row r="39" spans="2:8">
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
@@ -2830,16 +3057,18 @@
       <c r="E39" s="13"/>
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
-    </row>
-    <row r="40" spans="2:7">
+      <c r="H39" s="13"/>
+    </row>
+    <row r="40" spans="2:8">
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
-    </row>
-    <row r="41" spans="2:7">
+      <c r="H40" s="13"/>
+    </row>
+    <row r="41" spans="2:8">
       <c r="B41" s="7" t="s">
         <v>20</v>
       </c>
@@ -2856,8 +3085,11 @@
       <c r="G41" s="15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="42" spans="2:7">
+      <c r="H41" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="2:8">
       <c r="B42" s="6" t="s">
         <v>20</v>
       </c>
@@ -2874,8 +3106,11 @@
       <c r="G42" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="2:7">
+      <c r="H42" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8">
       <c r="B43" s="6" t="s">
         <v>21</v>
       </c>
@@ -2892,8 +3127,11 @@
       <c r="G43" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="44" spans="2:7">
+      <c r="H43" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8">
       <c r="B44" s="6" t="s">
         <v>21</v>
       </c>
@@ -2910,8 +3148,11 @@
       <c r="G44" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="45" spans="2:7">
+      <c r="H44" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8">
       <c r="B45" s="6" t="s">
         <v>22</v>
       </c>
@@ -2928,8 +3169,11 @@
       <c r="G45" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="46" spans="2:7">
+      <c r="H45" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8">
       <c r="B46" s="6" t="s">
         <v>22</v>
       </c>
@@ -2946,8 +3190,11 @@
       <c r="G46" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="47" spans="2:7">
+      <c r="H46" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8">
       <c r="B47" s="6" t="s">
         <v>23</v>
       </c>
@@ -2964,8 +3211,11 @@
       <c r="G47" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="48" spans="2:7">
+      <c r="H47" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8">
       <c r="B48" s="6" t="s">
         <v>23</v>
       </c>
@@ -2982,8 +3232,11 @@
       <c r="G48" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="49" spans="2:7">
+      <c r="H48" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8">
       <c r="B49" s="6" t="s">
         <v>24</v>
       </c>
@@ -3000,8 +3253,11 @@
       <c r="G49" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="50" spans="2:7">
+      <c r="H49" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8">
       <c r="B50" s="6" t="s">
         <v>24</v>
       </c>
@@ -3018,8 +3274,11 @@
       <c r="G50" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" spans="2:7">
+      <c r="H50" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8">
       <c r="B51" s="6" t="s">
         <v>25</v>
       </c>
@@ -3036,8 +3295,11 @@
       <c r="G51" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="52" spans="2:7">
+      <c r="H51" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8">
       <c r="B52" s="6" t="s">
         <v>25</v>
       </c>
@@ -3054,8 +3316,11 @@
       <c r="G52" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="53" spans="2:7">
+      <c r="H52" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8">
       <c r="B53" s="6" t="s">
         <v>26</v>
       </c>
@@ -3070,8 +3335,11 @@
       <c r="G53" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="54" spans="2:7">
+      <c r="H53" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8">
       <c r="B54" s="6" t="s">
         <v>26</v>
       </c>
@@ -3086,8 +3354,11 @@
       <c r="G54" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="55" spans="2:7">
+      <c r="H54" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8">
       <c r="B55" s="5" t="s">
         <v>8</v>
       </c>
@@ -3098,8 +3369,9 @@
       <c r="E55" s="13"/>
       <c r="F55" s="13"/>
       <c r="G55" s="13"/>
-    </row>
-    <row r="56" spans="2:7">
+      <c r="H55" s="13"/>
+    </row>
+    <row r="56" spans="2:8">
       <c r="B56" s="5" t="s">
         <v>8</v>
       </c>
@@ -3110,16 +3382,18 @@
       <c r="E56" s="13"/>
       <c r="F56" s="13"/>
       <c r="G56" s="13"/>
-    </row>
-    <row r="57" spans="2:7">
+      <c r="H56" s="13"/>
+    </row>
+    <row r="57" spans="2:8">
       <c r="B57" s="6"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="13"/>
       <c r="F57" s="13"/>
       <c r="G57" s="13"/>
-    </row>
-    <row r="58" spans="2:7">
+      <c r="H57" s="13"/>
+    </row>
+    <row r="58" spans="2:8">
       <c r="B58" s="6" t="s">
         <v>27</v>
       </c>
@@ -3136,8 +3410,11 @@
       <c r="G58" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="59" spans="2:7">
+      <c r="H58" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="2:8">
       <c r="B59" s="6" t="s">
         <v>27</v>
       </c>
@@ -3154,8 +3431,11 @@
       <c r="G59" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="60" spans="2:7">
+      <c r="H59" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="2:8">
       <c r="B60" s="5" t="s">
         <v>8</v>
       </c>
@@ -3166,8 +3446,9 @@
       <c r="E60" s="13"/>
       <c r="F60" s="13"/>
       <c r="G60" s="13"/>
-    </row>
-    <row r="61" spans="2:7">
+      <c r="H60" s="13"/>
+    </row>
+    <row r="61" spans="2:8">
       <c r="B61" s="5" t="s">
         <v>8</v>
       </c>
@@ -3178,8 +3459,9 @@
       <c r="E61" s="13"/>
       <c r="F61" s="13"/>
       <c r="G61" s="13"/>
-    </row>
-    <row r="62" spans="2:7">
+      <c r="H61" s="13"/>
+    </row>
+    <row r="62" spans="2:8">
       <c r="B62" s="6" t="s">
         <v>28</v>
       </c>
@@ -3196,8 +3478,11 @@
       <c r="G62" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="63" spans="2:7">
+      <c r="H62" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" spans="2:8">
       <c r="B63" s="6" t="s">
         <v>28</v>
       </c>
@@ -3214,8 +3499,11 @@
       <c r="G63" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="64" spans="2:7">
+      <c r="H63" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8">
       <c r="B64" s="6" t="s">
         <v>29</v>
       </c>
@@ -3232,8 +3520,11 @@
       <c r="G64" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="65" spans="2:7">
+      <c r="H64" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8">
       <c r="B65" s="6" t="s">
         <v>29</v>
       </c>
@@ -3250,8 +3541,11 @@
       <c r="G65" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="66" spans="2:7">
+      <c r="H65" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8">
       <c r="B66" s="6" t="s">
         <v>30</v>
       </c>
@@ -3264,8 +3558,9 @@
       <c r="E66" s="13"/>
       <c r="F66" s="13"/>
       <c r="G66" s="13"/>
-    </row>
-    <row r="67" spans="2:7">
+      <c r="H66" s="13"/>
+    </row>
+    <row r="67" spans="2:8">
       <c r="B67" s="6" t="s">
         <v>30</v>
       </c>
@@ -3278,8 +3573,9 @@
       <c r="E67" s="13"/>
       <c r="F67" s="13"/>
       <c r="G67" s="13"/>
-    </row>
-    <row r="68" spans="2:7">
+      <c r="H67" s="13"/>
+    </row>
+    <row r="68" spans="2:8">
       <c r="B68" s="5" t="s">
         <v>8</v>
       </c>
@@ -3290,8 +3586,9 @@
       <c r="E68" s="13"/>
       <c r="F68" s="13"/>
       <c r="G68" s="13"/>
-    </row>
-    <row r="69" spans="2:7">
+      <c r="H68" s="13"/>
+    </row>
+    <row r="69" spans="2:8">
       <c r="B69" s="5" t="s">
         <v>8</v>
       </c>
@@ -3302,8 +3599,9 @@
       <c r="E69" s="13"/>
       <c r="F69" s="13"/>
       <c r="G69" s="13"/>
-    </row>
-    <row r="70" spans="2:7">
+      <c r="H69" s="13"/>
+    </row>
+    <row r="70" spans="2:8">
       <c r="B70" s="5" t="s">
         <v>8</v>
       </c>
@@ -3314,8 +3612,9 @@
       <c r="E70" s="13"/>
       <c r="F70" s="13"/>
       <c r="G70" s="13"/>
-    </row>
-    <row r="71" spans="2:7">
+      <c r="H70" s="13"/>
+    </row>
+    <row r="71" spans="2:8">
       <c r="B71" s="5" t="s">
         <v>8</v>
       </c>
@@ -3326,8 +3625,9 @@
       <c r="E71" s="13"/>
       <c r="F71" s="13"/>
       <c r="G71" s="13"/>
-    </row>
-    <row r="72" spans="2:7">
+      <c r="H71" s="13"/>
+    </row>
+    <row r="72" spans="2:8">
       <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
@@ -3338,8 +3638,9 @@
       <c r="E72" s="13"/>
       <c r="F72" s="13"/>
       <c r="G72" s="13"/>
-    </row>
-    <row r="73" spans="2:7">
+      <c r="H72" s="13"/>
+    </row>
+    <row r="73" spans="2:8">
       <c r="B73" s="5" t="s">
         <v>8</v>
       </c>
@@ -3350,16 +3651,18 @@
       <c r="E73" s="13"/>
       <c r="F73" s="13"/>
       <c r="G73" s="13"/>
-    </row>
-    <row r="74" spans="2:7">
+      <c r="H73" s="13"/>
+    </row>
+    <row r="74" spans="2:8">
       <c r="B74" s="6"/>
       <c r="C74" s="3"/>
       <c r="D74" s="20"/>
       <c r="E74" s="13"/>
       <c r="F74" s="13"/>
       <c r="G74" s="13"/>
-    </row>
-    <row r="75" spans="2:7">
+      <c r="H74" s="13"/>
+    </row>
+    <row r="75" spans="2:8">
       <c r="B75" s="6" t="s">
         <v>13</v>
       </c>
@@ -3376,8 +3679,11 @@
       <c r="G75" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="76" spans="2:7">
+      <c r="H75" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="2:8">
       <c r="B76" s="6" t="s">
         <v>14</v>
       </c>
@@ -3396,8 +3702,11 @@
       <c r="G76" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="77" spans="2:7">
+      <c r="H76" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="2:8">
       <c r="B77" s="6" t="s">
         <v>15</v>
       </c>
@@ -3416,8 +3725,11 @@
       <c r="G77" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="78" spans="2:7">
+      <c r="H77" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="2:8">
       <c r="B78" s="6" t="s">
         <v>16</v>
       </c>
@@ -3434,8 +3746,11 @@
       <c r="G78" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="79" spans="2:7">
+      <c r="H78" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
       <c r="B79" s="6" t="s">
         <v>17</v>
       </c>
@@ -3452,8 +3767,11 @@
       <c r="G79" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="80" spans="2:7">
+      <c r="H79" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="2:8">
       <c r="B80" s="6" t="s">
         <v>18</v>
       </c>
@@ -3466,8 +3784,9 @@
       <c r="E80" s="13"/>
       <c r="F80" s="13"/>
       <c r="G80" s="13"/>
-    </row>
-    <row r="81" spans="2:7">
+      <c r="H80" s="13"/>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="6" t="s">
         <v>19</v>
       </c>
@@ -3484,8 +3803,11 @@
       <c r="G81" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="82" spans="2:7">
+      <c r="H81" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8">
       <c r="B82" s="5" t="s">
         <v>8</v>
       </c>
@@ -3496,8 +3818,9 @@
       <c r="E82" s="13"/>
       <c r="F82" s="13"/>
       <c r="G82" s="13"/>
-    </row>
-    <row r="83" spans="2:7">
+      <c r="H82" s="13"/>
+    </row>
+    <row r="83" spans="2:8">
       <c r="B83" s="6" t="s">
         <v>20</v>
       </c>
@@ -3514,8 +3837,11 @@
       <c r="G83" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="84" spans="2:7">
+      <c r="H83" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="B84" s="6" t="s">
         <v>21</v>
       </c>
@@ -3532,8 +3858,11 @@
       <c r="G84" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="85" spans="2:7">
+      <c r="H84" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="85" spans="2:8">
       <c r="B85" s="6" t="s">
         <v>22</v>
       </c>
@@ -3550,8 +3879,11 @@
       <c r="G85" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="86" spans="2:7">
+      <c r="H85" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
       <c r="B86" s="6" t="s">
         <v>23</v>
       </c>
@@ -3568,8 +3900,11 @@
       <c r="G86" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="87" spans="2:7">
+      <c r="H86" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="87" spans="2:8">
       <c r="B87" s="6" t="s">
         <v>24</v>
       </c>
@@ -3586,8 +3921,11 @@
       <c r="G87" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="88" spans="2:7">
+      <c r="H87" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="6" t="s">
         <v>25</v>
       </c>
@@ -3604,8 +3942,11 @@
       <c r="G88" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="89" spans="2:7">
+      <c r="H88" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="89" spans="2:8">
       <c r="B89" s="6" t="s">
         <v>26</v>
       </c>
@@ -3620,8 +3961,11 @@
       <c r="G89" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="90" spans="2:7">
+      <c r="H89" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="90" spans="2:8">
       <c r="B90" s="5" t="s">
         <v>8</v>
       </c>
@@ -3632,16 +3976,18 @@
       <c r="E90" s="13"/>
       <c r="F90" s="13"/>
       <c r="G90" s="13"/>
-    </row>
-    <row r="91" spans="2:7">
+      <c r="H90" s="13"/>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="6"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="13"/>
       <c r="F91" s="13"/>
       <c r="G91" s="13"/>
-    </row>
-    <row r="92" spans="2:7">
+      <c r="H91" s="13"/>
+    </row>
+    <row r="92" spans="2:8">
       <c r="B92" s="6" t="s">
         <v>27</v>
       </c>
@@ -3658,8 +4004,11 @@
       <c r="G92" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="93" spans="2:7">
+      <c r="H92" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="93" spans="2:8">
       <c r="B93" s="5" t="s">
         <v>8</v>
       </c>
@@ -3672,8 +4021,9 @@
       <c r="E93" s="13"/>
       <c r="F93" s="13"/>
       <c r="G93" s="13"/>
-    </row>
-    <row r="94" spans="2:7">
+      <c r="H93" s="13"/>
+    </row>
+    <row r="94" spans="2:8">
       <c r="B94" s="6" t="s">
         <v>28</v>
       </c>
@@ -3690,8 +4040,11 @@
       <c r="G94" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="95" spans="2:7">
+      <c r="H94" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8">
       <c r="B95" s="6" t="s">
         <v>29</v>
       </c>
@@ -3708,8 +4061,11 @@
       <c r="G95" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="96" spans="2:7">
+      <c r="H95" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8">
       <c r="B96" s="6" t="s">
         <v>30</v>
       </c>
@@ -3722,8 +4078,9 @@
       <c r="E96" s="13"/>
       <c r="F96" s="13"/>
       <c r="G96" s="13"/>
-    </row>
-    <row r="97" spans="2:7">
+      <c r="H96" s="13"/>
+    </row>
+    <row r="97" spans="2:8">
       <c r="B97" s="5" t="s">
         <v>8</v>
       </c>
@@ -3734,8 +4091,9 @@
       <c r="E97" s="13"/>
       <c r="F97" s="13"/>
       <c r="G97" s="13"/>
-    </row>
-    <row r="98" spans="2:7">
+      <c r="H97" s="13"/>
+    </row>
+    <row r="98" spans="2:8">
       <c r="B98" s="5" t="s">
         <v>8</v>
       </c>
@@ -3746,8 +4104,9 @@
       <c r="E98" s="13"/>
       <c r="F98" s="13"/>
       <c r="G98" s="13"/>
-    </row>
-    <row r="99" spans="2:7">
+      <c r="H98" s="13"/>
+    </row>
+    <row r="99" spans="2:8">
       <c r="B99" s="5" t="s">
         <v>8</v>
       </c>
@@ -3758,8 +4117,9 @@
       <c r="E99" s="13"/>
       <c r="F99" s="13"/>
       <c r="G99" s="13"/>
-    </row>
-    <row r="100" spans="2:7">
+      <c r="H99" s="13"/>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
@@ -3770,8 +4130,9 @@
       <c r="E100" s="13"/>
       <c r="F100" s="13"/>
       <c r="G100" s="13"/>
-    </row>
-    <row r="101" spans="2:7">
+      <c r="H100" s="13"/>
+    </row>
+    <row r="101" spans="2:8">
       <c r="B101" s="4" t="s">
         <v>31</v>
       </c>
@@ -3788,8 +4149,11 @@
       <c r="G101" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="102" spans="2:7">
+      <c r="H101" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" spans="2:8">
       <c r="B102" s="8" t="s">
         <v>32</v>
       </c>
@@ -3806,8 +4170,11 @@
       <c r="G102" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="103" spans="2:7">
+      <c r="H102" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
       <c r="B103" s="4" t="s">
         <v>33</v>
       </c>
@@ -3824,8 +4191,11 @@
       <c r="G103" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="104" spans="2:7">
+      <c r="H103" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="104" spans="2:8">
       <c r="B104" s="4" t="s">
         <v>34</v>
       </c>
@@ -3842,8 +4212,11 @@
       <c r="G104" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="105" spans="2:7">
+      <c r="H104" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8">
       <c r="B105" s="4" t="s">
         <v>35</v>
       </c>
@@ -3860,8 +4233,11 @@
       <c r="G105" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="106" spans="2:7">
+      <c r="H105" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="4" t="s">
         <v>36</v>
       </c>
@@ -3878,8 +4254,11 @@
       <c r="G106" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="107" spans="2:7">
+      <c r="H106" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="107" spans="2:8">
       <c r="B107" s="4" t="s">
         <v>37</v>
       </c>
@@ -3890,16 +4269,18 @@
       <c r="E107" s="13"/>
       <c r="F107" s="13"/>
       <c r="G107" s="13"/>
-    </row>
-    <row r="108" spans="2:7">
+      <c r="H107" s="13"/>
+    </row>
+    <row r="108" spans="2:8">
       <c r="B108" s="4"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="13"/>
       <c r="F108" s="13"/>
       <c r="G108" s="13"/>
-    </row>
-    <row r="109" spans="2:7">
+      <c r="H108" s="13"/>
+    </row>
+    <row r="109" spans="2:8">
       <c r="B109" s="4" t="s">
         <v>38</v>
       </c>
@@ -3916,8 +4297,11 @@
       <c r="G109" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="110" spans="2:7">
+      <c r="H109" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="2:8">
       <c r="B110" s="4" t="s">
         <v>39</v>
       </c>
@@ -3934,8 +4318,11 @@
       <c r="G110" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="111" spans="2:7">
+      <c r="H110" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="111" spans="2:8">
       <c r="B111" s="4" t="s">
         <v>40</v>
       </c>
@@ -3952,8 +4339,11 @@
       <c r="G111" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="112" spans="2:7">
+      <c r="H111" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="2:8">
       <c r="B112" s="4" t="s">
         <v>41</v>
       </c>
@@ -3970,16 +4360,20 @@
       <c r="G112" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="113" spans="2:7">
+      <c r="H112" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="113" spans="2:8">
       <c r="B113" s="4"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="13"/>
       <c r="F113" s="13"/>
       <c r="G113" s="13"/>
-    </row>
-    <row r="114" spans="2:7">
+      <c r="H113" s="13"/>
+    </row>
+    <row r="114" spans="2:8">
       <c r="B114" s="4" t="s">
         <v>42</v>
       </c>
@@ -3998,8 +4392,11 @@
       <c r="G114" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="115" spans="2:7">
+      <c r="H114" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8">
       <c r="B115" s="5" t="s">
         <v>8</v>
       </c>
@@ -4010,8 +4407,9 @@
       <c r="E115" s="13"/>
       <c r="F115" s="13"/>
       <c r="G115" s="13"/>
-    </row>
-    <row r="116" spans="2:7">
+      <c r="H115" s="13"/>
+    </row>
+    <row r="116" spans="2:8">
       <c r="B116" s="4" t="s">
         <v>43</v>
       </c>
@@ -4024,8 +4422,9 @@
       <c r="E116" s="13"/>
       <c r="F116" s="13"/>
       <c r="G116" s="13"/>
-    </row>
-    <row r="117" spans="2:7">
+      <c r="H116" s="13"/>
+    </row>
+    <row r="117" spans="2:8">
       <c r="B117" s="4" t="s">
         <v>44</v>
       </c>
@@ -4036,16 +4435,18 @@
       <c r="E117" s="13"/>
       <c r="F117" s="13"/>
       <c r="G117" s="13"/>
-    </row>
-    <row r="118" spans="2:7">
+      <c r="H117" s="13"/>
+    </row>
+    <row r="118" spans="2:8">
       <c r="B118" s="4"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="13"/>
       <c r="F118" s="13"/>
       <c r="G118" s="13"/>
-    </row>
-    <row r="119" spans="2:7">
+      <c r="H118" s="13"/>
+    </row>
+    <row r="119" spans="2:8">
       <c r="B119" s="4" t="s">
         <v>45</v>
       </c>
@@ -4062,8 +4463,11 @@
       <c r="G119" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="120" spans="2:7">
+      <c r="H119" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="2:8">
       <c r="B120" s="4" t="s">
         <v>46</v>
       </c>
@@ -4080,8 +4484,11 @@
       <c r="G120" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="121" spans="2:7">
+      <c r="H120" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="121" spans="2:8">
       <c r="B121" s="4" t="s">
         <v>47</v>
       </c>
@@ -4098,8 +4505,11 @@
       <c r="G121" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="122" spans="2:7">
+      <c r="H121" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="122" spans="2:8">
       <c r="B122" s="4" t="s">
         <v>48</v>
       </c>
@@ -4118,16 +4528,20 @@
       <c r="G122" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="123" spans="2:7">
+      <c r="H122" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123" spans="2:8">
       <c r="B123" s="4"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="13"/>
       <c r="F123" s="13"/>
       <c r="G123" s="13"/>
-    </row>
-    <row r="124" spans="2:7">
+      <c r="H123" s="13"/>
+    </row>
+    <row r="124" spans="2:8">
       <c r="B124" s="4" t="s">
         <v>49</v>
       </c>
@@ -4138,8 +4552,9 @@
       <c r="E124" s="13"/>
       <c r="F124" s="13"/>
       <c r="G124" s="13"/>
-    </row>
-    <row r="125" spans="2:7">
+      <c r="H124" s="13"/>
+    </row>
+    <row r="125" spans="2:8">
       <c r="B125" s="4" t="s">
         <v>50</v>
       </c>
@@ -4152,8 +4567,9 @@
       <c r="E125" s="13"/>
       <c r="F125" s="13"/>
       <c r="G125" s="13"/>
-    </row>
-    <row r="126" spans="2:7">
+      <c r="H125" s="13"/>
+    </row>
+    <row r="126" spans="2:8">
       <c r="B126" s="4" t="s">
         <v>51</v>
       </c>
@@ -4172,8 +4588,11 @@
       <c r="G126" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="127" spans="2:7">
+      <c r="H126" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" spans="2:8">
       <c r="B127" s="5" t="s">
         <v>8</v>
       </c>
@@ -4184,16 +4603,18 @@
       <c r="E127" s="13"/>
       <c r="F127" s="13"/>
       <c r="G127" s="13"/>
-    </row>
-    <row r="128" spans="2:7">
+      <c r="H127" s="13"/>
+    </row>
+    <row r="128" spans="2:8">
       <c r="B128" s="4"/>
       <c r="C128" s="3"/>
       <c r="D128" s="19"/>
       <c r="E128" s="13"/>
       <c r="F128" s="13"/>
       <c r="G128" s="13"/>
-    </row>
-    <row r="129" spans="2:7">
+      <c r="H128" s="13"/>
+    </row>
+    <row r="129" spans="2:8">
       <c r="B129" s="4" t="s">
         <v>52</v>
       </c>
@@ -4210,8 +4631,11 @@
       <c r="G129" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="130" spans="2:7">
+      <c r="H129" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130" spans="2:8">
       <c r="B130" s="4" t="s">
         <v>53</v>
       </c>
@@ -4228,8 +4652,11 @@
       <c r="G130" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="131" spans="2:7">
+      <c r="H130" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="131" spans="2:8">
       <c r="B131" s="4" t="s">
         <v>54</v>
       </c>
@@ -4246,8 +4673,11 @@
       <c r="G131" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="132" spans="2:7">
+      <c r="H131" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="132" spans="2:8">
       <c r="B132" s="4" t="s">
         <v>55</v>
       </c>
@@ -4258,16 +4688,18 @@
       <c r="E132" s="13"/>
       <c r="F132" s="13"/>
       <c r="G132" s="13"/>
-    </row>
-    <row r="133" spans="2:7">
+      <c r="H132" s="13"/>
+    </row>
+    <row r="133" spans="2:8">
       <c r="B133" s="4"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="13"/>
       <c r="F133" s="13"/>
       <c r="G133" s="13"/>
-    </row>
-    <row r="134" spans="2:7">
+      <c r="H133" s="13"/>
+    </row>
+    <row r="134" spans="2:8">
       <c r="B134" s="4" t="s">
         <v>56</v>
       </c>
@@ -4286,8 +4718,11 @@
       <c r="G134" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="135" spans="2:7">
+      <c r="H134" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="135" spans="2:8">
       <c r="B135" s="4" t="s">
         <v>57</v>
       </c>
@@ -4306,8 +4741,11 @@
       <c r="G135" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="136" spans="2:7">
+      <c r="H135" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8">
       <c r="B136" s="4" t="s">
         <v>58</v>
       </c>
@@ -4326,8 +4764,11 @@
       <c r="G136" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="137" spans="2:7">
+      <c r="H136" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="137" spans="2:8">
       <c r="B137" s="4" t="s">
         <v>59</v>
       </c>
@@ -4346,16 +4787,20 @@
       <c r="G137" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="138" spans="2:7">
+      <c r="H137" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8">
       <c r="B138" s="4"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="13"/>
       <c r="F138" s="13"/>
       <c r="G138" s="13"/>
-    </row>
-    <row r="139" spans="2:7">
+      <c r="H138" s="13"/>
+    </row>
+    <row r="139" spans="2:8">
       <c r="B139" s="4" t="s">
         <v>60</v>
       </c>
@@ -4372,16 +4817,20 @@
       <c r="G139" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="140" spans="2:7">
+      <c r="H139" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="140" spans="2:8">
       <c r="B140" s="4"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="13"/>
       <c r="F140" s="13"/>
       <c r="G140" s="13"/>
-    </row>
-    <row r="141" spans="2:7">
+      <c r="H140" s="13"/>
+    </row>
+    <row r="141" spans="2:8">
       <c r="B141" s="4" t="s">
         <v>61</v>
       </c>
@@ -4394,16 +4843,18 @@
       <c r="E141" s="14"/>
       <c r="F141" s="14"/>
       <c r="G141" s="14"/>
-    </row>
-    <row r="142" spans="2:7">
+      <c r="H141" s="14"/>
+    </row>
+    <row r="142" spans="2:8">
       <c r="B142" s="4"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="13"/>
       <c r="F142" s="13"/>
       <c r="G142" s="13"/>
-    </row>
-    <row r="143" spans="2:7">
+      <c r="H142" s="13"/>
+    </row>
+    <row r="143" spans="2:8">
       <c r="B143" s="4" t="s">
         <v>62</v>
       </c>
@@ -4420,8 +4871,11 @@
       <c r="G143" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="144" spans="2:7">
+      <c r="H143" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="144" spans="2:8">
       <c r="B144" s="4" t="s">
         <v>63</v>
       </c>
@@ -4438,8 +4892,11 @@
       <c r="G144" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="145" spans="2:7">
+      <c r="H144" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="2:8">
       <c r="B145" s="4" t="s">
         <v>64</v>
       </c>
@@ -4456,8 +4913,11 @@
       <c r="G145" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="146" spans="2:7">
+      <c r="H145" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="146" spans="2:8">
       <c r="B146" s="4" t="s">
         <v>65</v>
       </c>
@@ -4474,8 +4934,11 @@
       <c r="G146" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="147" spans="2:7">
+      <c r="H146" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="147" spans="2:8">
       <c r="B147" s="4" t="s">
         <v>66</v>
       </c>
@@ -4492,8 +4955,11 @@
       <c r="G147" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="148" spans="2:7">
+      <c r="H147" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" spans="2:8">
       <c r="B148" s="4" t="s">
         <v>67</v>
       </c>
@@ -4510,8 +4976,11 @@
       <c r="G148" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="149" spans="2:7">
+      <c r="H148" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="149" spans="2:8">
       <c r="B149" s="4" t="s">
         <v>68</v>
       </c>
@@ -4530,8 +4999,11 @@
       <c r="G149" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="150" spans="2:7">
+      <c r="H149" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="150" spans="2:8">
       <c r="B150" s="4" t="s">
         <v>69</v>
       </c>
@@ -4544,8 +5016,9 @@
       <c r="E150" s="13"/>
       <c r="F150" s="13"/>
       <c r="G150" s="13"/>
-    </row>
-    <row r="151" spans="2:7">
+      <c r="H150" s="13"/>
+    </row>
+    <row r="151" spans="2:8">
       <c r="B151" s="4" t="s">
         <v>70</v>
       </c>
@@ -4558,8 +5031,9 @@
       <c r="E151" s="13"/>
       <c r="F151" s="13"/>
       <c r="G151" s="13"/>
-    </row>
-    <row r="152" spans="2:7">
+      <c r="H151" s="13"/>
+    </row>
+    <row r="152" spans="2:8">
       <c r="B152" s="5" t="s">
         <v>8</v>
       </c>
@@ -4570,8 +5044,9 @@
       <c r="E152" s="13"/>
       <c r="F152" s="13"/>
       <c r="G152" s="13"/>
-    </row>
-    <row r="153" spans="2:7">
+      <c r="H152" s="13"/>
+    </row>
+    <row r="153" spans="2:8">
       <c r="B153" s="4" t="s">
         <v>71</v>
       </c>
@@ -4588,8 +5063,11 @@
       <c r="G153" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="154" spans="2:7">
+      <c r="H153" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="154" spans="2:8">
       <c r="B154" s="4" t="s">
         <v>71</v>
       </c>
@@ -4606,8 +5084,11 @@
       <c r="G154" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="155" spans="2:7">
+      <c r="H154" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="2:8">
       <c r="B155" s="4" t="s">
         <v>72</v>
       </c>
@@ -4626,8 +5107,11 @@
       <c r="G155" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="156" spans="2:7">
+      <c r="H155" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="156" spans="2:8">
       <c r="B156" s="4" t="s">
         <v>72</v>
       </c>
@@ -4646,8 +5130,11 @@
       <c r="G156" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="157" spans="2:7">
+      <c r="H156" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="157" spans="2:8">
       <c r="B157" s="5" t="s">
         <v>8</v>
       </c>
@@ -4658,8 +5145,9 @@
       <c r="E157" s="13"/>
       <c r="F157" s="13"/>
       <c r="G157" s="13"/>
-    </row>
-    <row r="158" spans="2:7">
+      <c r="H157" s="13"/>
+    </row>
+    <row r="158" spans="2:8">
       <c r="B158" s="5" t="s">
         <v>8</v>
       </c>
@@ -4670,16 +5158,18 @@
       <c r="E158" s="13"/>
       <c r="F158" s="13"/>
       <c r="G158" s="13"/>
-    </row>
-    <row r="159" spans="2:7">
+      <c r="H158" s="13"/>
+    </row>
+    <row r="159" spans="2:8">
       <c r="B159" s="4"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="13"/>
       <c r="F159" s="13"/>
       <c r="G159" s="13"/>
-    </row>
-    <row r="160" spans="2:7">
+      <c r="H159" s="13"/>
+    </row>
+    <row r="160" spans="2:8">
       <c r="B160" s="4" t="s">
         <v>73</v>
       </c>
@@ -4692,8 +5182,9 @@
       <c r="E160" s="13"/>
       <c r="F160" s="13"/>
       <c r="G160" s="13"/>
-    </row>
-    <row r="161" spans="2:7">
+      <c r="H160" s="13"/>
+    </row>
+    <row r="161" spans="2:8">
       <c r="B161" s="4" t="s">
         <v>73</v>
       </c>
@@ -4706,8 +5197,9 @@
       <c r="E161" s="13"/>
       <c r="F161" s="13"/>
       <c r="G161" s="13"/>
-    </row>
-    <row r="162" spans="2:7">
+      <c r="H161" s="13"/>
+    </row>
+    <row r="162" spans="2:8">
       <c r="B162" s="4" t="s">
         <v>74</v>
       </c>
@@ -4726,8 +5218,11 @@
       <c r="G162" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="163" spans="2:7">
+      <c r="H162" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="163" spans="2:8">
       <c r="B163" s="4" t="s">
         <v>74</v>
       </c>
@@ -4746,8 +5241,11 @@
       <c r="G163" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="164" spans="2:7">
+      <c r="H163" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="164" spans="2:8">
       <c r="B164" s="4" t="s">
         <v>75</v>
       </c>
@@ -4764,8 +5262,11 @@
       <c r="G164" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="165" spans="2:7">
+      <c r="H164" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="165" spans="2:8">
       <c r="B165" s="4" t="s">
         <v>75</v>
       </c>
@@ -4782,8 +5283,11 @@
       <c r="G165" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="166" spans="2:7">
+      <c r="H165" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="166" spans="2:8">
       <c r="B166" s="4" t="s">
         <v>76</v>
       </c>
@@ -4802,8 +5306,11 @@
       <c r="G166" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="167" spans="2:7">
+      <c r="H166" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="167" spans="2:8">
       <c r="B167" s="4" t="s">
         <v>76</v>
       </c>
@@ -4822,8 +5329,11 @@
       <c r="G167" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="168" spans="2:7">
+      <c r="H167" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="168" spans="2:8">
       <c r="B168" s="4" t="s">
         <v>77</v>
       </c>
@@ -4842,8 +5352,11 @@
       <c r="G168" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="169" spans="2:7">
+      <c r="H168" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="169" spans="2:8">
       <c r="B169" s="4" t="s">
         <v>77</v>
       </c>
@@ -4862,8 +5375,11 @@
       <c r="G169" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="170" spans="2:7">
+      <c r="H169" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="170" spans="2:8">
       <c r="B170" s="5" t="s">
         <v>8</v>
       </c>
@@ -4874,8 +5390,9 @@
       <c r="E170" s="13"/>
       <c r="F170" s="13"/>
       <c r="G170" s="13"/>
-    </row>
-    <row r="171" spans="2:7">
+      <c r="H170" s="13"/>
+    </row>
+    <row r="171" spans="2:8">
       <c r="B171" s="5" t="s">
         <v>8</v>
       </c>
@@ -4886,8 +5403,9 @@
       <c r="E171" s="13"/>
       <c r="F171" s="13"/>
       <c r="G171" s="13"/>
-    </row>
-    <row r="172" spans="2:7">
+      <c r="H171" s="13"/>
+    </row>
+    <row r="172" spans="2:8">
       <c r="B172" s="5" t="s">
         <v>8</v>
       </c>
@@ -4898,8 +5416,9 @@
       <c r="E172" s="13"/>
       <c r="F172" s="13"/>
       <c r="G172" s="13"/>
-    </row>
-    <row r="173" spans="2:7">
+      <c r="H172" s="13"/>
+    </row>
+    <row r="173" spans="2:8">
       <c r="B173" s="5" t="s">
         <v>8</v>
       </c>
@@ -4910,8 +5429,9 @@
       <c r="E173" s="13"/>
       <c r="F173" s="13"/>
       <c r="G173" s="13"/>
-    </row>
-    <row r="174" spans="2:7">
+      <c r="H173" s="13"/>
+    </row>
+    <row r="174" spans="2:8">
       <c r="B174" s="5" t="s">
         <v>8</v>
       </c>
@@ -4922,8 +5442,9 @@
       <c r="E174" s="13"/>
       <c r="F174" s="13"/>
       <c r="G174" s="13"/>
-    </row>
-    <row r="175" spans="2:7">
+      <c r="H174" s="13"/>
+    </row>
+    <row r="175" spans="2:8">
       <c r="B175" s="5" t="s">
         <v>8</v>
       </c>
@@ -4934,16 +5455,18 @@
       <c r="E175" s="13"/>
       <c r="F175" s="13"/>
       <c r="G175" s="13"/>
-    </row>
-    <row r="176" spans="2:7">
+      <c r="H175" s="13"/>
+    </row>
+    <row r="176" spans="2:8">
       <c r="B176" s="4"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="13"/>
       <c r="F176" s="13"/>
       <c r="G176" s="13"/>
-    </row>
-    <row r="177" spans="2:7">
+      <c r="H176" s="13"/>
+    </row>
+    <row r="177" spans="2:8">
       <c r="B177" s="4" t="s">
         <v>78</v>
       </c>
@@ -4958,8 +5481,11 @@
       <c r="G177" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="178" spans="2:7">
+      <c r="H177" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="178" spans="2:8">
       <c r="B178" s="4" t="s">
         <v>79</v>
       </c>
@@ -4974,8 +5500,11 @@
       <c r="G178" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="179" spans="2:7">
+      <c r="H178" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="179" spans="2:8">
       <c r="B179" s="4" t="s">
         <v>80</v>
       </c>
@@ -4990,8 +5519,11 @@
       <c r="G179" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="180" spans="2:7">
+      <c r="H179" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="180" spans="2:8">
       <c r="B180" s="4" t="s">
         <v>81</v>
       </c>
@@ -5006,8 +5538,11 @@
       <c r="G180" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="181" spans="2:7">
+      <c r="H180" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="181" spans="2:8">
       <c r="B181" s="5" t="s">
         <v>8</v>
       </c>
@@ -5018,8 +5553,9 @@
       <c r="E181" s="13"/>
       <c r="F181" s="13"/>
       <c r="G181" s="13"/>
-    </row>
-    <row r="182" spans="2:7">
+      <c r="H181" s="13"/>
+    </row>
+    <row r="182" spans="2:8">
       <c r="B182" s="5" t="s">
         <v>8</v>
       </c>
@@ -5030,8 +5566,9 @@
       <c r="E182" s="13"/>
       <c r="F182" s="13"/>
       <c r="G182" s="13"/>
-    </row>
-    <row r="183" spans="2:7">
+      <c r="H182" s="13"/>
+    </row>
+    <row r="183" spans="2:8">
       <c r="B183" s="4" t="s">
         <v>82</v>
       </c>
@@ -5044,8 +5581,9 @@
       <c r="E183" s="13"/>
       <c r="F183" s="13"/>
       <c r="G183" s="13"/>
-    </row>
-    <row r="184" spans="2:7">
+      <c r="H183" s="13"/>
+    </row>
+    <row r="184" spans="2:8">
       <c r="B184" s="4" t="s">
         <v>83</v>
       </c>
@@ -5058,8 +5596,9 @@
       <c r="E184" s="13"/>
       <c r="F184" s="13"/>
       <c r="G184" s="13"/>
-    </row>
-    <row r="185" spans="2:7">
+      <c r="H184" s="13"/>
+    </row>
+    <row r="185" spans="2:8">
       <c r="B185" s="4" t="s">
         <v>84</v>
       </c>
@@ -5072,8 +5611,9 @@
       <c r="E185" s="13"/>
       <c r="F185" s="13"/>
       <c r="G185" s="13"/>
-    </row>
-    <row r="186" spans="2:7">
+      <c r="H185" s="13"/>
+    </row>
+    <row r="186" spans="2:8">
       <c r="B186" s="4" t="s">
         <v>85</v>
       </c>
@@ -5086,8 +5626,9 @@
       <c r="E186" s="13"/>
       <c r="F186" s="13"/>
       <c r="G186" s="13"/>
-    </row>
-    <row r="187" spans="2:7">
+      <c r="H186" s="13"/>
+    </row>
+    <row r="187" spans="2:8">
       <c r="B187" s="4" t="s">
         <v>86</v>
       </c>
@@ -5100,8 +5641,9 @@
       <c r="E187" s="13"/>
       <c r="F187" s="13"/>
       <c r="G187" s="13"/>
-    </row>
-    <row r="188" spans="2:7">
+      <c r="H187" s="13"/>
+    </row>
+    <row r="188" spans="2:8">
       <c r="B188" s="4" t="s">
         <v>87</v>
       </c>
@@ -5114,8 +5656,9 @@
       <c r="E188" s="13"/>
       <c r="F188" s="13"/>
       <c r="G188" s="13"/>
-    </row>
-    <row r="189" spans="2:7">
+      <c r="H188" s="13"/>
+    </row>
+    <row r="189" spans="2:8">
       <c r="B189" s="4" t="s">
         <v>88</v>
       </c>
@@ -5128,8 +5671,9 @@
       <c r="E189" s="13"/>
       <c r="F189" s="13"/>
       <c r="G189" s="13"/>
-    </row>
-    <row r="190" spans="2:7">
+      <c r="H189" s="13"/>
+    </row>
+    <row r="190" spans="2:8">
       <c r="B190" s="5" t="s">
         <v>8</v>
       </c>
@@ -5140,8 +5684,9 @@
       <c r="E190" s="13"/>
       <c r="F190" s="13"/>
       <c r="G190" s="13"/>
-    </row>
-    <row r="191" spans="2:7">
+      <c r="H190" s="13"/>
+    </row>
+    <row r="191" spans="2:8">
       <c r="B191" s="5" t="s">
         <v>8</v>
       </c>
@@ -5152,8 +5697,9 @@
       <c r="E191" s="13"/>
       <c r="F191" s="13"/>
       <c r="G191" s="13"/>
-    </row>
-    <row r="192" spans="2:7">
+      <c r="H191" s="13"/>
+    </row>
+    <row r="192" spans="2:8">
       <c r="B192" s="5" t="s">
         <v>8</v>
       </c>
@@ -5164,16 +5710,18 @@
       <c r="E192" s="13"/>
       <c r="F192" s="13"/>
       <c r="G192" s="13"/>
-    </row>
-    <row r="193" spans="2:7">
+      <c r="H192" s="13"/>
+    </row>
+    <row r="193" spans="2:8">
       <c r="B193" s="4"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="13"/>
       <c r="F193" s="13"/>
       <c r="G193" s="13"/>
-    </row>
-    <row r="194" spans="2:7">
+      <c r="H193" s="13"/>
+    </row>
+    <row r="194" spans="2:8">
       <c r="B194" s="4" t="s">
         <v>71</v>
       </c>
@@ -5190,8 +5738,11 @@
       <c r="G194" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="195" spans="2:7">
+      <c r="H194" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="195" spans="2:8">
       <c r="B195" s="4" t="s">
         <v>71</v>
       </c>
@@ -5208,8 +5759,11 @@
       <c r="G195" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="196" spans="2:7">
+      <c r="H195" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="196" spans="2:8">
       <c r="B196" s="4" t="s">
         <v>72</v>
       </c>
@@ -5228,8 +5782,11 @@
       <c r="G196" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="197" spans="2:7">
+      <c r="H196" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="197" spans="2:8">
       <c r="B197" s="4" t="s">
         <v>73</v>
       </c>
@@ -5242,8 +5799,9 @@
       <c r="E197" s="13"/>
       <c r="F197" s="13"/>
       <c r="G197" s="13"/>
-    </row>
-    <row r="198" spans="2:7">
+      <c r="H197" s="13"/>
+    </row>
+    <row r="198" spans="2:8">
       <c r="B198" s="4" t="s">
         <v>74</v>
       </c>
@@ -5262,8 +5820,11 @@
       <c r="G198" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="199" spans="2:7">
+      <c r="H198" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="199" spans="2:8">
       <c r="B199" s="4" t="s">
         <v>75</v>
       </c>
@@ -5280,8 +5841,11 @@
       <c r="G199" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="200" spans="2:7">
+      <c r="H199" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="200" spans="2:8">
       <c r="B200" s="4" t="s">
         <v>76</v>
       </c>
@@ -5300,8 +5864,11 @@
       <c r="G200" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="201" spans="2:7">
+      <c r="H200" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="201" spans="2:8">
       <c r="B201" s="4" t="s">
         <v>76</v>
       </c>
@@ -5320,8 +5887,11 @@
       <c r="G201" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="202" spans="2:7">
+      <c r="H201" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="202" spans="2:8">
       <c r="B202" s="4" t="s">
         <v>77</v>
       </c>
@@ -5340,8 +5910,11 @@
       <c r="G202" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="203" spans="2:7">
+      <c r="H202" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="203" spans="2:8">
       <c r="B203" s="5" t="s">
         <v>8</v>
       </c>
@@ -5352,8 +5925,9 @@
       <c r="E203" s="13"/>
       <c r="F203" s="13"/>
       <c r="G203" s="13"/>
-    </row>
-    <row r="204" spans="2:7">
+      <c r="H203" s="13"/>
+    </row>
+    <row r="204" spans="2:8">
       <c r="B204" s="4" t="s">
         <v>89</v>
       </c>
@@ -5370,8 +5944,11 @@
       <c r="G204" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="205" spans="2:7">
+      <c r="H204" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="205" spans="2:8">
       <c r="B205" s="5" t="s">
         <v>8</v>
       </c>
@@ -5382,8 +5959,9 @@
       <c r="E205" s="13"/>
       <c r="F205" s="13"/>
       <c r="G205" s="13"/>
-    </row>
-    <row r="206" spans="2:7">
+      <c r="H205" s="13"/>
+    </row>
+    <row r="206" spans="2:8">
       <c r="B206" s="5" t="s">
         <v>8</v>
       </c>
@@ -5394,8 +5972,9 @@
       <c r="E206" s="13"/>
       <c r="F206" s="13"/>
       <c r="G206" s="13"/>
-    </row>
-    <row r="207" spans="2:7">
+      <c r="H206" s="13"/>
+    </row>
+    <row r="207" spans="2:8">
       <c r="B207" s="5" t="s">
         <v>8</v>
       </c>
@@ -5406,8 +5985,9 @@
       <c r="E207" s="13"/>
       <c r="F207" s="13"/>
       <c r="G207" s="13"/>
-    </row>
-    <row r="208" spans="2:7">
+      <c r="H207" s="13"/>
+    </row>
+    <row r="208" spans="2:8">
       <c r="B208" s="5" t="s">
         <v>8</v>
       </c>
@@ -5418,8 +5998,9 @@
       <c r="E208" s="13"/>
       <c r="F208" s="13"/>
       <c r="G208" s="13"/>
-    </row>
-    <row r="209" spans="2:7">
+      <c r="H208" s="13"/>
+    </row>
+    <row r="209" spans="2:8">
       <c r="B209" s="5" t="s">
         <v>8</v>
       </c>
@@ -5430,16 +6011,18 @@
       <c r="E209" s="13"/>
       <c r="F209" s="13"/>
       <c r="G209" s="13"/>
-    </row>
-    <row r="210" spans="2:7">
+      <c r="H209" s="13"/>
+    </row>
+    <row r="210" spans="2:8">
       <c r="B210" s="4"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="13"/>
       <c r="F210" s="13"/>
       <c r="G210" s="13"/>
-    </row>
-    <row r="211" spans="2:7">
+      <c r="H210" s="13"/>
+    </row>
+    <row r="211" spans="2:8">
       <c r="B211" s="4" t="s">
         <v>90</v>
       </c>
@@ -5456,8 +6039,11 @@
       <c r="G211" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="212" spans="2:7">
+      <c r="H211" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="212" spans="2:8">
       <c r="B212" s="4" t="s">
         <v>91</v>
       </c>
@@ -5474,8 +6060,11 @@
       <c r="G212" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="213" spans="2:7">
+      <c r="H212" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="213" spans="2:8">
       <c r="B213" s="4" t="s">
         <v>92</v>
       </c>
@@ -5488,8 +6077,9 @@
       <c r="E213" s="13"/>
       <c r="F213" s="13"/>
       <c r="G213" s="13"/>
-    </row>
-    <row r="214" spans="2:7">
+      <c r="H213" s="13"/>
+    </row>
+    <row r="214" spans="2:8">
       <c r="B214" s="4" t="s">
         <v>93</v>
       </c>
@@ -5506,16 +6096,20 @@
       <c r="G214" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="215" spans="2:7">
+      <c r="H214" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="215" spans="2:8">
       <c r="B215" s="4"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="13"/>
       <c r="F215" s="13"/>
       <c r="G215" s="13"/>
-    </row>
-    <row r="216" spans="2:7">
+      <c r="H215" s="13"/>
+    </row>
+    <row r="216" spans="2:8">
       <c r="B216" s="4" t="s">
         <v>94</v>
       </c>
@@ -5526,8 +6120,9 @@
       <c r="E216" s="13"/>
       <c r="F216" s="13"/>
       <c r="G216" s="13"/>
-    </row>
-    <row r="217" spans="2:7">
+      <c r="H216" s="13"/>
+    </row>
+    <row r="217" spans="2:8">
       <c r="B217" s="4" t="s">
         <v>95</v>
       </c>
@@ -5542,8 +6137,11 @@
       <c r="G217" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="218" spans="2:7">
+      <c r="H217" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="218" spans="2:8">
       <c r="B218" s="4" t="s">
         <v>96</v>
       </c>
@@ -5558,8 +6156,11 @@
       <c r="G218" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="219" spans="2:7">
+      <c r="H218" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="219" spans="2:8">
       <c r="B219" s="4" t="s">
         <v>97</v>
       </c>
@@ -5576,8 +6177,11 @@
       <c r="G219" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="220" spans="2:7">
+      <c r="H219" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="220" spans="2:8">
       <c r="B220" s="4" t="s">
         <v>98</v>
       </c>
@@ -5590,8 +6194,9 @@
       <c r="E220" s="13"/>
       <c r="F220" s="13"/>
       <c r="G220" s="13"/>
-    </row>
-    <row r="221" spans="2:7">
+      <c r="H220" s="13"/>
+    </row>
+    <row r="221" spans="2:8">
       <c r="B221" s="4" t="s">
         <v>99</v>
       </c>
@@ -5604,8 +6209,9 @@
       <c r="E221" s="13"/>
       <c r="F221" s="13"/>
       <c r="G221" s="13"/>
-    </row>
-    <row r="222" spans="2:7">
+      <c r="H221" s="13"/>
+    </row>
+    <row r="222" spans="2:8">
       <c r="B222" s="4" t="s">
         <v>100</v>
       </c>
@@ -5618,8 +6224,9 @@
       <c r="E222" s="13"/>
       <c r="F222" s="13"/>
       <c r="G222" s="13"/>
-    </row>
-    <row r="223" spans="2:7">
+      <c r="H222" s="13"/>
+    </row>
+    <row r="223" spans="2:8">
       <c r="B223" s="4" t="s">
         <v>101</v>
       </c>
@@ -5638,16 +6245,20 @@
       <c r="G223" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="224" spans="2:7">
+      <c r="H223" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="224" spans="2:8">
       <c r="B224" s="4"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="13"/>
       <c r="F224" s="13"/>
       <c r="G224" s="13"/>
-    </row>
-    <row r="225" spans="2:7">
+      <c r="H224" s="13"/>
+    </row>
+    <row r="225" spans="2:8">
       <c r="B225" s="4" t="s">
         <v>71</v>
       </c>
@@ -5664,8 +6275,11 @@
       <c r="G225" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="226" spans="2:7">
+      <c r="H225" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="226" spans="2:8">
       <c r="B226" s="4" t="s">
         <v>76</v>
       </c>
@@ -5684,8 +6298,11 @@
       <c r="G226" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="227" spans="2:7">
+      <c r="H226" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="227" spans="2:8">
       <c r="B227" s="5" t="s">
         <v>8</v>
       </c>
@@ -5696,8 +6313,9 @@
       <c r="E227" s="13"/>
       <c r="F227" s="13"/>
       <c r="G227" s="13"/>
-    </row>
-    <row r="228" spans="2:7">
+      <c r="H227" s="13"/>
+    </row>
+    <row r="228" spans="2:8">
       <c r="B228" s="5" t="s">
         <v>8</v>
       </c>
@@ -5708,16 +6326,18 @@
       <c r="E228" s="13"/>
       <c r="F228" s="13"/>
       <c r="G228" s="13"/>
-    </row>
-    <row r="229" spans="2:7">
+      <c r="H228" s="13"/>
+    </row>
+    <row r="229" spans="2:8">
       <c r="B229" s="4"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="13"/>
       <c r="F229" s="13"/>
       <c r="G229" s="13"/>
-    </row>
-    <row r="230" spans="2:7">
+      <c r="H229" s="13"/>
+    </row>
+    <row r="230" spans="2:8">
       <c r="B230" s="4"/>
       <c r="C230" s="3" t="s">
         <v>234</v>
@@ -5730,8 +6350,11 @@
       <c r="G230" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="231" spans="2:7">
+      <c r="H230" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="231" spans="2:8">
       <c r="B231" s="4"/>
       <c r="C231" s="3" t="s">
         <v>235</v>
@@ -5744,16 +6367,20 @@
       <c r="G231" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="232" spans="2:7">
+      <c r="H231" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="232" spans="2:8">
       <c r="B232" s="4"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="13"/>
       <c r="F232" s="13"/>
       <c r="G232" s="13"/>
-    </row>
-    <row r="233" spans="2:7">
+      <c r="H232" s="13"/>
+    </row>
+    <row r="233" spans="2:8">
       <c r="B233" s="4" t="s">
         <v>102</v>
       </c>
@@ -5768,8 +6395,11 @@
       <c r="G233" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="234" spans="2:7">
+      <c r="H233" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="234" spans="2:8">
       <c r="B234" s="4" t="s">
         <v>103</v>
       </c>
@@ -5784,8 +6414,11 @@
       <c r="G234" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="235" spans="2:7">
+      <c r="H234" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="235" spans="2:8">
       <c r="B235" s="4" t="s">
         <v>104</v>
       </c>
@@ -5800,8 +6433,11 @@
       <c r="G235" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="236" spans="2:7">
+      <c r="H235" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="236" spans="2:8">
       <c r="B236" s="5" t="s">
         <v>8</v>
       </c>
@@ -5816,16 +6452,20 @@
       <c r="G236" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="237" spans="2:7">
+      <c r="H236" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="237" spans="2:8">
       <c r="B237" s="4"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="13"/>
       <c r="F237" s="13"/>
       <c r="G237" s="13"/>
-    </row>
-    <row r="238" spans="2:7">
+      <c r="H237" s="13"/>
+    </row>
+    <row r="238" spans="2:8">
       <c r="B238" s="4" t="s">
         <v>105</v>
       </c>
@@ -5840,8 +6480,11 @@
       <c r="G238" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="239" spans="2:7">
+      <c r="H238" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="239" spans="2:8">
       <c r="B239" s="4" t="s">
         <v>80</v>
       </c>
@@ -5856,8 +6499,11 @@
       <c r="G239" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="240" spans="2:7">
+      <c r="H239" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="240" spans="2:8">
       <c r="B240" s="4" t="s">
         <v>106</v>
       </c>
@@ -5872,8 +6518,11 @@
       <c r="G240" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="241" spans="2:7">
+      <c r="H240" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="241" spans="2:8">
       <c r="B241" s="4" t="s">
         <v>81</v>
       </c>
@@ -5888,16 +6537,20 @@
       <c r="G241" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="242" spans="2:7">
+      <c r="H241" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="242" spans="2:8">
       <c r="B242" s="4"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="13"/>
       <c r="F242" s="13"/>
       <c r="G242" s="13"/>
-    </row>
-    <row r="243" spans="2:7">
+      <c r="H242" s="13"/>
+    </row>
+    <row r="243" spans="2:8">
       <c r="B243" s="4" t="s">
         <v>107</v>
       </c>
@@ -5912,8 +6565,11 @@
       <c r="G243" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="244" spans="2:7">
+      <c r="H243" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="244" spans="2:8">
       <c r="B244" s="4" t="s">
         <v>108</v>
       </c>
@@ -5930,8 +6586,11 @@
       <c r="G244" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="245" spans="2:7">
+      <c r="H244" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="245" spans="2:8">
       <c r="B245" s="4" t="s">
         <v>109</v>
       </c>
@@ -5948,8 +6607,11 @@
       <c r="G245" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="246" spans="2:7">
+      <c r="H245" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="246" spans="2:8">
       <c r="B246" s="4" t="s">
         <v>110</v>
       </c>
@@ -5966,8 +6628,11 @@
       <c r="G246" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="247" spans="2:7">
+      <c r="H246" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="247" spans="2:8">
       <c r="B247" s="4" t="s">
         <v>111</v>
       </c>
@@ -5984,8 +6649,11 @@
       <c r="G247" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="248" spans="2:7">
+      <c r="H247" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="248" spans="2:8">
       <c r="B248" s="4" t="s">
         <v>112</v>
       </c>
@@ -6002,8 +6670,11 @@
       <c r="G248" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="249" spans="2:7">
+      <c r="H248" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="249" spans="2:8">
       <c r="B249" s="4" t="s">
         <v>113</v>
       </c>
@@ -6020,8 +6691,11 @@
       <c r="G249" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="250" spans="2:7">
+      <c r="H249" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="250" spans="2:8">
       <c r="B250" s="4" t="s">
         <v>114</v>
       </c>
@@ -6038,8 +6712,11 @@
       <c r="G250" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="251" spans="2:7">
+      <c r="H250" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="251" spans="2:8">
       <c r="B251" s="4" t="s">
         <v>115</v>
       </c>
@@ -6056,8 +6733,11 @@
       <c r="G251" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="252" spans="2:7">
+      <c r="H251" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="252" spans="2:8">
       <c r="B252" s="4" t="s">
         <v>116</v>
       </c>
@@ -6068,8 +6748,9 @@
       <c r="E252" s="13"/>
       <c r="F252" s="13"/>
       <c r="G252" s="13"/>
-    </row>
-    <row r="253" spans="2:7">
+      <c r="H252" s="13"/>
+    </row>
+    <row r="253" spans="2:8">
       <c r="B253" s="4" t="s">
         <v>117</v>
       </c>
@@ -6086,8 +6767,11 @@
       <c r="G253" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="254" spans="2:7">
+      <c r="H253" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="254" spans="2:8">
       <c r="B254" s="5" t="s">
         <v>8</v>
       </c>
@@ -6098,8 +6782,9 @@
       <c r="E254" s="13"/>
       <c r="F254" s="13"/>
       <c r="G254" s="13"/>
-    </row>
-    <row r="255" spans="2:7">
+      <c r="H254" s="13"/>
+    </row>
+    <row r="255" spans="2:8">
       <c r="B255" s="4" t="s">
         <v>118</v>
       </c>
@@ -6110,8 +6795,9 @@
       <c r="E255" s="13"/>
       <c r="F255" s="13"/>
       <c r="G255" s="13"/>
-    </row>
-    <row r="256" spans="2:7">
+      <c r="H255" s="13"/>
+    </row>
+    <row r="256" spans="2:8">
       <c r="B256" s="4" t="s">
         <v>119</v>
       </c>
@@ -6124,8 +6810,9 @@
       <c r="E256" s="13"/>
       <c r="F256" s="13"/>
       <c r="G256" s="13"/>
-    </row>
-    <row r="257" spans="2:7">
+      <c r="H256" s="13"/>
+    </row>
+    <row r="257" spans="2:8">
       <c r="B257" s="4" t="s">
         <v>120</v>
       </c>
@@ -6138,8 +6825,9 @@
       <c r="E257" s="13"/>
       <c r="F257" s="13"/>
       <c r="G257" s="13"/>
-    </row>
-    <row r="258" spans="2:7">
+      <c r="H257" s="13"/>
+    </row>
+    <row r="258" spans="2:8">
       <c r="B258" s="4" t="s">
         <v>121</v>
       </c>
@@ -6156,8 +6844,11 @@
       <c r="G258" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="259" spans="2:7">
+      <c r="H258" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="259" spans="2:8">
       <c r="B259" s="4" t="s">
         <v>122</v>
       </c>
@@ -6174,8 +6865,11 @@
       <c r="G259" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="260" spans="2:7">
+      <c r="H259" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="260" spans="2:8">
       <c r="B260" s="4" t="s">
         <v>123</v>
       </c>
@@ -6192,8 +6886,11 @@
       <c r="G260" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="261" spans="2:7">
+      <c r="H260" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="261" spans="2:8">
       <c r="B261" s="4" t="s">
         <v>124</v>
       </c>
@@ -6210,8 +6907,11 @@
       <c r="G261" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="262" spans="2:7">
+      <c r="H261" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="262" spans="2:8">
       <c r="B262" s="4" t="s">
         <v>125</v>
       </c>
@@ -6230,8 +6930,11 @@
       <c r="G262" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="263" spans="2:7">
+      <c r="H262" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="263" spans="2:8">
       <c r="B263" s="5" t="s">
         <v>8</v>
       </c>
@@ -6242,8 +6945,9 @@
       <c r="E263" s="13"/>
       <c r="F263" s="13"/>
       <c r="G263" s="13"/>
-    </row>
-    <row r="264" spans="2:7">
+      <c r="H263" s="13"/>
+    </row>
+    <row r="264" spans="2:8">
       <c r="B264" s="4" t="s">
         <v>126</v>
       </c>
@@ -6260,8 +6964,11 @@
       <c r="G264" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="265" spans="2:7">
+      <c r="H264" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="265" spans="2:8">
       <c r="B265" s="4" t="s">
         <v>127</v>
       </c>
@@ -6278,8 +6985,11 @@
       <c r="G265" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="266" spans="2:7">
+      <c r="H265" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="266" spans="2:8">
       <c r="B266" s="5" t="s">
         <v>8</v>
       </c>
@@ -6290,8 +7000,9 @@
       <c r="E266" s="13"/>
       <c r="F266" s="13"/>
       <c r="G266" s="13"/>
-    </row>
-    <row r="267" spans="2:7">
+      <c r="H266" s="13"/>
+    </row>
+    <row r="267" spans="2:8">
       <c r="B267" s="5" t="s">
         <v>128</v>
       </c>
@@ -6302,8 +7013,9 @@
       <c r="E267" s="13"/>
       <c r="F267" s="13"/>
       <c r="G267" s="13"/>
-    </row>
-    <row r="268" spans="2:7">
+      <c r="H267" s="13"/>
+    </row>
+    <row r="268" spans="2:8">
       <c r="B268" s="5" t="s">
         <v>128</v>
       </c>
@@ -6314,8 +7026,9 @@
       <c r="E268" s="13"/>
       <c r="F268" s="13"/>
       <c r="G268" s="13"/>
-    </row>
-    <row r="269" spans="2:7">
+      <c r="H268" s="13"/>
+    </row>
+    <row r="269" spans="2:8">
       <c r="B269" s="5" t="s">
         <v>128</v>
       </c>
@@ -6326,8 +7039,9 @@
       <c r="E269" s="13"/>
       <c r="F269" s="13"/>
       <c r="G269" s="13"/>
-    </row>
-    <row r="270" spans="2:7">
+      <c r="H269" s="13"/>
+    </row>
+    <row r="270" spans="2:8">
       <c r="B270" s="5" t="s">
         <v>128</v>
       </c>
@@ -6338,8 +7052,9 @@
       <c r="E270" s="13"/>
       <c r="F270" s="13"/>
       <c r="G270" s="13"/>
-    </row>
-    <row r="271" spans="2:7">
+      <c r="H270" s="13"/>
+    </row>
+    <row r="271" spans="2:8">
       <c r="B271" s="5" t="s">
         <v>128</v>
       </c>
@@ -6350,8 +7065,9 @@
       <c r="E271" s="13"/>
       <c r="F271" s="13"/>
       <c r="G271" s="13"/>
-    </row>
-    <row r="272" spans="2:7">
+      <c r="H271" s="13"/>
+    </row>
+    <row r="272" spans="2:8">
       <c r="B272" s="5" t="s">
         <v>128</v>
       </c>
@@ -6362,8 +7078,9 @@
       <c r="E272" s="13"/>
       <c r="F272" s="13"/>
       <c r="G272" s="13"/>
-    </row>
-    <row r="273" spans="2:7">
+      <c r="H272" s="13"/>
+    </row>
+    <row r="273" spans="2:8">
       <c r="B273" s="5" t="s">
         <v>128</v>
       </c>
@@ -6374,8 +7091,9 @@
       <c r="E273" s="13"/>
       <c r="F273" s="13"/>
       <c r="G273" s="13"/>
-    </row>
-    <row r="274" spans="2:7">
+      <c r="H273" s="13"/>
+    </row>
+    <row r="274" spans="2:8">
       <c r="B274" s="5" t="s">
         <v>128</v>
       </c>
@@ -6386,624 +7104,702 @@
       <c r="E274" s="13"/>
       <c r="F274" s="13"/>
       <c r="G274" s="13"/>
-    </row>
-    <row r="275" spans="2:7">
+      <c r="H274" s="13"/>
+    </row>
+    <row r="275" spans="2:8">
       <c r="B275" s="4"/>
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="13"/>
       <c r="F275" s="13"/>
       <c r="G275" s="13"/>
-    </row>
-    <row r="276" spans="2:7">
+      <c r="H275" s="13"/>
+    </row>
+    <row r="276" spans="2:8">
       <c r="B276" s="4"/>
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="14"/>
       <c r="F276" s="14"/>
       <c r="G276" s="14"/>
-    </row>
-    <row r="277" spans="2:7">
+      <c r="H276" s="14"/>
+    </row>
+    <row r="277" spans="2:8">
       <c r="B277" s="4"/>
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="14"/>
       <c r="F277" s="14"/>
       <c r="G277" s="14"/>
-    </row>
-    <row r="278" spans="2:7">
+      <c r="H277" s="14"/>
+    </row>
+    <row r="278" spans="2:8">
       <c r="B278" s="4"/>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="14"/>
       <c r="F278" s="14"/>
       <c r="G278" s="14"/>
-    </row>
-    <row r="279" spans="2:7">
+      <c r="H278" s="14"/>
+    </row>
+    <row r="279" spans="2:8">
       <c r="B279" s="4"/>
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="14"/>
       <c r="F279" s="14"/>
       <c r="G279" s="14"/>
-    </row>
-    <row r="280" spans="2:7">
+      <c r="H279" s="14"/>
+    </row>
+    <row r="280" spans="2:8">
       <c r="B280" s="4"/>
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="14"/>
       <c r="F280" s="14"/>
       <c r="G280" s="14"/>
-    </row>
-    <row r="281" spans="2:7">
+      <c r="H280" s="14"/>
+    </row>
+    <row r="281" spans="2:8">
       <c r="B281" s="4"/>
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="14"/>
       <c r="F281" s="14"/>
       <c r="G281" s="14"/>
-    </row>
-    <row r="282" spans="2:7">
+      <c r="H281" s="14"/>
+    </row>
+    <row r="282" spans="2:8">
       <c r="B282" s="4"/>
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="14"/>
       <c r="F282" s="14"/>
       <c r="G282" s="14"/>
-    </row>
-    <row r="283" spans="2:7">
+      <c r="H282" s="14"/>
+    </row>
+    <row r="283" spans="2:8">
       <c r="B283" s="4"/>
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="14"/>
       <c r="F283" s="14"/>
       <c r="G283" s="14"/>
-    </row>
-    <row r="284" spans="2:7">
+      <c r="H283" s="14"/>
+    </row>
+    <row r="284" spans="2:8">
       <c r="B284" s="4"/>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="14"/>
       <c r="F284" s="14"/>
       <c r="G284" s="14"/>
-    </row>
-    <row r="285" spans="2:7">
+      <c r="H284" s="14"/>
+    </row>
+    <row r="285" spans="2:8">
       <c r="B285" s="5"/>
       <c r="C285" s="17"/>
       <c r="D285" s="3"/>
       <c r="E285" s="14"/>
       <c r="F285" s="14"/>
       <c r="G285" s="14"/>
-    </row>
-    <row r="286" spans="2:7">
+      <c r="H285" s="14"/>
+    </row>
+    <row r="286" spans="2:8">
       <c r="B286" s="4"/>
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="14"/>
       <c r="F286" s="14"/>
       <c r="G286" s="14"/>
-    </row>
-    <row r="287" spans="2:7">
+      <c r="H286" s="14"/>
+    </row>
+    <row r="287" spans="2:8">
       <c r="B287" s="5"/>
       <c r="C287" s="17"/>
       <c r="D287" s="3"/>
       <c r="E287" s="14"/>
       <c r="F287" s="14"/>
       <c r="G287" s="14"/>
-    </row>
-    <row r="288" spans="2:7">
+      <c r="H287" s="14"/>
+    </row>
+    <row r="288" spans="2:8">
       <c r="B288" s="5"/>
       <c r="C288" s="17"/>
       <c r="D288" s="3"/>
       <c r="E288" s="14"/>
       <c r="F288" s="14"/>
       <c r="G288" s="14"/>
-    </row>
-    <row r="289" spans="2:7">
+      <c r="H288" s="14"/>
+    </row>
+    <row r="289" spans="2:8">
       <c r="B289" s="4"/>
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="14"/>
       <c r="F289" s="14"/>
       <c r="G289" s="14"/>
-    </row>
-    <row r="290" spans="2:7">
+      <c r="H289" s="14"/>
+    </row>
+    <row r="290" spans="2:8">
       <c r="B290" s="4"/>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="14"/>
       <c r="F290" s="14"/>
       <c r="G290" s="14"/>
-    </row>
-    <row r="291" spans="2:7">
+      <c r="H290" s="14"/>
+    </row>
+    <row r="291" spans="2:8">
       <c r="B291" s="4"/>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="14"/>
       <c r="F291" s="14"/>
       <c r="G291" s="14"/>
-    </row>
-    <row r="292" spans="2:7">
+      <c r="H291" s="14"/>
+    </row>
+    <row r="292" spans="2:8">
       <c r="B292" s="4"/>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="13"/>
       <c r="F292" s="13"/>
       <c r="G292" s="13"/>
-    </row>
-    <row r="293" spans="2:7">
+      <c r="H292" s="13"/>
+    </row>
+    <row r="293" spans="2:8">
       <c r="B293" s="4"/>
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="14"/>
       <c r="F293" s="14"/>
       <c r="G293" s="14"/>
-    </row>
-    <row r="294" spans="2:7">
+      <c r="H293" s="14"/>
+    </row>
+    <row r="294" spans="2:8">
       <c r="B294" s="4"/>
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="14"/>
       <c r="F294" s="14"/>
       <c r="G294" s="14"/>
-    </row>
-    <row r="295" spans="2:7">
+      <c r="H294" s="14"/>
+    </row>
+    <row r="295" spans="2:8">
       <c r="B295" s="4"/>
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="14"/>
       <c r="F295" s="14"/>
       <c r="G295" s="14"/>
-    </row>
-    <row r="296" spans="2:7">
+      <c r="H295" s="14"/>
+    </row>
+    <row r="296" spans="2:8">
       <c r="B296" s="4"/>
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="14"/>
       <c r="F296" s="14"/>
       <c r="G296" s="14"/>
-    </row>
-    <row r="297" spans="2:7">
+      <c r="H296" s="14"/>
+    </row>
+    <row r="297" spans="2:8">
       <c r="B297" s="4"/>
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="14"/>
       <c r="F297" s="14"/>
       <c r="G297" s="14"/>
-    </row>
-    <row r="298" spans="2:7">
+      <c r="H297" s="14"/>
+    </row>
+    <row r="298" spans="2:8">
       <c r="B298" s="4"/>
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="14"/>
       <c r="F298" s="14"/>
       <c r="G298" s="14"/>
-    </row>
-    <row r="299" spans="2:7">
+      <c r="H298" s="14"/>
+    </row>
+    <row r="299" spans="2:8">
       <c r="B299" s="4"/>
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="14"/>
       <c r="F299" s="14"/>
       <c r="G299" s="14"/>
-    </row>
-    <row r="300" spans="2:7">
+      <c r="H299" s="14"/>
+    </row>
+    <row r="300" spans="2:8">
       <c r="B300" s="4"/>
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="14"/>
       <c r="F300" s="14"/>
       <c r="G300" s="14"/>
-    </row>
-    <row r="301" spans="2:7">
+      <c r="H300" s="14"/>
+    </row>
+    <row r="301" spans="2:8">
       <c r="B301" s="4"/>
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="14"/>
       <c r="F301" s="14"/>
       <c r="G301" s="14"/>
-    </row>
-    <row r="302" spans="2:7">
+      <c r="H301" s="14"/>
+    </row>
+    <row r="302" spans="2:8">
       <c r="B302" s="5"/>
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
       <c r="E302" s="14"/>
       <c r="F302" s="14"/>
       <c r="G302" s="14"/>
-    </row>
-    <row r="303" spans="2:7">
+      <c r="H302" s="14"/>
+    </row>
+    <row r="303" spans="2:8">
       <c r="B303" s="4"/>
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
       <c r="E303" s="14"/>
       <c r="F303" s="14"/>
       <c r="G303" s="14"/>
-    </row>
-    <row r="304" spans="2:7">
+      <c r="H303" s="14"/>
+    </row>
+    <row r="304" spans="2:8">
       <c r="B304" s="5"/>
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
       <c r="E304" s="14"/>
       <c r="F304" s="14"/>
       <c r="G304" s="14"/>
-    </row>
-    <row r="305" spans="2:7">
+      <c r="H304" s="14"/>
+    </row>
+    <row r="305" spans="2:8">
       <c r="B305" s="5"/>
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
       <c r="E305" s="14"/>
       <c r="F305" s="14"/>
       <c r="G305" s="14"/>
-    </row>
-    <row r="306" spans="2:7">
+      <c r="H305" s="14"/>
+    </row>
+    <row r="306" spans="2:8">
       <c r="B306" s="4"/>
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
       <c r="E306" s="14"/>
       <c r="F306" s="14"/>
       <c r="G306" s="14"/>
-    </row>
-    <row r="307" spans="2:7">
+      <c r="H306" s="14"/>
+    </row>
+    <row r="307" spans="2:8">
       <c r="B307" s="4"/>
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
       <c r="E307" s="14"/>
       <c r="F307" s="14"/>
       <c r="G307" s="14"/>
-    </row>
-    <row r="308" spans="2:7">
+      <c r="H307" s="14"/>
+    </row>
+    <row r="308" spans="2:8">
       <c r="B308" s="4"/>
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
       <c r="E308" s="14"/>
       <c r="F308" s="14"/>
       <c r="G308" s="14"/>
-    </row>
-    <row r="309" spans="2:7">
+      <c r="H308" s="14"/>
+    </row>
+    <row r="309" spans="2:8">
       <c r="B309" s="4"/>
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
       <c r="E309" s="13"/>
       <c r="F309" s="13"/>
       <c r="G309" s="13"/>
-    </row>
-    <row r="310" spans="2:7">
+      <c r="H309" s="13"/>
+    </row>
+    <row r="310" spans="2:8">
       <c r="B310" s="4"/>
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
       <c r="E310" s="14"/>
       <c r="F310" s="14"/>
       <c r="G310" s="14"/>
-    </row>
-    <row r="311" spans="2:7">
+      <c r="H310" s="14"/>
+    </row>
+    <row r="311" spans="2:8">
       <c r="B311" s="4"/>
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
       <c r="E311" s="14"/>
       <c r="F311" s="14"/>
       <c r="G311" s="14"/>
-    </row>
-    <row r="312" spans="2:7">
+      <c r="H311" s="14"/>
+    </row>
+    <row r="312" spans="2:8">
       <c r="B312" s="4"/>
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
       <c r="E312" s="14"/>
       <c r="F312" s="14"/>
       <c r="G312" s="14"/>
-    </row>
-    <row r="313" spans="2:7">
+      <c r="H312" s="14"/>
+    </row>
+    <row r="313" spans="2:8">
       <c r="B313" s="4"/>
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
       <c r="E313" s="14"/>
       <c r="F313" s="14"/>
       <c r="G313" s="14"/>
-    </row>
-    <row r="314" spans="2:7">
+      <c r="H313" s="14"/>
+    </row>
+    <row r="314" spans="2:8">
       <c r="B314" s="4"/>
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
       <c r="E314" s="14"/>
       <c r="F314" s="14"/>
       <c r="G314" s="14"/>
-    </row>
-    <row r="315" spans="2:7">
+      <c r="H314" s="14"/>
+    </row>
+    <row r="315" spans="2:8">
       <c r="B315" s="4"/>
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
       <c r="E315" s="14"/>
       <c r="F315" s="14"/>
       <c r="G315" s="14"/>
-    </row>
-    <row r="316" spans="2:7">
+      <c r="H315" s="14"/>
+    </row>
+    <row r="316" spans="2:8">
       <c r="B316" s="4"/>
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
       <c r="E316" s="14"/>
       <c r="F316" s="14"/>
       <c r="G316" s="14"/>
-    </row>
-    <row r="317" spans="2:7">
+      <c r="H316" s="14"/>
+    </row>
+    <row r="317" spans="2:8">
       <c r="B317" s="4"/>
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
       <c r="E317" s="14"/>
       <c r="F317" s="14"/>
       <c r="G317" s="14"/>
-    </row>
-    <row r="318" spans="2:7">
+      <c r="H317" s="14"/>
+    </row>
+    <row r="318" spans="2:8">
       <c r="B318" s="4"/>
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
       <c r="E318" s="14"/>
       <c r="F318" s="14"/>
       <c r="G318" s="14"/>
-    </row>
-    <row r="319" spans="2:7">
+      <c r="H318" s="14"/>
+    </row>
+    <row r="319" spans="2:8">
       <c r="B319" s="5"/>
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
       <c r="E319" s="14"/>
       <c r="F319" s="14"/>
       <c r="G319" s="14"/>
-    </row>
-    <row r="320" spans="2:7">
+      <c r="H319" s="14"/>
+    </row>
+    <row r="320" spans="2:8">
       <c r="B320" s="4"/>
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
       <c r="E320" s="14"/>
       <c r="F320" s="14"/>
       <c r="G320" s="14"/>
-    </row>
-    <row r="321" spans="2:7">
+      <c r="H320" s="14"/>
+    </row>
+    <row r="321" spans="2:8">
       <c r="B321" s="5"/>
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
       <c r="E321" s="14"/>
       <c r="F321" s="14"/>
       <c r="G321" s="14"/>
-    </row>
-    <row r="322" spans="2:7">
+      <c r="H321" s="14"/>
+    </row>
+    <row r="322" spans="2:8">
       <c r="B322" s="5"/>
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
       <c r="E322" s="14"/>
       <c r="F322" s="14"/>
       <c r="G322" s="14"/>
-    </row>
-    <row r="323" spans="2:7">
+      <c r="H322" s="14"/>
+    </row>
+    <row r="323" spans="2:8">
       <c r="B323" s="4"/>
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
       <c r="E323" s="14"/>
       <c r="F323" s="14"/>
       <c r="G323" s="14"/>
-    </row>
-    <row r="324" spans="2:7">
+      <c r="H323" s="14"/>
+    </row>
+    <row r="324" spans="2:8">
       <c r="B324" s="4"/>
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
       <c r="E324" s="14"/>
       <c r="F324" s="14"/>
       <c r="G324" s="14"/>
-    </row>
-    <row r="325" spans="2:7">
+      <c r="H324" s="14"/>
+    </row>
+    <row r="325" spans="2:8">
       <c r="B325" s="4"/>
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
       <c r="E325" s="14"/>
       <c r="F325" s="14"/>
       <c r="G325" s="14"/>
-    </row>
-    <row r="326" spans="2:7">
+      <c r="H325" s="14"/>
+    </row>
+    <row r="326" spans="2:8">
       <c r="B326" s="4"/>
       <c r="C326" s="19"/>
       <c r="D326" s="19"/>
       <c r="E326" s="13"/>
       <c r="F326" s="13"/>
       <c r="G326" s="13"/>
-    </row>
-    <row r="327" spans="2:7">
+      <c r="H326" s="13"/>
+    </row>
+    <row r="327" spans="2:8">
       <c r="B327" s="4"/>
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
       <c r="E327" s="14"/>
       <c r="F327" s="14"/>
       <c r="G327" s="14"/>
-    </row>
-    <row r="328" spans="2:7">
+      <c r="H327" s="14"/>
+    </row>
+    <row r="328" spans="2:8">
       <c r="B328" s="4"/>
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
       <c r="E328" s="14"/>
       <c r="F328" s="14"/>
       <c r="G328" s="14"/>
-    </row>
-    <row r="329" spans="2:7">
+      <c r="H328" s="14"/>
+    </row>
+    <row r="329" spans="2:8">
       <c r="B329" s="4"/>
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
       <c r="E329" s="14"/>
       <c r="F329" s="14"/>
       <c r="G329" s="14"/>
-    </row>
-    <row r="330" spans="2:7">
+      <c r="H329" s="14"/>
+    </row>
+    <row r="330" spans="2:8">
       <c r="B330" s="4"/>
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
       <c r="E330" s="14"/>
       <c r="F330" s="14"/>
       <c r="G330" s="14"/>
-    </row>
-    <row r="331" spans="2:7">
+      <c r="H330" s="14"/>
+    </row>
+    <row r="331" spans="2:8">
       <c r="B331" s="4"/>
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
       <c r="E331" s="14"/>
       <c r="F331" s="14"/>
       <c r="G331" s="14"/>
-    </row>
-    <row r="332" spans="2:7">
+      <c r="H331" s="14"/>
+    </row>
+    <row r="332" spans="2:8">
       <c r="B332" s="4"/>
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
       <c r="E332" s="14"/>
       <c r="F332" s="14"/>
       <c r="G332" s="14"/>
-    </row>
-    <row r="333" spans="2:7">
+      <c r="H332" s="14"/>
+    </row>
+    <row r="333" spans="2:8">
       <c r="B333" s="4"/>
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
       <c r="E333" s="14"/>
       <c r="F333" s="14"/>
       <c r="G333" s="14"/>
-    </row>
-    <row r="334" spans="2:7">
+      <c r="H333" s="14"/>
+    </row>
+    <row r="334" spans="2:8">
       <c r="B334" s="4"/>
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
       <c r="E334" s="14"/>
       <c r="F334" s="14"/>
       <c r="G334" s="14"/>
-    </row>
-    <row r="335" spans="2:7">
+      <c r="H334" s="14"/>
+    </row>
+    <row r="335" spans="2:8">
       <c r="B335" s="4"/>
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
       <c r="E335" s="14"/>
       <c r="F335" s="14"/>
       <c r="G335" s="14"/>
-    </row>
-    <row r="336" spans="2:7">
+      <c r="H335" s="14"/>
+    </row>
+    <row r="336" spans="2:8">
       <c r="B336" s="5"/>
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
       <c r="E336" s="14"/>
       <c r="F336" s="14"/>
       <c r="G336" s="14"/>
-    </row>
-    <row r="337" spans="2:7">
+      <c r="H336" s="14"/>
+    </row>
+    <row r="337" spans="2:8">
       <c r="B337" s="4"/>
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
       <c r="E337" s="14"/>
       <c r="F337" s="14"/>
       <c r="G337" s="14"/>
-    </row>
-    <row r="338" spans="2:7">
+      <c r="H337" s="14"/>
+    </row>
+    <row r="338" spans="2:8">
       <c r="B338" s="5"/>
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
       <c r="E338" s="14"/>
       <c r="F338" s="14"/>
       <c r="G338" s="14"/>
-    </row>
-    <row r="339" spans="2:7">
+      <c r="H338" s="14"/>
+    </row>
+    <row r="339" spans="2:8">
       <c r="B339" s="5"/>
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
       <c r="E339" s="14"/>
       <c r="F339" s="14"/>
       <c r="G339" s="14"/>
-    </row>
-    <row r="340" spans="2:7">
+      <c r="H339" s="14"/>
+    </row>
+    <row r="340" spans="2:8">
       <c r="B340" s="4"/>
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
       <c r="E340" s="14"/>
       <c r="F340" s="14"/>
       <c r="G340" s="14"/>
-    </row>
-    <row r="341" spans="2:7">
+      <c r="H340" s="14"/>
+    </row>
+    <row r="341" spans="2:8">
       <c r="B341" s="4"/>
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
       <c r="E341" s="14"/>
       <c r="F341" s="14"/>
       <c r="G341" s="14"/>
-    </row>
-    <row r="342" spans="2:7">
+      <c r="H341" s="14"/>
+    </row>
+    <row r="342" spans="2:8">
       <c r="B342" s="4"/>
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
       <c r="E342" s="14"/>
       <c r="F342" s="14"/>
       <c r="G342" s="14"/>
-    </row>
-    <row r="343" spans="2:7">
+      <c r="H342" s="14"/>
+    </row>
+    <row r="343" spans="2:8">
       <c r="B343" s="4"/>
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
       <c r="E343" s="14"/>
       <c r="F343" s="14"/>
       <c r="G343" s="14"/>
-    </row>
-    <row r="344" spans="2:7">
+      <c r="H343" s="14"/>
+    </row>
+    <row r="344" spans="2:8">
       <c r="B344" s="4"/>
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
       <c r="E344" s="14"/>
       <c r="F344" s="14"/>
       <c r="G344" s="14"/>
-    </row>
-    <row r="345" spans="2:7">
+      <c r="H344" s="14"/>
+    </row>
+    <row r="345" spans="2:8">
       <c r="B345" s="4"/>
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
       <c r="E345" s="14"/>
       <c r="F345" s="14"/>
       <c r="G345" s="14"/>
-    </row>
-    <row r="346" spans="2:7">
+      <c r="H345" s="14"/>
+    </row>
+    <row r="346" spans="2:8">
       <c r="B346" s="4"/>
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
       <c r="E346" s="14"/>
       <c r="F346" s="14"/>
       <c r="G346" s="14"/>
-    </row>
-    <row r="347" spans="2:7">
+      <c r="H346" s="14"/>
+    </row>
+    <row r="347" spans="2:8">
       <c r="B347" s="4"/>
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
       <c r="E347" s="14"/>
       <c r="F347" s="14"/>
       <c r="G347" s="14"/>
-    </row>
-    <row r="348" spans="2:7">
+      <c r="H347" s="14"/>
+    </row>
+    <row r="348" spans="2:8">
       <c r="B348" s="4"/>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
       <c r="E348" s="14"/>
       <c r="F348" s="14"/>
       <c r="G348" s="14"/>
-    </row>
-    <row r="349" spans="2:7">
+      <c r="H348" s="14"/>
+    </row>
+    <row r="349" spans="2:8">
       <c r="B349" s="4"/>
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
       <c r="E349" s="14"/>
       <c r="F349" s="14"/>
       <c r="G349" s="14"/>
-    </row>
-    <row r="350" spans="2:7">
+      <c r="H349" s="14"/>
+    </row>
+    <row r="350" spans="2:8">
       <c r="B350" s="4"/>
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
       <c r="E350" s="14"/>
       <c r="F350" s="14"/>
       <c r="G350" s="14"/>
-    </row>
-    <row r="351" spans="2:7">
+      <c r="H350" s="14"/>
+    </row>
+    <row r="351" spans="2:8">
       <c r="B351" s="4"/>
       <c r="C351" s="19"/>
       <c r="D351" s="19"/>
       <c r="E351" s="13"/>
       <c r="F351" s="13"/>
       <c r="G351" s="13"/>
-    </row>
-    <row r="352" spans="2:7">
+      <c r="H351" s="13"/>
+    </row>
+    <row r="352" spans="2:8">
       <c r="B352" s="4" t="s">
         <v>49</v>
       </c>
@@ -7020,8 +7816,11 @@
       <c r="G352" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="353" spans="2:7">
+      <c r="H352" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="353" spans="2:8">
       <c r="B353" s="4" t="s">
         <v>50</v>
       </c>
@@ -7040,8 +7839,11 @@
       <c r="G353" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="354" spans="2:7">
+      <c r="H353" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="354" spans="2:8">
       <c r="B354" s="4" t="s">
         <v>129</v>
       </c>
@@ -7058,8 +7860,11 @@
       <c r="G354" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="355" spans="2:7">
+      <c r="H354" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="355" spans="2:8">
       <c r="B355" s="4" t="s">
         <v>130</v>
       </c>
@@ -7072,16 +7877,18 @@
       <c r="E355" s="13"/>
       <c r="F355" s="13"/>
       <c r="G355" s="13"/>
-    </row>
-    <row r="356" spans="2:7">
+      <c r="H355" s="13"/>
+    </row>
+    <row r="356" spans="2:8">
       <c r="B356" s="4"/>
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
       <c r="E356" s="13"/>
       <c r="F356" s="13"/>
       <c r="G356" s="13"/>
-    </row>
-    <row r="357" spans="2:7">
+      <c r="H356" s="13"/>
+    </row>
+    <row r="357" spans="2:8">
       <c r="B357" s="4" t="s">
         <v>131</v>
       </c>
@@ -7092,8 +7899,9 @@
       <c r="E357" s="13"/>
       <c r="F357" s="13"/>
       <c r="G357" s="13"/>
-    </row>
-    <row r="358" spans="2:7">
+      <c r="H357" s="13"/>
+    </row>
+    <row r="358" spans="2:8">
       <c r="B358" s="4" t="s">
         <v>132</v>
       </c>
@@ -7104,8 +7912,9 @@
       <c r="E358" s="13"/>
       <c r="F358" s="13"/>
       <c r="G358" s="13"/>
-    </row>
-    <row r="359" spans="2:7">
+      <c r="H358" s="13"/>
+    </row>
+    <row r="359" spans="2:8">
       <c r="B359" s="4" t="s">
         <v>133</v>
       </c>
@@ -7116,8 +7925,9 @@
       <c r="E359" s="13"/>
       <c r="F359" s="13"/>
       <c r="G359" s="13"/>
-    </row>
-    <row r="360" spans="2:7">
+      <c r="H359" s="13"/>
+    </row>
+    <row r="360" spans="2:8">
       <c r="B360" s="4" t="s">
         <v>134</v>
       </c>
@@ -7128,8 +7938,9 @@
       <c r="E360" s="13"/>
       <c r="F360" s="13"/>
       <c r="G360" s="13"/>
-    </row>
-    <row r="361" spans="2:7">
+      <c r="H360" s="13"/>
+    </row>
+    <row r="361" spans="2:8">
       <c r="B361" s="4" t="s">
         <v>135</v>
       </c>
@@ -7140,16 +7951,18 @@
       <c r="E361" s="13"/>
       <c r="F361" s="13"/>
       <c r="G361" s="13"/>
-    </row>
-    <row r="362" spans="2:7">
+      <c r="H361" s="13"/>
+    </row>
+    <row r="362" spans="2:8">
       <c r="B362" s="4"/>
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
       <c r="E362" s="13"/>
       <c r="F362" s="13"/>
       <c r="G362" s="13"/>
-    </row>
-    <row r="363" spans="2:7">
+      <c r="H362" s="13"/>
+    </row>
+    <row r="363" spans="2:8">
       <c r="B363" s="4" t="s">
         <v>131</v>
       </c>
@@ -7160,8 +7973,9 @@
       <c r="E363" s="13"/>
       <c r="F363" s="13"/>
       <c r="G363" s="13"/>
-    </row>
-    <row r="364" spans="2:7">
+      <c r="H363" s="13"/>
+    </row>
+    <row r="364" spans="2:8">
       <c r="B364" s="4" t="s">
         <v>132</v>
       </c>
@@ -7172,8 +7986,9 @@
       <c r="E364" s="13"/>
       <c r="F364" s="13"/>
       <c r="G364" s="13"/>
-    </row>
-    <row r="365" spans="2:7">
+      <c r="H364" s="13"/>
+    </row>
+    <row r="365" spans="2:8">
       <c r="B365" s="4" t="s">
         <v>133</v>
       </c>
@@ -7184,8 +7999,9 @@
       <c r="E365" s="13"/>
       <c r="F365" s="13"/>
       <c r="G365" s="13"/>
-    </row>
-    <row r="366" spans="2:7">
+      <c r="H365" s="13"/>
+    </row>
+    <row r="366" spans="2:8">
       <c r="B366" s="4" t="s">
         <v>134</v>
       </c>
@@ -7196,8 +8012,9 @@
       <c r="E366" s="13"/>
       <c r="F366" s="13"/>
       <c r="G366" s="13"/>
-    </row>
-    <row r="367" spans="2:7">
+      <c r="H366" s="13"/>
+    </row>
+    <row r="367" spans="2:8">
       <c r="B367" s="4" t="s">
         <v>135</v>
       </c>
@@ -7208,16 +8025,18 @@
       <c r="E367" s="13"/>
       <c r="F367" s="13"/>
       <c r="G367" s="13"/>
-    </row>
-    <row r="368" spans="2:7">
+      <c r="H367" s="13"/>
+    </row>
+    <row r="368" spans="2:8">
       <c r="B368" s="4"/>
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
       <c r="E368" s="13"/>
       <c r="F368" s="13"/>
       <c r="G368" s="13"/>
-    </row>
-    <row r="369" spans="2:7">
+      <c r="H368" s="13"/>
+    </row>
+    <row r="369" spans="2:8">
       <c r="B369" s="4" t="s">
         <v>136</v>
       </c>
@@ -7230,8 +8049,9 @@
       <c r="E369" s="13"/>
       <c r="F369" s="13"/>
       <c r="G369" s="13"/>
-    </row>
-    <row r="370" spans="2:7">
+      <c r="H369" s="13"/>
+    </row>
+    <row r="370" spans="2:8">
       <c r="B370" s="4" t="s">
         <v>137</v>
       </c>
@@ -7244,8 +8064,9 @@
       <c r="E370" s="13"/>
       <c r="F370" s="13"/>
       <c r="G370" s="13"/>
-    </row>
-    <row r="371" spans="2:7">
+      <c r="H370" s="13"/>
+    </row>
+    <row r="371" spans="2:8">
       <c r="B371" s="4" t="s">
         <v>138</v>
       </c>
@@ -7258,16 +8079,18 @@
       <c r="E371" s="13"/>
       <c r="F371" s="13"/>
       <c r="G371" s="13"/>
-    </row>
-    <row r="372" spans="2:7">
+      <c r="H371" s="13"/>
+    </row>
+    <row r="372" spans="2:8">
       <c r="B372" s="4"/>
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
       <c r="E372" s="13"/>
       <c r="F372" s="13"/>
       <c r="G372" s="13"/>
-    </row>
-    <row r="373" spans="2:7">
+      <c r="H372" s="13"/>
+    </row>
+    <row r="373" spans="2:8">
       <c r="B373" s="4" t="s">
         <v>136</v>
       </c>
@@ -7280,8 +8103,9 @@
       <c r="E373" s="13"/>
       <c r="F373" s="13"/>
       <c r="G373" s="13"/>
-    </row>
-    <row r="374" spans="2:7">
+      <c r="H373" s="13"/>
+    </row>
+    <row r="374" spans="2:8">
       <c r="B374" s="4" t="s">
         <v>137</v>
       </c>
@@ -7294,8 +8118,9 @@
       <c r="E374" s="13"/>
       <c r="F374" s="13"/>
       <c r="G374" s="13"/>
-    </row>
-    <row r="375" spans="2:7">
+      <c r="H374" s="13"/>
+    </row>
+    <row r="375" spans="2:8">
       <c r="B375" s="4" t="s">
         <v>138</v>
       </c>
@@ -7308,214 +8133,241 @@
       <c r="E375" s="13"/>
       <c r="F375" s="13"/>
       <c r="G375" s="13"/>
-    </row>
-    <row r="376" spans="2:7">
+      <c r="H375" s="13"/>
+    </row>
+    <row r="376" spans="2:8">
       <c r="B376" s="4"/>
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
       <c r="E376" s="13"/>
       <c r="F376" s="13"/>
       <c r="G376" s="13"/>
-    </row>
-    <row r="377" spans="2:7">
+      <c r="H376" s="13"/>
+    </row>
+    <row r="377" spans="2:8">
       <c r="B377" s="4"/>
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
       <c r="E377" s="13"/>
       <c r="F377" s="13"/>
       <c r="G377" s="13"/>
-    </row>
-    <row r="378" spans="2:7">
+      <c r="H377" s="13"/>
+    </row>
+    <row r="378" spans="2:8">
       <c r="B378" s="4"/>
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
       <c r="E378" s="13"/>
       <c r="F378" s="13"/>
       <c r="G378" s="13"/>
-    </row>
-    <row r="379" spans="2:7">
+      <c r="H378" s="13"/>
+    </row>
+    <row r="379" spans="2:8">
       <c r="B379" s="4"/>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
       <c r="E379" s="13"/>
       <c r="F379" s="13"/>
       <c r="G379" s="13"/>
-    </row>
-    <row r="380" spans="2:7">
+      <c r="H379" s="13"/>
+    </row>
+    <row r="380" spans="2:8">
       <c r="B380" s="4"/>
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
       <c r="E380" s="13"/>
       <c r="F380" s="13"/>
       <c r="G380" s="13"/>
-    </row>
-    <row r="381" spans="2:7">
+      <c r="H380" s="13"/>
+    </row>
+    <row r="381" spans="2:8">
       <c r="B381" s="4"/>
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
       <c r="E381" s="13"/>
       <c r="F381" s="13"/>
       <c r="G381" s="13"/>
-    </row>
-    <row r="382" spans="2:7">
+      <c r="H381" s="13"/>
+    </row>
+    <row r="382" spans="2:8">
       <c r="B382" s="4"/>
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
       <c r="E382" s="13"/>
       <c r="F382" s="13"/>
       <c r="G382" s="13"/>
-    </row>
-    <row r="383" spans="2:7">
+      <c r="H382" s="13"/>
+    </row>
+    <row r="383" spans="2:8">
       <c r="B383" s="4"/>
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
       <c r="E383" s="13"/>
       <c r="F383" s="13"/>
       <c r="G383" s="13"/>
-    </row>
-    <row r="384" spans="2:7">
+      <c r="H383" s="13"/>
+    </row>
+    <row r="384" spans="2:8">
       <c r="B384" s="4"/>
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
       <c r="E384" s="13"/>
       <c r="F384" s="13"/>
       <c r="G384" s="13"/>
-    </row>
-    <row r="385" spans="2:7">
+      <c r="H384" s="13"/>
+    </row>
+    <row r="385" spans="2:8">
       <c r="B385" s="4"/>
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
       <c r="E385" s="13"/>
       <c r="F385" s="13"/>
       <c r="G385" s="13"/>
-    </row>
-    <row r="386" spans="2:7">
+      <c r="H385" s="13"/>
+    </row>
+    <row r="386" spans="2:8">
       <c r="B386" s="4"/>
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
       <c r="E386" s="13"/>
       <c r="F386" s="13"/>
       <c r="G386" s="13"/>
-    </row>
-    <row r="387" spans="2:7">
+      <c r="H386" s="13"/>
+    </row>
+    <row r="387" spans="2:8">
       <c r="B387" s="4"/>
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
       <c r="E387" s="13"/>
       <c r="F387" s="13"/>
       <c r="G387" s="13"/>
-    </row>
-    <row r="388" spans="2:7">
+      <c r="H387" s="13"/>
+    </row>
+    <row r="388" spans="2:8">
       <c r="B388" s="4"/>
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
       <c r="E388" s="13"/>
       <c r="F388" s="13"/>
       <c r="G388" s="13"/>
-    </row>
-    <row r="389" spans="2:7">
+      <c r="H388" s="13"/>
+    </row>
+    <row r="389" spans="2:8">
       <c r="B389" s="4"/>
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
       <c r="E389" s="13"/>
       <c r="F389" s="13"/>
       <c r="G389" s="13"/>
-    </row>
-    <row r="390" spans="2:7">
+      <c r="H389" s="13"/>
+    </row>
+    <row r="390" spans="2:8">
       <c r="B390" s="4"/>
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
       <c r="E390" s="13"/>
       <c r="F390" s="13"/>
       <c r="G390" s="13"/>
-    </row>
-    <row r="391" spans="2:7">
+      <c r="H390" s="13"/>
+    </row>
+    <row r="391" spans="2:8">
       <c r="B391" s="4"/>
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
       <c r="E391" s="13"/>
       <c r="F391" s="13"/>
       <c r="G391" s="13"/>
-    </row>
-    <row r="392" spans="2:7">
+      <c r="H391" s="13"/>
+    </row>
+    <row r="392" spans="2:8">
       <c r="B392" s="4"/>
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
       <c r="E392" s="13"/>
       <c r="F392" s="13"/>
       <c r="G392" s="13"/>
-    </row>
-    <row r="393" spans="2:7">
+      <c r="H392" s="13"/>
+    </row>
+    <row r="393" spans="2:8">
       <c r="B393" s="4"/>
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
       <c r="E393" s="13"/>
       <c r="F393" s="13"/>
       <c r="G393" s="13"/>
-    </row>
-    <row r="394" spans="2:7">
+      <c r="H393" s="13"/>
+    </row>
+    <row r="394" spans="2:8">
       <c r="B394" s="4"/>
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
       <c r="E394" s="13"/>
       <c r="F394" s="13"/>
       <c r="G394" s="13"/>
-    </row>
-    <row r="395" spans="2:7">
+      <c r="H394" s="13"/>
+    </row>
+    <row r="395" spans="2:8">
       <c r="B395" s="4"/>
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
       <c r="E395" s="13"/>
       <c r="F395" s="13"/>
       <c r="G395" s="13"/>
-    </row>
-    <row r="396" spans="2:7">
+      <c r="H395" s="13"/>
+    </row>
+    <row r="396" spans="2:8">
       <c r="B396" s="4"/>
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
       <c r="E396" s="13"/>
       <c r="F396" s="13"/>
       <c r="G396" s="13"/>
-    </row>
-    <row r="397" spans="2:7">
+      <c r="H396" s="13"/>
+    </row>
+    <row r="397" spans="2:8">
       <c r="B397" s="9"/>
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
       <c r="E397" s="13"/>
       <c r="F397" s="13"/>
       <c r="G397" s="13"/>
-    </row>
-    <row r="398" spans="2:7">
+      <c r="H397" s="13"/>
+    </row>
+    <row r="398" spans="2:8">
       <c r="B398" s="9"/>
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
       <c r="E398" s="13"/>
       <c r="F398" s="13"/>
       <c r="G398" s="13"/>
-    </row>
-    <row r="399" spans="2:7">
+      <c r="H398" s="13"/>
+    </row>
+    <row r="399" spans="2:8">
       <c r="B399" s="9"/>
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
       <c r="E399" s="13"/>
       <c r="F399" s="13"/>
       <c r="G399" s="13"/>
-    </row>
-    <row r="400" spans="2:7">
+      <c r="H399" s="13"/>
+    </row>
+    <row r="400" spans="2:8">
       <c r="B400" s="9"/>
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
       <c r="E400" s="13"/>
       <c r="F400" s="13"/>
       <c r="G400" s="13"/>
-    </row>
-    <row r="401" spans="2:7">
+      <c r="H400" s="13"/>
+    </row>
+    <row r="401" spans="2:8">
       <c r="B401" s="4"/>
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
       <c r="E401" s="13"/>
       <c r="F401" s="13"/>
       <c r="G401" s="13"/>
+      <c r="H401" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="E1:G401" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}"/>

--- a/testBrew.xlsx
+++ b/testBrew.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\Agentic World\TestDB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SETUMHNE\Downloads\myLearning\gitPlayGround\TestDB\git_CodePlayground\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F535A0A9-3B48-4134-A4A9-548BA04D1965}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4747BC-9C74-40E9-AFBB-C2D094475637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="585" yWindow="15" windowWidth="27870" windowHeight="16440" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2440DDF5-C456-4655-B2B4-B11D9C3116FA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$1:$G$401</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$E$2:$K$401</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,8 +50,7 @@
     <author>tc={932F2D4C-D793-48A0-8BED-5F38FC3D7DAF}</author>
     <author>tc={E1E2F944-CF9F-4061-9330-99AC06440908}</author>
     <author>tc={F8073023-E3D6-437F-A368-4B60DA804058}</author>
-    <author>tc={DA4D74A7-C735-4500-AC22-C9E4A5C304D0}</author>
-    <author>tc={72ED2E73-21B1-4D03-AEDB-85B3EA8C35E8}</author>
+    <author>tc={ED46C518-7286-47D1-963D-3F59595A0F45}</author>
     <author>tc={FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}</author>
     <author>tc={C29E9803-A59F-4197-99DC-10131D1A8691}</author>
     <author>tc={F05B5C03-D80C-44EE-911F-FD4F08369CD1}</author>
@@ -61,19 +60,11 @@
   <commentList>
     <comment ref="B110" authorId="0" shapeId="0" xr:uid="{73D4B7F6-243F-4FF2-99C8-413E3B588F2F}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PIT220-1 / PIT221-1</t>
-        </r>
       </text>
     </comment>
     <comment ref="E110" authorId="1" shapeId="0" xr:uid="{ACEAC60E-563F-4328-B54F-2D31DA895568}">
@@ -132,38 +123,64 @@
         </r>
       </text>
     </comment>
-    <comment ref="B116" authorId="2" shapeId="0" xr:uid="{4608516B-34DA-4E87-85F1-345F80F368D2}">
+    <comment ref="I110" authorId="1" shapeId="0" xr:uid="{52A056F7-EBFA-4DD8-9ED8-A662BE57EA32}">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>[Threaded comment]
+          <t>PIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J110" authorId="1" shapeId="0" xr:uid="{6DC0557E-87DA-4071-BE3B-0BAC8D10C192}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K110" authorId="1" shapeId="0" xr:uid="{F8D448DB-CECF-49C0-8AF3-F3C3D638CD0F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B116" authorId="2" shapeId="0" xr:uid="{4608516B-34DA-4E87-85F1-345F80F368D2}">
+      <text>
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PIT221-1 / PIT220-1</t>
-        </r>
       </text>
     </comment>
     <comment ref="B130" authorId="3" shapeId="0" xr:uid="{37D13463-1186-4BC6-8059-F81F589B8465}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PCV220-1 / PCV221-1</t>
-        </r>
       </text>
     </comment>
     <comment ref="E130" authorId="1" shapeId="0" xr:uid="{A163B90D-1EF5-443F-899F-87AE8DB0F188}">
@@ -222,38 +239,64 @@
         </r>
       </text>
     </comment>
-    <comment ref="B132" authorId="4" shapeId="0" xr:uid="{330CC50C-0FF1-4C20-92A7-B1A460F72FE0}">
+    <comment ref="I130" authorId="1" shapeId="0" xr:uid="{B028D9C4-8A91-4F1A-B03F-F95E53612E68}">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>[Threaded comment]
+          <t>PCV220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J130" authorId="1" shapeId="0" xr:uid="{B653603D-B8C4-499E-8D79-0EDF1FEBCC0F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PCV220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K130" authorId="1" shapeId="0" xr:uid="{36EA815E-49A5-4F8A-BD6C-F23647CB58BF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PCV220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B132" authorId="4" shapeId="0" xr:uid="{330CC50C-0FF1-4C20-92A7-B1A460F72FE0}">
+      <text>
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 PCV221-1 / PCV220-1</t>
-        </r>
       </text>
     </comment>
     <comment ref="B139" authorId="5" shapeId="0" xr:uid="{C128BBFA-0A9E-4E10-9DCF-02753B677457}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 ST740/ST741</t>
-        </r>
       </text>
     </comment>
     <comment ref="E139" authorId="1" shapeId="0" xr:uid="{71DF5CC9-8C1C-486E-B5BB-3BCC7CA84727}">
@@ -312,38 +355,106 @@
         </r>
       </text>
     </comment>
-    <comment ref="B187" authorId="6" shapeId="0" xr:uid="{FAC71602-7205-4D4E-A8A7-63E13947D7F3}">
+    <comment ref="I139" authorId="1" shapeId="0" xr:uid="{262C6CE9-4124-4B0E-AB22-44D9BE213916}">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>[Threaded comment]
+          <t>ST740</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J139" authorId="1" shapeId="0" xr:uid="{6091D210-338E-4D61-9BA8-CBA7E63E32F0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ST740</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K139" authorId="1" shapeId="0" xr:uid="{0AC2DD8A-E157-4484-BA93-7CC58784A7F0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>ST740</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B187" authorId="6" shapeId="0" xr:uid="{FAC71602-7205-4D4E-A8A7-63E13947D7F3}">
+      <text>
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative tag labels:
 LS422b / LS423</t>
+      </text>
+    </comment>
+    <comment ref="I187" authorId="1" shapeId="0" xr:uid="{7BE8016D-9A39-41FB-B16C-9D5E1B3F75EA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>LS422b</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J187" authorId="1" shapeId="0" xr:uid="{756E087A-7C22-4FC3-8CE9-D90E6AA482A2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>LS422b</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K187" authorId="1" shapeId="0" xr:uid="{4AC88A31-E21E-456E-9A3C-2428DBFEE87A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>LS423</t>
         </r>
       </text>
     </comment>
     <comment ref="B212" authorId="7" shapeId="0" xr:uid="{4A8C6723-E87B-4DCF-BC82-3EEAFFA13634}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 YT750/YT752</t>
-        </r>
       </text>
     </comment>
     <comment ref="E212" authorId="1" shapeId="0" xr:uid="{7A748396-5D90-45A2-BCDA-09E9D00EB824}">
@@ -402,21 +513,55 @@
         </r>
       </text>
     </comment>
-    <comment ref="B214" authorId="8" shapeId="0" xr:uid="{932F2D4C-D793-48A0-8BED-5F38FC3D7DAF}">
+    <comment ref="I212" authorId="1" shapeId="0" xr:uid="{45C7977D-D581-4C81-BB31-F76C2214F7C8}">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>[Threaded comment]
+          <t>YT750</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J212" authorId="1" shapeId="0" xr:uid="{34094221-2B53-4421-950A-1CA3D200105A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>YT750</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K212" authorId="1" shapeId="0" xr:uid="{44C9CA7F-14F0-4702-89C0-C7EE1E25DBDE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>YT750</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B214" authorId="8" shapeId="0" xr:uid="{932F2D4C-D793-48A0-8BED-5F38FC3D7DAF}">
+      <text>
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 PT375-1/PT376-1</t>
-        </r>
       </text>
     </comment>
     <comment ref="F214" authorId="1" shapeId="0" xr:uid="{A7A9E8D1-727E-4B93-BDEB-E67DFF623450}">
@@ -461,82 +606,136 @@
         </r>
       </text>
     </comment>
-    <comment ref="B218" authorId="9" shapeId="0" xr:uid="{E1E2F944-CF9F-4061-9330-99AC06440908}">
+    <comment ref="I214" authorId="1" shapeId="0" xr:uid="{F36F2DF6-C8FC-4FD6-93EA-7ACB2DA57AF6}">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>[Threaded comment]
+          <t>PT376-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J214" authorId="1" shapeId="0" xr:uid="{51D8B727-8225-4795-BDE9-FF9194CD0E91}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PT376-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K214" authorId="1" shapeId="0" xr:uid="{441FD2D9-D0CD-4CD9-8D96-8BA081DEBB56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>PT376-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I216" authorId="1" shapeId="0" xr:uid="{17CB5577-3ABD-4AEA-83D7-68A683ADAE56}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT730a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J216" authorId="1" shapeId="0" xr:uid="{90ADF558-91A0-4E4C-808B-786CD0944716}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT730a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K216" authorId="1" shapeId="0" xr:uid="{F814AE73-B49C-4857-94D2-5D83D6E75CE1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT730a</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K217" authorId="1" shapeId="0" xr:uid="{8470B15F-7325-4951-83C8-82D183ACB1B9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT731A</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B218" authorId="9" shapeId="0" xr:uid="{E1E2F944-CF9F-4061-9330-99AC06440908}">
+      <text>
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative sensors, same PIW:
 TT731b/TT733</t>
-        </r>
       </text>
     </comment>
     <comment ref="F218" authorId="10" shapeId="0" xr:uid="{F8073023-E3D6-437F-A368-4B60DA804058}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Sensor: TT733</t>
-        </r>
       </text>
     </comment>
-    <comment ref="G218" authorId="11" shapeId="0" xr:uid="{A9D86EE3-DF9D-4BE8-AB28-2DFBCAEFC0D2}">
+    <comment ref="K218" authorId="11" shapeId="0" xr:uid="{ED46C518-7286-47D1-963D-3F59595A0F45}">
       <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="MS Sans Serif"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Sensor: TT733</t>
-        </r>
+    Sensor: TT731b</t>
       </text>
     </comment>
-    <comment ref="H218" authorId="12" shapeId="0" xr:uid="{FAD37F86-ED48-4D18-BA32-262C45C29066}">
+    <comment ref="B223" authorId="12" shapeId="0" xr:uid="{FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}">
       <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="MS Sans Serif"/>
-          </rPr>
-          <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Sensor: TT733</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B223" authorId="13" shapeId="0" xr:uid="{FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 TT410-1/TT412-1</t>
-        </r>
       </text>
     </comment>
     <comment ref="E223" authorId="1" shapeId="0" xr:uid="{3F0AF3B0-2ABB-45F3-8CF9-4442E029B36F}">
@@ -595,37 +794,63 @@
         </r>
       </text>
     </comment>
-    <comment ref="B243" authorId="14" shapeId="0" xr:uid="{C29E9803-A59F-4197-99DC-10131D1A8691}">
+    <comment ref="I223" authorId="1" shapeId="0" xr:uid="{68CA402B-928D-499F-B753-F2DB9222DC2E}">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>[Threaded comment]
+          <t>TT412-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J223" authorId="1" shapeId="0" xr:uid="{48F2AD4D-FA90-4530-9EA4-A06041D60053}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT412-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K223" authorId="1" shapeId="0" xr:uid="{6DFD1F1E-D97B-4BBD-86A1-DD1B642CAFFC}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>TT412-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B243" authorId="13" shapeId="0" xr:uid="{C29E9803-A59F-4197-99DC-10131D1A8691}">
+      <text>
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Old AV635b-1</t>
-        </r>
       </text>
     </comment>
-    <comment ref="B248" authorId="15" shapeId="0" xr:uid="{F05B5C03-D80C-44EE-911F-FD4F08369CD1}">
+    <comment ref="B248" authorId="14" shapeId="0" xr:uid="{F05B5C03-D80C-44EE-911F-FD4F08369CD1}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 AV375-1/AV376-1</t>
-        </r>
       </text>
     </comment>
     <comment ref="E248" authorId="1" shapeId="0" xr:uid="{7EF7BC57-4FCC-448F-8A09-38CD88A5340F}">
@@ -684,38 +909,64 @@
         </r>
       </text>
     </comment>
-    <comment ref="B252" authorId="16" shapeId="0" xr:uid="{6BE60107-F28C-41F1-A623-84DD5A6A045C}">
+    <comment ref="I248" authorId="1" shapeId="0" xr:uid="{F71E2F64-00C9-4D6B-B59C-139DE9588317}">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>[Threaded comment]
+          <t>AV375-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J248" authorId="1" shapeId="0" xr:uid="{051266AC-15F1-43F7-8703-FEB08FA807CA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>AV375-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K248" authorId="1" shapeId="0" xr:uid="{E23412EA-B558-4CE0-B343-898A61943724}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>AV375-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B252" authorId="15" shapeId="0" xr:uid="{6BE60107-F28C-41F1-A623-84DD5A6A045C}">
+      <text>
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 AV441-1/AV630-1</t>
-        </r>
       </text>
     </comment>
-    <comment ref="B253" authorId="17" shapeId="0" xr:uid="{573F35F3-86C4-417F-BDB5-9F88836E09BB}">
+    <comment ref="B253" authorId="16" shapeId="0" xr:uid="{573F35F3-86C4-417F-BDB5-9F88836E09BB}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Alfa Laval Offc"/>
-            <family val="2"/>
-          </rPr>
-          <t>[Threaded comment]
+        <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Alternative labels:
 506c/AV372-1</t>
-        </r>
       </text>
     </comment>
     <comment ref="E253" authorId="1" shapeId="0" xr:uid="{68836ADC-7909-428F-90A1-5710219BA6C4}">
@@ -771,6 +1022,48 @@
             <family val="2"/>
           </rPr>
           <t>506c</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I253" authorId="1" shapeId="0" xr:uid="{349086F0-6A9F-49D5-A102-9A7EA0C19C98}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>506c</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J253" authorId="1" shapeId="0" xr:uid="{D6CB1710-1714-4861-A5BA-1B7F23715B4D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>506c</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K253" authorId="1" shapeId="0" xr:uid="{E92F502C-6570-468A-9732-36F99B083B81}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>506b</t>
         </r>
       </text>
     </comment>
@@ -830,12 +1123,54 @@
         </r>
       </text>
     </comment>
+    <comment ref="I354" authorId="1" shapeId="0" xr:uid="{36FF1E64-6471-4653-B1F0-0FAA16B29916}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J354" authorId="1" shapeId="0" xr:uid="{7DBD095E-E2BC-4769-9A92-480138A3F271}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIT220-1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K354" authorId="1" shapeId="0" xr:uid="{E1A905A5-6F64-4A3F-A10D-A47C8A33385D}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>FIT220-1</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1694" uniqueCount="281">
   <si>
     <t>Tag Label</t>
   </si>
@@ -1669,13 +2004,22 @@
   </si>
   <si>
     <t>BREW 750H</t>
+  </si>
+  <si>
+    <t>BREW 600e</t>
+  </si>
+  <si>
+    <t>BREW 750e</t>
+  </si>
+  <si>
+    <t>BREW 750L</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1724,8 +2068,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="MS Sans Serif"/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -2344,8 +2690,11 @@
     <text>Alternative sensors, same PIW:
 TT731b/TT733</text>
   </threadedComment>
-  <threadedComment ref="E218" dT="2024-02-05T11:21:30.31" personId="{03B332EA-821B-4AFF-86E9-85F720276E0F}" id="{F8073023-E3D6-437F-A368-4B60DA804058}">
+  <threadedComment ref="F218" dT="2024-02-05T11:21:30.31" personId="{03B332EA-821B-4AFF-86E9-85F720276E0F}" id="{F8073023-E3D6-437F-A368-4B60DA804058}">
     <text>Sensor: TT733</text>
+  </threadedComment>
+  <threadedComment ref="K218" dT="2024-01-02T12:48:07.21" personId="{03B332EA-821B-4AFF-86E9-85F720276E0F}" id="{ED46C518-7286-47D1-963D-3F59595A0F45}">
+    <text>Sensor: TT731b</text>
   </threadedComment>
   <threadedComment ref="B223" dT="2023-02-15T10:09:59.94" personId="{03B332EA-821B-4AFF-86E9-85F720276E0F}" id="{FCEB49F4-8B73-4CA2-A393-7AEBAA66145D}">
     <text>Alternative labels:
@@ -2371,17 +2720,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}">
-  <dimension ref="B2:H401"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="B2:K401"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="10.75" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.75" style="1" customWidth="1"/>
-    <col min="5" max="6" width="2.25" style="10" customWidth="1"/>
-    <col min="7" max="8" width="2.875" style="10" customWidth="1"/>
+    <col min="2" max="2" width="10.69921875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="31.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="2.19921875" style="10" customWidth="1"/>
+    <col min="7" max="8" width="2.8984375" style="10" customWidth="1"/>
+    <col min="9" max="11" width="2.296875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="55.5">
+    <row r="2" spans="2:11" ht="55.5" x14ac:dyDescent="0.4">
       <c r="B2"/>
       <c r="C2"/>
       <c r="D2"/>
@@ -2397,8 +2747,17 @@
       <c r="H2" s="11" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="3" spans="2:8">
+      <c r="I2" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="J2" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
@@ -2412,8 +2771,11 @@
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
-    </row>
-    <row r="4" spans="2:8">
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -2421,8 +2783,11 @@
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="2:8">
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B5" s="4"/>
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
@@ -2430,8 +2795,11 @@
       <c r="F5" s="14"/>
       <c r="G5" s="14"/>
       <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="2:8">
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="4"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -2439,8 +2807,11 @@
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="2:8">
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B7" s="4" t="s">
         <v>1</v>
       </c>
@@ -2460,8 +2831,17 @@
       <c r="H7" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="8" spans="2:8">
+      <c r="I7" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B8" s="4" t="s">
         <v>2</v>
       </c>
@@ -2481,8 +2861,17 @@
       <c r="H8" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="9" spans="2:8">
+      <c r="I8" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B9" s="4" t="s">
         <v>3</v>
       </c>
@@ -2502,8 +2891,17 @@
       <c r="H9" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="10" spans="2:8">
+      <c r="I9" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -2517,8 +2915,11 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-    </row>
-    <row r="11" spans="2:8">
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
@@ -2538,8 +2939,17 @@
       <c r="H11" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="12" spans="2:8">
+      <c r="I11" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
@@ -2559,8 +2969,17 @@
       <c r="H12" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="13" spans="2:8">
+      <c r="I12" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" s="4" t="s">
         <v>7</v>
       </c>
@@ -2580,8 +2999,17 @@
       <c r="H13" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="14" spans="2:8">
+      <c r="I13" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
@@ -2593,8 +3021,11 @@
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="13"/>
-    </row>
-    <row r="15" spans="2:8">
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
@@ -2606,8 +3037,11 @@
       <c r="F15" s="13"/>
       <c r="G15" s="13"/>
       <c r="H15" s="13"/>
-    </row>
-    <row r="16" spans="2:8">
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B16" s="4" t="s">
         <v>9</v>
       </c>
@@ -2627,8 +3061,17 @@
       <c r="H16" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="17" spans="2:8">
+      <c r="I16" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J16" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B17" s="4" t="s">
         <v>10</v>
       </c>
@@ -2648,8 +3091,17 @@
       <c r="H17" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="18" spans="2:8">
+      <c r="I17" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
@@ -2671,8 +3123,17 @@
       <c r="H18" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="19" spans="2:8">
+      <c r="I18" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
@@ -2684,8 +3145,11 @@
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
       <c r="H19" s="13"/>
-    </row>
-    <row r="20" spans="2:8">
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
@@ -2697,8 +3161,11 @@
       <c r="F20" s="13"/>
       <c r="G20" s="13"/>
       <c r="H20" s="13"/>
-    </row>
-    <row r="21" spans="2:8">
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
@@ -2710,8 +3177,11 @@
       <c r="F21" s="13"/>
       <c r="G21" s="13"/>
       <c r="H21" s="13"/>
-    </row>
-    <row r="22" spans="2:8">
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B22" s="4" t="s">
         <v>12</v>
       </c>
@@ -2733,8 +3203,17 @@
       <c r="H22" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="23" spans="2:8">
+      <c r="I22" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J22" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B23" s="4"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -2742,8 +3221,11 @@
       <c r="F23" s="13"/>
       <c r="G23" s="13"/>
       <c r="H23" s="13"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B24" s="6" t="s">
         <v>13</v>
       </c>
@@ -2763,8 +3245,17 @@
       <c r="H24" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="I24" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B25" s="6" t="s">
         <v>13</v>
       </c>
@@ -2784,8 +3275,17 @@
       <c r="H25" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="I25" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J25" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
@@ -2807,8 +3307,17 @@
       <c r="H26" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="27" spans="2:8">
+      <c r="I26" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J26" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
@@ -2830,8 +3339,17 @@
       <c r="H27" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="28" spans="2:8">
+      <c r="I27" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B28" s="6" t="s">
         <v>15</v>
       </c>
@@ -2853,8 +3371,17 @@
       <c r="H28" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="29" spans="2:8">
+      <c r="I28" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B29" s="6" t="s">
         <v>15</v>
       </c>
@@ -2876,8 +3403,17 @@
       <c r="H29" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="30" spans="2:8">
+      <c r="I29" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B30" s="6" t="s">
         <v>16</v>
       </c>
@@ -2897,8 +3433,17 @@
       <c r="H30" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="31" spans="2:8">
+      <c r="I30" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B31" s="6" t="s">
         <v>16</v>
       </c>
@@ -2918,8 +3463,17 @@
       <c r="H31" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="32" spans="2:8">
+      <c r="I31" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B32" s="6" t="s">
         <v>17</v>
       </c>
@@ -2939,8 +3493,17 @@
       <c r="H32" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="33" spans="2:8">
+      <c r="I32" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J32" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B33" s="6" t="s">
         <v>17</v>
       </c>
@@ -2960,8 +3523,17 @@
       <c r="H33" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="I33" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J33" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B34" s="6" t="s">
         <v>18</v>
       </c>
@@ -2975,8 +3547,11 @@
       <c r="F34" s="13"/>
       <c r="G34" s="13"/>
       <c r="H34" s="13"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B35" s="6" t="s">
         <v>18</v>
       </c>
@@ -2990,8 +3565,11 @@
       <c r="F35" s="13"/>
       <c r="G35" s="13"/>
       <c r="H35" s="13"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B36" s="6" t="s">
         <v>19</v>
       </c>
@@ -3011,8 +3589,17 @@
       <c r="H36" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="37" spans="2:8">
+      <c r="I36" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B37" s="7" t="s">
         <v>19</v>
       </c>
@@ -3032,8 +3619,17 @@
       <c r="H37" s="15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="38" spans="2:8">
+      <c r="I37" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B38" s="5" t="s">
         <v>8</v>
       </c>
@@ -3045,8 +3641,11 @@
       <c r="F38" s="13"/>
       <c r="G38" s="13"/>
       <c r="H38" s="13"/>
-    </row>
-    <row r="39" spans="2:8">
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B39" s="5" t="s">
         <v>8</v>
       </c>
@@ -3058,8 +3657,11 @@
       <c r="F39" s="13"/>
       <c r="G39" s="13"/>
       <c r="H39" s="13"/>
-    </row>
-    <row r="40" spans="2:8">
+      <c r="I39" s="13"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B40" s="4"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -3067,8 +3669,11 @@
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
       <c r="H40" s="13"/>
-    </row>
-    <row r="41" spans="2:8">
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B41" s="7" t="s">
         <v>20</v>
       </c>
@@ -3088,8 +3693,17 @@
       <c r="H41" s="15" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="42" spans="2:8">
+      <c r="I41" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B42" s="6" t="s">
         <v>20</v>
       </c>
@@ -3109,8 +3723,17 @@
       <c r="H42" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="43" spans="2:8">
+      <c r="I42" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J42" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K42" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B43" s="6" t="s">
         <v>21</v>
       </c>
@@ -3130,8 +3753,17 @@
       <c r="H43" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="44" spans="2:8">
+      <c r="I43" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J43" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K43" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B44" s="6" t="s">
         <v>21</v>
       </c>
@@ -3151,8 +3783,17 @@
       <c r="H44" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="45" spans="2:8">
+      <c r="I44" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J44" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B45" s="6" t="s">
         <v>22</v>
       </c>
@@ -3172,8 +3813,17 @@
       <c r="H45" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="46" spans="2:8">
+      <c r="I45" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J45" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K45" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B46" s="6" t="s">
         <v>22</v>
       </c>
@@ -3193,8 +3843,17 @@
       <c r="H46" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="47" spans="2:8">
+      <c r="I46" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J46" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K46" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B47" s="6" t="s">
         <v>23</v>
       </c>
@@ -3214,8 +3873,17 @@
       <c r="H47" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="I47" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J47" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K47" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B48" s="6" t="s">
         <v>23</v>
       </c>
@@ -3235,8 +3903,17 @@
       <c r="H48" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="49" spans="2:8">
+      <c r="I48" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J48" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K48" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B49" s="6" t="s">
         <v>24</v>
       </c>
@@ -3256,8 +3933,17 @@
       <c r="H49" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="50" spans="2:8">
+      <c r="I49" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J49" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K49" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B50" s="6" t="s">
         <v>24</v>
       </c>
@@ -3277,8 +3963,17 @@
       <c r="H50" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="51" spans="2:8">
+      <c r="I50" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J50" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K50" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B51" s="6" t="s">
         <v>25</v>
       </c>
@@ -3298,8 +3993,17 @@
       <c r="H51" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="52" spans="2:8">
+      <c r="I51" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J51" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K51" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B52" s="6" t="s">
         <v>25</v>
       </c>
@@ -3319,8 +4023,17 @@
       <c r="H52" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="53" spans="2:8">
+      <c r="I52" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J52" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K52" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B53" s="6" t="s">
         <v>26</v>
       </c>
@@ -3338,8 +4051,17 @@
       <c r="H53" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="54" spans="2:8">
+      <c r="I53" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J53" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K53" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B54" s="6" t="s">
         <v>26</v>
       </c>
@@ -3357,8 +4079,17 @@
       <c r="H54" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="55" spans="2:8">
+      <c r="I54" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J54" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K54" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B55" s="5" t="s">
         <v>8</v>
       </c>
@@ -3370,8 +4101,11 @@
       <c r="F55" s="13"/>
       <c r="G55" s="13"/>
       <c r="H55" s="13"/>
-    </row>
-    <row r="56" spans="2:8">
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B56" s="5" t="s">
         <v>8</v>
       </c>
@@ -3383,8 +4117,11 @@
       <c r="F56" s="13"/>
       <c r="G56" s="13"/>
       <c r="H56" s="13"/>
-    </row>
-    <row r="57" spans="2:8">
+      <c r="I56" s="13"/>
+      <c r="J56" s="13"/>
+      <c r="K56" s="13"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B57" s="6"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -3392,8 +4129,11 @@
       <c r="F57" s="13"/>
       <c r="G57" s="13"/>
       <c r="H57" s="13"/>
-    </row>
-    <row r="58" spans="2:8">
+      <c r="I57" s="13"/>
+      <c r="J57" s="13"/>
+      <c r="K57" s="13"/>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B58" s="6" t="s">
         <v>27</v>
       </c>
@@ -3413,8 +4153,17 @@
       <c r="H58" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="59" spans="2:8">
+      <c r="I58" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J58" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K58" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B59" s="6" t="s">
         <v>27</v>
       </c>
@@ -3434,8 +4183,17 @@
       <c r="H59" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="60" spans="2:8">
+      <c r="I59" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J59" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K59" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B60" s="5" t="s">
         <v>8</v>
       </c>
@@ -3447,8 +4205,11 @@
       <c r="F60" s="13"/>
       <c r="G60" s="13"/>
       <c r="H60" s="13"/>
-    </row>
-    <row r="61" spans="2:8">
+      <c r="I60" s="13"/>
+      <c r="J60" s="13"/>
+      <c r="K60" s="13"/>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B61" s="5" t="s">
         <v>8</v>
       </c>
@@ -3460,8 +4221,11 @@
       <c r="F61" s="13"/>
       <c r="G61" s="13"/>
       <c r="H61" s="13"/>
-    </row>
-    <row r="62" spans="2:8">
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B62" s="6" t="s">
         <v>28</v>
       </c>
@@ -3481,8 +4245,17 @@
       <c r="H62" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="63" spans="2:8">
+      <c r="I62" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J62" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K62" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B63" s="6" t="s">
         <v>28</v>
       </c>
@@ -3502,8 +4275,17 @@
       <c r="H63" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="64" spans="2:8">
+      <c r="I63" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J63" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K63" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B64" s="6" t="s">
         <v>29</v>
       </c>
@@ -3523,8 +4305,17 @@
       <c r="H64" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="65" spans="2:8">
+      <c r="I64" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J64" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K64" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B65" s="6" t="s">
         <v>29</v>
       </c>
@@ -3544,8 +4335,17 @@
       <c r="H65" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="66" spans="2:8">
+      <c r="I65" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J65" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K65" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B66" s="6" t="s">
         <v>30</v>
       </c>
@@ -3559,8 +4359,11 @@
       <c r="F66" s="13"/>
       <c r="G66" s="13"/>
       <c r="H66" s="13"/>
-    </row>
-    <row r="67" spans="2:8">
+      <c r="I66" s="13"/>
+      <c r="J66" s="13"/>
+      <c r="K66" s="13"/>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B67" s="6" t="s">
         <v>30</v>
       </c>
@@ -3574,8 +4377,11 @@
       <c r="F67" s="13"/>
       <c r="G67" s="13"/>
       <c r="H67" s="13"/>
-    </row>
-    <row r="68" spans="2:8">
+      <c r="I67" s="13"/>
+      <c r="J67" s="13"/>
+      <c r="K67" s="13"/>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B68" s="5" t="s">
         <v>8</v>
       </c>
@@ -3587,8 +4393,11 @@
       <c r="F68" s="13"/>
       <c r="G68" s="13"/>
       <c r="H68" s="13"/>
-    </row>
-    <row r="69" spans="2:8">
+      <c r="I68" s="13"/>
+      <c r="J68" s="13"/>
+      <c r="K68" s="13"/>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B69" s="5" t="s">
         <v>8</v>
       </c>
@@ -3600,8 +4409,11 @@
       <c r="F69" s="13"/>
       <c r="G69" s="13"/>
       <c r="H69" s="13"/>
-    </row>
-    <row r="70" spans="2:8">
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B70" s="5" t="s">
         <v>8</v>
       </c>
@@ -3613,8 +4425,11 @@
       <c r="F70" s="13"/>
       <c r="G70" s="13"/>
       <c r="H70" s="13"/>
-    </row>
-    <row r="71" spans="2:8">
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
+      <c r="K70" s="13"/>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B71" s="5" t="s">
         <v>8</v>
       </c>
@@ -3626,8 +4441,11 @@
       <c r="F71" s="13"/>
       <c r="G71" s="13"/>
       <c r="H71" s="13"/>
-    </row>
-    <row r="72" spans="2:8">
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
+      <c r="K71" s="13"/>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B72" s="5" t="s">
         <v>8</v>
       </c>
@@ -3639,8 +4457,11 @@
       <c r="F72" s="13"/>
       <c r="G72" s="13"/>
       <c r="H72" s="13"/>
-    </row>
-    <row r="73" spans="2:8">
+      <c r="I72" s="13"/>
+      <c r="J72" s="13"/>
+      <c r="K72" s="13"/>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B73" s="5" t="s">
         <v>8</v>
       </c>
@@ -3652,8 +4473,11 @@
       <c r="F73" s="13"/>
       <c r="G73" s="13"/>
       <c r="H73" s="13"/>
-    </row>
-    <row r="74" spans="2:8">
+      <c r="I73" s="13"/>
+      <c r="J73" s="13"/>
+      <c r="K73" s="13"/>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B74" s="6"/>
       <c r="C74" s="3"/>
       <c r="D74" s="20"/>
@@ -3661,8 +4485,11 @@
       <c r="F74" s="13"/>
       <c r="G74" s="13"/>
       <c r="H74" s="13"/>
-    </row>
-    <row r="75" spans="2:8">
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
+      <c r="K74" s="13"/>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B75" s="6" t="s">
         <v>13</v>
       </c>
@@ -3682,8 +4509,17 @@
       <c r="H75" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="76" spans="2:8">
+      <c r="I75" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J75" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K75" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B76" s="6" t="s">
         <v>14</v>
       </c>
@@ -3705,8 +4541,17 @@
       <c r="H76" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="77" spans="2:8">
+      <c r="I76" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K76" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B77" s="6" t="s">
         <v>15</v>
       </c>
@@ -3728,8 +4573,17 @@
       <c r="H77" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="78" spans="2:8">
+      <c r="I77" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J77" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K77" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B78" s="6" t="s">
         <v>16</v>
       </c>
@@ -3749,8 +4603,17 @@
       <c r="H78" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="79" spans="2:8">
+      <c r="I78" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J78" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K78" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B79" s="6" t="s">
         <v>17</v>
       </c>
@@ -3770,8 +4633,17 @@
       <c r="H79" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="80" spans="2:8">
+      <c r="I79" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J79" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K79" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B80" s="6" t="s">
         <v>18</v>
       </c>
@@ -3785,8 +4657,11 @@
       <c r="F80" s="13"/>
       <c r="G80" s="13"/>
       <c r="H80" s="13"/>
-    </row>
-    <row r="81" spans="2:8">
+      <c r="I80" s="13"/>
+      <c r="J80" s="13"/>
+      <c r="K80" s="13"/>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B81" s="6" t="s">
         <v>19</v>
       </c>
@@ -3806,8 +4681,17 @@
       <c r="H81" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="82" spans="2:8">
+      <c r="I81" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J81" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K81" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B82" s="5" t="s">
         <v>8</v>
       </c>
@@ -3819,8 +4703,11 @@
       <c r="F82" s="13"/>
       <c r="G82" s="13"/>
       <c r="H82" s="13"/>
-    </row>
-    <row r="83" spans="2:8">
+      <c r="I82" s="13"/>
+      <c r="J82" s="13"/>
+      <c r="K82" s="13"/>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B83" s="6" t="s">
         <v>20</v>
       </c>
@@ -3840,8 +4727,17 @@
       <c r="H83" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="84" spans="2:8">
+      <c r="I83" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J83" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K83" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B84" s="6" t="s">
         <v>21</v>
       </c>
@@ -3861,8 +4757,17 @@
       <c r="H84" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="85" spans="2:8">
+      <c r="I84" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J84" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K84" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B85" s="6" t="s">
         <v>22</v>
       </c>
@@ -3882,8 +4787,17 @@
       <c r="H85" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="86" spans="2:8">
+      <c r="I85" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J85" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K85" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B86" s="6" t="s">
         <v>23</v>
       </c>
@@ -3903,8 +4817,17 @@
       <c r="H86" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="87" spans="2:8">
+      <c r="I86" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J86" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K86" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B87" s="6" t="s">
         <v>24</v>
       </c>
@@ -3924,8 +4847,17 @@
       <c r="H87" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="88" spans="2:8">
+      <c r="I87" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J87" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K87" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B88" s="6" t="s">
         <v>25</v>
       </c>
@@ -3945,8 +4877,17 @@
       <c r="H88" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="89" spans="2:8">
+      <c r="I88" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J88" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K88" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B89" s="6" t="s">
         <v>26</v>
       </c>
@@ -3964,8 +4905,17 @@
       <c r="H89" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="90" spans="2:8">
+      <c r="I89" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J89" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K89" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B90" s="5" t="s">
         <v>8</v>
       </c>
@@ -3977,8 +4927,11 @@
       <c r="F90" s="13"/>
       <c r="G90" s="13"/>
       <c r="H90" s="13"/>
-    </row>
-    <row r="91" spans="2:8">
+      <c r="I90" s="13"/>
+      <c r="J90" s="13"/>
+      <c r="K90" s="13"/>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B91" s="6"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
@@ -3986,8 +4939,11 @@
       <c r="F91" s="13"/>
       <c r="G91" s="13"/>
       <c r="H91" s="13"/>
-    </row>
-    <row r="92" spans="2:8">
+      <c r="I91" s="13"/>
+      <c r="J91" s="13"/>
+      <c r="K91" s="13"/>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B92" s="6" t="s">
         <v>27</v>
       </c>
@@ -4007,8 +4963,17 @@
       <c r="H92" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="93" spans="2:8">
+      <c r="I92" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J92" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K92" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B93" s="5" t="s">
         <v>8</v>
       </c>
@@ -4022,8 +4987,11 @@
       <c r="F93" s="13"/>
       <c r="G93" s="13"/>
       <c r="H93" s="13"/>
-    </row>
-    <row r="94" spans="2:8">
+      <c r="I93" s="13"/>
+      <c r="J93" s="13"/>
+      <c r="K93" s="13"/>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B94" s="6" t="s">
         <v>28</v>
       </c>
@@ -4043,8 +5011,17 @@
       <c r="H94" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="95" spans="2:8">
+      <c r="I94" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J94" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K94" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B95" s="6" t="s">
         <v>29</v>
       </c>
@@ -4064,8 +5041,17 @@
       <c r="H95" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="96" spans="2:8">
+      <c r="I95" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J95" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K95" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B96" s="6" t="s">
         <v>30</v>
       </c>
@@ -4079,8 +5065,11 @@
       <c r="F96" s="13"/>
       <c r="G96" s="13"/>
       <c r="H96" s="13"/>
-    </row>
-    <row r="97" spans="2:8">
+      <c r="I96" s="13"/>
+      <c r="J96" s="13"/>
+      <c r="K96" s="13"/>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B97" s="5" t="s">
         <v>8</v>
       </c>
@@ -4092,8 +5081,11 @@
       <c r="F97" s="13"/>
       <c r="G97" s="13"/>
       <c r="H97" s="13"/>
-    </row>
-    <row r="98" spans="2:8">
+      <c r="I97" s="13"/>
+      <c r="J97" s="13"/>
+      <c r="K97" s="13"/>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B98" s="5" t="s">
         <v>8</v>
       </c>
@@ -4105,8 +5097,11 @@
       <c r="F98" s="13"/>
       <c r="G98" s="13"/>
       <c r="H98" s="13"/>
-    </row>
-    <row r="99" spans="2:8">
+      <c r="I98" s="13"/>
+      <c r="J98" s="13"/>
+      <c r="K98" s="13"/>
+    </row>
+    <row r="99" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B99" s="5" t="s">
         <v>8</v>
       </c>
@@ -4118,8 +5113,11 @@
       <c r="F99" s="13"/>
       <c r="G99" s="13"/>
       <c r="H99" s="13"/>
-    </row>
-    <row r="100" spans="2:8">
+      <c r="I99" s="13"/>
+      <c r="J99" s="13"/>
+      <c r="K99" s="13"/>
+    </row>
+    <row r="100" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B100" s="5" t="s">
         <v>8</v>
       </c>
@@ -4131,8 +5129,11 @@
       <c r="F100" s="13"/>
       <c r="G100" s="13"/>
       <c r="H100" s="13"/>
-    </row>
-    <row r="101" spans="2:8">
+      <c r="I100" s="13"/>
+      <c r="J100" s="13"/>
+      <c r="K100" s="13"/>
+    </row>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B101" s="4" t="s">
         <v>31</v>
       </c>
@@ -4152,8 +5153,17 @@
       <c r="H101" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="102" spans="2:8">
+      <c r="I101" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J101" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K101" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B102" s="8" t="s">
         <v>32</v>
       </c>
@@ -4173,8 +5183,17 @@
       <c r="H102" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="103" spans="2:8">
+      <c r="I102" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J102" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K102" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B103" s="4" t="s">
         <v>33</v>
       </c>
@@ -4194,8 +5213,17 @@
       <c r="H103" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="104" spans="2:8">
+      <c r="I103" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J103" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K103" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="104" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B104" s="4" t="s">
         <v>34</v>
       </c>
@@ -4215,8 +5243,17 @@
       <c r="H104" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="105" spans="2:8">
+      <c r="I104" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J104" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K104" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="105" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B105" s="4" t="s">
         <v>35</v>
       </c>
@@ -4236,8 +5273,17 @@
       <c r="H105" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="106" spans="2:8">
+      <c r="I105" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J105" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K105" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="106" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B106" s="4" t="s">
         <v>36</v>
       </c>
@@ -4257,8 +5303,17 @@
       <c r="H106" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="107" spans="2:8">
+      <c r="I106" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J106" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K106" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B107" s="4" t="s">
         <v>37</v>
       </c>
@@ -4270,8 +5325,11 @@
       <c r="F107" s="13"/>
       <c r="G107" s="13"/>
       <c r="H107" s="13"/>
-    </row>
-    <row r="108" spans="2:8">
+      <c r="I107" s="13"/>
+      <c r="J107" s="13"/>
+      <c r="K107" s="13"/>
+    </row>
+    <row r="108" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B108" s="4"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
@@ -4279,8 +5337,11 @@
       <c r="F108" s="13"/>
       <c r="G108" s="13"/>
       <c r="H108" s="13"/>
-    </row>
-    <row r="109" spans="2:8">
+      <c r="I108" s="13"/>
+      <c r="J108" s="13"/>
+      <c r="K108" s="13"/>
+    </row>
+    <row r="109" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B109" s="4" t="s">
         <v>38</v>
       </c>
@@ -4300,8 +5361,17 @@
       <c r="H109" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="110" spans="2:8">
+      <c r="I109" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J109" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K109" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B110" s="4" t="s">
         <v>39</v>
       </c>
@@ -4321,8 +5391,17 @@
       <c r="H110" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="111" spans="2:8">
+      <c r="I110" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J110" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K110" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B111" s="4" t="s">
         <v>40</v>
       </c>
@@ -4342,8 +5421,17 @@
       <c r="H111" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="112" spans="2:8">
+      <c r="I111" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J111" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K111" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="112" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B112" s="4" t="s">
         <v>41</v>
       </c>
@@ -4363,8 +5451,17 @@
       <c r="H112" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="113" spans="2:8">
+      <c r="I112" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J112" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K112" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="113" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B113" s="4"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
@@ -4372,8 +5469,11 @@
       <c r="F113" s="13"/>
       <c r="G113" s="13"/>
       <c r="H113" s="13"/>
-    </row>
-    <row r="114" spans="2:8">
+      <c r="I113" s="13"/>
+      <c r="J113" s="13"/>
+      <c r="K113" s="13"/>
+    </row>
+    <row r="114" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B114" s="4" t="s">
         <v>42</v>
       </c>
@@ -4395,8 +5495,17 @@
       <c r="H114" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="115" spans="2:8">
+      <c r="I114" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J114" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K114" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="115" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B115" s="5" t="s">
         <v>8</v>
       </c>
@@ -4408,8 +5517,11 @@
       <c r="F115" s="13"/>
       <c r="G115" s="13"/>
       <c r="H115" s="13"/>
-    </row>
-    <row r="116" spans="2:8">
+      <c r="I115" s="13"/>
+      <c r="J115" s="13"/>
+      <c r="K115" s="13"/>
+    </row>
+    <row r="116" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B116" s="4" t="s">
         <v>43</v>
       </c>
@@ -4423,8 +5535,11 @@
       <c r="F116" s="13"/>
       <c r="G116" s="13"/>
       <c r="H116" s="13"/>
-    </row>
-    <row r="117" spans="2:8">
+      <c r="I116" s="13"/>
+      <c r="J116" s="13"/>
+      <c r="K116" s="13"/>
+    </row>
+    <row r="117" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B117" s="4" t="s">
         <v>44</v>
       </c>
@@ -4436,8 +5551,13 @@
       <c r="F117" s="13"/>
       <c r="G117" s="13"/>
       <c r="H117" s="13"/>
-    </row>
-    <row r="118" spans="2:8">
+      <c r="I117" s="13"/>
+      <c r="J117" s="13"/>
+      <c r="K117" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="118" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B118" s="4"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
@@ -4445,8 +5565,11 @@
       <c r="F118" s="13"/>
       <c r="G118" s="13"/>
       <c r="H118" s="13"/>
-    </row>
-    <row r="119" spans="2:8">
+      <c r="I118" s="13"/>
+      <c r="J118" s="13"/>
+      <c r="K118" s="13"/>
+    </row>
+    <row r="119" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B119" s="4" t="s">
         <v>45</v>
       </c>
@@ -4466,8 +5589,17 @@
       <c r="H119" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="120" spans="2:8">
+      <c r="I119" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J119" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K119" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="120" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B120" s="4" t="s">
         <v>46</v>
       </c>
@@ -4487,8 +5619,17 @@
       <c r="H120" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="121" spans="2:8">
+      <c r="I120" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J120" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K120" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="121" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B121" s="4" t="s">
         <v>47</v>
       </c>
@@ -4508,8 +5649,17 @@
       <c r="H121" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="122" spans="2:8">
+      <c r="I121" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J121" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K121" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="122" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B122" s="4" t="s">
         <v>48</v>
       </c>
@@ -4531,8 +5681,17 @@
       <c r="H122" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="123" spans="2:8">
+      <c r="I122" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J122" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K122" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="123" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B123" s="4"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
@@ -4540,8 +5699,11 @@
       <c r="F123" s="13"/>
       <c r="G123" s="13"/>
       <c r="H123" s="13"/>
-    </row>
-    <row r="124" spans="2:8">
+      <c r="I123" s="13"/>
+      <c r="J123" s="13"/>
+      <c r="K123" s="13"/>
+    </row>
+    <row r="124" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B124" s="4" t="s">
         <v>49</v>
       </c>
@@ -4553,8 +5715,11 @@
       <c r="F124" s="13"/>
       <c r="G124" s="13"/>
       <c r="H124" s="13"/>
-    </row>
-    <row r="125" spans="2:8">
+      <c r="I124" s="13"/>
+      <c r="J124" s="13"/>
+      <c r="K124" s="13"/>
+    </row>
+    <row r="125" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B125" s="4" t="s">
         <v>50</v>
       </c>
@@ -4568,8 +5733,11 @@
       <c r="F125" s="13"/>
       <c r="G125" s="13"/>
       <c r="H125" s="13"/>
-    </row>
-    <row r="126" spans="2:8">
+      <c r="I125" s="13"/>
+      <c r="J125" s="13"/>
+      <c r="K125" s="13"/>
+    </row>
+    <row r="126" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B126" s="4" t="s">
         <v>51</v>
       </c>
@@ -4591,8 +5759,17 @@
       <c r="H126" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="127" spans="2:8">
+      <c r="I126" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J126" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K126" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="127" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B127" s="5" t="s">
         <v>8</v>
       </c>
@@ -4604,8 +5781,11 @@
       <c r="F127" s="13"/>
       <c r="G127" s="13"/>
       <c r="H127" s="13"/>
-    </row>
-    <row r="128" spans="2:8">
+      <c r="I127" s="13"/>
+      <c r="J127" s="13"/>
+      <c r="K127" s="13"/>
+    </row>
+    <row r="128" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B128" s="4"/>
       <c r="C128" s="3"/>
       <c r="D128" s="19"/>
@@ -4613,8 +5793,11 @@
       <c r="F128" s="13"/>
       <c r="G128" s="13"/>
       <c r="H128" s="13"/>
-    </row>
-    <row r="129" spans="2:8">
+      <c r="I128" s="13"/>
+      <c r="J128" s="13"/>
+      <c r="K128" s="13"/>
+    </row>
+    <row r="129" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B129" s="4" t="s">
         <v>52</v>
       </c>
@@ -4634,8 +5817,17 @@
       <c r="H129" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="130" spans="2:8">
+      <c r="I129" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J129" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K129" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="130" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B130" s="4" t="s">
         <v>53</v>
       </c>
@@ -4655,8 +5847,17 @@
       <c r="H130" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="131" spans="2:8">
+      <c r="I130" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J130" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K130" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="131" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B131" s="4" t="s">
         <v>54</v>
       </c>
@@ -4676,8 +5877,17 @@
       <c r="H131" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="132" spans="2:8">
+      <c r="I131" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J131" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K131" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="132" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B132" s="4" t="s">
         <v>55</v>
       </c>
@@ -4689,8 +5899,11 @@
       <c r="F132" s="13"/>
       <c r="G132" s="13"/>
       <c r="H132" s="13"/>
-    </row>
-    <row r="133" spans="2:8">
+      <c r="I132" s="13"/>
+      <c r="J132" s="13"/>
+      <c r="K132" s="13"/>
+    </row>
+    <row r="133" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B133" s="4"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
@@ -4698,8 +5911,11 @@
       <c r="F133" s="13"/>
       <c r="G133" s="13"/>
       <c r="H133" s="13"/>
-    </row>
-    <row r="134" spans="2:8">
+      <c r="I133" s="13"/>
+      <c r="J133" s="13"/>
+      <c r="K133" s="13"/>
+    </row>
+    <row r="134" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B134" s="4" t="s">
         <v>56</v>
       </c>
@@ -4721,8 +5937,17 @@
       <c r="H134" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="135" spans="2:8">
+      <c r="I134" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J134" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K134" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="135" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B135" s="4" t="s">
         <v>57</v>
       </c>
@@ -4744,8 +5969,17 @@
       <c r="H135" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="136" spans="2:8">
+      <c r="I135" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J135" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K135" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="136" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B136" s="4" t="s">
         <v>58</v>
       </c>
@@ -4767,8 +6001,17 @@
       <c r="H136" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="137" spans="2:8">
+      <c r="I136" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J136" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K136" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="137" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B137" s="4" t="s">
         <v>59</v>
       </c>
@@ -4790,8 +6033,17 @@
       <c r="H137" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="138" spans="2:8">
+      <c r="I137" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J137" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K137" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="138" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B138" s="4"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
@@ -4799,8 +6051,11 @@
       <c r="F138" s="13"/>
       <c r="G138" s="13"/>
       <c r="H138" s="13"/>
-    </row>
-    <row r="139" spans="2:8">
+      <c r="I138" s="13"/>
+      <c r="J138" s="13"/>
+      <c r="K138" s="13"/>
+    </row>
+    <row r="139" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B139" s="4" t="s">
         <v>60</v>
       </c>
@@ -4820,8 +6075,17 @@
       <c r="H139" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="140" spans="2:8">
+      <c r="I139" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J139" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K139" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="140" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B140" s="4"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
@@ -4829,8 +6093,11 @@
       <c r="F140" s="13"/>
       <c r="G140" s="13"/>
       <c r="H140" s="13"/>
-    </row>
-    <row r="141" spans="2:8">
+      <c r="I140" s="13"/>
+      <c r="J140" s="13"/>
+      <c r="K140" s="13"/>
+    </row>
+    <row r="141" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B141" s="4" t="s">
         <v>61</v>
       </c>
@@ -4844,8 +6111,13 @@
       <c r="F141" s="14"/>
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
-    </row>
-    <row r="142" spans="2:8">
+      <c r="I141" s="14"/>
+      <c r="J141" s="14"/>
+      <c r="K141" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B142" s="4"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
@@ -4853,8 +6125,11 @@
       <c r="F142" s="13"/>
       <c r="G142" s="13"/>
       <c r="H142" s="13"/>
-    </row>
-    <row r="143" spans="2:8">
+      <c r="I142" s="13"/>
+      <c r="J142" s="13"/>
+      <c r="K142" s="13"/>
+    </row>
+    <row r="143" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B143" s="4" t="s">
         <v>62</v>
       </c>
@@ -4874,8 +6149,17 @@
       <c r="H143" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="144" spans="2:8">
+      <c r="I143" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J143" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K143" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="144" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B144" s="4" t="s">
         <v>63</v>
       </c>
@@ -4895,8 +6179,17 @@
       <c r="H144" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="145" spans="2:8">
+      <c r="I144" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J144" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K144" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="145" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B145" s="4" t="s">
         <v>64</v>
       </c>
@@ -4916,8 +6209,17 @@
       <c r="H145" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="146" spans="2:8">
+      <c r="I145" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J145" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K145" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="146" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B146" s="4" t="s">
         <v>65</v>
       </c>
@@ -4937,8 +6239,17 @@
       <c r="H146" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="147" spans="2:8">
+      <c r="I146" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J146" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K146" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="147" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B147" s="4" t="s">
         <v>66</v>
       </c>
@@ -4958,8 +6269,17 @@
       <c r="H147" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="148" spans="2:8">
+      <c r="I147" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J147" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K147" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B148" s="4" t="s">
         <v>67</v>
       </c>
@@ -4979,8 +6299,13 @@
       <c r="H148" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="149" spans="2:8">
+      <c r="I148" s="13"/>
+      <c r="J148" s="13"/>
+      <c r="K148" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="149" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B149" s="4" t="s">
         <v>68</v>
       </c>
@@ -5002,8 +6327,17 @@
       <c r="H149" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="150" spans="2:8">
+      <c r="I149" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J149" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K149" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="150" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B150" s="4" t="s">
         <v>69</v>
       </c>
@@ -5017,8 +6351,13 @@
       <c r="F150" s="13"/>
       <c r="G150" s="13"/>
       <c r="H150" s="13"/>
-    </row>
-    <row r="151" spans="2:8">
+      <c r="I150" s="13"/>
+      <c r="J150" s="13"/>
+      <c r="K150" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="151" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B151" s="4" t="s">
         <v>70</v>
       </c>
@@ -5032,8 +6371,13 @@
       <c r="F151" s="13"/>
       <c r="G151" s="13"/>
       <c r="H151" s="13"/>
-    </row>
-    <row r="152" spans="2:8">
+      <c r="I151" s="13"/>
+      <c r="J151" s="13"/>
+      <c r="K151" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="152" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B152" s="5" t="s">
         <v>8</v>
       </c>
@@ -5045,8 +6389,11 @@
       <c r="F152" s="13"/>
       <c r="G152" s="13"/>
       <c r="H152" s="13"/>
-    </row>
-    <row r="153" spans="2:8">
+      <c r="I152" s="13"/>
+      <c r="J152" s="13"/>
+      <c r="K152" s="13"/>
+    </row>
+    <row r="153" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B153" s="4" t="s">
         <v>71</v>
       </c>
@@ -5066,8 +6413,17 @@
       <c r="H153" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="154" spans="2:8">
+      <c r="I153" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J153" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K153" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="154" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B154" s="4" t="s">
         <v>71</v>
       </c>
@@ -5087,8 +6443,17 @@
       <c r="H154" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="155" spans="2:8">
+      <c r="I154" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J154" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K154" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="155" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B155" s="4" t="s">
         <v>72</v>
       </c>
@@ -5110,8 +6475,17 @@
       <c r="H155" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="156" spans="2:8">
+      <c r="I155" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J155" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K155" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="156" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B156" s="4" t="s">
         <v>72</v>
       </c>
@@ -5133,8 +6507,17 @@
       <c r="H156" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="157" spans="2:8">
+      <c r="I156" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J156" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K156" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="157" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B157" s="5" t="s">
         <v>8</v>
       </c>
@@ -5146,8 +6529,11 @@
       <c r="F157" s="13"/>
       <c r="G157" s="13"/>
       <c r="H157" s="13"/>
-    </row>
-    <row r="158" spans="2:8">
+      <c r="I157" s="13"/>
+      <c r="J157" s="13"/>
+      <c r="K157" s="13"/>
+    </row>
+    <row r="158" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B158" s="5" t="s">
         <v>8</v>
       </c>
@@ -5159,8 +6545,11 @@
       <c r="F158" s="13"/>
       <c r="G158" s="13"/>
       <c r="H158" s="13"/>
-    </row>
-    <row r="159" spans="2:8">
+      <c r="I158" s="13"/>
+      <c r="J158" s="13"/>
+      <c r="K158" s="13"/>
+    </row>
+    <row r="159" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B159" s="4"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
@@ -5168,8 +6557,11 @@
       <c r="F159" s="13"/>
       <c r="G159" s="13"/>
       <c r="H159" s="13"/>
-    </row>
-    <row r="160" spans="2:8">
+      <c r="I159" s="13"/>
+      <c r="J159" s="13"/>
+      <c r="K159" s="13"/>
+    </row>
+    <row r="160" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B160" s="4" t="s">
         <v>73</v>
       </c>
@@ -5183,8 +6575,15 @@
       <c r="F160" s="13"/>
       <c r="G160" s="13"/>
       <c r="H160" s="13"/>
-    </row>
-    <row r="161" spans="2:8">
+      <c r="I160" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J160" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K160" s="13"/>
+    </row>
+    <row r="161" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B161" s="4" t="s">
         <v>73</v>
       </c>
@@ -5198,8 +6597,15 @@
       <c r="F161" s="13"/>
       <c r="G161" s="13"/>
       <c r="H161" s="13"/>
-    </row>
-    <row r="162" spans="2:8">
+      <c r="I161" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J161" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K161" s="13"/>
+    </row>
+    <row r="162" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B162" s="4" t="s">
         <v>74</v>
       </c>
@@ -5221,8 +6627,17 @@
       <c r="H162" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="163" spans="2:8">
+      <c r="I162" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J162" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K162" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="163" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B163" s="4" t="s">
         <v>74</v>
       </c>
@@ -5244,8 +6659,17 @@
       <c r="H163" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="164" spans="2:8">
+      <c r="I163" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J163" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K163" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="164" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B164" s="4" t="s">
         <v>75</v>
       </c>
@@ -5265,8 +6689,17 @@
       <c r="H164" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="165" spans="2:8">
+      <c r="I164" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J164" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K164" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="165" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B165" s="4" t="s">
         <v>75</v>
       </c>
@@ -5286,8 +6719,17 @@
       <c r="H165" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="166" spans="2:8">
+      <c r="I165" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J165" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K165" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="166" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B166" s="4" t="s">
         <v>76</v>
       </c>
@@ -5309,8 +6751,17 @@
       <c r="H166" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="167" spans="2:8">
+      <c r="I166" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J166" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K166" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="167" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B167" s="4" t="s">
         <v>76</v>
       </c>
@@ -5332,8 +6783,17 @@
       <c r="H167" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="168" spans="2:8">
+      <c r="I167" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J167" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K167" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="168" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B168" s="4" t="s">
         <v>77</v>
       </c>
@@ -5355,8 +6815,17 @@
       <c r="H168" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="169" spans="2:8">
+      <c r="I168" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J168" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K168" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="169" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B169" s="4" t="s">
         <v>77</v>
       </c>
@@ -5378,8 +6847,17 @@
       <c r="H169" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="170" spans="2:8">
+      <c r="I169" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J169" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K169" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="170" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B170" s="5" t="s">
         <v>8</v>
       </c>
@@ -5391,8 +6869,11 @@
       <c r="F170" s="13"/>
       <c r="G170" s="13"/>
       <c r="H170" s="13"/>
-    </row>
-    <row r="171" spans="2:8">
+      <c r="I170" s="13"/>
+      <c r="J170" s="13"/>
+      <c r="K170" s="13"/>
+    </row>
+    <row r="171" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B171" s="5" t="s">
         <v>8</v>
       </c>
@@ -5404,8 +6885,11 @@
       <c r="F171" s="13"/>
       <c r="G171" s="13"/>
       <c r="H171" s="13"/>
-    </row>
-    <row r="172" spans="2:8">
+      <c r="I171" s="13"/>
+      <c r="J171" s="13"/>
+      <c r="K171" s="13"/>
+    </row>
+    <row r="172" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B172" s="5" t="s">
         <v>8</v>
       </c>
@@ -5417,8 +6901,11 @@
       <c r="F172" s="13"/>
       <c r="G172" s="13"/>
       <c r="H172" s="13"/>
-    </row>
-    <row r="173" spans="2:8">
+      <c r="I172" s="13"/>
+      <c r="J172" s="13"/>
+      <c r="K172" s="13"/>
+    </row>
+    <row r="173" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B173" s="5" t="s">
         <v>8</v>
       </c>
@@ -5430,8 +6917,11 @@
       <c r="F173" s="13"/>
       <c r="G173" s="13"/>
       <c r="H173" s="13"/>
-    </row>
-    <row r="174" spans="2:8">
+      <c r="I173" s="13"/>
+      <c r="J173" s="13"/>
+      <c r="K173" s="13"/>
+    </row>
+    <row r="174" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B174" s="5" t="s">
         <v>8</v>
       </c>
@@ -5443,8 +6933,11 @@
       <c r="F174" s="13"/>
       <c r="G174" s="13"/>
       <c r="H174" s="13"/>
-    </row>
-    <row r="175" spans="2:8">
+      <c r="I174" s="13"/>
+      <c r="J174" s="13"/>
+      <c r="K174" s="13"/>
+    </row>
+    <row r="175" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B175" s="5" t="s">
         <v>8</v>
       </c>
@@ -5456,8 +6949,11 @@
       <c r="F175" s="13"/>
       <c r="G175" s="13"/>
       <c r="H175" s="13"/>
-    </row>
-    <row r="176" spans="2:8">
+      <c r="I175" s="13"/>
+      <c r="J175" s="13"/>
+      <c r="K175" s="13"/>
+    </row>
+    <row r="176" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B176" s="4"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
@@ -5465,8 +6961,11 @@
       <c r="F176" s="13"/>
       <c r="G176" s="13"/>
       <c r="H176" s="13"/>
-    </row>
-    <row r="177" spans="2:8">
+      <c r="I176" s="13"/>
+      <c r="J176" s="13"/>
+      <c r="K176" s="13"/>
+    </row>
+    <row r="177" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B177" s="4" t="s">
         <v>78</v>
       </c>
@@ -5484,8 +6983,17 @@
       <c r="H177" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="178" spans="2:8">
+      <c r="I177" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J177" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K177" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="178" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B178" s="4" t="s">
         <v>79</v>
       </c>
@@ -5503,8 +7011,17 @@
       <c r="H178" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="179" spans="2:8">
+      <c r="I178" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J178" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K178" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="179" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B179" s="4" t="s">
         <v>80</v>
       </c>
@@ -5522,8 +7039,17 @@
       <c r="H179" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="180" spans="2:8">
+      <c r="I179" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J179" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K179" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="180" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B180" s="4" t="s">
         <v>81</v>
       </c>
@@ -5541,8 +7067,17 @@
       <c r="H180" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="181" spans="2:8">
+      <c r="I180" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J180" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K180" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="181" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B181" s="5" t="s">
         <v>8</v>
       </c>
@@ -5554,8 +7089,11 @@
       <c r="F181" s="13"/>
       <c r="G181" s="13"/>
       <c r="H181" s="13"/>
-    </row>
-    <row r="182" spans="2:8">
+      <c r="I181" s="13"/>
+      <c r="J181" s="13"/>
+      <c r="K181" s="13"/>
+    </row>
+    <row r="182" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B182" s="5" t="s">
         <v>8</v>
       </c>
@@ -5567,8 +7105,11 @@
       <c r="F182" s="13"/>
       <c r="G182" s="13"/>
       <c r="H182" s="13"/>
-    </row>
-    <row r="183" spans="2:8">
+      <c r="I182" s="13"/>
+      <c r="J182" s="13"/>
+      <c r="K182" s="13"/>
+    </row>
+    <row r="183" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B183" s="4" t="s">
         <v>82</v>
       </c>
@@ -5582,8 +7123,15 @@
       <c r="F183" s="13"/>
       <c r="G183" s="13"/>
       <c r="H183" s="13"/>
-    </row>
-    <row r="184" spans="2:8">
+      <c r="I183" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J183" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K183" s="13"/>
+    </row>
+    <row r="184" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B184" s="4" t="s">
         <v>83</v>
       </c>
@@ -5597,8 +7145,15 @@
       <c r="F184" s="13"/>
       <c r="G184" s="13"/>
       <c r="H184" s="13"/>
-    </row>
-    <row r="185" spans="2:8">
+      <c r="I184" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J184" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K184" s="13"/>
+    </row>
+    <row r="185" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B185" s="4" t="s">
         <v>84</v>
       </c>
@@ -5612,8 +7167,15 @@
       <c r="F185" s="13"/>
       <c r="G185" s="13"/>
       <c r="H185" s="13"/>
-    </row>
-    <row r="186" spans="2:8">
+      <c r="I185" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J185" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K185" s="13"/>
+    </row>
+    <row r="186" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B186" s="4" t="s">
         <v>85</v>
       </c>
@@ -5627,8 +7189,15 @@
       <c r="F186" s="13"/>
       <c r="G186" s="13"/>
       <c r="H186" s="13"/>
-    </row>
-    <row r="187" spans="2:8">
+      <c r="I186" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J186" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K186" s="13"/>
+    </row>
+    <row r="187" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B187" s="4" t="s">
         <v>86</v>
       </c>
@@ -5642,8 +7211,17 @@
       <c r="F187" s="13"/>
       <c r="G187" s="13"/>
       <c r="H187" s="13"/>
-    </row>
-    <row r="188" spans="2:8">
+      <c r="I187" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J187" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K187" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="188" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B188" s="4" t="s">
         <v>87</v>
       </c>
@@ -5657,8 +7235,15 @@
       <c r="F188" s="13"/>
       <c r="G188" s="13"/>
       <c r="H188" s="13"/>
-    </row>
-    <row r="189" spans="2:8">
+      <c r="I188" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J188" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K188" s="13"/>
+    </row>
+    <row r="189" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B189" s="4" t="s">
         <v>88</v>
       </c>
@@ -5672,8 +7257,13 @@
       <c r="F189" s="13"/>
       <c r="G189" s="13"/>
       <c r="H189" s="13"/>
-    </row>
-    <row r="190" spans="2:8">
+      <c r="I189" s="13"/>
+      <c r="J189" s="13"/>
+      <c r="K189" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="190" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B190" s="5" t="s">
         <v>8</v>
       </c>
@@ -5685,8 +7275,11 @@
       <c r="F190" s="13"/>
       <c r="G190" s="13"/>
       <c r="H190" s="13"/>
-    </row>
-    <row r="191" spans="2:8">
+      <c r="I190" s="13"/>
+      <c r="J190" s="13"/>
+      <c r="K190" s="13"/>
+    </row>
+    <row r="191" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B191" s="5" t="s">
         <v>8</v>
       </c>
@@ -5698,8 +7291,11 @@
       <c r="F191" s="13"/>
       <c r="G191" s="13"/>
       <c r="H191" s="13"/>
-    </row>
-    <row r="192" spans="2:8">
+      <c r="I191" s="13"/>
+      <c r="J191" s="13"/>
+      <c r="K191" s="13"/>
+    </row>
+    <row r="192" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B192" s="5" t="s">
         <v>8</v>
       </c>
@@ -5711,8 +7307,11 @@
       <c r="F192" s="13"/>
       <c r="G192" s="13"/>
       <c r="H192" s="13"/>
-    </row>
-    <row r="193" spans="2:8">
+      <c r="I192" s="13"/>
+      <c r="J192" s="13"/>
+      <c r="K192" s="13"/>
+    </row>
+    <row r="193" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B193" s="4"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
@@ -5720,8 +7319,11 @@
       <c r="F193" s="13"/>
       <c r="G193" s="13"/>
       <c r="H193" s="13"/>
-    </row>
-    <row r="194" spans="2:8">
+      <c r="I193" s="13"/>
+      <c r="J193" s="13"/>
+      <c r="K193" s="13"/>
+    </row>
+    <row r="194" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B194" s="4" t="s">
         <v>71</v>
       </c>
@@ -5741,8 +7343,17 @@
       <c r="H194" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="195" spans="2:8">
+      <c r="I194" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J194" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K194" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="195" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B195" s="4" t="s">
         <v>71</v>
       </c>
@@ -5762,8 +7373,17 @@
       <c r="H195" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="196" spans="2:8">
+      <c r="I195" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J195" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K195" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="196" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B196" s="4" t="s">
         <v>72</v>
       </c>
@@ -5785,8 +7405,17 @@
       <c r="H196" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="197" spans="2:8">
+      <c r="I196" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J196" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K196" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="197" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B197" s="4" t="s">
         <v>73</v>
       </c>
@@ -5800,8 +7429,15 @@
       <c r="F197" s="13"/>
       <c r="G197" s="13"/>
       <c r="H197" s="13"/>
-    </row>
-    <row r="198" spans="2:8">
+      <c r="I197" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J197" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K197" s="13"/>
+    </row>
+    <row r="198" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B198" s="4" t="s">
         <v>74</v>
       </c>
@@ -5823,8 +7459,17 @@
       <c r="H198" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="199" spans="2:8">
+      <c r="I198" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J198" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K198" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="199" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B199" s="4" t="s">
         <v>75</v>
       </c>
@@ -5844,8 +7489,17 @@
       <c r="H199" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="200" spans="2:8">
+      <c r="I199" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J199" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K199" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="200" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B200" s="4" t="s">
         <v>76</v>
       </c>
@@ -5867,8 +7521,17 @@
       <c r="H200" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="201" spans="2:8">
+      <c r="I200" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J200" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K200" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="201" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B201" s="4" t="s">
         <v>76</v>
       </c>
@@ -5890,8 +7553,17 @@
       <c r="H201" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="202" spans="2:8">
+      <c r="I201" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J201" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K201" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="202" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B202" s="4" t="s">
         <v>77</v>
       </c>
@@ -5913,8 +7585,17 @@
       <c r="H202" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="203" spans="2:8">
+      <c r="I202" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J202" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K202" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="203" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B203" s="5" t="s">
         <v>8</v>
       </c>
@@ -5926,8 +7607,11 @@
       <c r="F203" s="13"/>
       <c r="G203" s="13"/>
       <c r="H203" s="13"/>
-    </row>
-    <row r="204" spans="2:8">
+      <c r="I203" s="13"/>
+      <c r="J203" s="13"/>
+      <c r="K203" s="13"/>
+    </row>
+    <row r="204" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B204" s="4" t="s">
         <v>89</v>
       </c>
@@ -5947,8 +7631,17 @@
       <c r="H204" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="205" spans="2:8">
+      <c r="I204" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J204" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K204" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="205" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B205" s="5" t="s">
         <v>8</v>
       </c>
@@ -5960,8 +7653,11 @@
       <c r="F205" s="13"/>
       <c r="G205" s="13"/>
       <c r="H205" s="13"/>
-    </row>
-    <row r="206" spans="2:8">
+      <c r="I205" s="13"/>
+      <c r="J205" s="13"/>
+      <c r="K205" s="13"/>
+    </row>
+    <row r="206" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B206" s="5" t="s">
         <v>8</v>
       </c>
@@ -5973,8 +7669,11 @@
       <c r="F206" s="13"/>
       <c r="G206" s="13"/>
       <c r="H206" s="13"/>
-    </row>
-    <row r="207" spans="2:8">
+      <c r="I206" s="13"/>
+      <c r="J206" s="13"/>
+      <c r="K206" s="13"/>
+    </row>
+    <row r="207" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B207" s="5" t="s">
         <v>8</v>
       </c>
@@ -5986,8 +7685,11 @@
       <c r="F207" s="13"/>
       <c r="G207" s="13"/>
       <c r="H207" s="13"/>
-    </row>
-    <row r="208" spans="2:8">
+      <c r="I207" s="13"/>
+      <c r="J207" s="13"/>
+      <c r="K207" s="13"/>
+    </row>
+    <row r="208" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B208" s="5" t="s">
         <v>8</v>
       </c>
@@ -5999,8 +7701,11 @@
       <c r="F208" s="13"/>
       <c r="G208" s="13"/>
       <c r="H208" s="13"/>
-    </row>
-    <row r="209" spans="2:8">
+      <c r="I208" s="13"/>
+      <c r="J208" s="13"/>
+      <c r="K208" s="13"/>
+    </row>
+    <row r="209" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B209" s="5" t="s">
         <v>8</v>
       </c>
@@ -6012,8 +7717,11 @@
       <c r="F209" s="13"/>
       <c r="G209" s="13"/>
       <c r="H209" s="13"/>
-    </row>
-    <row r="210" spans="2:8">
+      <c r="I209" s="13"/>
+      <c r="J209" s="13"/>
+      <c r="K209" s="13"/>
+    </row>
+    <row r="210" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B210" s="4"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
@@ -6021,8 +7729,11 @@
       <c r="F210" s="13"/>
       <c r="G210" s="13"/>
       <c r="H210" s="13"/>
-    </row>
-    <row r="211" spans="2:8">
+      <c r="I210" s="13"/>
+      <c r="J210" s="13"/>
+      <c r="K210" s="13"/>
+    </row>
+    <row r="211" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B211" s="4" t="s">
         <v>90</v>
       </c>
@@ -6042,8 +7753,17 @@
       <c r="H211" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="212" spans="2:8">
+      <c r="I211" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J211" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K211" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="212" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B212" s="4" t="s">
         <v>91</v>
       </c>
@@ -6063,8 +7783,17 @@
       <c r="H212" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="213" spans="2:8">
+      <c r="I212" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J212" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K212" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="213" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B213" s="4" t="s">
         <v>92</v>
       </c>
@@ -6078,8 +7807,15 @@
       <c r="F213" s="13"/>
       <c r="G213" s="13"/>
       <c r="H213" s="13"/>
-    </row>
-    <row r="214" spans="2:8">
+      <c r="I213" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J213" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K213" s="13"/>
+    </row>
+    <row r="214" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B214" s="4" t="s">
         <v>93</v>
       </c>
@@ -6099,8 +7835,17 @@
       <c r="H214" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="215" spans="2:8">
+      <c r="I214" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J214" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K214" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="215" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B215" s="4"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
@@ -6108,8 +7853,11 @@
       <c r="F215" s="13"/>
       <c r="G215" s="13"/>
       <c r="H215" s="13"/>
-    </row>
-    <row r="216" spans="2:8">
+      <c r="I215" s="13"/>
+      <c r="J215" s="13"/>
+      <c r="K215" s="13"/>
+    </row>
+    <row r="216" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B216" s="4" t="s">
         <v>94</v>
       </c>
@@ -6121,8 +7869,17 @@
       <c r="F216" s="13"/>
       <c r="G216" s="13"/>
       <c r="H216" s="13"/>
-    </row>
-    <row r="217" spans="2:8">
+      <c r="I216" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J216" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K216" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="217" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B217" s="4" t="s">
         <v>95</v>
       </c>
@@ -6140,8 +7897,17 @@
       <c r="H217" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="218" spans="2:8">
+      <c r="I217" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J217" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K217" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="218" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B218" s="4" t="s">
         <v>96</v>
       </c>
@@ -6159,8 +7925,13 @@
       <c r="H218" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="219" spans="2:8">
+      <c r="I218" s="13"/>
+      <c r="J218" s="13"/>
+      <c r="K218" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="219" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B219" s="4" t="s">
         <v>97</v>
       </c>
@@ -6180,8 +7951,17 @@
       <c r="H219" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="220" spans="2:8">
+      <c r="I219" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J219" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K219" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="220" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B220" s="4" t="s">
         <v>98</v>
       </c>
@@ -6195,8 +7975,15 @@
       <c r="F220" s="13"/>
       <c r="G220" s="13"/>
       <c r="H220" s="13"/>
-    </row>
-    <row r="221" spans="2:8">
+      <c r="I220" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J220" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K220" s="13"/>
+    </row>
+    <row r="221" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B221" s="4" t="s">
         <v>99</v>
       </c>
@@ -6210,8 +7997,15 @@
       <c r="F221" s="13"/>
       <c r="G221" s="13"/>
       <c r="H221" s="13"/>
-    </row>
-    <row r="222" spans="2:8">
+      <c r="I221" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J221" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K221" s="13"/>
+    </row>
+    <row r="222" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B222" s="4" t="s">
         <v>100</v>
       </c>
@@ -6225,8 +8019,17 @@
       <c r="F222" s="13"/>
       <c r="G222" s="13"/>
       <c r="H222" s="13"/>
-    </row>
-    <row r="223" spans="2:8">
+      <c r="I222" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J222" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K222" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="223" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B223" s="4" t="s">
         <v>101</v>
       </c>
@@ -6248,8 +8051,17 @@
       <c r="H223" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="224" spans="2:8">
+      <c r="I223" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J223" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K223" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="224" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B224" s="4"/>
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
@@ -6257,8 +8069,11 @@
       <c r="F224" s="13"/>
       <c r="G224" s="13"/>
       <c r="H224" s="13"/>
-    </row>
-    <row r="225" spans="2:8">
+      <c r="I224" s="13"/>
+      <c r="J224" s="13"/>
+      <c r="K224" s="13"/>
+    </row>
+    <row r="225" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B225" s="4" t="s">
         <v>71</v>
       </c>
@@ -6278,8 +8093,17 @@
       <c r="H225" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="226" spans="2:8">
+      <c r="I225" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J225" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K225" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="226" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B226" s="4" t="s">
         <v>76</v>
       </c>
@@ -6301,8 +8125,17 @@
       <c r="H226" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="227" spans="2:8">
+      <c r="I226" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J226" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K226" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="227" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B227" s="5" t="s">
         <v>8</v>
       </c>
@@ -6314,8 +8147,11 @@
       <c r="F227" s="13"/>
       <c r="G227" s="13"/>
       <c r="H227" s="13"/>
-    </row>
-    <row r="228" spans="2:8">
+      <c r="I227" s="13"/>
+      <c r="J227" s="13"/>
+      <c r="K227" s="13"/>
+    </row>
+    <row r="228" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B228" s="5" t="s">
         <v>8</v>
       </c>
@@ -6327,8 +8163,11 @@
       <c r="F228" s="13"/>
       <c r="G228" s="13"/>
       <c r="H228" s="13"/>
-    </row>
-    <row r="229" spans="2:8">
+      <c r="I228" s="13"/>
+      <c r="J228" s="13"/>
+      <c r="K228" s="13"/>
+    </row>
+    <row r="229" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B229" s="4"/>
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
@@ -6336,8 +8175,11 @@
       <c r="F229" s="13"/>
       <c r="G229" s="13"/>
       <c r="H229" s="13"/>
-    </row>
-    <row r="230" spans="2:8">
+      <c r="I229" s="13"/>
+      <c r="J229" s="13"/>
+      <c r="K229" s="13"/>
+    </row>
+    <row r="230" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B230" s="4"/>
       <c r="C230" s="3" t="s">
         <v>234</v>
@@ -6353,8 +8195,17 @@
       <c r="H230" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="231" spans="2:8">
+      <c r="I230" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J230" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K230" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="231" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B231" s="4"/>
       <c r="C231" s="3" t="s">
         <v>235</v>
@@ -6370,8 +8221,17 @@
       <c r="H231" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="232" spans="2:8">
+      <c r="I231" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J231" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K231" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="232" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B232" s="4"/>
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
@@ -6379,8 +8239,11 @@
       <c r="F232" s="13"/>
       <c r="G232" s="13"/>
       <c r="H232" s="13"/>
-    </row>
-    <row r="233" spans="2:8">
+      <c r="I232" s="13"/>
+      <c r="J232" s="13"/>
+      <c r="K232" s="13"/>
+    </row>
+    <row r="233" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B233" s="4" t="s">
         <v>102</v>
       </c>
@@ -6398,8 +8261,17 @@
       <c r="H233" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="234" spans="2:8">
+      <c r="I233" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J233" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K233" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="234" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B234" s="4" t="s">
         <v>103</v>
       </c>
@@ -6417,8 +8289,17 @@
       <c r="H234" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="235" spans="2:8">
+      <c r="I234" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J234" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K234" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="235" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B235" s="4" t="s">
         <v>104</v>
       </c>
@@ -6436,8 +8317,17 @@
       <c r="H235" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="236" spans="2:8">
+      <c r="I235" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J235" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K235" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="236" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B236" s="5" t="s">
         <v>8</v>
       </c>
@@ -6455,8 +8345,17 @@
       <c r="H236" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="237" spans="2:8">
+      <c r="I236" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J236" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K236" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="237" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B237" s="4"/>
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
@@ -6464,8 +8363,11 @@
       <c r="F237" s="13"/>
       <c r="G237" s="13"/>
       <c r="H237" s="13"/>
-    </row>
-    <row r="238" spans="2:8">
+      <c r="I237" s="13"/>
+      <c r="J237" s="13"/>
+      <c r="K237" s="13"/>
+    </row>
+    <row r="238" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B238" s="4" t="s">
         <v>105</v>
       </c>
@@ -6483,8 +8385,17 @@
       <c r="H238" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="239" spans="2:8">
+      <c r="I238" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J238" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K238" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="239" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B239" s="4" t="s">
         <v>80</v>
       </c>
@@ -6502,8 +8413,17 @@
       <c r="H239" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="240" spans="2:8">
+      <c r="I239" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J239" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K239" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="240" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B240" s="4" t="s">
         <v>106</v>
       </c>
@@ -6521,8 +8441,17 @@
       <c r="H240" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="241" spans="2:8">
+      <c r="I240" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J240" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K240" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="241" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B241" s="4" t="s">
         <v>81</v>
       </c>
@@ -6540,8 +8469,17 @@
       <c r="H241" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="242" spans="2:8">
+      <c r="I241" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J241" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K241" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="242" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B242" s="4"/>
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
@@ -6549,8 +8487,11 @@
       <c r="F242" s="13"/>
       <c r="G242" s="13"/>
       <c r="H242" s="13"/>
-    </row>
-    <row r="243" spans="2:8">
+      <c r="I242" s="13"/>
+      <c r="J242" s="13"/>
+      <c r="K242" s="13"/>
+    </row>
+    <row r="243" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B243" s="4" t="s">
         <v>107</v>
       </c>
@@ -6568,8 +8509,17 @@
       <c r="H243" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="244" spans="2:8">
+      <c r="I243" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J243" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K243" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="244" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B244" s="4" t="s">
         <v>108</v>
       </c>
@@ -6589,8 +8539,17 @@
       <c r="H244" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="245" spans="2:8">
+      <c r="I244" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J244" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K244" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="245" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B245" s="4" t="s">
         <v>109</v>
       </c>
@@ -6610,8 +8569,17 @@
       <c r="H245" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="246" spans="2:8">
+      <c r="I245" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J245" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K245" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="246" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B246" s="4" t="s">
         <v>110</v>
       </c>
@@ -6631,8 +8599,17 @@
       <c r="H246" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="247" spans="2:8">
+      <c r="I246" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J246" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K246" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="247" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B247" s="4" t="s">
         <v>111</v>
       </c>
@@ -6652,8 +8629,17 @@
       <c r="H247" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="248" spans="2:8">
+      <c r="I247" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J247" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K247" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="248" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B248" s="4" t="s">
         <v>112</v>
       </c>
@@ -6673,8 +8659,17 @@
       <c r="H248" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="249" spans="2:8">
+      <c r="I248" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J248" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K248" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="249" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B249" s="4" t="s">
         <v>113</v>
       </c>
@@ -6694,8 +8689,17 @@
       <c r="H249" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="250" spans="2:8">
+      <c r="I249" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J249" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K249" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="250" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B250" s="4" t="s">
         <v>114</v>
       </c>
@@ -6715,8 +8719,17 @@
       <c r="H250" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="251" spans="2:8">
+      <c r="I250" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J250" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K250" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="251" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B251" s="4" t="s">
         <v>115</v>
       </c>
@@ -6736,8 +8749,17 @@
       <c r="H251" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="252" spans="2:8">
+      <c r="I251" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J251" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K251" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="252" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B252" s="4" t="s">
         <v>116</v>
       </c>
@@ -6749,8 +8771,11 @@
       <c r="F252" s="13"/>
       <c r="G252" s="13"/>
       <c r="H252" s="13"/>
-    </row>
-    <row r="253" spans="2:8">
+      <c r="I252" s="13"/>
+      <c r="J252" s="13"/>
+      <c r="K252" s="13"/>
+    </row>
+    <row r="253" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B253" s="4" t="s">
         <v>117</v>
       </c>
@@ -6770,8 +8795,17 @@
       <c r="H253" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="254" spans="2:8">
+      <c r="I253" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J253" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K253" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="254" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B254" s="5" t="s">
         <v>8</v>
       </c>
@@ -6783,8 +8817,11 @@
       <c r="F254" s="13"/>
       <c r="G254" s="13"/>
       <c r="H254" s="13"/>
-    </row>
-    <row r="255" spans="2:8">
+      <c r="I254" s="13"/>
+      <c r="J254" s="13"/>
+      <c r="K254" s="13"/>
+    </row>
+    <row r="255" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B255" s="4" t="s">
         <v>118</v>
       </c>
@@ -6796,8 +8833,13 @@
       <c r="F255" s="13"/>
       <c r="G255" s="13"/>
       <c r="H255" s="13"/>
-    </row>
-    <row r="256" spans="2:8">
+      <c r="I255" s="13"/>
+      <c r="J255" s="13"/>
+      <c r="K255" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="256" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B256" s="4" t="s">
         <v>119</v>
       </c>
@@ -6811,8 +8853,15 @@
       <c r="F256" s="13"/>
       <c r="G256" s="13"/>
       <c r="H256" s="13"/>
-    </row>
-    <row r="257" spans="2:8">
+      <c r="I256" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J256" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K256" s="13"/>
+    </row>
+    <row r="257" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B257" s="4" t="s">
         <v>120</v>
       </c>
@@ -6826,8 +8875,17 @@
       <c r="F257" s="13"/>
       <c r="G257" s="13"/>
       <c r="H257" s="13"/>
-    </row>
-    <row r="258" spans="2:8">
+      <c r="I257" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J257" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K257" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="258" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B258" s="4" t="s">
         <v>121</v>
       </c>
@@ -6847,8 +8905,17 @@
       <c r="H258" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="259" spans="2:8">
+      <c r="I258" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J258" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K258" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="259" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B259" s="4" t="s">
         <v>122</v>
       </c>
@@ -6868,8 +8935,17 @@
       <c r="H259" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="260" spans="2:8">
+      <c r="I259" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J259" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K259" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="260" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B260" s="4" t="s">
         <v>123</v>
       </c>
@@ -6889,8 +8965,17 @@
       <c r="H260" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="261" spans="2:8">
+      <c r="I260" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J260" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K260" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="261" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B261" s="4" t="s">
         <v>124</v>
       </c>
@@ -6910,8 +8995,17 @@
       <c r="H261" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="262" spans="2:8">
+      <c r="I261" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J261" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K261" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="262" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B262" s="4" t="s">
         <v>125</v>
       </c>
@@ -6933,8 +9027,17 @@
       <c r="H262" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="263" spans="2:8">
+      <c r="I262" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J262" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K262" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="263" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B263" s="5" t="s">
         <v>8</v>
       </c>
@@ -6946,8 +9049,11 @@
       <c r="F263" s="13"/>
       <c r="G263" s="13"/>
       <c r="H263" s="13"/>
-    </row>
-    <row r="264" spans="2:8">
+      <c r="I263" s="13"/>
+      <c r="J263" s="13"/>
+      <c r="K263" s="13"/>
+    </row>
+    <row r="264" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B264" s="4" t="s">
         <v>126</v>
       </c>
@@ -6967,8 +9073,17 @@
       <c r="H264" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="265" spans="2:8">
+      <c r="I264" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J264" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K264" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="265" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B265" s="4" t="s">
         <v>127</v>
       </c>
@@ -6988,8 +9103,17 @@
       <c r="H265" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="266" spans="2:8">
+      <c r="I265" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J265" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K265" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="266" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B266" s="5" t="s">
         <v>8</v>
       </c>
@@ -7001,8 +9125,11 @@
       <c r="F266" s="13"/>
       <c r="G266" s="13"/>
       <c r="H266" s="13"/>
-    </row>
-    <row r="267" spans="2:8">
+      <c r="I266" s="13"/>
+      <c r="J266" s="13"/>
+      <c r="K266" s="13"/>
+    </row>
+    <row r="267" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B267" s="5" t="s">
         <v>128</v>
       </c>
@@ -7014,8 +9141,11 @@
       <c r="F267" s="13"/>
       <c r="G267" s="13"/>
       <c r="H267" s="13"/>
-    </row>
-    <row r="268" spans="2:8">
+      <c r="I267" s="13"/>
+      <c r="J267" s="13"/>
+      <c r="K267" s="13"/>
+    </row>
+    <row r="268" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B268" s="5" t="s">
         <v>128</v>
       </c>
@@ -7027,8 +9157,11 @@
       <c r="F268" s="13"/>
       <c r="G268" s="13"/>
       <c r="H268" s="13"/>
-    </row>
-    <row r="269" spans="2:8">
+      <c r="I268" s="13"/>
+      <c r="J268" s="13"/>
+      <c r="K268" s="13"/>
+    </row>
+    <row r="269" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B269" s="5" t="s">
         <v>128</v>
       </c>
@@ -7040,8 +9173,11 @@
       <c r="F269" s="13"/>
       <c r="G269" s="13"/>
       <c r="H269" s="13"/>
-    </row>
-    <row r="270" spans="2:8">
+      <c r="I269" s="13"/>
+      <c r="J269" s="13"/>
+      <c r="K269" s="13"/>
+    </row>
+    <row r="270" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B270" s="5" t="s">
         <v>128</v>
       </c>
@@ -7053,8 +9189,11 @@
       <c r="F270" s="13"/>
       <c r="G270" s="13"/>
       <c r="H270" s="13"/>
-    </row>
-    <row r="271" spans="2:8">
+      <c r="I270" s="13"/>
+      <c r="J270" s="13"/>
+      <c r="K270" s="13"/>
+    </row>
+    <row r="271" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B271" s="5" t="s">
         <v>128</v>
       </c>
@@ -7066,8 +9205,11 @@
       <c r="F271" s="13"/>
       <c r="G271" s="13"/>
       <c r="H271" s="13"/>
-    </row>
-    <row r="272" spans="2:8">
+      <c r="I271" s="13"/>
+      <c r="J271" s="13"/>
+      <c r="K271" s="13"/>
+    </row>
+    <row r="272" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B272" s="5" t="s">
         <v>128</v>
       </c>
@@ -7079,8 +9221,11 @@
       <c r="F272" s="13"/>
       <c r="G272" s="13"/>
       <c r="H272" s="13"/>
-    </row>
-    <row r="273" spans="2:8">
+      <c r="I272" s="13"/>
+      <c r="J272" s="13"/>
+      <c r="K272" s="13"/>
+    </row>
+    <row r="273" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B273" s="5" t="s">
         <v>128</v>
       </c>
@@ -7092,8 +9237,11 @@
       <c r="F273" s="13"/>
       <c r="G273" s="13"/>
       <c r="H273" s="13"/>
-    </row>
-    <row r="274" spans="2:8">
+      <c r="I273" s="13"/>
+      <c r="J273" s="13"/>
+      <c r="K273" s="13"/>
+    </row>
+    <row r="274" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B274" s="5" t="s">
         <v>128</v>
       </c>
@@ -7105,8 +9253,11 @@
       <c r="F274" s="13"/>
       <c r="G274" s="13"/>
       <c r="H274" s="13"/>
-    </row>
-    <row r="275" spans="2:8">
+      <c r="I274" s="13"/>
+      <c r="J274" s="13"/>
+      <c r="K274" s="13"/>
+    </row>
+    <row r="275" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B275" s="4"/>
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
@@ -7114,8 +9265,11 @@
       <c r="F275" s="13"/>
       <c r="G275" s="13"/>
       <c r="H275" s="13"/>
-    </row>
-    <row r="276" spans="2:8">
+      <c r="I275" s="13"/>
+      <c r="J275" s="13"/>
+      <c r="K275" s="13"/>
+    </row>
+    <row r="276" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B276" s="4"/>
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
@@ -7123,8 +9277,11 @@
       <c r="F276" s="14"/>
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
-    </row>
-    <row r="277" spans="2:8">
+      <c r="I276" s="14"/>
+      <c r="J276" s="14"/>
+      <c r="K276" s="14"/>
+    </row>
+    <row r="277" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B277" s="4"/>
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
@@ -7132,8 +9289,11 @@
       <c r="F277" s="14"/>
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
-    </row>
-    <row r="278" spans="2:8">
+      <c r="I277" s="14"/>
+      <c r="J277" s="14"/>
+      <c r="K277" s="14"/>
+    </row>
+    <row r="278" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B278" s="4"/>
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
@@ -7141,8 +9301,11 @@
       <c r="F278" s="14"/>
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
-    </row>
-    <row r="279" spans="2:8">
+      <c r="I278" s="14"/>
+      <c r="J278" s="14"/>
+      <c r="K278" s="14"/>
+    </row>
+    <row r="279" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B279" s="4"/>
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
@@ -7150,8 +9313,11 @@
       <c r="F279" s="14"/>
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
-    </row>
-    <row r="280" spans="2:8">
+      <c r="I279" s="14"/>
+      <c r="J279" s="14"/>
+      <c r="K279" s="14"/>
+    </row>
+    <row r="280" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B280" s="4"/>
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
@@ -7159,8 +9325,11 @@
       <c r="F280" s="14"/>
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
-    </row>
-    <row r="281" spans="2:8">
+      <c r="I280" s="14"/>
+      <c r="J280" s="14"/>
+      <c r="K280" s="14"/>
+    </row>
+    <row r="281" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B281" s="4"/>
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
@@ -7168,8 +9337,11 @@
       <c r="F281" s="14"/>
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
-    </row>
-    <row r="282" spans="2:8">
+      <c r="I281" s="14"/>
+      <c r="J281" s="14"/>
+      <c r="K281" s="14"/>
+    </row>
+    <row r="282" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B282" s="4"/>
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
@@ -7177,8 +9349,11 @@
       <c r="F282" s="14"/>
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
-    </row>
-    <row r="283" spans="2:8">
+      <c r="I282" s="14"/>
+      <c r="J282" s="14"/>
+      <c r="K282" s="14"/>
+    </row>
+    <row r="283" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B283" s="4"/>
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
@@ -7186,8 +9361,11 @@
       <c r="F283" s="14"/>
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
-    </row>
-    <row r="284" spans="2:8">
+      <c r="I283" s="14"/>
+      <c r="J283" s="14"/>
+      <c r="K283" s="14"/>
+    </row>
+    <row r="284" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B284" s="4"/>
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
@@ -7195,8 +9373,11 @@
       <c r="F284" s="14"/>
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
-    </row>
-    <row r="285" spans="2:8">
+      <c r="I284" s="14"/>
+      <c r="J284" s="14"/>
+      <c r="K284" s="14"/>
+    </row>
+    <row r="285" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B285" s="5"/>
       <c r="C285" s="17"/>
       <c r="D285" s="3"/>
@@ -7204,8 +9385,11 @@
       <c r="F285" s="14"/>
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
-    </row>
-    <row r="286" spans="2:8">
+      <c r="I285" s="14"/>
+      <c r="J285" s="14"/>
+      <c r="K285" s="14"/>
+    </row>
+    <row r="286" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B286" s="4"/>
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
@@ -7213,8 +9397,11 @@
       <c r="F286" s="14"/>
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
-    </row>
-    <row r="287" spans="2:8">
+      <c r="I286" s="14"/>
+      <c r="J286" s="14"/>
+      <c r="K286" s="14"/>
+    </row>
+    <row r="287" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B287" s="5"/>
       <c r="C287" s="17"/>
       <c r="D287" s="3"/>
@@ -7222,8 +9409,11 @@
       <c r="F287" s="14"/>
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
-    </row>
-    <row r="288" spans="2:8">
+      <c r="I287" s="14"/>
+      <c r="J287" s="14"/>
+      <c r="K287" s="14"/>
+    </row>
+    <row r="288" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B288" s="5"/>
       <c r="C288" s="17"/>
       <c r="D288" s="3"/>
@@ -7231,8 +9421,11 @@
       <c r="F288" s="14"/>
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
-    </row>
-    <row r="289" spans="2:8">
+      <c r="I288" s="14"/>
+      <c r="J288" s="14"/>
+      <c r="K288" s="14"/>
+    </row>
+    <row r="289" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B289" s="4"/>
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
@@ -7240,8 +9433,11 @@
       <c r="F289" s="14"/>
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
-    </row>
-    <row r="290" spans="2:8">
+      <c r="I289" s="14"/>
+      <c r="J289" s="14"/>
+      <c r="K289" s="14"/>
+    </row>
+    <row r="290" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B290" s="4"/>
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
@@ -7249,8 +9445,11 @@
       <c r="F290" s="14"/>
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
-    </row>
-    <row r="291" spans="2:8">
+      <c r="I290" s="14"/>
+      <c r="J290" s="14"/>
+      <c r="K290" s="14"/>
+    </row>
+    <row r="291" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B291" s="4"/>
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
@@ -7258,8 +9457,11 @@
       <c r="F291" s="14"/>
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
-    </row>
-    <row r="292" spans="2:8">
+      <c r="I291" s="14"/>
+      <c r="J291" s="14"/>
+      <c r="K291" s="14"/>
+    </row>
+    <row r="292" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B292" s="4"/>
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
@@ -7267,8 +9469,11 @@
       <c r="F292" s="13"/>
       <c r="G292" s="13"/>
       <c r="H292" s="13"/>
-    </row>
-    <row r="293" spans="2:8">
+      <c r="I292" s="13"/>
+      <c r="J292" s="13"/>
+      <c r="K292" s="13"/>
+    </row>
+    <row r="293" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B293" s="4"/>
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
@@ -7276,8 +9481,11 @@
       <c r="F293" s="14"/>
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
-    </row>
-    <row r="294" spans="2:8">
+      <c r="I293" s="14"/>
+      <c r="J293" s="14"/>
+      <c r="K293" s="14"/>
+    </row>
+    <row r="294" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B294" s="4"/>
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
@@ -7285,8 +9493,11 @@
       <c r="F294" s="14"/>
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
-    </row>
-    <row r="295" spans="2:8">
+      <c r="I294" s="14"/>
+      <c r="J294" s="14"/>
+      <c r="K294" s="14"/>
+    </row>
+    <row r="295" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B295" s="4"/>
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
@@ -7294,8 +9505,11 @@
       <c r="F295" s="14"/>
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
-    </row>
-    <row r="296" spans="2:8">
+      <c r="I295" s="14"/>
+      <c r="J295" s="14"/>
+      <c r="K295" s="14"/>
+    </row>
+    <row r="296" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B296" s="4"/>
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
@@ -7303,8 +9517,11 @@
       <c r="F296" s="14"/>
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
-    </row>
-    <row r="297" spans="2:8">
+      <c r="I296" s="14"/>
+      <c r="J296" s="14"/>
+      <c r="K296" s="14"/>
+    </row>
+    <row r="297" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B297" s="4"/>
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
@@ -7312,8 +9529,11 @@
       <c r="F297" s="14"/>
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
-    </row>
-    <row r="298" spans="2:8">
+      <c r="I297" s="14"/>
+      <c r="J297" s="14"/>
+      <c r="K297" s="14"/>
+    </row>
+    <row r="298" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B298" s="4"/>
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
@@ -7321,8 +9541,11 @@
       <c r="F298" s="14"/>
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
-    </row>
-    <row r="299" spans="2:8">
+      <c r="I298" s="14"/>
+      <c r="J298" s="14"/>
+      <c r="K298" s="14"/>
+    </row>
+    <row r="299" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B299" s="4"/>
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
@@ -7330,8 +9553,11 @@
       <c r="F299" s="14"/>
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
-    </row>
-    <row r="300" spans="2:8">
+      <c r="I299" s="14"/>
+      <c r="J299" s="14"/>
+      <c r="K299" s="14"/>
+    </row>
+    <row r="300" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B300" s="4"/>
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
@@ -7339,8 +9565,11 @@
       <c r="F300" s="14"/>
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
-    </row>
-    <row r="301" spans="2:8">
+      <c r="I300" s="14"/>
+      <c r="J300" s="14"/>
+      <c r="K300" s="14"/>
+    </row>
+    <row r="301" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B301" s="4"/>
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
@@ -7348,8 +9577,11 @@
       <c r="F301" s="14"/>
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
-    </row>
-    <row r="302" spans="2:8">
+      <c r="I301" s="14"/>
+      <c r="J301" s="14"/>
+      <c r="K301" s="14"/>
+    </row>
+    <row r="302" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B302" s="5"/>
       <c r="C302" s="3"/>
       <c r="D302" s="3"/>
@@ -7357,8 +9589,11 @@
       <c r="F302" s="14"/>
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
-    </row>
-    <row r="303" spans="2:8">
+      <c r="I302" s="14"/>
+      <c r="J302" s="14"/>
+      <c r="K302" s="14"/>
+    </row>
+    <row r="303" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B303" s="4"/>
       <c r="C303" s="3"/>
       <c r="D303" s="3"/>
@@ -7366,8 +9601,11 @@
       <c r="F303" s="14"/>
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
-    </row>
-    <row r="304" spans="2:8">
+      <c r="I303" s="14"/>
+      <c r="J303" s="14"/>
+      <c r="K303" s="14"/>
+    </row>
+    <row r="304" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B304" s="5"/>
       <c r="C304" s="3"/>
       <c r="D304" s="3"/>
@@ -7375,8 +9613,11 @@
       <c r="F304" s="14"/>
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
-    </row>
-    <row r="305" spans="2:8">
+      <c r="I304" s="14"/>
+      <c r="J304" s="14"/>
+      <c r="K304" s="14"/>
+    </row>
+    <row r="305" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B305" s="5"/>
       <c r="C305" s="3"/>
       <c r="D305" s="3"/>
@@ -7384,8 +9625,11 @@
       <c r="F305" s="14"/>
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
-    </row>
-    <row r="306" spans="2:8">
+      <c r="I305" s="14"/>
+      <c r="J305" s="14"/>
+      <c r="K305" s="14"/>
+    </row>
+    <row r="306" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B306" s="4"/>
       <c r="C306" s="3"/>
       <c r="D306" s="3"/>
@@ -7393,8 +9637,11 @@
       <c r="F306" s="14"/>
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
-    </row>
-    <row r="307" spans="2:8">
+      <c r="I306" s="14"/>
+      <c r="J306" s="14"/>
+      <c r="K306" s="14"/>
+    </row>
+    <row r="307" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B307" s="4"/>
       <c r="C307" s="3"/>
       <c r="D307" s="3"/>
@@ -7402,8 +9649,11 @@
       <c r="F307" s="14"/>
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
-    </row>
-    <row r="308" spans="2:8">
+      <c r="I307" s="14"/>
+      <c r="J307" s="14"/>
+      <c r="K307" s="14"/>
+    </row>
+    <row r="308" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B308" s="4"/>
       <c r="C308" s="3"/>
       <c r="D308" s="3"/>
@@ -7411,8 +9661,11 @@
       <c r="F308" s="14"/>
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
-    </row>
-    <row r="309" spans="2:8">
+      <c r="I308" s="14"/>
+      <c r="J308" s="14"/>
+      <c r="K308" s="14"/>
+    </row>
+    <row r="309" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B309" s="4"/>
       <c r="C309" s="3"/>
       <c r="D309" s="3"/>
@@ -7420,8 +9673,11 @@
       <c r="F309" s="13"/>
       <c r="G309" s="13"/>
       <c r="H309" s="13"/>
-    </row>
-    <row r="310" spans="2:8">
+      <c r="I309" s="13"/>
+      <c r="J309" s="13"/>
+      <c r="K309" s="13"/>
+    </row>
+    <row r="310" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B310" s="4"/>
       <c r="C310" s="3"/>
       <c r="D310" s="3"/>
@@ -7429,8 +9685,11 @@
       <c r="F310" s="14"/>
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
-    </row>
-    <row r="311" spans="2:8">
+      <c r="I310" s="14"/>
+      <c r="J310" s="14"/>
+      <c r="K310" s="14"/>
+    </row>
+    <row r="311" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B311" s="4"/>
       <c r="C311" s="3"/>
       <c r="D311" s="3"/>
@@ -7438,8 +9697,11 @@
       <c r="F311" s="14"/>
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
-    </row>
-    <row r="312" spans="2:8">
+      <c r="I311" s="14"/>
+      <c r="J311" s="14"/>
+      <c r="K311" s="14"/>
+    </row>
+    <row r="312" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B312" s="4"/>
       <c r="C312" s="3"/>
       <c r="D312" s="3"/>
@@ -7447,8 +9709,11 @@
       <c r="F312" s="14"/>
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
-    </row>
-    <row r="313" spans="2:8">
+      <c r="I312" s="14"/>
+      <c r="J312" s="14"/>
+      <c r="K312" s="14"/>
+    </row>
+    <row r="313" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B313" s="4"/>
       <c r="C313" s="3"/>
       <c r="D313" s="3"/>
@@ -7456,8 +9721,11 @@
       <c r="F313" s="14"/>
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
-    </row>
-    <row r="314" spans="2:8">
+      <c r="I313" s="14"/>
+      <c r="J313" s="14"/>
+      <c r="K313" s="14"/>
+    </row>
+    <row r="314" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B314" s="4"/>
       <c r="C314" s="3"/>
       <c r="D314" s="3"/>
@@ -7465,8 +9733,11 @@
       <c r="F314" s="14"/>
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
-    </row>
-    <row r="315" spans="2:8">
+      <c r="I314" s="14"/>
+      <c r="J314" s="14"/>
+      <c r="K314" s="14"/>
+    </row>
+    <row r="315" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B315" s="4"/>
       <c r="C315" s="3"/>
       <c r="D315" s="3"/>
@@ -7474,8 +9745,11 @@
       <c r="F315" s="14"/>
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
-    </row>
-    <row r="316" spans="2:8">
+      <c r="I315" s="14"/>
+      <c r="J315" s="14"/>
+      <c r="K315" s="14"/>
+    </row>
+    <row r="316" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B316" s="4"/>
       <c r="C316" s="3"/>
       <c r="D316" s="3"/>
@@ -7483,8 +9757,11 @@
       <c r="F316" s="14"/>
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
-    </row>
-    <row r="317" spans="2:8">
+      <c r="I316" s="14"/>
+      <c r="J316" s="14"/>
+      <c r="K316" s="14"/>
+    </row>
+    <row r="317" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B317" s="4"/>
       <c r="C317" s="3"/>
       <c r="D317" s="3"/>
@@ -7492,8 +9769,11 @@
       <c r="F317" s="14"/>
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
-    </row>
-    <row r="318" spans="2:8">
+      <c r="I317" s="14"/>
+      <c r="J317" s="14"/>
+      <c r="K317" s="14"/>
+    </row>
+    <row r="318" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B318" s="4"/>
       <c r="C318" s="3"/>
       <c r="D318" s="3"/>
@@ -7501,8 +9781,11 @@
       <c r="F318" s="14"/>
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
-    </row>
-    <row r="319" spans="2:8">
+      <c r="I318" s="14"/>
+      <c r="J318" s="14"/>
+      <c r="K318" s="14"/>
+    </row>
+    <row r="319" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B319" s="5"/>
       <c r="C319" s="3"/>
       <c r="D319" s="3"/>
@@ -7510,8 +9793,11 @@
       <c r="F319" s="14"/>
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
-    </row>
-    <row r="320" spans="2:8">
+      <c r="I319" s="14"/>
+      <c r="J319" s="14"/>
+      <c r="K319" s="14"/>
+    </row>
+    <row r="320" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B320" s="4"/>
       <c r="C320" s="3"/>
       <c r="D320" s="3"/>
@@ -7519,8 +9805,11 @@
       <c r="F320" s="14"/>
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
-    </row>
-    <row r="321" spans="2:8">
+      <c r="I320" s="14"/>
+      <c r="J320" s="14"/>
+      <c r="K320" s="14"/>
+    </row>
+    <row r="321" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B321" s="5"/>
       <c r="C321" s="3"/>
       <c r="D321" s="3"/>
@@ -7528,8 +9817,11 @@
       <c r="F321" s="14"/>
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
-    </row>
-    <row r="322" spans="2:8">
+      <c r="I321" s="14"/>
+      <c r="J321" s="14"/>
+      <c r="K321" s="14"/>
+    </row>
+    <row r="322" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B322" s="5"/>
       <c r="C322" s="3"/>
       <c r="D322" s="3"/>
@@ -7537,8 +9829,11 @@
       <c r="F322" s="14"/>
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
-    </row>
-    <row r="323" spans="2:8">
+      <c r="I322" s="14"/>
+      <c r="J322" s="14"/>
+      <c r="K322" s="14"/>
+    </row>
+    <row r="323" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B323" s="4"/>
       <c r="C323" s="3"/>
       <c r="D323" s="3"/>
@@ -7546,8 +9841,11 @@
       <c r="F323" s="14"/>
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
-    </row>
-    <row r="324" spans="2:8">
+      <c r="I323" s="14"/>
+      <c r="J323" s="14"/>
+      <c r="K323" s="14"/>
+    </row>
+    <row r="324" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B324" s="4"/>
       <c r="C324" s="3"/>
       <c r="D324" s="3"/>
@@ -7555,8 +9853,11 @@
       <c r="F324" s="14"/>
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
-    </row>
-    <row r="325" spans="2:8">
+      <c r="I324" s="14"/>
+      <c r="J324" s="14"/>
+      <c r="K324" s="14"/>
+    </row>
+    <row r="325" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B325" s="4"/>
       <c r="C325" s="3"/>
       <c r="D325" s="3"/>
@@ -7564,8 +9865,11 @@
       <c r="F325" s="14"/>
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
-    </row>
-    <row r="326" spans="2:8">
+      <c r="I325" s="14"/>
+      <c r="J325" s="14"/>
+      <c r="K325" s="14"/>
+    </row>
+    <row r="326" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B326" s="4"/>
       <c r="C326" s="19"/>
       <c r="D326" s="19"/>
@@ -7573,8 +9877,11 @@
       <c r="F326" s="13"/>
       <c r="G326" s="13"/>
       <c r="H326" s="13"/>
-    </row>
-    <row r="327" spans="2:8">
+      <c r="I326" s="13"/>
+      <c r="J326" s="13"/>
+      <c r="K326" s="13"/>
+    </row>
+    <row r="327" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B327" s="4"/>
       <c r="C327" s="3"/>
       <c r="D327" s="3"/>
@@ -7582,8 +9889,11 @@
       <c r="F327" s="14"/>
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
-    </row>
-    <row r="328" spans="2:8">
+      <c r="I327" s="14"/>
+      <c r="J327" s="14"/>
+      <c r="K327" s="14"/>
+    </row>
+    <row r="328" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B328" s="4"/>
       <c r="C328" s="3"/>
       <c r="D328" s="3"/>
@@ -7591,8 +9901,11 @@
       <c r="F328" s="14"/>
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
-    </row>
-    <row r="329" spans="2:8">
+      <c r="I328" s="14"/>
+      <c r="J328" s="14"/>
+      <c r="K328" s="14"/>
+    </row>
+    <row r="329" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B329" s="4"/>
       <c r="C329" s="3"/>
       <c r="D329" s="3"/>
@@ -7600,8 +9913,11 @@
       <c r="F329" s="14"/>
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
-    </row>
-    <row r="330" spans="2:8">
+      <c r="I329" s="14"/>
+      <c r="J329" s="14"/>
+      <c r="K329" s="14"/>
+    </row>
+    <row r="330" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B330" s="4"/>
       <c r="C330" s="3"/>
       <c r="D330" s="3"/>
@@ -7609,8 +9925,11 @@
       <c r="F330" s="14"/>
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
-    </row>
-    <row r="331" spans="2:8">
+      <c r="I330" s="14"/>
+      <c r="J330" s="14"/>
+      <c r="K330" s="14"/>
+    </row>
+    <row r="331" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B331" s="4"/>
       <c r="C331" s="3"/>
       <c r="D331" s="3"/>
@@ -7618,8 +9937,11 @@
       <c r="F331" s="14"/>
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
-    </row>
-    <row r="332" spans="2:8">
+      <c r="I331" s="14"/>
+      <c r="J331" s="14"/>
+      <c r="K331" s="14"/>
+    </row>
+    <row r="332" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B332" s="4"/>
       <c r="C332" s="3"/>
       <c r="D332" s="3"/>
@@ -7627,8 +9949,11 @@
       <c r="F332" s="14"/>
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
-    </row>
-    <row r="333" spans="2:8">
+      <c r="I332" s="14"/>
+      <c r="J332" s="14"/>
+      <c r="K332" s="14"/>
+    </row>
+    <row r="333" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B333" s="4"/>
       <c r="C333" s="3"/>
       <c r="D333" s="3"/>
@@ -7636,8 +9961,11 @@
       <c r="F333" s="14"/>
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
-    </row>
-    <row r="334" spans="2:8">
+      <c r="I333" s="14"/>
+      <c r="J333" s="14"/>
+      <c r="K333" s="14"/>
+    </row>
+    <row r="334" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B334" s="4"/>
       <c r="C334" s="3"/>
       <c r="D334" s="3"/>
@@ -7645,8 +9973,11 @@
       <c r="F334" s="14"/>
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
-    </row>
-    <row r="335" spans="2:8">
+      <c r="I334" s="14"/>
+      <c r="J334" s="14"/>
+      <c r="K334" s="14"/>
+    </row>
+    <row r="335" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B335" s="4"/>
       <c r="C335" s="3"/>
       <c r="D335" s="3"/>
@@ -7654,8 +9985,11 @@
       <c r="F335" s="14"/>
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
-    </row>
-    <row r="336" spans="2:8">
+      <c r="I335" s="14"/>
+      <c r="J335" s="14"/>
+      <c r="K335" s="14"/>
+    </row>
+    <row r="336" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B336" s="5"/>
       <c r="C336" s="3"/>
       <c r="D336" s="3"/>
@@ -7663,8 +9997,11 @@
       <c r="F336" s="14"/>
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
-    </row>
-    <row r="337" spans="2:8">
+      <c r="I336" s="14"/>
+      <c r="J336" s="14"/>
+      <c r="K336" s="14"/>
+    </row>
+    <row r="337" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B337" s="4"/>
       <c r="C337" s="3"/>
       <c r="D337" s="3"/>
@@ -7672,8 +10009,11 @@
       <c r="F337" s="14"/>
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
-    </row>
-    <row r="338" spans="2:8">
+      <c r="I337" s="14"/>
+      <c r="J337" s="14"/>
+      <c r="K337" s="14"/>
+    </row>
+    <row r="338" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B338" s="5"/>
       <c r="C338" s="3"/>
       <c r="D338" s="3"/>
@@ -7681,8 +10021,11 @@
       <c r="F338" s="14"/>
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
-    </row>
-    <row r="339" spans="2:8">
+      <c r="I338" s="14"/>
+      <c r="J338" s="14"/>
+      <c r="K338" s="14"/>
+    </row>
+    <row r="339" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B339" s="5"/>
       <c r="C339" s="3"/>
       <c r="D339" s="3"/>
@@ -7690,8 +10033,11 @@
       <c r="F339" s="14"/>
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
-    </row>
-    <row r="340" spans="2:8">
+      <c r="I339" s="14"/>
+      <c r="J339" s="14"/>
+      <c r="K339" s="14"/>
+    </row>
+    <row r="340" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B340" s="4"/>
       <c r="C340" s="3"/>
       <c r="D340" s="3"/>
@@ -7699,8 +10045,11 @@
       <c r="F340" s="14"/>
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
-    </row>
-    <row r="341" spans="2:8">
+      <c r="I340" s="14"/>
+      <c r="J340" s="14"/>
+      <c r="K340" s="14"/>
+    </row>
+    <row r="341" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B341" s="4"/>
       <c r="C341" s="3"/>
       <c r="D341" s="3"/>
@@ -7708,8 +10057,11 @@
       <c r="F341" s="14"/>
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
-    </row>
-    <row r="342" spans="2:8">
+      <c r="I341" s="14"/>
+      <c r="J341" s="14"/>
+      <c r="K341" s="14"/>
+    </row>
+    <row r="342" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B342" s="4"/>
       <c r="C342" s="3"/>
       <c r="D342" s="3"/>
@@ -7717,8 +10069,11 @@
       <c r="F342" s="14"/>
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
-    </row>
-    <row r="343" spans="2:8">
+      <c r="I342" s="14"/>
+      <c r="J342" s="14"/>
+      <c r="K342" s="14"/>
+    </row>
+    <row r="343" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B343" s="4"/>
       <c r="C343" s="3"/>
       <c r="D343" s="3"/>
@@ -7726,8 +10081,11 @@
       <c r="F343" s="14"/>
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
-    </row>
-    <row r="344" spans="2:8">
+      <c r="I343" s="14"/>
+      <c r="J343" s="14"/>
+      <c r="K343" s="14"/>
+    </row>
+    <row r="344" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B344" s="4"/>
       <c r="C344" s="3"/>
       <c r="D344" s="3"/>
@@ -7735,8 +10093,11 @@
       <c r="F344" s="14"/>
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
-    </row>
-    <row r="345" spans="2:8">
+      <c r="I344" s="14"/>
+      <c r="J344" s="14"/>
+      <c r="K344" s="14"/>
+    </row>
+    <row r="345" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B345" s="4"/>
       <c r="C345" s="3"/>
       <c r="D345" s="3"/>
@@ -7744,8 +10105,11 @@
       <c r="F345" s="14"/>
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
-    </row>
-    <row r="346" spans="2:8">
+      <c r="I345" s="14"/>
+      <c r="J345" s="14"/>
+      <c r="K345" s="14"/>
+    </row>
+    <row r="346" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B346" s="4"/>
       <c r="C346" s="3"/>
       <c r="D346" s="3"/>
@@ -7753,8 +10117,11 @@
       <c r="F346" s="14"/>
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
-    </row>
-    <row r="347" spans="2:8">
+      <c r="I346" s="14"/>
+      <c r="J346" s="14"/>
+      <c r="K346" s="14"/>
+    </row>
+    <row r="347" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B347" s="4"/>
       <c r="C347" s="3"/>
       <c r="D347" s="3"/>
@@ -7762,8 +10129,11 @@
       <c r="F347" s="14"/>
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
-    </row>
-    <row r="348" spans="2:8">
+      <c r="I347" s="14"/>
+      <c r="J347" s="14"/>
+      <c r="K347" s="14"/>
+    </row>
+    <row r="348" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B348" s="4"/>
       <c r="C348" s="3"/>
       <c r="D348" s="3"/>
@@ -7771,8 +10141,11 @@
       <c r="F348" s="14"/>
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
-    </row>
-    <row r="349" spans="2:8">
+      <c r="I348" s="14"/>
+      <c r="J348" s="14"/>
+      <c r="K348" s="14"/>
+    </row>
+    <row r="349" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B349" s="4"/>
       <c r="C349" s="3"/>
       <c r="D349" s="3"/>
@@ -7780,8 +10153,11 @@
       <c r="F349" s="14"/>
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
-    </row>
-    <row r="350" spans="2:8">
+      <c r="I349" s="14"/>
+      <c r="J349" s="14"/>
+      <c r="K349" s="14"/>
+    </row>
+    <row r="350" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B350" s="4"/>
       <c r="C350" s="3"/>
       <c r="D350" s="3"/>
@@ -7789,8 +10165,11 @@
       <c r="F350" s="14"/>
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
-    </row>
-    <row r="351" spans="2:8">
+      <c r="I350" s="14"/>
+      <c r="J350" s="14"/>
+      <c r="K350" s="14"/>
+    </row>
+    <row r="351" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B351" s="4"/>
       <c r="C351" s="19"/>
       <c r="D351" s="19"/>
@@ -7798,8 +10177,11 @@
       <c r="F351" s="13"/>
       <c r="G351" s="13"/>
       <c r="H351" s="13"/>
-    </row>
-    <row r="352" spans="2:8">
+      <c r="I351" s="13"/>
+      <c r="J351" s="13"/>
+      <c r="K351" s="13"/>
+    </row>
+    <row r="352" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B352" s="4" t="s">
         <v>49</v>
       </c>
@@ -7819,8 +10201,17 @@
       <c r="H352" s="13" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="353" spans="2:8">
+      <c r="I352" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="J352" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="K352" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="353" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B353" s="4" t="s">
         <v>50</v>
       </c>
@@ -7842,8 +10233,17 @@
       <c r="H353" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="354" spans="2:8">
+      <c r="I353" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J353" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K353" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="354" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B354" s="4" t="s">
         <v>129</v>
       </c>
@@ -7863,8 +10263,17 @@
       <c r="H354" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="355" spans="2:8">
+      <c r="I354" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="J354" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="K354" s="13" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="355" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B355" s="4" t="s">
         <v>130</v>
       </c>
@@ -7878,8 +10287,11 @@
       <c r="F355" s="13"/>
       <c r="G355" s="13"/>
       <c r="H355" s="13"/>
-    </row>
-    <row r="356" spans="2:8">
+      <c r="I355" s="13"/>
+      <c r="J355" s="13"/>
+      <c r="K355" s="13"/>
+    </row>
+    <row r="356" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B356" s="4"/>
       <c r="C356" s="3"/>
       <c r="D356" s="3"/>
@@ -7887,8 +10299,11 @@
       <c r="F356" s="13"/>
       <c r="G356" s="13"/>
       <c r="H356" s="13"/>
-    </row>
-    <row r="357" spans="2:8">
+      <c r="I356" s="13"/>
+      <c r="J356" s="13"/>
+      <c r="K356" s="13"/>
+    </row>
+    <row r="357" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B357" s="4" t="s">
         <v>131</v>
       </c>
@@ -7900,8 +10315,11 @@
       <c r="F357" s="13"/>
       <c r="G357" s="13"/>
       <c r="H357" s="13"/>
-    </row>
-    <row r="358" spans="2:8">
+      <c r="I357" s="13"/>
+      <c r="J357" s="13"/>
+      <c r="K357" s="13"/>
+    </row>
+    <row r="358" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B358" s="4" t="s">
         <v>132</v>
       </c>
@@ -7913,8 +10331,11 @@
       <c r="F358" s="13"/>
       <c r="G358" s="13"/>
       <c r="H358" s="13"/>
-    </row>
-    <row r="359" spans="2:8">
+      <c r="I358" s="13"/>
+      <c r="J358" s="13"/>
+      <c r="K358" s="13"/>
+    </row>
+    <row r="359" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B359" s="4" t="s">
         <v>133</v>
       </c>
@@ -7926,8 +10347,11 @@
       <c r="F359" s="13"/>
       <c r="G359" s="13"/>
       <c r="H359" s="13"/>
-    </row>
-    <row r="360" spans="2:8">
+      <c r="I359" s="13"/>
+      <c r="J359" s="13"/>
+      <c r="K359" s="13"/>
+    </row>
+    <row r="360" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B360" s="4" t="s">
         <v>134</v>
       </c>
@@ -7939,8 +10363,11 @@
       <c r="F360" s="13"/>
       <c r="G360" s="13"/>
       <c r="H360" s="13"/>
-    </row>
-    <row r="361" spans="2:8">
+      <c r="I360" s="13"/>
+      <c r="J360" s="13"/>
+      <c r="K360" s="13"/>
+    </row>
+    <row r="361" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B361" s="4" t="s">
         <v>135</v>
       </c>
@@ -7952,8 +10379,11 @@
       <c r="F361" s="13"/>
       <c r="G361" s="13"/>
       <c r="H361" s="13"/>
-    </row>
-    <row r="362" spans="2:8">
+      <c r="I361" s="13"/>
+      <c r="J361" s="13"/>
+      <c r="K361" s="13"/>
+    </row>
+    <row r="362" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B362" s="4"/>
       <c r="C362" s="3"/>
       <c r="D362" s="3"/>
@@ -7961,8 +10391,11 @@
       <c r="F362" s="13"/>
       <c r="G362" s="13"/>
       <c r="H362" s="13"/>
-    </row>
-    <row r="363" spans="2:8">
+      <c r="I362" s="13"/>
+      <c r="J362" s="13"/>
+      <c r="K362" s="13"/>
+    </row>
+    <row r="363" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B363" s="4" t="s">
         <v>131</v>
       </c>
@@ -7974,8 +10407,11 @@
       <c r="F363" s="13"/>
       <c r="G363" s="13"/>
       <c r="H363" s="13"/>
-    </row>
-    <row r="364" spans="2:8">
+      <c r="I363" s="13"/>
+      <c r="J363" s="13"/>
+      <c r="K363" s="13"/>
+    </row>
+    <row r="364" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B364" s="4" t="s">
         <v>132</v>
       </c>
@@ -7987,8 +10423,11 @@
       <c r="F364" s="13"/>
       <c r="G364" s="13"/>
       <c r="H364" s="13"/>
-    </row>
-    <row r="365" spans="2:8">
+      <c r="I364" s="13"/>
+      <c r="J364" s="13"/>
+      <c r="K364" s="13"/>
+    </row>
+    <row r="365" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B365" s="4" t="s">
         <v>133</v>
       </c>
@@ -8000,8 +10439,11 @@
       <c r="F365" s="13"/>
       <c r="G365" s="13"/>
       <c r="H365" s="13"/>
-    </row>
-    <row r="366" spans="2:8">
+      <c r="I365" s="13"/>
+      <c r="J365" s="13"/>
+      <c r="K365" s="13"/>
+    </row>
+    <row r="366" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B366" s="4" t="s">
         <v>134</v>
       </c>
@@ -8013,8 +10455,11 @@
       <c r="F366" s="13"/>
       <c r="G366" s="13"/>
       <c r="H366" s="13"/>
-    </row>
-    <row r="367" spans="2:8">
+      <c r="I366" s="13"/>
+      <c r="J366" s="13"/>
+      <c r="K366" s="13"/>
+    </row>
+    <row r="367" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B367" s="4" t="s">
         <v>135</v>
       </c>
@@ -8026,8 +10471,11 @@
       <c r="F367" s="13"/>
       <c r="G367" s="13"/>
       <c r="H367" s="13"/>
-    </row>
-    <row r="368" spans="2:8">
+      <c r="I367" s="13"/>
+      <c r="J367" s="13"/>
+      <c r="K367" s="13"/>
+    </row>
+    <row r="368" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B368" s="4"/>
       <c r="C368" s="3"/>
       <c r="D368" s="3"/>
@@ -8035,8 +10483,11 @@
       <c r="F368" s="13"/>
       <c r="G368" s="13"/>
       <c r="H368" s="13"/>
-    </row>
-    <row r="369" spans="2:8">
+      <c r="I368" s="13"/>
+      <c r="J368" s="13"/>
+      <c r="K368" s="13"/>
+    </row>
+    <row r="369" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B369" s="4" t="s">
         <v>136</v>
       </c>
@@ -8050,8 +10501,11 @@
       <c r="F369" s="13"/>
       <c r="G369" s="13"/>
       <c r="H369" s="13"/>
-    </row>
-    <row r="370" spans="2:8">
+      <c r="I369" s="13"/>
+      <c r="J369" s="13"/>
+      <c r="K369" s="13"/>
+    </row>
+    <row r="370" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B370" s="4" t="s">
         <v>137</v>
       </c>
@@ -8065,8 +10519,11 @@
       <c r="F370" s="13"/>
       <c r="G370" s="13"/>
       <c r="H370" s="13"/>
-    </row>
-    <row r="371" spans="2:8">
+      <c r="I370" s="13"/>
+      <c r="J370" s="13"/>
+      <c r="K370" s="13"/>
+    </row>
+    <row r="371" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B371" s="4" t="s">
         <v>138</v>
       </c>
@@ -8080,8 +10537,11 @@
       <c r="F371" s="13"/>
       <c r="G371" s="13"/>
       <c r="H371" s="13"/>
-    </row>
-    <row r="372" spans="2:8">
+      <c r="I371" s="13"/>
+      <c r="J371" s="13"/>
+      <c r="K371" s="13"/>
+    </row>
+    <row r="372" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B372" s="4"/>
       <c r="C372" s="3"/>
       <c r="D372" s="3"/>
@@ -8089,8 +10549,11 @@
       <c r="F372" s="13"/>
       <c r="G372" s="13"/>
       <c r="H372" s="13"/>
-    </row>
-    <row r="373" spans="2:8">
+      <c r="I372" s="13"/>
+      <c r="J372" s="13"/>
+      <c r="K372" s="13"/>
+    </row>
+    <row r="373" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B373" s="4" t="s">
         <v>136</v>
       </c>
@@ -8104,8 +10567,11 @@
       <c r="F373" s="13"/>
       <c r="G373" s="13"/>
       <c r="H373" s="13"/>
-    </row>
-    <row r="374" spans="2:8">
+      <c r="I373" s="13"/>
+      <c r="J373" s="13"/>
+      <c r="K373" s="13"/>
+    </row>
+    <row r="374" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B374" s="4" t="s">
         <v>137</v>
       </c>
@@ -8119,8 +10585,11 @@
       <c r="F374" s="13"/>
       <c r="G374" s="13"/>
       <c r="H374" s="13"/>
-    </row>
-    <row r="375" spans="2:8">
+      <c r="I374" s="13"/>
+      <c r="J374" s="13"/>
+      <c r="K374" s="13"/>
+    </row>
+    <row r="375" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B375" s="4" t="s">
         <v>138</v>
       </c>
@@ -8134,8 +10603,11 @@
       <c r="F375" s="13"/>
       <c r="G375" s="13"/>
       <c r="H375" s="13"/>
-    </row>
-    <row r="376" spans="2:8">
+      <c r="I375" s="13"/>
+      <c r="J375" s="13"/>
+      <c r="K375" s="13"/>
+    </row>
+    <row r="376" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B376" s="4"/>
       <c r="C376" s="3"/>
       <c r="D376" s="3"/>
@@ -8143,8 +10615,11 @@
       <c r="F376" s="13"/>
       <c r="G376" s="13"/>
       <c r="H376" s="13"/>
-    </row>
-    <row r="377" spans="2:8">
+      <c r="I376" s="13"/>
+      <c r="J376" s="13"/>
+      <c r="K376" s="13"/>
+    </row>
+    <row r="377" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B377" s="4"/>
       <c r="C377" s="3"/>
       <c r="D377" s="3"/>
@@ -8152,8 +10627,11 @@
       <c r="F377" s="13"/>
       <c r="G377" s="13"/>
       <c r="H377" s="13"/>
-    </row>
-    <row r="378" spans="2:8">
+      <c r="I377" s="13"/>
+      <c r="J377" s="13"/>
+      <c r="K377" s="13"/>
+    </row>
+    <row r="378" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B378" s="4"/>
       <c r="C378" s="3"/>
       <c r="D378" s="3"/>
@@ -8161,8 +10639,11 @@
       <c r="F378" s="13"/>
       <c r="G378" s="13"/>
       <c r="H378" s="13"/>
-    </row>
-    <row r="379" spans="2:8">
+      <c r="I378" s="13"/>
+      <c r="J378" s="13"/>
+      <c r="K378" s="13"/>
+    </row>
+    <row r="379" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B379" s="4"/>
       <c r="C379" s="3"/>
       <c r="D379" s="3"/>
@@ -8170,8 +10651,11 @@
       <c r="F379" s="13"/>
       <c r="G379" s="13"/>
       <c r="H379" s="13"/>
-    </row>
-    <row r="380" spans="2:8">
+      <c r="I379" s="13"/>
+      <c r="J379" s="13"/>
+      <c r="K379" s="13"/>
+    </row>
+    <row r="380" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B380" s="4"/>
       <c r="C380" s="3"/>
       <c r="D380" s="3"/>
@@ -8179,8 +10663,11 @@
       <c r="F380" s="13"/>
       <c r="G380" s="13"/>
       <c r="H380" s="13"/>
-    </row>
-    <row r="381" spans="2:8">
+      <c r="I380" s="13"/>
+      <c r="J380" s="13"/>
+      <c r="K380" s="13"/>
+    </row>
+    <row r="381" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B381" s="4"/>
       <c r="C381" s="3"/>
       <c r="D381" s="3"/>
@@ -8188,8 +10675,11 @@
       <c r="F381" s="13"/>
       <c r="G381" s="13"/>
       <c r="H381" s="13"/>
-    </row>
-    <row r="382" spans="2:8">
+      <c r="I381" s="13"/>
+      <c r="J381" s="13"/>
+      <c r="K381" s="13"/>
+    </row>
+    <row r="382" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B382" s="4"/>
       <c r="C382" s="3"/>
       <c r="D382" s="3"/>
@@ -8197,8 +10687,11 @@
       <c r="F382" s="13"/>
       <c r="G382" s="13"/>
       <c r="H382" s="13"/>
-    </row>
-    <row r="383" spans="2:8">
+      <c r="I382" s="13"/>
+      <c r="J382" s="13"/>
+      <c r="K382" s="13"/>
+    </row>
+    <row r="383" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B383" s="4"/>
       <c r="C383" s="3"/>
       <c r="D383" s="3"/>
@@ -8206,8 +10699,11 @@
       <c r="F383" s="13"/>
       <c r="G383" s="13"/>
       <c r="H383" s="13"/>
-    </row>
-    <row r="384" spans="2:8">
+      <c r="I383" s="13"/>
+      <c r="J383" s="13"/>
+      <c r="K383" s="13"/>
+    </row>
+    <row r="384" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B384" s="4"/>
       <c r="C384" s="3"/>
       <c r="D384" s="3"/>
@@ -8215,8 +10711,11 @@
       <c r="F384" s="13"/>
       <c r="G384" s="13"/>
       <c r="H384" s="13"/>
-    </row>
-    <row r="385" spans="2:8">
+      <c r="I384" s="13"/>
+      <c r="J384" s="13"/>
+      <c r="K384" s="13"/>
+    </row>
+    <row r="385" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B385" s="4"/>
       <c r="C385" s="3"/>
       <c r="D385" s="3"/>
@@ -8224,8 +10723,11 @@
       <c r="F385" s="13"/>
       <c r="G385" s="13"/>
       <c r="H385" s="13"/>
-    </row>
-    <row r="386" spans="2:8">
+      <c r="I385" s="13"/>
+      <c r="J385" s="13"/>
+      <c r="K385" s="13"/>
+    </row>
+    <row r="386" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B386" s="4"/>
       <c r="C386" s="3"/>
       <c r="D386" s="3"/>
@@ -8233,8 +10735,11 @@
       <c r="F386" s="13"/>
       <c r="G386" s="13"/>
       <c r="H386" s="13"/>
-    </row>
-    <row r="387" spans="2:8">
+      <c r="I386" s="13"/>
+      <c r="J386" s="13"/>
+      <c r="K386" s="13"/>
+    </row>
+    <row r="387" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B387" s="4"/>
       <c r="C387" s="3"/>
       <c r="D387" s="3"/>
@@ -8242,8 +10747,11 @@
       <c r="F387" s="13"/>
       <c r="G387" s="13"/>
       <c r="H387" s="13"/>
-    </row>
-    <row r="388" spans="2:8">
+      <c r="I387" s="13"/>
+      <c r="J387" s="13"/>
+      <c r="K387" s="13"/>
+    </row>
+    <row r="388" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B388" s="4"/>
       <c r="C388" s="3"/>
       <c r="D388" s="3"/>
@@ -8251,8 +10759,11 @@
       <c r="F388" s="13"/>
       <c r="G388" s="13"/>
       <c r="H388" s="13"/>
-    </row>
-    <row r="389" spans="2:8">
+      <c r="I388" s="13"/>
+      <c r="J388" s="13"/>
+      <c r="K388" s="13"/>
+    </row>
+    <row r="389" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B389" s="4"/>
       <c r="C389" s="3"/>
       <c r="D389" s="3"/>
@@ -8260,8 +10771,11 @@
       <c r="F389" s="13"/>
       <c r="G389" s="13"/>
       <c r="H389" s="13"/>
-    </row>
-    <row r="390" spans="2:8">
+      <c r="I389" s="13"/>
+      <c r="J389" s="13"/>
+      <c r="K389" s="13"/>
+    </row>
+    <row r="390" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B390" s="4"/>
       <c r="C390" s="3"/>
       <c r="D390" s="3"/>
@@ -8269,8 +10783,11 @@
       <c r="F390" s="13"/>
       <c r="G390" s="13"/>
       <c r="H390" s="13"/>
-    </row>
-    <row r="391" spans="2:8">
+      <c r="I390" s="13"/>
+      <c r="J390" s="13"/>
+      <c r="K390" s="13"/>
+    </row>
+    <row r="391" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B391" s="4"/>
       <c r="C391" s="3"/>
       <c r="D391" s="3"/>
@@ -8278,8 +10795,11 @@
       <c r="F391" s="13"/>
       <c r="G391" s="13"/>
       <c r="H391" s="13"/>
-    </row>
-    <row r="392" spans="2:8">
+      <c r="I391" s="13"/>
+      <c r="J391" s="13"/>
+      <c r="K391" s="13"/>
+    </row>
+    <row r="392" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B392" s="4"/>
       <c r="C392" s="3"/>
       <c r="D392" s="3"/>
@@ -8287,8 +10807,11 @@
       <c r="F392" s="13"/>
       <c r="G392" s="13"/>
       <c r="H392" s="13"/>
-    </row>
-    <row r="393" spans="2:8">
+      <c r="I392" s="13"/>
+      <c r="J392" s="13"/>
+      <c r="K392" s="13"/>
+    </row>
+    <row r="393" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B393" s="4"/>
       <c r="C393" s="3"/>
       <c r="D393" s="3"/>
@@ -8296,8 +10819,11 @@
       <c r="F393" s="13"/>
       <c r="G393" s="13"/>
       <c r="H393" s="13"/>
-    </row>
-    <row r="394" spans="2:8">
+      <c r="I393" s="13"/>
+      <c r="J393" s="13"/>
+      <c r="K393" s="13"/>
+    </row>
+    <row r="394" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B394" s="4"/>
       <c r="C394" s="3"/>
       <c r="D394" s="3"/>
@@ -8305,8 +10831,11 @@
       <c r="F394" s="13"/>
       <c r="G394" s="13"/>
       <c r="H394" s="13"/>
-    </row>
-    <row r="395" spans="2:8">
+      <c r="I394" s="13"/>
+      <c r="J394" s="13"/>
+      <c r="K394" s="13"/>
+    </row>
+    <row r="395" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B395" s="4"/>
       <c r="C395" s="3"/>
       <c r="D395" s="3"/>
@@ -8314,8 +10843,11 @@
       <c r="F395" s="13"/>
       <c r="G395" s="13"/>
       <c r="H395" s="13"/>
-    </row>
-    <row r="396" spans="2:8">
+      <c r="I395" s="13"/>
+      <c r="J395" s="13"/>
+      <c r="K395" s="13"/>
+    </row>
+    <row r="396" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B396" s="4"/>
       <c r="C396" s="3"/>
       <c r="D396" s="3"/>
@@ -8323,8 +10855,11 @@
       <c r="F396" s="13"/>
       <c r="G396" s="13"/>
       <c r="H396" s="13"/>
-    </row>
-    <row r="397" spans="2:8">
+      <c r="I396" s="13"/>
+      <c r="J396" s="13"/>
+      <c r="K396" s="13"/>
+    </row>
+    <row r="397" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B397" s="9"/>
       <c r="C397" s="3"/>
       <c r="D397" s="3"/>
@@ -8332,8 +10867,11 @@
       <c r="F397" s="13"/>
       <c r="G397" s="13"/>
       <c r="H397" s="13"/>
-    </row>
-    <row r="398" spans="2:8">
+      <c r="I397" s="13"/>
+      <c r="J397" s="13"/>
+      <c r="K397" s="13"/>
+    </row>
+    <row r="398" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B398" s="9"/>
       <c r="C398" s="3"/>
       <c r="D398" s="3"/>
@@ -8341,8 +10879,11 @@
       <c r="F398" s="13"/>
       <c r="G398" s="13"/>
       <c r="H398" s="13"/>
-    </row>
-    <row r="399" spans="2:8">
+      <c r="I398" s="13"/>
+      <c r="J398" s="13"/>
+      <c r="K398" s="13"/>
+    </row>
+    <row r="399" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B399" s="9"/>
       <c r="C399" s="3"/>
       <c r="D399" s="3"/>
@@ -8350,8 +10891,11 @@
       <c r="F399" s="13"/>
       <c r="G399" s="13"/>
       <c r="H399" s="13"/>
-    </row>
-    <row r="400" spans="2:8">
+      <c r="I399" s="13"/>
+      <c r="J399" s="13"/>
+      <c r="K399" s="13"/>
+    </row>
+    <row r="400" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B400" s="9"/>
       <c r="C400" s="3"/>
       <c r="D400" s="3"/>
@@ -8359,8 +10903,11 @@
       <c r="F400" s="13"/>
       <c r="G400" s="13"/>
       <c r="H400" s="13"/>
-    </row>
-    <row r="401" spans="2:8">
+      <c r="I400" s="13"/>
+      <c r="J400" s="13"/>
+      <c r="K400" s="13"/>
+    </row>
+    <row r="401" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B401" s="4"/>
       <c r="C401" s="3"/>
       <c r="D401" s="3"/>
@@ -8368,9 +10915,12 @@
       <c r="F401" s="13"/>
       <c r="G401" s="13"/>
       <c r="H401" s="13"/>
+      <c r="I401" s="13"/>
+      <c r="J401" s="13"/>
+      <c r="K401" s="13"/>
     </row>
   </sheetData>
-  <autoFilter ref="E1:G401" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}"/>
+  <autoFilter ref="E2:K401" xr:uid="{5555E797-91C5-44FA-95FC-58DB33F30F80}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;L_x000D_&amp;1#&amp;"Arial"&amp;8&amp;K737373 Classified by Alfa Laval as: Business</oddFooter>
